--- a/datos/maestros/md_partidos.xlsx
+++ b/datos/maestros/md_partidos.xlsx
@@ -21773,7 +21773,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bb</t>
+          <t>6a4af7f0ae633549bd0f03bf</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -21786,19 +21786,19 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="inlineStr"/>
       <c r="H382" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -21869,7 +21869,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bc</t>
+          <t>6a4af7f0ae633549bd0f03ba</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -21882,29 +21882,29 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="inlineStr"/>
       <c r="H384" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
@@ -21917,7 +21917,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ba</t>
+          <t>6a4af7f0ae633549bd0f03bb</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -21930,19 +21930,19 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -22013,7 +22013,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bf</t>
+          <t>6a4af7f0ae633549bd0f03be</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -22026,29 +22026,29 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F387" t="inlineStr"/>
       <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
@@ -22061,7 +22061,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b9</t>
+          <t>6a4af7f0ae633549bd0f03bc</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -22074,19 +22074,19 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -22109,7 +22109,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c0</t>
+          <t>6a4af7f0ae633549bd0f03b9</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -22122,33 +22122,29 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
-        </is>
-      </c>
-      <c r="F389" t="n">
-        <v>0</v>
-      </c>
-      <c r="G389" t="n">
-        <v>0</v>
-      </c>
+          <t>520e4ee4a776cc826b00004b</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
@@ -22156,16 +22152,12 @@
           <t>closed</t>
         </is>
       </c>
-      <c r="L389" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="L389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b8</t>
+          <t>6a4af7f0ae633549bd0f03c0</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -22178,29 +22170,33 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
-        </is>
-      </c>
-      <c r="F390" t="inlineStr"/>
-      <c r="G390" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000d9</t>
+        </is>
+      </c>
+      <c r="F390" t="n">
+        <v>0</v>
+      </c>
+      <c r="G390" t="n">
+        <v>0</v>
+      </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
@@ -22208,12 +22204,16 @@
           <t>closed</t>
         </is>
       </c>
-      <c r="L390" t="inlineStr"/>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03be</t>
+          <t>6a4af7f0ae633549bd0f03b8</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -22226,29 +22226,29 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
@@ -22261,7 +22261,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0387</t>
+          <t>6a4af7efae633549bd0f0385</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -22274,33 +22274,33 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F392" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G392" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
           <t>19:00</t>
-        </is>
-      </c>
-      <c r="J392" t="inlineStr">
-        <is>
-          <t>21:00</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
@@ -22317,7 +22317,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0389</t>
+          <t>6a4af7efae633549bd0f0386</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -22330,33 +22330,33 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F393" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G393" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
@@ -22373,7 +22373,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0383</t>
+          <t>6a4af7efae633549bd0f0382</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -22386,19 +22386,19 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G394" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H394" t="inlineStr">
         <is>
@@ -22407,12 +22407,12 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
@@ -22429,7 +22429,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0384</t>
+          <t>6a4af7efae633549bd0f0381</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -22442,23 +22442,23 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G395" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -22485,7 +22485,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0385</t>
+          <t>6a4af7efae633549bd0f0380</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -22498,12 +22498,12 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F396" t="n">
@@ -22514,17 +22514,17 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
@@ -22597,7 +22597,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0382</t>
+          <t>6a4af7efae633549bd0f0383</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -22610,20 +22610,20 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F398" t="n">
+        <v>1</v>
+      </c>
+      <c r="G398" t="n">
         <v>2</v>
       </c>
-      <c r="G398" t="n">
-        <v>0</v>
-      </c>
       <c r="H398" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -22631,12 +22631,12 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
@@ -22653,7 +22653,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0381</t>
+          <t>6a4af7efae633549bd0f0384</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -22666,23 +22666,23 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F399" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G399" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -22709,7 +22709,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0386</t>
+          <t>6a4af7efae633549bd0f0389</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -22722,33 +22722,33 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F400" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
@@ -22765,7 +22765,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0380</t>
+          <t>6a4af7efae633549bd0f0387</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -22778,33 +22778,33 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F401" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G401" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
@@ -22821,7 +22821,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038b</t>
+          <t>6a4af7efae633549bd0f0391</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -22834,33 +22834,33 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F402" t="n">
         <v>1</v>
       </c>
       <c r="G402" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
@@ -22877,7 +22877,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038e</t>
+          <t>6a4af7efae633549bd0f038f</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -22890,23 +22890,23 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F403" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G403" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -22933,7 +22933,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038f</t>
+          <t>6a4af7efae633549bd0f0392</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -22946,33 +22946,33 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F404" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G404" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
           <t>19:30</t>
-        </is>
-      </c>
-      <c r="J404" t="inlineStr">
-        <is>
-          <t>21:30</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
@@ -22989,7 +22989,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0392</t>
+          <t>6a4af7efae633549bd0f0394</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -23002,12 +23002,12 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F405" t="n">
@@ -23018,7 +23018,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -23101,7 +23101,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0394</t>
+          <t>6a4af7efae633549bd0f0390</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -23114,23 +23114,23 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G407" t="n">
         <v>0</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -23157,7 +23157,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0391</t>
+          <t>6a4af7efae633549bd0f038d</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -23170,33 +23170,33 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F408" t="n">
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
@@ -23213,7 +23213,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038d</t>
+          <t>6a4af7efae633549bd0f038b</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -23226,33 +23226,33 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F409" t="n">
         <v>1</v>
       </c>
       <c r="G409" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
@@ -23269,7 +23269,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0390</t>
+          <t>6a4af7efae633549bd0f038c</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -23282,19 +23282,19 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G410" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
@@ -23303,12 +23303,12 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
@@ -23325,7 +23325,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038c</t>
+          <t>6a4af7efae633549bd0f038e</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -23338,19 +23338,19 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G411" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
@@ -23359,12 +23359,12 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
@@ -23381,7 +23381,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039b</t>
+          <t>6a4af7efae633549bd0f039e</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -23394,33 +23394,33 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F412" t="n">
+        <v>2</v>
+      </c>
+      <c r="G412" t="n">
         <v>1</v>
       </c>
-      <c r="G412" t="n">
-        <v>0</v>
-      </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
@@ -23437,7 +23437,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0396</t>
+          <t>6a4af7efae633549bd0f0399</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -23450,33 +23450,33 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F413" t="n">
+        <v>3</v>
+      </c>
+      <c r="G413" t="n">
         <v>1</v>
       </c>
-      <c r="G413" t="n">
-        <v>0</v>
-      </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
           <t>19:30</t>
-        </is>
-      </c>
-      <c r="J413" t="inlineStr">
-        <is>
-          <t>21:30</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
@@ -23493,7 +23493,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039e</t>
+          <t>6a4af7efae633549bd0f039f</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -23506,19 +23506,19 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
@@ -23527,12 +23527,12 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
@@ -23605,7 +23605,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039c</t>
+          <t>6a4af7efae633549bd0f0398</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -23618,33 +23618,33 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G416" t="n">
         <v>2</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
@@ -23661,7 +23661,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039d</t>
+          <t>6a4af7efae633549bd0f039a</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -23674,23 +23674,23 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G417" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -23717,7 +23717,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0398</t>
+          <t>6a4af7efae633549bd0f039c</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -23730,33 +23730,33 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F418" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G418" t="n">
         <v>2</v>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
@@ -23773,7 +23773,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039f</t>
+          <t>6a4af7efae633549bd0f039d</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -23786,33 +23786,33 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F419" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G419" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
@@ -23829,7 +23829,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039a</t>
+          <t>6a4af7efae633549bd0f039b</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -23842,33 +23842,33 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F420" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G420" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
@@ -23885,7 +23885,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0399</t>
+          <t>6a4af7efae633549bd0f0396</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -23898,33 +23898,33 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F421" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G421" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
@@ -23941,7 +23941,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a2</t>
+          <t>6a4af7efae633549bd0f03aa</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -23954,20 +23954,20 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F422" t="n">
+        <v>2</v>
+      </c>
+      <c r="G422" t="n">
         <v>3</v>
       </c>
-      <c r="G422" t="n">
-        <v>0</v>
-      </c>
       <c r="H422" t="inlineStr">
         <is>
           <t>2026-09-05</t>
@@ -23975,12 +23975,12 @@
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
@@ -23997,7 +23997,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03aa</t>
+          <t>6a4af7efae633549bd0f03a5</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -24010,23 +24010,23 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F423" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G423" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -24053,7 +24053,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a3</t>
+          <t>6a4af7efae633549bd0f03a6</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -24066,50 +24066,42 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
-        </is>
-      </c>
-      <c r="F424" t="n">
-        <v>1</v>
-      </c>
-      <c r="G424" t="n">
-        <v>0</v>
-      </c>
+          <t>504e581e4d8bec9a670000d9</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="inlineStr"/>
       <c r="H424" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="J424" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
       <c r="K424" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="L424" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="L424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a5</t>
+          <t>6a4af7efae633549bd0f03a4</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -24122,29 +24114,29 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F425" t="inlineStr"/>
       <c r="G425" t="inlineStr"/>
       <c r="H425" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K425" t="inlineStr">
@@ -24157,7 +24149,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a9</t>
+          <t>6a4af7efae633549bd0f03a7</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -24170,16 +24162,20 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
-        </is>
-      </c>
-      <c r="F426" t="inlineStr"/>
-      <c r="G426" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000cf</t>
+        </is>
+      </c>
+      <c r="F426" t="n">
+        <v>0</v>
+      </c>
+      <c r="G426" t="n">
+        <v>0</v>
+      </c>
       <c r="H426" t="inlineStr">
         <is>
           <t>2026-09-06</t>
@@ -24187,12 +24183,12 @@
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
@@ -24200,12 +24196,16 @@
           <t>running</t>
         </is>
       </c>
-      <c r="L426" t="inlineStr"/>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a1</t>
+          <t>6a4af7efae633549bd0f03a8</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -24218,19 +24218,23 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
-        </is>
-      </c>
-      <c r="F427" t="inlineStr"/>
-      <c r="G427" t="inlineStr"/>
+          <t>520e4ee4a776cc826b00004b</t>
+        </is>
+      </c>
+      <c r="F427" t="n">
+        <v>3</v>
+      </c>
+      <c r="G427" t="n">
+        <v>2</v>
+      </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -24248,12 +24252,16 @@
           <t>running</t>
         </is>
       </c>
-      <c r="L427" t="inlineStr"/>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a8</t>
+          <t>6a4af7efae633549bd0f03a9</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -24266,33 +24274,33 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G428" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
@@ -24309,7 +24317,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a4</t>
+          <t>6a4af7efae633549bd0f03a2</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -24322,29 +24330,33 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
-        </is>
-      </c>
-      <c r="F429" t="inlineStr"/>
-      <c r="G429" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000c8</t>
+        </is>
+      </c>
+      <c r="F429" t="n">
+        <v>3</v>
+      </c>
+      <c r="G429" t="n">
+        <v>0</v>
+      </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
@@ -24352,12 +24364,16 @@
           <t>running</t>
         </is>
       </c>
-      <c r="L429" t="inlineStr"/>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a6</t>
+          <t>6a4af7efae633549bd0f03a1</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -24370,29 +24386,33 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
-        </is>
-      </c>
-      <c r="F430" t="inlineStr"/>
-      <c r="G430" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000d1</t>
+        </is>
+      </c>
+      <c r="F430" t="n">
+        <v>5</v>
+      </c>
+      <c r="G430" t="n">
+        <v>2</v>
+      </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
@@ -24400,12 +24420,16 @@
           <t>running</t>
         </is>
       </c>
-      <c r="L430" t="inlineStr"/>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a7</t>
+          <t>6a4af7efae633549bd0f03a3</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -24418,29 +24442,33 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
-        </is>
-      </c>
-      <c r="F431" t="inlineStr"/>
-      <c r="G431" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000c6</t>
+        </is>
+      </c>
+      <c r="F431" t="n">
+        <v>1</v>
+      </c>
+      <c r="G431" t="n">
+        <v>0</v>
+      </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
@@ -24448,12 +24476,16 @@
           <t>running</t>
         </is>
       </c>
-      <c r="L431" t="inlineStr"/>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b1</t>
+          <t>6a4af7efae633549bd0f03af</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -24466,29 +24498,29 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
       <c r="G432" t="inlineStr"/>
       <c r="H432" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
@@ -24549,7 +24581,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b3</t>
+          <t>6a4af7f0ae633549bd0f03b5</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -24562,19 +24594,19 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr"/>
       <c r="H434" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -24597,7 +24629,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b5</t>
+          <t>6a4af7efae633549bd0f03ae</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -24610,29 +24642,29 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F435" t="inlineStr"/>
       <c r="G435" t="inlineStr"/>
       <c r="H435" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
@@ -24645,7 +24677,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ae</t>
+          <t>6a4af7efae633549bd0f03b3</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -24658,12 +24690,12 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -24675,12 +24707,12 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
@@ -24693,7 +24725,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b2</t>
+          <t>6a4af7efae633549bd0f03b0</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -24706,12 +24738,12 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
@@ -24723,12 +24755,12 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
@@ -24789,7 +24821,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b0</t>
+          <t>6a4af7efae633549bd0f03b2</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -24802,12 +24834,12 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
@@ -24819,12 +24851,12 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
@@ -24885,7 +24917,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03af</t>
+          <t>6a4af7efae633549bd0f03b1</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -24898,29 +24930,29 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
       <c r="G441" t="inlineStr"/>
       <c r="H441" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K441" t="inlineStr">
@@ -24933,7 +24965,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cb</t>
+          <t>6a4af7f0ae633549bd0f03c5</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -24946,12 +24978,12 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -24981,7 +25013,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c2</t>
+          <t>6a4af7f0ae633549bd0f03c3</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -24994,19 +25026,19 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
       <c r="G443" t="inlineStr"/>
       <c r="H443" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -25029,7 +25061,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c4</t>
+          <t>6a4af7f0ae633549bd0f03c2</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -25042,12 +25074,12 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
@@ -25059,12 +25091,12 @@
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K444" t="inlineStr">
@@ -25077,7 +25109,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c3</t>
+          <t>6a4af7f0ae633549bd0f03c4</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -25090,29 +25122,29 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
       <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
@@ -25173,7 +25205,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c5</t>
+          <t>6a4af7f0ae633549bd0f03c9</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -25186,29 +25218,29 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
       <c r="G447" t="inlineStr"/>
       <c r="H447" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K447" t="inlineStr">
@@ -25221,7 +25253,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c9</t>
+          <t>6a4af7f0ae633549bd0f03cb</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -25234,29 +25266,29 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
       <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K448" t="inlineStr">
@@ -25317,7 +25349,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c6</t>
+          <t>6a4af7f0ae633549bd0f03c7</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -25330,29 +25362,29 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
       <c r="G450" t="inlineStr"/>
       <c r="H450" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K450" t="inlineStr">
@@ -25365,7 +25397,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c7</t>
+          <t>6a4af7f0ae633549bd0f03c6</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -25378,29 +25410,29 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr"/>
       <c r="H451" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K451" t="inlineStr">
@@ -25413,7 +25445,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cf</t>
+          <t>6a4af7f0ae633549bd0f03ce</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -25426,12 +25458,12 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
@@ -25509,7 +25541,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d3</t>
+          <t>6a4af7f0ae633549bd0f03d2</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -25522,12 +25554,12 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F454" t="inlineStr"/>
@@ -25557,7 +25589,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cd</t>
+          <t>6a4af7f0ae633549bd0f03d3</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -25570,12 +25602,12 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -25605,7 +25637,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d0</t>
+          <t>6a4af7f0ae633549bd0f03cd</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -25618,12 +25650,12 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
@@ -25653,7 +25685,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d4</t>
+          <t>6a4af7f0ae633549bd0f03cf</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -25666,12 +25698,12 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -25701,7 +25733,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d5</t>
+          <t>6a4af7f0ae633549bd0f03d0</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -25714,12 +25746,12 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -25749,7 +25781,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d6</t>
+          <t>6a4af7f0ae633549bd0f03d4</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -25762,12 +25794,12 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -25797,7 +25829,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ce</t>
+          <t>6a4af7f0ae633549bd0f03d5</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -25810,12 +25842,12 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
@@ -25845,7 +25877,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d2</t>
+          <t>6a4af7f0ae633549bd0f03d6</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -25858,12 +25890,12 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -25989,7 +26021,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e0</t>
+          <t>6a4af7f0ae633549bd0f03de</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -26002,12 +26034,12 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -26277,7 +26309,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d9</t>
+          <t>6a4af7f0ae633549bd0f03e0</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -26290,12 +26322,12 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
@@ -26325,7 +26357,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03de</t>
+          <t>6a4af7f0ae633549bd0f03d9</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -26338,12 +26370,12 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -26373,7 +26405,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e3</t>
+          <t>6a4af7f0ae633549bd0f03e8</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -26386,12 +26418,12 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -26421,7 +26453,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e4</t>
+          <t>6a4af7f0ae633549bd0f03e7</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -26434,12 +26466,12 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -26469,7 +26501,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e6</t>
+          <t>6a4af7f0ae633549bd0f03eb</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -26482,12 +26514,12 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -26499,12 +26531,12 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K474" t="inlineStr">
@@ -26517,7 +26549,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03eb</t>
+          <t>6a4af7f0ae633549bd0f03e4</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -26530,12 +26562,12 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -26565,7 +26597,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e7</t>
+          <t>6a4af7f0ae633549bd0f03e6</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -26578,12 +26610,12 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
@@ -26595,12 +26627,12 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K476" t="inlineStr">
@@ -26613,7 +26645,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e8</t>
+          <t>6a4af7f0ae633549bd0f03e9</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -26626,12 +26658,12 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
@@ -26661,7 +26693,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e5</t>
+          <t>6a4af7f0ae633549bd0f03ec</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -26674,12 +26706,12 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -26709,7 +26741,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ea</t>
+          <t>6a4af7f0ae633549bd0f03e3</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -26722,12 +26754,12 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
@@ -26757,7 +26789,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e9</t>
+          <t>6a4af7f0ae633549bd0f03e5</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -26770,12 +26802,12 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -26805,7 +26837,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ec</t>
+          <t>6a4af7f0ae633549bd0f03ea</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -26818,12 +26850,12 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
@@ -26853,7 +26885,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f2</t>
+          <t>6a4af7f0ae633549bd0f03ef</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -26866,12 +26898,12 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -26901,7 +26933,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ef</t>
+          <t>6a4af7f0ae633549bd0f03f1</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -26914,12 +26946,12 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -26949,7 +26981,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f5</t>
+          <t>6a4af7f0ae633549bd0f03f2</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -26962,12 +26994,12 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F484" t="inlineStr"/>
@@ -26997,7 +27029,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ee</t>
+          <t>6a4af7f0ae633549bd0f03f5</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -27010,12 +27042,12 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -27045,7 +27077,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f3</t>
+          <t>6a4af7f0ae633549bd0f03f7</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -27058,12 +27090,12 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
@@ -27141,7 +27173,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f7</t>
+          <t>6a4af7f0ae633549bd0f03ee</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -27154,12 +27186,12 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -27189,7 +27221,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f6</t>
+          <t>6a4af7f0ae633549bd0f03f3</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -27202,12 +27234,12 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -27237,7 +27269,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f0</t>
+          <t>6a4af7f0ae633549bd0f03f6</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -27250,12 +27282,12 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -27285,7 +27317,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f1</t>
+          <t>6a4af7f0ae633549bd0f03f0</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -27298,12 +27330,12 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -27381,7 +27413,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03ff</t>
+          <t>6a4af7f1ae633549bd0f03fc</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -27394,12 +27426,12 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
@@ -27429,7 +27461,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fe</t>
+          <t>6a4af7f1ae633549bd0f03ff</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -27442,12 +27474,12 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F494" t="inlineStr"/>
@@ -27477,7 +27509,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0400</t>
+          <t>6a4af7f1ae633549bd0f03fd</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -27490,12 +27522,12 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -27525,7 +27557,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fb</t>
+          <t>6a4af7f0ae633549bd0f03fa</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -27538,12 +27570,12 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -27573,7 +27605,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0402</t>
+          <t>6a4af7f1ae633549bd0f0401</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -27586,12 +27618,12 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F497" t="inlineStr"/>
@@ -27621,7 +27653,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fc</t>
+          <t>6a4af7f0ae633549bd0f03fb</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -27634,12 +27666,12 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
@@ -27669,7 +27701,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0401</t>
+          <t>6a4af7f1ae633549bd0f0402</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -27682,12 +27714,12 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -27717,7 +27749,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fa</t>
+          <t>6a4af7f1ae633549bd0f03fe</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -27730,12 +27762,12 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -27765,7 +27797,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fd</t>
+          <t>6a4af7f1ae633549bd0f0400</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -27778,12 +27810,12 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -27861,7 +27893,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0408</t>
+          <t>6a4af7f1ae633549bd0f040c</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -27874,12 +27906,12 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -27909,7 +27941,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0409</t>
+          <t>6a4af7f1ae633549bd0f0406</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -27922,12 +27954,12 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -27957,7 +27989,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040b</t>
+          <t>6a4af7f1ae633549bd0f040a</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -27970,12 +28002,12 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -28005,7 +28037,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0406</t>
+          <t>6a4af7f1ae633549bd0f040d</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -28018,12 +28050,12 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F506" t="inlineStr"/>
@@ -28053,7 +28085,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040a</t>
+          <t>6a4af7f1ae633549bd0f040b</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -28066,12 +28098,12 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F507" t="inlineStr"/>
@@ -28101,7 +28133,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040c</t>
+          <t>6a4af7f1ae633549bd0f0408</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -28114,12 +28146,12 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -28149,7 +28181,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0407</t>
+          <t>6a4af7f1ae633549bd0f0409</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -28162,12 +28194,12 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
@@ -28197,7 +28229,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040d</t>
+          <t>6a4af7f1ae633549bd0f0404</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -28210,12 +28242,12 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
@@ -28245,7 +28277,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0404</t>
+          <t>6a4af7f1ae633549bd0f0407</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -28258,12 +28290,12 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -28293,7 +28325,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040f</t>
+          <t>6a4af7f1ae633549bd0f0410</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -28306,12 +28338,12 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F512" t="inlineStr"/>
@@ -28341,7 +28373,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0410</t>
+          <t>6a4af7f1ae633549bd0f0418</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -28354,12 +28386,12 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F513" t="inlineStr"/>
@@ -28389,7 +28421,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0413</t>
+          <t>6a4af7f1ae633549bd0f040f</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -28402,12 +28434,12 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -28437,7 +28469,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0415</t>
+          <t>6a4af7f1ae633549bd0f0416</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -28450,12 +28482,12 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F515" t="inlineStr"/>
@@ -28485,7 +28517,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0417</t>
+          <t>6a4af7f1ae633549bd0f0412</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -28498,12 +28530,12 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F516" t="inlineStr"/>
@@ -28533,7 +28565,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0418</t>
+          <t>6a4af7f1ae633549bd0f0411</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -28546,12 +28578,12 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F517" t="inlineStr"/>
@@ -28581,7 +28613,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0411</t>
+          <t>6a4af7f1ae633549bd0f0414</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -28594,12 +28626,12 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
@@ -28629,7 +28661,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0414</t>
+          <t>6a4af7f1ae633549bd0f0413</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -28642,12 +28674,12 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -28677,7 +28709,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0416</t>
+          <t>6a4af7f1ae633549bd0f0417</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -28690,12 +28722,12 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F520" t="inlineStr"/>
@@ -28725,7 +28757,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0412</t>
+          <t>6a4af7f1ae633549bd0f0415</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -28738,12 +28770,12 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F521" t="inlineStr"/>
@@ -28773,7 +28805,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041b</t>
+          <t>6a4af7f1ae633549bd0f0422</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -28786,12 +28818,12 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F522" t="inlineStr"/>
@@ -28821,7 +28853,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041d</t>
+          <t>6a4af7f1ae633549bd0f041c</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -28834,12 +28866,12 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F523" t="inlineStr"/>
@@ -28869,7 +28901,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0423</t>
+          <t>6a4af7f1ae633549bd0f041b</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -28882,12 +28914,12 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F524" t="inlineStr"/>
@@ -28917,7 +28949,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0422</t>
+          <t>6a4af7f1ae633549bd0f041d</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -28930,12 +28962,12 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F525" t="inlineStr"/>
@@ -28965,7 +28997,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041c</t>
+          <t>6a4af7f1ae633549bd0f0420</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -28978,12 +29010,12 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F526" t="inlineStr"/>
@@ -29013,7 +29045,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0420</t>
+          <t>6a4af7f1ae633549bd0f0423</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -29026,12 +29058,12 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F527" t="inlineStr"/>
@@ -29061,7 +29093,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041f</t>
+          <t>6a4af7f1ae633549bd0f0421</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -29074,12 +29106,12 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F528" t="inlineStr"/>
@@ -29109,7 +29141,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041a</t>
+          <t>6a4af7f1ae633549bd0f041e</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -29122,12 +29154,12 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -29157,7 +29189,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0421</t>
+          <t>6a4af7f1ae633549bd0f041f</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -29170,12 +29202,12 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -29205,7 +29237,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041e</t>
+          <t>6a4af7f1ae633549bd0f041a</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -29218,12 +29250,12 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -29253,7 +29285,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0428</t>
+          <t>6a4af7f1ae633549bd0f042b</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -29266,12 +29298,12 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -29301,7 +29333,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0426</t>
+          <t>6a4af7f1ae633549bd0f042c</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -29314,12 +29346,12 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
@@ -29349,7 +29381,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042d</t>
+          <t>6a4af7f1ae633549bd0f0428</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -29362,12 +29394,12 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
@@ -29397,7 +29429,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0425</t>
+          <t>6a4af7f1ae633549bd0f042e</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -29410,12 +29442,12 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -29445,7 +29477,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0429</t>
+          <t>6a4af7f1ae633549bd0f0425</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -29458,12 +29490,12 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -29493,7 +29525,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0427</t>
+          <t>6a4af7f1ae633549bd0f042a</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -29506,12 +29538,12 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -29541,7 +29573,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042a</t>
+          <t>6a4af7f1ae633549bd0f0427</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -29554,12 +29586,12 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -29589,7 +29621,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042e</t>
+          <t>6a4af7f1ae633549bd0f0426</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -29602,12 +29634,12 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F539" t="inlineStr"/>
@@ -29637,7 +29669,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042c</t>
+          <t>6a4af7f1ae633549bd0f042d</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -29650,12 +29682,12 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -29685,7 +29717,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042b</t>
+          <t>6a4af7f1ae633549bd0f0429</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -29698,12 +29730,12 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F541" t="inlineStr"/>
@@ -29733,7 +29765,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0434</t>
+          <t>6a4af7f1ae633549bd0f0430</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -29746,12 +29778,12 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F542" t="inlineStr"/>
@@ -29781,7 +29813,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0437</t>
+          <t>6a4af7f1ae633549bd0f0432</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -29794,12 +29826,12 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F543" t="inlineStr"/>
@@ -29829,7 +29861,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0439</t>
+          <t>6a4af7f1ae633549bd0f0435</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -29842,12 +29874,12 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
@@ -29877,7 +29909,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0431</t>
+          <t>6a4af7f1ae633549bd0f0437</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -29890,12 +29922,12 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -29925,7 +29957,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0433</t>
+          <t>6a4af7f1ae633549bd0f0439</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -29938,12 +29970,12 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -29973,7 +30005,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0436</t>
+          <t>6a4af7f1ae633549bd0f0438</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -29986,12 +30018,12 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
@@ -30021,7 +30053,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0438</t>
+          <t>6a4af7f1ae633549bd0f0431</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -30034,12 +30066,12 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -30069,7 +30101,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0430</t>
+          <t>6a4af7f1ae633549bd0f0433</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -30082,12 +30114,12 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -30117,7 +30149,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0432</t>
+          <t>6a4af7f1ae633549bd0f0436</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -30130,12 +30162,12 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
@@ -30165,7 +30197,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0435</t>
+          <t>6a4af7f1ae633549bd0f0434</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -30178,12 +30210,12 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F551" t="inlineStr"/>
@@ -30213,7 +30245,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0442</t>
+          <t>6a4af7f1ae633549bd0f043d</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -30226,12 +30258,12 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -30261,7 +30293,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043e</t>
+          <t>6a4af7f2ae633549bd0f0441</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -30274,12 +30306,12 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -30405,7 +30437,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0441</t>
+          <t>6a4af7f1ae633549bd0f043e</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -30418,12 +30450,12 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -30453,7 +30485,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043d</t>
+          <t>6a4af7f2ae633549bd0f043f</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -30466,12 +30498,12 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -30501,7 +30533,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0444</t>
+          <t>6a4af7f2ae633549bd0f0442</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -30514,12 +30546,12 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
@@ -30645,7 +30677,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f043f</t>
+          <t>6a4af7f2ae633549bd0f0444</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -30658,12 +30690,12 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -30693,7 +30725,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0446</t>
+          <t>6a4af7f2ae633549bd0f044e</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -30706,12 +30738,12 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -30837,7 +30869,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044d</t>
+          <t>6a4af7f2ae633549bd0f044c</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -30850,12 +30882,12 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F565" t="inlineStr"/>
@@ -30933,7 +30965,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044c</t>
+          <t>6a4af7f2ae633549bd0f044d</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -30946,12 +30978,12 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F567" t="inlineStr"/>
@@ -30981,7 +31013,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044e</t>
+          <t>6a4af7f2ae633549bd0f044f</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -30994,12 +31026,12 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F568" t="inlineStr"/>
@@ -31029,7 +31061,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044f</t>
+          <t>6a4af7f2ae633549bd0f0446</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -31042,12 +31074,12 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F569" t="inlineStr"/>
@@ -31077,7 +31109,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044b</t>
+          <t>6a4af7f2ae633549bd0f044a</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -31090,12 +31122,12 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F570" t="inlineStr"/>
@@ -31125,7 +31157,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044a</t>
+          <t>6a4af7f2ae633549bd0f044b</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -31138,12 +31170,12 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -31173,7 +31205,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0455</t>
+          <t>6a4af7f2ae633549bd0f0451</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -31186,12 +31218,12 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F572" t="inlineStr"/>
@@ -31221,7 +31253,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0457</t>
+          <t>6a4af7f2ae633549bd0f045a</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -31234,12 +31266,12 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F573" t="inlineStr"/>
@@ -31269,7 +31301,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0458</t>
+          <t>6a4af7f2ae633549bd0f0453</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -31282,12 +31314,12 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F574" t="inlineStr"/>
@@ -31317,7 +31349,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0451</t>
+          <t>6a4af7f2ae633549bd0f0455</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -31330,12 +31362,12 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -31365,7 +31397,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0459</t>
+          <t>6a4af7f2ae633549bd0f0458</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -31378,12 +31410,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F576" t="inlineStr"/>
@@ -31413,7 +31445,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0454</t>
+          <t>6a4af7f2ae633549bd0f0456</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -31426,12 +31458,12 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -31461,7 +31493,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045a</t>
+          <t>6a4af7f2ae633549bd0f0457</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -31474,12 +31506,12 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -31509,7 +31541,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0453</t>
+          <t>6a4af7f2ae633549bd0f0454</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -31522,12 +31554,12 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F579" t="inlineStr"/>
@@ -31605,7 +31637,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0456</t>
+          <t>6a4af7f2ae633549bd0f0459</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -31618,12 +31650,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -31653,7 +31685,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0462</t>
+          <t>6a4af7f2ae633549bd0f045d</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -31666,12 +31698,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F582" t="inlineStr"/>
@@ -31701,7 +31733,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0461</t>
+          <t>6a4af7f2ae633549bd0f045f</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -31714,12 +31746,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -31749,7 +31781,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0463</t>
+          <t>6a4af7f2ae633549bd0f0464</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -31762,12 +31794,12 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F584" t="inlineStr"/>
@@ -31797,7 +31829,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045d</t>
+          <t>6a4af7f2ae633549bd0f045e</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -31810,12 +31842,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -31845,7 +31877,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0465</t>
+          <t>6a4af7f2ae633549bd0f045c</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -31858,12 +31890,12 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F586" t="inlineStr"/>
@@ -31893,7 +31925,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0460</t>
+          <t>6a4af7f2ae633549bd0f0461</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -31906,12 +31938,12 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -31941,7 +31973,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045f</t>
+          <t>6a4af7f2ae633549bd0f0462</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -31954,12 +31986,12 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -31989,7 +32021,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0464</t>
+          <t>6a4af7f2ae633549bd0f0463</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -32002,12 +32034,12 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -32037,7 +32069,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045e</t>
+          <t>6a4af7f2ae633549bd0f0465</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -32050,12 +32082,12 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -32085,7 +32117,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045c</t>
+          <t>6a4af7f2ae633549bd0f0460</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -32098,12 +32130,12 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -32421,7 +32453,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0469</t>
+          <t>6a4af7f2ae633549bd0f046d</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -32434,12 +32466,12 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F598" t="inlineStr"/>
@@ -32469,7 +32501,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046d</t>
+          <t>6a4af7f2ae633549bd0f0469</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -32482,12 +32514,12 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -32613,7 +32645,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0474</t>
+          <t>6a4af7f2ae633549bd0f047b</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -32626,12 +32658,12 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F602" t="inlineStr"/>
@@ -32661,7 +32693,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0475</t>
+          <t>6a4af7f2ae633549bd0f0479</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -32674,12 +32706,12 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
@@ -32709,7 +32741,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0472</t>
+          <t>6a4af7f2ae633549bd0f047a</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -32722,12 +32754,12 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -32757,7 +32789,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0473</t>
+          <t>6a4af7f2ae633549bd0f0472</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -32770,12 +32802,12 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F605" t="inlineStr"/>
@@ -32805,7 +32837,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0476</t>
+          <t>6a4af7f2ae633549bd0f0473</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -32818,12 +32850,12 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
@@ -32853,7 +32885,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0477</t>
+          <t>6a4af7f2ae633549bd0f0476</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -32866,12 +32898,12 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -32901,7 +32933,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0478</t>
+          <t>6a4af7f2ae633549bd0f0477</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -32914,12 +32946,12 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
@@ -32949,7 +32981,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047b</t>
+          <t>6a4af7f2ae633549bd0f0475</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -32962,12 +32994,12 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F609" t="inlineStr"/>
@@ -32997,7 +33029,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047a</t>
+          <t>6a4af7f2ae633549bd0f0474</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -33010,12 +33042,12 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F610" t="inlineStr"/>
@@ -33045,7 +33077,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0479</t>
+          <t>6a4af7f2ae633549bd0f0478</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -33058,12 +33090,12 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -33093,7 +33125,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0481</t>
+          <t>6a4af7f2ae633549bd0f0482</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -33106,12 +33138,12 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F612" t="inlineStr"/>
@@ -33237,7 +33269,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0485</t>
+          <t>6a4af7f2ae633549bd0f0480</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -33250,12 +33282,12 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -33285,7 +33317,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0482</t>
+          <t>6a4af7f2ae633549bd0f0481</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -33298,12 +33330,12 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F616" t="inlineStr"/>
@@ -33333,7 +33365,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047d</t>
+          <t>6a4af7f3ae633549bd0f0485</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -33346,12 +33378,12 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F617" t="inlineStr"/>
@@ -33381,7 +33413,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0483</t>
+          <t>6a4af7f2ae633549bd0f047e</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -33394,12 +33426,12 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -33429,7 +33461,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047e</t>
+          <t>6a4af7f2ae633549bd0f047d</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -33442,12 +33474,12 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -33525,7 +33557,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0480</t>
+          <t>6a4af7f2ae633549bd0f0483</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -33538,12 +33570,12 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F621" t="inlineStr"/>
@@ -33573,7 +33605,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0488</t>
+          <t>6a4af7f3ae633549bd0f048d</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -33586,12 +33618,12 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F622" t="inlineStr"/>
@@ -33669,7 +33701,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048d</t>
+          <t>6a4af7f3ae633549bd0f0491</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -33682,12 +33714,12 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
@@ -33717,7 +33749,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0491</t>
+          <t>6a4af7f3ae633549bd0f048b</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -33730,12 +33762,12 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F625" t="inlineStr"/>
@@ -33765,7 +33797,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048b</t>
+          <t>6a4af7f3ae633549bd0f0490</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -33778,12 +33810,12 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F626" t="inlineStr"/>
@@ -33813,7 +33845,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048c</t>
+          <t>6a4af7f3ae633549bd0f048a</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -33826,12 +33858,12 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F627" t="inlineStr"/>
@@ -33861,7 +33893,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048e</t>
+          <t>6a4af7f3ae633549bd0f048c</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -33874,12 +33906,12 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F628" t="inlineStr"/>
@@ -33909,7 +33941,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048a</t>
+          <t>6a4af7f3ae633549bd0f0488</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -33922,12 +33954,12 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F629" t="inlineStr"/>
@@ -33957,7 +33989,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0490</t>
+          <t>6a4af7f3ae633549bd0f048e</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -33970,12 +34002,12 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F630" t="inlineStr"/>
@@ -34053,7 +34085,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049c</t>
+          <t>6a4af7f3ae633549bd0f049a</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -34066,12 +34098,12 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F632" t="inlineStr"/>
@@ -34149,7 +34181,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049a</t>
+          <t>6a4af7f3ae633549bd0f0493</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -34162,12 +34194,12 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F634" t="inlineStr"/>
@@ -34197,7 +34229,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0494</t>
+          <t>6a4af7f3ae633549bd0f0496</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -34210,12 +34242,12 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F635" t="inlineStr"/>
@@ -34245,7 +34277,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0497</t>
+          <t>6a4af7f3ae633549bd0f0499</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -34258,12 +34290,12 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F636" t="inlineStr"/>
@@ -34293,7 +34325,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0493</t>
+          <t>6a4af7f3ae633549bd0f0494</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -34306,12 +34338,12 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F637" t="inlineStr"/>
@@ -34341,7 +34373,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0496</t>
+          <t>6a4af7f3ae633549bd0f0497</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -34354,12 +34386,12 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F638" t="inlineStr"/>
@@ -34389,7 +34421,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0499</t>
+          <t>6a4af7f3ae633549bd0f049c</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -34402,12 +34434,12 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
@@ -34437,7 +34469,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0495</t>
+          <t>6a4af7f3ae633549bd0f0498</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -34450,12 +34482,12 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F640" t="inlineStr"/>
@@ -34485,7 +34517,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0498</t>
+          <t>6a4af7f3ae633549bd0f0495</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -34498,12 +34530,12 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F641" t="inlineStr"/>
@@ -34581,7 +34613,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a5</t>
+          <t>6a4af7f3ae633549bd0f04a3</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -34594,12 +34626,12 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
@@ -34629,7 +34661,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a6</t>
+          <t>6a4af7f3ae633549bd0f04a5</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -34642,12 +34674,12 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -34773,7 +34805,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a0</t>
+          <t>6a4af7f3ae633549bd0f04a7</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -34786,12 +34818,12 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -34821,7 +34853,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a2</t>
+          <t>6a4af7f3ae633549bd0f04a6</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -34834,12 +34866,12 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -34869,7 +34901,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a3</t>
+          <t>6a4af7f3ae633549bd0f04a4</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -34882,12 +34914,12 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -34917,7 +34949,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a4</t>
+          <t>6a4af7f3ae633549bd0f04a0</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -34930,12 +34962,12 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F650" t="inlineStr"/>
@@ -34965,7 +34997,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a7</t>
+          <t>6a4af7f3ae633549bd0f04a2</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -34978,12 +35010,12 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F651" t="inlineStr"/>
@@ -35013,7 +35045,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ac</t>
+          <t>6a4af7f3ae633549bd0f04b0</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -35026,12 +35058,12 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -35061,7 +35093,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ae</t>
+          <t>6a4af7f3ae633549bd0f04a9</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -35074,12 +35106,12 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F653" t="inlineStr"/>
@@ -35109,7 +35141,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b1</t>
+          <t>6a4af7f3ae633549bd0f04aa</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -35122,12 +35154,12 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F654" t="inlineStr"/>
@@ -35157,7 +35189,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ad</t>
+          <t>6a4af7f3ae633549bd0f04b2</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -35170,12 +35202,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F655" t="inlineStr"/>
@@ -35205,7 +35237,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b0</t>
+          <t>6a4af7f3ae633549bd0f04ac</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -35218,12 +35250,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F656" t="inlineStr"/>
@@ -35253,7 +35285,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ab</t>
+          <t>6a4af7f3ae633549bd0f04ae</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -35266,12 +35298,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F657" t="inlineStr"/>
@@ -35301,7 +35333,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04af</t>
+          <t>6a4af7f3ae633549bd0f04b1</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -35314,12 +35346,12 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F658" t="inlineStr"/>
@@ -35349,7 +35381,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a9</t>
+          <t>6a4af7f3ae633549bd0f04ad</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -35362,12 +35394,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -35397,7 +35429,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04aa</t>
+          <t>6a4af7f3ae633549bd0f04af</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -35410,12 +35442,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F660" t="inlineStr"/>
@@ -35445,7 +35477,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b2</t>
+          <t>6a4af7f3ae633549bd0f04ab</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -35458,12 +35490,12 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F661" t="inlineStr"/>
@@ -35493,7 +35525,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b9</t>
+          <t>6a4af7f3ae633549bd0f04b7</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -35506,12 +35538,12 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F662" t="inlineStr"/>
@@ -35541,7 +35573,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bc</t>
+          <t>6a4af7f3ae633549bd0f04b8</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -35554,12 +35586,12 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F663" t="inlineStr"/>
@@ -35589,7 +35621,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ba</t>
+          <t>6a4af7f3ae633549bd0f04bb</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -35602,12 +35634,12 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F664" t="inlineStr"/>
@@ -35637,7 +35669,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bd</t>
+          <t>6a4af7f3ae633549bd0f04b9</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -35650,12 +35682,12 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F665" t="inlineStr"/>
@@ -35685,7 +35717,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bb</t>
+          <t>6a4af7f3ae633549bd0f04ba</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -35698,12 +35730,12 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F666" t="inlineStr"/>
@@ -35733,7 +35765,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b6</t>
+          <t>6a4af7f3ae633549bd0f04bd</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -35746,12 +35778,12 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F667" t="inlineStr"/>
@@ -35781,7 +35813,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b4</t>
+          <t>6a4af7f3ae633549bd0f04b5</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -35794,12 +35826,12 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F668" t="inlineStr"/>
@@ -35829,7 +35861,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b7</t>
+          <t>6a4af7f3ae633549bd0f04bc</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -35842,12 +35874,12 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
@@ -35877,7 +35909,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b8</t>
+          <t>6a4af7f3ae633549bd0f04b6</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -35890,12 +35922,12 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F670" t="inlineStr"/>
@@ -35925,7 +35957,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b5</t>
+          <t>6a4af7f3ae633549bd0f04b4</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -35938,12 +35970,12 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F671" t="inlineStr"/>
@@ -35973,7 +36005,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c0</t>
+          <t>6a4af7f3ae633549bd0f04bf</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -35986,12 +36018,12 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F672" t="inlineStr"/>
@@ -36021,7 +36053,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c5</t>
+          <t>6a4af7f3ae633549bd0f04c2</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -36034,12 +36066,12 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
@@ -36069,7 +36101,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c2</t>
+          <t>6a4af7f3ae633549bd0f04c0</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -36082,12 +36114,12 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F674" t="inlineStr"/>
@@ -36117,7 +36149,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c8</t>
+          <t>6a4af7f3ae633549bd0f04c1</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -36130,12 +36162,12 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F675" t="inlineStr"/>
@@ -36165,7 +36197,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c1</t>
+          <t>6a4af7f3ae633549bd0f04c3</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -36178,12 +36210,12 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -36213,7 +36245,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c3</t>
+          <t>6a4af7f3ae633549bd0f04c5</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -36226,12 +36258,12 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
@@ -36309,7 +36341,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c4</t>
+          <t>6a4af7f3ae633549bd0f04c8</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -36322,12 +36354,12 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F679" t="inlineStr"/>
@@ -36405,7 +36437,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bf</t>
+          <t>6a4af7f3ae633549bd0f04c4</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -36418,12 +36450,12 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
@@ -36453,7 +36485,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cf</t>
+          <t>6a4af7f4ae633549bd0f04d1</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -36466,12 +36498,12 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F682" t="inlineStr"/>
@@ -36501,7 +36533,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cd</t>
+          <t>6a4af7f4ae633549bd0f04d2</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -36514,12 +36546,12 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F683" t="inlineStr"/>
@@ -36549,7 +36581,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d0</t>
+          <t>6a4af7f4ae633549bd0f04ca</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -36562,12 +36594,12 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F684" t="inlineStr"/>
@@ -36597,7 +36629,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d3</t>
+          <t>6a4af7f4ae633549bd0f04cb</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -36610,12 +36642,12 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F685" t="inlineStr"/>
@@ -36645,7 +36677,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cb</t>
+          <t>6a4af7f4ae633549bd0f04cc</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -36658,12 +36690,12 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F686" t="inlineStr"/>
@@ -36693,7 +36725,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cc</t>
+          <t>6a4af7f4ae633549bd0f04d3</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -36706,12 +36738,12 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F687" t="inlineStr"/>
@@ -36789,7 +36821,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ca</t>
+          <t>6a4af7f4ae633549bd0f04d0</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -36802,12 +36834,12 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F689" t="inlineStr"/>
@@ -36837,7 +36869,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d1</t>
+          <t>6a4af7f4ae633549bd0f04cd</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -36850,12 +36882,12 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F690" t="inlineStr"/>
@@ -36885,7 +36917,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d2</t>
+          <t>6a4af7f4ae633549bd0f04cf</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -36898,12 +36930,12 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F691" t="inlineStr"/>
@@ -37077,7 +37109,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d8</t>
+          <t>6a4af7f4ae633549bd0f04dd</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -37090,12 +37122,12 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F695" t="inlineStr"/>
@@ -37125,7 +37157,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d9</t>
+          <t>6a4af7f4ae633549bd0f04d8</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -37138,12 +37170,12 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F696" t="inlineStr"/>
@@ -37173,7 +37205,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04db</t>
+          <t>6a4af7f4ae633549bd0f04d9</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -37186,12 +37218,12 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F697" t="inlineStr"/>
@@ -37269,7 +37301,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dd</t>
+          <t>6a4af7f4ae633549bd0f04db</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -37282,12 +37314,12 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F699" t="inlineStr"/>
@@ -37413,7 +37445,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e0</t>
+          <t>6a4af7f4ae633549bd0f04e2</t>
         </is>
       </c>
       <c r="B702" t="n">
@@ -37426,12 +37458,12 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F702" t="inlineStr"/>
@@ -37461,7 +37493,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e4</t>
+          <t>6a4af7f4ae633549bd0f04e3</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -37474,12 +37506,12 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F703" t="inlineStr"/>
@@ -37509,7 +37541,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e9</t>
+          <t>6a4af7f4ae633549bd0f04e5</t>
         </is>
       </c>
       <c r="B704" t="n">
@@ -37522,12 +37554,12 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F704" t="inlineStr"/>
@@ -37557,7 +37589,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e5</t>
+          <t>6a4af7f4ae633549bd0f04e1</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -37570,12 +37602,12 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
@@ -37605,7 +37637,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e1</t>
+          <t>6a4af7f4ae633549bd0f04e6</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -37618,12 +37650,12 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F706" t="inlineStr"/>
@@ -37653,7 +37685,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e2</t>
+          <t>6a4af7f4ae633549bd0f04e7</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -37666,12 +37698,12 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F707" t="inlineStr"/>
@@ -37701,7 +37733,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e3</t>
+          <t>6a4af7f4ae633549bd0f04e8</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -37714,12 +37746,12 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F708" t="inlineStr"/>
@@ -37749,7 +37781,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e6</t>
+          <t>6a4af7f4ae633549bd0f04e9</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -37762,12 +37794,12 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F709" t="inlineStr"/>
@@ -37797,7 +37829,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e7</t>
+          <t>6a4af7f4ae633549bd0f04e0</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -37810,12 +37842,12 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F710" t="inlineStr"/>
@@ -37845,7 +37877,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e8</t>
+          <t>6a4af7f4ae633549bd0f04e4</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -37858,12 +37890,12 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F711" t="inlineStr"/>
@@ -37893,7 +37925,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f3</t>
+          <t>6a4af7f4ae633549bd0f04ec</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -37906,12 +37938,12 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F712" t="inlineStr"/>
@@ -37989,7 +38021,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ee</t>
+          <t>6a4af7f4ae633549bd0f04f4</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -38002,12 +38034,12 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -38037,7 +38069,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f4</t>
+          <t>6a4af7f4ae633549bd0f04ee</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -38050,12 +38082,12 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F715" t="inlineStr"/>
@@ -38133,7 +38165,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f1</t>
+          <t>6a4af7f4ae633549bd0f04f2</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -38146,12 +38178,12 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F717" t="inlineStr"/>
@@ -38181,7 +38213,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f2</t>
+          <t>6a4af7f4ae633549bd0f04f3</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -38194,12 +38226,12 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F718" t="inlineStr"/>
@@ -38229,7 +38261,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ec</t>
+          <t>6a4af7f4ae633549bd0f04f1</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -38242,12 +38274,12 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F719" t="inlineStr"/>
@@ -38277,7 +38309,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ed</t>
+          <t>6a4af7f4ae633549bd0f04ef</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -38290,12 +38322,12 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F720" t="inlineStr"/>
@@ -38325,7 +38357,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ef</t>
+          <t>6a4af7f4ae633549bd0f04ed</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -38338,12 +38370,12 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F721" t="inlineStr"/>
@@ -38373,7 +38405,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f9</t>
+          <t>6a4af7f4ae633549bd0f04f7</t>
         </is>
       </c>
       <c r="B722" t="n">
@@ -38386,12 +38418,12 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F722" t="inlineStr"/>
@@ -38421,7 +38453,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fb</t>
+          <t>6a4af7f4ae633549bd0f04fa</t>
         </is>
       </c>
       <c r="B723" t="n">
@@ -38434,12 +38466,12 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F723" t="inlineStr"/>
@@ -38469,7 +38501,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fc</t>
+          <t>6a4af7f4ae633549bd0f04f6</t>
         </is>
       </c>
       <c r="B724" t="n">
@@ -38482,12 +38514,12 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F724" t="inlineStr"/>
@@ -38517,7 +38549,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fd</t>
+          <t>6a4af7f4ae633549bd0f04f8</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -38530,12 +38562,12 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
@@ -38565,7 +38597,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f7</t>
+          <t>6a4af7f4ae633549bd0f04fb</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -38578,12 +38610,12 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F726" t="inlineStr"/>
@@ -38613,7 +38645,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fa</t>
+          <t>6a4af7f4ae633549bd0f04fd</t>
         </is>
       </c>
       <c r="B727" t="n">
@@ -38626,12 +38658,12 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F727" t="inlineStr"/>
@@ -38661,7 +38693,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f8</t>
+          <t>6a4af7f4ae633549bd0f04fe</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -38674,12 +38706,12 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F728" t="inlineStr"/>
@@ -38709,7 +38741,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f6</t>
+          <t>6a4af7f4ae633549bd0f04f9</t>
         </is>
       </c>
       <c r="B729" t="n">
@@ -38722,12 +38754,12 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F729" t="inlineStr"/>
@@ -38757,7 +38789,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ff</t>
+          <t>6a4af7f4ae633549bd0f04fc</t>
         </is>
       </c>
       <c r="B730" t="n">
@@ -38770,12 +38802,12 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F730" t="inlineStr"/>
@@ -38805,7 +38837,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fe</t>
+          <t>6a4af7f4ae633549bd0f04ff</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -38818,12 +38850,12 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F731" t="inlineStr"/>
@@ -38853,7 +38885,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0505</t>
+          <t>6a4af7f4ae633549bd0f0502</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -38866,12 +38898,12 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F732" t="inlineStr"/>
@@ -38949,7 +38981,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0504</t>
+          <t>6a4af7f4ae633549bd0f0503</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -38962,12 +38994,12 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
@@ -38997,7 +39029,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0509</t>
+          <t>6a4af7f4ae633549bd0f0507</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -39010,12 +39042,12 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -39045,7 +39077,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0506</t>
+          <t>6a4af7f4ae633549bd0f0501</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -39058,12 +39090,12 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
@@ -39093,7 +39125,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0503</t>
+          <t>6a4af7f4ae633549bd0f0504</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -39106,12 +39138,12 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F737" t="inlineStr"/>
@@ -39141,7 +39173,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0507</t>
+          <t>6a4af7f4ae633549bd0f0506</t>
         </is>
       </c>
       <c r="B738" t="n">
@@ -39154,12 +39186,12 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F738" t="inlineStr"/>
@@ -39189,7 +39221,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0501</t>
+          <t>6a4af7f4ae633549bd0f0505</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -39202,12 +39234,12 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F739" t="inlineStr"/>
@@ -39285,7 +39317,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0502</t>
+          <t>6a4af7f4ae633549bd0f0509</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -39298,12 +39330,12 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F741" t="inlineStr"/>
@@ -39333,7 +39365,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050e</t>
+          <t>6a4af7f4ae633549bd0f050c</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -39346,12 +39378,12 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F742" t="inlineStr"/>
@@ -39381,7 +39413,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0513</t>
+          <t>6a4af7f5ae633549bd0f050f</t>
         </is>
       </c>
       <c r="B743" t="n">
@@ -39394,12 +39426,12 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F743" t="inlineStr"/>
@@ -39429,7 +39461,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0514</t>
+          <t>6a4af7f5ae633549bd0f0511</t>
         </is>
       </c>
       <c r="B744" t="n">
@@ -39442,12 +39474,12 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F744" t="inlineStr"/>
@@ -39477,7 +39509,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0512</t>
+          <t>6a4af7f5ae633549bd0f0515</t>
         </is>
       </c>
       <c r="B745" t="n">
@@ -39490,12 +39522,12 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F745" t="inlineStr"/>
@@ -39525,7 +39557,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0510</t>
+          <t>6a4af7f4ae633549bd0f050d</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -39538,12 +39570,12 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F746" t="inlineStr"/>
@@ -39573,7 +39605,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050d</t>
+          <t>6a4af7f5ae633549bd0f0510</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -39586,12 +39618,12 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F747" t="inlineStr"/>
@@ -39621,7 +39653,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0511</t>
+          <t>6a4af7f5ae633549bd0f0512</t>
         </is>
       </c>
       <c r="B748" t="n">
@@ -39634,12 +39666,12 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F748" t="inlineStr"/>
@@ -39669,7 +39701,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0515</t>
+          <t>6a4af7f5ae633549bd0f0514</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -39682,12 +39714,12 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
@@ -39717,7 +39749,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050c</t>
+          <t>6a4af7f5ae633549bd0f0513</t>
         </is>
       </c>
       <c r="B750" t="n">
@@ -39730,12 +39762,12 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F750" t="inlineStr"/>
@@ -39765,7 +39797,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050f</t>
+          <t>6a4af7f5ae633549bd0f050e</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -39778,12 +39810,12 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F751" t="inlineStr"/>
@@ -39909,7 +39941,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051c</t>
+          <t>6a4af7f5ae633549bd0f051d</t>
         </is>
       </c>
       <c r="B754" t="n">
@@ -39922,12 +39954,12 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F754" t="inlineStr"/>
@@ -39957,7 +39989,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051d</t>
+          <t>6a4af7f5ae633549bd0f051c</t>
         </is>
       </c>
       <c r="B755" t="n">
@@ -39970,12 +40002,12 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F755" t="inlineStr"/>

--- a/datos/maestros/md_partidos.xlsx
+++ b/datos/maestros/md_partidos.xlsx
@@ -21773,7 +21773,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bf</t>
+          <t>6a4af7f0ae633549bd0f03b8</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -21786,19 +21786,19 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="inlineStr"/>
       <c r="H382" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -21821,7 +21821,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b7</t>
+          <t>6a4af7f0ae633549bd0f03bf</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -21834,12 +21834,12 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
@@ -21851,12 +21851,12 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
@@ -21869,7 +21869,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ba</t>
+          <t>6a4af7f0ae633549bd0f03b9</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -21882,29 +21882,29 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="inlineStr"/>
       <c r="H384" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
@@ -21917,7 +21917,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bb</t>
+          <t>6a4af7f0ae633549bd0f03b7</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -21930,29 +21930,29 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
@@ -22013,7 +22013,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03be</t>
+          <t>6a4af7f0ae633549bd0f03ba</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -22026,12 +22026,12 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F387" t="inlineStr"/>
@@ -22043,12 +22043,12 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
@@ -22061,7 +22061,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bc</t>
+          <t>6a4af7f0ae633549bd0f03be</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -22074,19 +22074,19 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -22109,7 +22109,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b9</t>
+          <t>6a4af7f0ae633549bd0f03bb</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -22122,12 +22122,12 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
@@ -22139,12 +22139,12 @@
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
@@ -22157,7 +22157,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c0</t>
+          <t>6a4af7f0ae633549bd0f03bc</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -22170,33 +22170,29 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
-        </is>
-      </c>
-      <c r="F390" t="n">
-        <v>0</v>
-      </c>
-      <c r="G390" t="n">
-        <v>0</v>
-      </c>
+          <t>504e581e4d8bec9a670000c6</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
@@ -22204,16 +22200,12 @@
           <t>closed</t>
         </is>
       </c>
-      <c r="L390" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="L390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b8</t>
+          <t>6a4af7f0ae633549bd0f03c0</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -22226,29 +22218,33 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
-        </is>
-      </c>
-      <c r="F391" t="inlineStr"/>
-      <c r="G391" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000d9</t>
+        </is>
+      </c>
+      <c r="F391" t="n">
+        <v>0</v>
+      </c>
+      <c r="G391" t="n">
+        <v>0</v>
+      </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
@@ -22256,7 +22252,11 @@
           <t>closed</t>
         </is>
       </c>
-      <c r="L391" t="inlineStr"/>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -22373,7 +22373,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0382</t>
+          <t>6a4af7efae633549bd0f0381</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -22386,12 +22386,12 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F394" t="n">
@@ -22402,7 +22402,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -22429,7 +22429,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0381</t>
+          <t>6a4af7efae633549bd0f0380</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -22442,33 +22442,33 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G395" t="n">
         <v>0</v>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
@@ -22485,7 +22485,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0380</t>
+          <t>6a4af7efae633549bd0f0384</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -22498,33 +22498,33 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G396" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
@@ -22541,7 +22541,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0388</t>
+          <t>6a4af7efae633549bd0f0383</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -22554,33 +22554,33 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F397" t="n">
+        <v>1</v>
+      </c>
+      <c r="G397" t="n">
         <v>2</v>
       </c>
-      <c r="G397" t="n">
-        <v>1</v>
-      </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
@@ -22597,7 +22597,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0383</t>
+          <t>6a4af7efae633549bd0f0388</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -22610,33 +22610,33 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F398" t="n">
+        <v>2</v>
+      </c>
+      <c r="G398" t="n">
         <v>1</v>
       </c>
-      <c r="G398" t="n">
-        <v>2</v>
-      </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
@@ -22653,7 +22653,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0384</t>
+          <t>6a4af7efae633549bd0f0387</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -22666,23 +22666,23 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F399" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G399" t="n">
         <v>1</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -22765,7 +22765,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0387</t>
+          <t>6a4af7efae633549bd0f0382</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -22778,23 +22778,23 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F401" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -22821,7 +22821,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0391</t>
+          <t>6a4af7efae633549bd0f0392</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -22834,19 +22834,19 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F402" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G402" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H402" t="inlineStr">
         <is>
@@ -22855,12 +22855,12 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
           <t>19:30</t>
-        </is>
-      </c>
-      <c r="J402" t="inlineStr">
-        <is>
-          <t>21:30</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
@@ -22877,7 +22877,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038f</t>
+          <t>6a4af7efae633549bd0f038b</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -22890,19 +22890,19 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F403" t="n">
         <v>1</v>
       </c>
       <c r="G403" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H403" t="inlineStr">
         <is>
@@ -22911,12 +22911,12 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
@@ -22933,7 +22933,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0392</t>
+          <t>6a4af7efae633549bd0f038c</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -22946,33 +22946,33 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F404" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G404" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
@@ -22989,7 +22989,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0394</t>
+          <t>6a4af7efae633549bd0f038d</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -23002,33 +23002,33 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F405" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G405" t="n">
         <v>0</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
@@ -23045,7 +23045,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0393</t>
+          <t>6a4af7efae633549bd0f038e</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -23058,33 +23058,33 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F406" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G406" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
@@ -23157,7 +23157,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038d</t>
+          <t>6a4af7efae633549bd0f0391</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -23170,33 +23170,33 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F408" t="n">
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
@@ -23213,7 +23213,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038b</t>
+          <t>6a4af7efae633549bd0f0394</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -23226,19 +23226,19 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G409" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
@@ -23247,12 +23247,12 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
@@ -23269,7 +23269,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038c</t>
+          <t>6a4af7efae633549bd0f0393</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -23282,33 +23282,33 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
@@ -23325,7 +23325,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038e</t>
+          <t>6a4af7efae633549bd0f038f</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -23338,23 +23338,23 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -23381,7 +23381,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039e</t>
+          <t>6a4af7efae633549bd0f039b</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -23394,33 +23394,33 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
@@ -23437,7 +23437,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0399</t>
+          <t>6a4af7efae633549bd0f039f</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -23450,33 +23450,33 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F413" t="n">
+        <v>1</v>
+      </c>
+      <c r="G413" t="n">
         <v>3</v>
       </c>
-      <c r="G413" t="n">
-        <v>1</v>
-      </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
@@ -23493,7 +23493,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039f</t>
+          <t>6a4af7efae633549bd0f0399</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -23506,33 +23506,33 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F414" t="n">
+        <v>3</v>
+      </c>
+      <c r="G414" t="n">
         <v>1</v>
       </c>
-      <c r="G414" t="n">
-        <v>3</v>
-      </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
           <t>19:30</t>
-        </is>
-      </c>
-      <c r="J414" t="inlineStr">
-        <is>
-          <t>21:30</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
@@ -23549,7 +23549,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0397</t>
+          <t>6a4af7efae633549bd0f039a</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -23562,12 +23562,12 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F415" t="n">
@@ -23578,17 +23578,17 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
@@ -23605,7 +23605,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0398</t>
+          <t>6a4af7efae633549bd0f039d</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -23618,20 +23618,20 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F416" t="n">
+        <v>4</v>
+      </c>
+      <c r="G416" t="n">
         <v>0</v>
       </c>
-      <c r="G416" t="n">
-        <v>2</v>
-      </c>
       <c r="H416" t="inlineStr">
         <is>
           <t>2026-08-30</t>
@@ -23639,12 +23639,12 @@
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
@@ -23661,7 +23661,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039a</t>
+          <t>6a4af7efae633549bd0f0398</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -23674,33 +23674,33 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G417" t="n">
         <v>2</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
@@ -23717,7 +23717,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039c</t>
+          <t>6a4af7efae633549bd0f0397</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -23730,33 +23730,33 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F418" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G418" t="n">
         <v>2</v>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
@@ -23773,7 +23773,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039d</t>
+          <t>6a4af7efae633549bd0f039c</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -23786,33 +23786,33 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F419" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G419" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
@@ -23829,7 +23829,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039b</t>
+          <t>6a4af7efae633549bd0f0396</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -23842,12 +23842,12 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F420" t="n">
@@ -23858,17 +23858,17 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
@@ -23885,7 +23885,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0396</t>
+          <t>6a4af7efae633549bd0f039e</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -23898,33 +23898,33 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F421" t="n">
+        <v>2</v>
+      </c>
+      <c r="G421" t="n">
         <v>1</v>
       </c>
-      <c r="G421" t="n">
-        <v>0</v>
-      </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
@@ -23941,7 +23941,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03aa</t>
+          <t>6a4af7efae633549bd0f03a2</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -23954,19 +23954,19 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G422" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H422" t="inlineStr">
         <is>
@@ -23975,17 +23975,17 @@
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
@@ -23997,7 +23997,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a5</t>
+          <t>6a4af7efae633549bd0f03a1</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -24010,19 +24010,19 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F423" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G423" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
@@ -24031,17 +24031,17 @@
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
@@ -24053,7 +24053,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a6</t>
+          <t>6a4af7efae633549bd0f03a3</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -24066,37 +24066,45 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
-        </is>
-      </c>
-      <c r="F424" t="inlineStr"/>
-      <c r="G424" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000c6</t>
+        </is>
+      </c>
+      <c r="F424" t="n">
+        <v>1</v>
+      </c>
+      <c r="G424" t="n">
+        <v>0</v>
+      </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="L424" t="inlineStr"/>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -24122,8 +24130,12 @@
           <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
-      <c r="F425" t="inlineStr"/>
-      <c r="G425" t="inlineStr"/>
+      <c r="F425" t="n">
+        <v>2</v>
+      </c>
+      <c r="G425" t="n">
+        <v>3</v>
+      </c>
       <c r="H425" t="inlineStr">
         <is>
           <t>2026-09-07</t>
@@ -24141,15 +24153,19 @@
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="L425" t="inlineStr"/>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a7</t>
+          <t>6a4af7efae633549bd0f03a6</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -24162,38 +24178,38 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F426" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G426" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
@@ -24205,7 +24221,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a8</t>
+          <t>6a4af7efae633549bd0f03a9</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -24218,38 +24234,38 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G427" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
@@ -24261,7 +24277,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a9</t>
+          <t>6a4af7efae633549bd0f03aa</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -24274,38 +24290,38 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G428" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
@@ -24317,7 +24333,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a2</t>
+          <t>6a4af7efae633549bd0f03a5</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -24330,38 +24346,38 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G429" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
@@ -24373,7 +24389,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a1</t>
+          <t>6a4af7efae633549bd0f03a7</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -24386,19 +24402,19 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G430" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H430" t="inlineStr">
         <is>
@@ -24417,7 +24433,7 @@
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
@@ -24429,7 +24445,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a3</t>
+          <t>6a4af7efae633549bd0f03a8</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -24442,38 +24458,38 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G431" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
@@ -24485,7 +24501,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03af</t>
+          <t>6a4af7efae633549bd0f03b3</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -24498,12 +24514,12 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -24515,12 +24531,12 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
@@ -24533,7 +24549,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ac</t>
+          <t>6a4af7efae633549bd0f03af</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -24546,29 +24562,29 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr"/>
       <c r="H433" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
@@ -24581,7 +24597,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b5</t>
+          <t>6a4af7efae633549bd0f03b1</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -24594,29 +24610,29 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr"/>
       <c r="H434" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
@@ -24629,7 +24645,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ae</t>
+          <t>6a4af7efae633549bd0f03b4</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -24642,29 +24658,29 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F435" t="inlineStr"/>
       <c r="G435" t="inlineStr"/>
       <c r="H435" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
@@ -24677,7 +24693,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b3</t>
+          <t>6a4af7efae633549bd0f03b0</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -24690,29 +24706,29 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
       <c r="G436" t="inlineStr"/>
       <c r="H436" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
@@ -24725,7 +24741,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b0</t>
+          <t>6a4af7efae633549bd0f03ad</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -24738,29 +24754,29 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr"/>
       <c r="H437" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
@@ -24773,7 +24789,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ad</t>
+          <t>6a4af7efae633549bd0f03b2</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -24786,29 +24802,29 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr"/>
       <c r="H438" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K438" t="inlineStr">
@@ -24821,7 +24837,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b2</t>
+          <t>6a4af7f0ae633549bd0f03b5</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -24834,19 +24850,19 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr"/>
       <c r="H439" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -24869,7 +24885,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b4</t>
+          <t>6a4af7efae633549bd0f03ae</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -24882,29 +24898,29 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
       <c r="G440" t="inlineStr"/>
       <c r="H440" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
@@ -24917,7 +24933,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b1</t>
+          <t>6a4af7efae633549bd0f03ac</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -24930,12 +24946,12 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -24947,12 +24963,12 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K441" t="inlineStr">
@@ -24965,7 +24981,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c5</t>
+          <t>6a4af7f0ae633549bd0f03c3</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -24978,12 +24994,12 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -24995,12 +25011,12 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
@@ -25013,7 +25029,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c3</t>
+          <t>6a4af7f0ae633549bd0f03c5</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -25026,12 +25042,12 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
@@ -25043,12 +25059,12 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K443" t="inlineStr">
@@ -25061,7 +25077,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c2</t>
+          <t>6a4af7f0ae633549bd0f03c9</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -25074,12 +25090,12 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
@@ -25091,12 +25107,12 @@
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K444" t="inlineStr">
@@ -25109,7 +25125,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c4</t>
+          <t>6a4af7f0ae633549bd0f03cb</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -25122,19 +25138,19 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
       <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -25157,7 +25173,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c8</t>
+          <t>6a4af7f0ae633549bd0f03c2</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -25170,12 +25186,12 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -25187,12 +25203,12 @@
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K446" t="inlineStr">
@@ -25205,7 +25221,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c9</t>
+          <t>6a4af7f0ae633549bd0f03c4</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -25218,12 +25234,12 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -25235,12 +25251,12 @@
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K447" t="inlineStr">
@@ -25253,7 +25269,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cb</t>
+          <t>6a4af7f0ae633549bd0f03c8</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -25266,29 +25282,29 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
       <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K448" t="inlineStr">
@@ -25301,7 +25317,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ca</t>
+          <t>6a4af7f0ae633549bd0f03c6</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -25314,19 +25330,19 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
       <c r="G449" t="inlineStr"/>
       <c r="H449" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -25397,7 +25413,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c6</t>
+          <t>6a4af7f0ae633549bd0f03ca</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -25410,19 +25426,19 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr"/>
       <c r="H451" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -25445,7 +25461,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ce</t>
+          <t>6a4af7f0ae633549bd0f03cd</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -25458,12 +25474,12 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
@@ -25493,7 +25509,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d1</t>
+          <t>6a4af7f0ae633549bd0f03d0</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -25506,12 +25522,12 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
@@ -25589,7 +25605,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d3</t>
+          <t>6a4af7f0ae633549bd0f03d1</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -25602,12 +25618,12 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -25637,7 +25653,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cd</t>
+          <t>6a4af7f0ae633549bd0f03d3</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -25650,12 +25666,12 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
@@ -25685,7 +25701,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cf</t>
+          <t>6a4af7f0ae633549bd0f03ce</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -25698,12 +25714,12 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -25733,7 +25749,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d0</t>
+          <t>6a4af7f0ae633549bd0f03d5</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -25746,12 +25762,12 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -25781,7 +25797,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d4</t>
+          <t>6a4af7f0ae633549bd0f03d6</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -25794,12 +25810,12 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -25829,7 +25845,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d5</t>
+          <t>6a4af7f0ae633549bd0f03cf</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -25842,12 +25858,12 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
@@ -25877,7 +25893,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d6</t>
+          <t>6a4af7f0ae633549bd0f03d4</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -25890,12 +25906,12 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -25925,7 +25941,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03db</t>
+          <t>6a4af7f0ae633549bd0f03d8</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -25938,12 +25954,12 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
@@ -25973,7 +25989,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dd</t>
+          <t>6a4af7f0ae633549bd0f03dc</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -25986,12 +26002,12 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -26021,7 +26037,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03de</t>
+          <t>6a4af7f0ae633549bd0f03e1</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -26034,12 +26050,12 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -26069,7 +26085,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03df</t>
+          <t>6a4af7f0ae633549bd0f03db</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -26082,12 +26098,12 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
@@ -26117,7 +26133,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e1</t>
+          <t>6a4af7f0ae633549bd0f03dd</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -26130,12 +26146,12 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F466" t="inlineStr"/>
@@ -26165,7 +26181,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d8</t>
+          <t>6a4af7f0ae633549bd0f03de</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -26178,12 +26194,12 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -26213,7 +26229,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dc</t>
+          <t>6a4af7f0ae633549bd0f03d9</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -26226,12 +26242,12 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F468" t="inlineStr"/>
@@ -26357,7 +26373,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d9</t>
+          <t>6a4af7f0ae633549bd0f03df</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -26370,12 +26386,12 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -26405,7 +26421,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e8</t>
+          <t>6a4af7f0ae633549bd0f03e7</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -26418,12 +26434,12 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -26453,7 +26469,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e7</t>
+          <t>6a4af7f0ae633549bd0f03e8</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -26466,12 +26482,12 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -26693,7 +26709,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ec</t>
+          <t>6a4af7f0ae633549bd0f03e3</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -26706,12 +26722,12 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -26741,7 +26757,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e3</t>
+          <t>6a4af7f0ae633549bd0f03ec</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -26754,12 +26770,12 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
@@ -26885,7 +26901,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ef</t>
+          <t>6a4af7f0ae633549bd0f03f5</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -26898,12 +26914,12 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -26933,7 +26949,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f1</t>
+          <t>6a4af7f0ae633549bd0f03f0</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -26946,12 +26962,12 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -26981,7 +26997,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f2</t>
+          <t>6a4af7f0ae633549bd0f03f1</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -26994,12 +27010,12 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F484" t="inlineStr"/>
@@ -27029,7 +27045,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f5</t>
+          <t>6a4af7f0ae633549bd0f03f7</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -27042,12 +27058,12 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -27077,7 +27093,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f7</t>
+          <t>6a4af7f0ae633549bd0f03f6</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -27090,12 +27106,12 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
@@ -27125,7 +27141,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f4</t>
+          <t>6a4af7f0ae633549bd0f03ee</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -27138,12 +27154,12 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F487" t="inlineStr"/>
@@ -27173,7 +27189,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ee</t>
+          <t>6a4af7f0ae633549bd0f03f3</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -27186,12 +27202,12 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -27221,7 +27237,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f3</t>
+          <t>6a4af7f0ae633549bd0f03f4</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -27234,12 +27250,12 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -27269,7 +27285,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f6</t>
+          <t>6a4af7f0ae633549bd0f03f2</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -27282,12 +27298,12 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -27317,7 +27333,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f0</t>
+          <t>6a4af7f0ae633549bd0f03ef</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -27330,12 +27346,12 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -27365,7 +27381,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f9</t>
+          <t>6a4af7f1ae633549bd0f0402</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -27378,12 +27394,12 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
@@ -27413,7 +27429,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fc</t>
+          <t>6a4af7f0ae633549bd0f03fb</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -27426,12 +27442,12 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
@@ -27509,7 +27525,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fd</t>
+          <t>6a4af7f1ae633549bd0f0400</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -27522,12 +27538,12 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -27557,7 +27573,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fa</t>
+          <t>6a4af7f1ae633549bd0f03fe</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -27570,12 +27586,12 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -27605,7 +27621,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0401</t>
+          <t>6a4af7f1ae633549bd0f03fd</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -27618,12 +27634,12 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F497" t="inlineStr"/>
@@ -27653,7 +27669,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fb</t>
+          <t>6a4af7f0ae633549bd0f03f9</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -27666,12 +27682,12 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
@@ -27701,7 +27717,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0402</t>
+          <t>6a4af7f1ae633549bd0f03fc</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -27714,12 +27730,12 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -27749,7 +27765,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fe</t>
+          <t>6a4af7f1ae633549bd0f0401</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -27762,12 +27778,12 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -27797,7 +27813,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0400</t>
+          <t>6a4af7f0ae633549bd0f03fa</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -27810,12 +27826,12 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -27845,7 +27861,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0405</t>
+          <t>6a4af7f1ae633549bd0f040c</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -27858,12 +27874,12 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -27893,7 +27909,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040c</t>
+          <t>6a4af7f1ae633549bd0f0407</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -27906,12 +27922,12 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -27941,7 +27957,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0406</t>
+          <t>6a4af7f1ae633549bd0f040d</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -27954,12 +27970,12 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -27989,7 +28005,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040a</t>
+          <t>6a4af7f1ae633549bd0f0404</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -28002,12 +28018,12 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -28037,7 +28053,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040d</t>
+          <t>6a4af7f1ae633549bd0f0405</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -28050,12 +28066,12 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F506" t="inlineStr"/>
@@ -28085,7 +28101,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040b</t>
+          <t>6a4af7f1ae633549bd0f0408</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -28098,12 +28114,12 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F507" t="inlineStr"/>
@@ -28133,7 +28149,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0408</t>
+          <t>6a4af7f1ae633549bd0f0409</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -28146,12 +28162,12 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -28181,7 +28197,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0409</t>
+          <t>6a4af7f1ae633549bd0f040b</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -28194,12 +28210,12 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
@@ -28229,7 +28245,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0404</t>
+          <t>6a4af7f1ae633549bd0f0406</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -28242,12 +28258,12 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
@@ -28277,7 +28293,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0407</t>
+          <t>6a4af7f1ae633549bd0f040a</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -28290,12 +28306,12 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -28325,7 +28341,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0410</t>
+          <t>6a4af7f1ae633549bd0f0412</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -28338,12 +28354,12 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F512" t="inlineStr"/>
@@ -28373,7 +28389,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0418</t>
+          <t>6a4af7f1ae633549bd0f0411</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -28386,12 +28402,12 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F513" t="inlineStr"/>
@@ -28421,7 +28437,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040f</t>
+          <t>6a4af7f1ae633549bd0f0414</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -28434,12 +28450,12 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -28469,7 +28485,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0416</t>
+          <t>6a4af7f1ae633549bd0f040f</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -28482,12 +28498,12 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F515" t="inlineStr"/>
@@ -28517,7 +28533,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0412</t>
+          <t>6a4af7f1ae633549bd0f0410</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -28530,12 +28546,12 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F516" t="inlineStr"/>
@@ -28565,7 +28581,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0411</t>
+          <t>6a4af7f1ae633549bd0f0413</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -28578,12 +28594,12 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F517" t="inlineStr"/>
@@ -28613,7 +28629,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0414</t>
+          <t>6a4af7f1ae633549bd0f0415</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -28626,12 +28642,12 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
@@ -28661,7 +28677,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0413</t>
+          <t>6a4af7f1ae633549bd0f0417</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -28674,12 +28690,12 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -28709,7 +28725,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0417</t>
+          <t>6a4af7f1ae633549bd0f0418</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -28722,12 +28738,12 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F520" t="inlineStr"/>
@@ -28757,7 +28773,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0415</t>
+          <t>6a4af7f1ae633549bd0f0416</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -28770,12 +28786,12 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F521" t="inlineStr"/>
@@ -28805,7 +28821,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0422</t>
+          <t>6a4af7f1ae633549bd0f041e</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -28818,12 +28834,12 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F522" t="inlineStr"/>
@@ -28853,7 +28869,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041c</t>
+          <t>6a4af7f1ae633549bd0f0421</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -28866,12 +28882,12 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F523" t="inlineStr"/>
@@ -28901,7 +28917,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041b</t>
+          <t>6a4af7f1ae633549bd0f041f</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -28914,12 +28930,12 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F524" t="inlineStr"/>
@@ -28949,7 +28965,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041d</t>
+          <t>6a4af7f1ae633549bd0f041a</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -28962,12 +28978,12 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F525" t="inlineStr"/>
@@ -28997,7 +29013,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0420</t>
+          <t>6a4af7f1ae633549bd0f0422</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -29010,12 +29026,12 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F526" t="inlineStr"/>
@@ -29093,7 +29109,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0421</t>
+          <t>6a4af7f1ae633549bd0f041c</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -29106,12 +29122,12 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F528" t="inlineStr"/>
@@ -29141,7 +29157,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041e</t>
+          <t>6a4af7f1ae633549bd0f0420</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -29154,12 +29170,12 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -29189,7 +29205,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041f</t>
+          <t>6a4af7f1ae633549bd0f041d</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -29202,12 +29218,12 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -29237,7 +29253,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041a</t>
+          <t>6a4af7f1ae633549bd0f041b</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -29250,12 +29266,12 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -29285,7 +29301,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042b</t>
+          <t>6a4af7f1ae633549bd0f042a</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -29298,12 +29314,12 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -29333,7 +29349,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042c</t>
+          <t>6a4af7f1ae633549bd0f042e</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -29346,12 +29362,12 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
@@ -29381,7 +29397,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0428</t>
+          <t>6a4af7f1ae633549bd0f042c</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -29394,12 +29410,12 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
@@ -29429,7 +29445,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042e</t>
+          <t>6a4af7f1ae633549bd0f042b</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -29442,12 +29458,12 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -29477,7 +29493,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0425</t>
+          <t>6a4af7f1ae633549bd0f0428</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -29490,12 +29506,12 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -29525,7 +29541,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042a</t>
+          <t>6a4af7f1ae633549bd0f0426</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -29538,12 +29554,12 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -29573,7 +29589,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0427</t>
+          <t>6a4af7f1ae633549bd0f042d</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -29586,12 +29602,12 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -29621,7 +29637,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0426</t>
+          <t>6a4af7f1ae633549bd0f0425</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -29634,12 +29650,12 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F539" t="inlineStr"/>
@@ -29669,7 +29685,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042d</t>
+          <t>6a4af7f1ae633549bd0f0429</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -29682,12 +29698,12 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -29717,7 +29733,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0429</t>
+          <t>6a4af7f1ae633549bd0f0427</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -29730,12 +29746,12 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F541" t="inlineStr"/>
@@ -29861,7 +29877,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0435</t>
+          <t>6a4af7f1ae633549bd0f0434</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -29874,12 +29890,12 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
@@ -29909,7 +29925,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0437</t>
+          <t>6a4af7f1ae633549bd0f0433</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -29922,12 +29938,12 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -29957,7 +29973,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0439</t>
+          <t>6a4af7f1ae633549bd0f0431</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -29970,12 +29986,12 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -30005,7 +30021,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0438</t>
+          <t>6a4af7f1ae633549bd0f0436</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -30018,12 +30034,12 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
@@ -30053,7 +30069,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0431</t>
+          <t>6a4af7f1ae633549bd0f0438</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -30066,12 +30082,12 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -30101,7 +30117,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0433</t>
+          <t>6a4af7f1ae633549bd0f0437</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -30114,12 +30130,12 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -30149,7 +30165,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0436</t>
+          <t>6a4af7f1ae633549bd0f0439</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -30162,12 +30178,12 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
@@ -30197,7 +30213,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0434</t>
+          <t>6a4af7f1ae633549bd0f0435</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -30210,12 +30226,12 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F551" t="inlineStr"/>
@@ -30245,7 +30261,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043d</t>
+          <t>6a4af7f1ae633549bd0f043b</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -30258,12 +30274,12 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -30293,7 +30309,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0441</t>
+          <t>6a4af7f2ae633549bd0f0444</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -30306,12 +30322,12 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -30341,7 +30357,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043c</t>
+          <t>6a4af7f2ae633549bd0f043f</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -30354,12 +30370,12 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -30389,7 +30405,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0440</t>
+          <t>6a4af7f2ae633549bd0f0442</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -30402,12 +30418,12 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F555" t="inlineStr"/>
@@ -30437,7 +30453,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043e</t>
+          <t>6a4af7f2ae633549bd0f0443</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -30450,12 +30466,12 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -30485,7 +30501,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f043f</t>
+          <t>6a4af7f1ae633549bd0f043c</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -30498,12 +30514,12 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -30533,7 +30549,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0442</t>
+          <t>6a4af7f2ae633549bd0f0440</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -30546,12 +30562,12 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
@@ -30581,7 +30597,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043b</t>
+          <t>6a4af7f1ae633549bd0f043e</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -30594,12 +30610,12 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F559" t="inlineStr"/>
@@ -30629,7 +30645,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0443</t>
+          <t>6a4af7f2ae633549bd0f0441</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -30642,12 +30658,12 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -30677,7 +30693,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0444</t>
+          <t>6a4af7f1ae633549bd0f043d</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -30690,12 +30706,12 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -30725,7 +30741,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044e</t>
+          <t>6a4af7f2ae633549bd0f044f</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -30738,12 +30754,12 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -30773,7 +30789,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0447</t>
+          <t>6a4af7f2ae633549bd0f0449</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -30786,12 +30802,12 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F563" t="inlineStr"/>
@@ -30821,7 +30837,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0448</t>
+          <t>6a4af7f2ae633549bd0f044c</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -30834,12 +30850,12 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F564" t="inlineStr"/>
@@ -30869,7 +30885,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044c</t>
+          <t>6a4af7f2ae633549bd0f044d</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -30882,12 +30898,12 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F565" t="inlineStr"/>
@@ -30917,7 +30933,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0449</t>
+          <t>6a4af7f2ae633549bd0f0447</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -30930,12 +30946,12 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
@@ -30965,7 +30981,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044d</t>
+          <t>6a4af7f2ae633549bd0f0448</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -30978,12 +30994,12 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F567" t="inlineStr"/>
@@ -31013,7 +31029,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044f</t>
+          <t>6a4af7f2ae633549bd0f0446</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -31026,12 +31042,12 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F568" t="inlineStr"/>
@@ -31061,7 +31077,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0446</t>
+          <t>6a4af7f2ae633549bd0f044b</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -31074,12 +31090,12 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F569" t="inlineStr"/>
@@ -31157,7 +31173,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044b</t>
+          <t>6a4af7f2ae633549bd0f044e</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -31170,12 +31186,12 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -31205,7 +31221,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0451</t>
+          <t>6a4af7f2ae633549bd0f0459</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -31218,12 +31234,12 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F572" t="inlineStr"/>
@@ -31253,7 +31269,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045a</t>
+          <t>6a4af7f2ae633549bd0f0453</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -31266,12 +31282,12 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F573" t="inlineStr"/>
@@ -31301,7 +31317,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0453</t>
+          <t>6a4af7f2ae633549bd0f045a</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -31314,12 +31330,12 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F574" t="inlineStr"/>
@@ -31349,7 +31365,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0455</t>
+          <t>6a4af7f2ae633549bd0f0456</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -31362,12 +31378,12 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -31397,7 +31413,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0458</t>
+          <t>6a4af7f2ae633549bd0f0455</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -31410,12 +31426,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F576" t="inlineStr"/>
@@ -31445,7 +31461,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0456</t>
+          <t>6a4af7f2ae633549bd0f0457</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -31458,12 +31474,12 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -31493,7 +31509,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0457</t>
+          <t>6a4af7f2ae633549bd0f0452</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -31506,12 +31522,12 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -31541,7 +31557,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0454</t>
+          <t>6a4af7f2ae633549bd0f0458</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -31554,12 +31570,12 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F579" t="inlineStr"/>
@@ -31589,7 +31605,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0452</t>
+          <t>6a4af7f2ae633549bd0f0454</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -31602,12 +31618,12 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F580" t="inlineStr"/>
@@ -31637,7 +31653,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0459</t>
+          <t>6a4af7f2ae633549bd0f0451</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -31650,12 +31666,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -31685,7 +31701,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045d</t>
+          <t>6a4af7f2ae633549bd0f0465</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -31698,12 +31714,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F582" t="inlineStr"/>
@@ -31733,7 +31749,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045f</t>
+          <t>6a4af7f2ae633549bd0f045e</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -31746,12 +31762,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -31829,7 +31845,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045e</t>
+          <t>6a4af7f2ae633549bd0f045f</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -31842,12 +31858,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -31925,7 +31941,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0461</t>
+          <t>6a4af7f2ae633549bd0f0463</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -31938,12 +31954,12 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -31973,7 +31989,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0462</t>
+          <t>6a4af7f2ae633549bd0f0461</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -31986,12 +32002,12 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -32021,7 +32037,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0463</t>
+          <t>6a4af7f2ae633549bd0f0462</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -32034,12 +32050,12 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -32069,7 +32085,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0465</t>
+          <t>6a4af7f2ae633549bd0f0460</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -32082,12 +32098,12 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -32117,7 +32133,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0460</t>
+          <t>6a4af7f2ae633549bd0f045d</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -32130,12 +32146,12 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -32165,7 +32181,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046b</t>
+          <t>6a4af7f2ae633549bd0f0469</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -32178,12 +32194,12 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F592" t="inlineStr"/>
@@ -32213,7 +32229,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046e</t>
+          <t>6a4af7f2ae633549bd0f046a</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -32226,12 +32242,12 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F593" t="inlineStr"/>
@@ -32261,7 +32277,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046f</t>
+          <t>6a4af7f2ae633549bd0f046c</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -32274,12 +32290,12 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F594" t="inlineStr"/>
@@ -32309,7 +32325,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046c</t>
+          <t>6a4af7f2ae633549bd0f046b</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -32322,12 +32338,12 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F595" t="inlineStr"/>
@@ -32357,7 +32373,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046a</t>
+          <t>6a4af7f2ae633549bd0f046f</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -32370,12 +32386,12 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F596" t="inlineStr"/>
@@ -32405,7 +32421,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0467</t>
+          <t>6a4af7f2ae633549bd0f0468</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -32418,12 +32434,12 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F597" t="inlineStr"/>
@@ -32453,7 +32469,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046d</t>
+          <t>6a4af7f2ae633549bd0f0470</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -32466,12 +32482,12 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F598" t="inlineStr"/>
@@ -32501,7 +32517,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0469</t>
+          <t>6a4af7f2ae633549bd0f046e</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -32514,12 +32530,12 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -32549,7 +32565,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0470</t>
+          <t>6a4af7f2ae633549bd0f0467</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -32562,12 +32578,12 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F600" t="inlineStr"/>
@@ -32597,7 +32613,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0468</t>
+          <t>6a4af7f2ae633549bd0f046d</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -32610,12 +32626,12 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F601" t="inlineStr"/>
@@ -32645,7 +32661,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047b</t>
+          <t>6a4af7f2ae633549bd0f0473</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -32658,12 +32674,12 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F602" t="inlineStr"/>
@@ -32693,7 +32709,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0479</t>
+          <t>6a4af7f2ae633549bd0f0476</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -32706,12 +32722,12 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
@@ -32741,7 +32757,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047a</t>
+          <t>6a4af7f2ae633549bd0f0477</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -32754,12 +32770,12 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -32789,7 +32805,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0472</t>
+          <t>6a4af7f2ae633549bd0f047a</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -32802,12 +32818,12 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F605" t="inlineStr"/>
@@ -32837,7 +32853,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0473</t>
+          <t>6a4af7f2ae633549bd0f0479</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -32850,12 +32866,12 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
@@ -32885,7 +32901,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0476</t>
+          <t>6a4af7f2ae633549bd0f0475</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -32898,12 +32914,12 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -32933,7 +32949,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0477</t>
+          <t>6a4af7f2ae633549bd0f0474</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -32946,12 +32962,12 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
@@ -32981,7 +32997,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0475</t>
+          <t>6a4af7f2ae633549bd0f047b</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -32994,12 +33010,12 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F609" t="inlineStr"/>
@@ -33029,7 +33045,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0474</t>
+          <t>6a4af7f2ae633549bd0f0478</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -33042,12 +33058,12 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F610" t="inlineStr"/>
@@ -33077,7 +33093,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0478</t>
+          <t>6a4af7f2ae633549bd0f0472</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -33090,12 +33106,12 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -33269,7 +33285,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0480</t>
+          <t>6a4af7f3ae633549bd0f0485</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -33282,12 +33298,12 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -33365,7 +33381,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0485</t>
+          <t>6a4af7f2ae633549bd0f047e</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -33378,12 +33394,12 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F617" t="inlineStr"/>
@@ -33413,7 +33429,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047e</t>
+          <t>6a4af7f2ae633549bd0f047f</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -33426,12 +33442,12 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -33509,7 +33525,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047f</t>
+          <t>6a4af7f2ae633549bd0f0480</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -33522,12 +33538,12 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -33605,7 +33621,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048d</t>
+          <t>6a4af7f3ae633549bd0f048c</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -33618,12 +33634,12 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F622" t="inlineStr"/>
@@ -33653,7 +33669,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0489</t>
+          <t>6a4af7f3ae633549bd0f048a</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -33666,12 +33682,12 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F623" t="inlineStr"/>
@@ -33701,7 +33717,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0491</t>
+          <t>6a4af7f3ae633549bd0f048e</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -33714,12 +33730,12 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
@@ -33749,7 +33765,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048b</t>
+          <t>6a4af7f3ae633549bd0f0490</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -33762,12 +33778,12 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F625" t="inlineStr"/>
@@ -33797,7 +33813,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0490</t>
+          <t>6a4af7f3ae633549bd0f0488</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -33810,12 +33826,12 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F626" t="inlineStr"/>
@@ -33845,7 +33861,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048a</t>
+          <t>6a4af7f3ae633549bd0f048f</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -33858,12 +33874,12 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F627" t="inlineStr"/>
@@ -33893,7 +33909,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048c</t>
+          <t>6a4af7f3ae633549bd0f048d</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -33906,12 +33922,12 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F628" t="inlineStr"/>
@@ -33941,7 +33957,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0488</t>
+          <t>6a4af7f3ae633549bd0f0491</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -33954,12 +33970,12 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F629" t="inlineStr"/>
@@ -33989,7 +34005,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048e</t>
+          <t>6a4af7f3ae633549bd0f0489</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -34002,12 +34018,12 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F630" t="inlineStr"/>
@@ -34037,7 +34053,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048f</t>
+          <t>6a4af7f3ae633549bd0f048b</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -34050,12 +34066,12 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F631" t="inlineStr"/>
@@ -34085,7 +34101,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049a</t>
+          <t>6a4af7f3ae633549bd0f0498</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -34098,12 +34114,12 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F632" t="inlineStr"/>
@@ -34133,7 +34149,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049b</t>
+          <t>6a4af7f3ae633549bd0f049c</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -34146,12 +34162,12 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F633" t="inlineStr"/>
@@ -34181,7 +34197,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0493</t>
+          <t>6a4af7f3ae633549bd0f0495</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -34194,12 +34210,12 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F634" t="inlineStr"/>
@@ -34229,7 +34245,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0496</t>
+          <t>6a4af7f3ae633549bd0f0494</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -34242,12 +34258,12 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F635" t="inlineStr"/>
@@ -34277,7 +34293,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0499</t>
+          <t>6a4af7f3ae633549bd0f0497</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -34290,12 +34306,12 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F636" t="inlineStr"/>
@@ -34325,7 +34341,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0494</t>
+          <t>6a4af7f3ae633549bd0f0493</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -34338,12 +34354,12 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F637" t="inlineStr"/>
@@ -34373,7 +34389,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0497</t>
+          <t>6a4af7f3ae633549bd0f0496</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -34386,12 +34402,12 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F638" t="inlineStr"/>
@@ -34421,7 +34437,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049c</t>
+          <t>6a4af7f3ae633549bd0f0499</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -34434,12 +34450,12 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
@@ -34469,7 +34485,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0498</t>
+          <t>6a4af7f3ae633549bd0f049b</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -34482,12 +34498,12 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F640" t="inlineStr"/>
@@ -34517,7 +34533,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0495</t>
+          <t>6a4af7f3ae633549bd0f049a</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -34530,12 +34546,12 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F641" t="inlineStr"/>
@@ -34565,7 +34581,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a1</t>
+          <t>6a4af7f3ae633549bd0f049e</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -34578,12 +34594,12 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F642" t="inlineStr"/>
@@ -34613,7 +34629,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a3</t>
+          <t>6a4af7f3ae633549bd0f04a1</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -34626,12 +34642,12 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
@@ -34709,7 +34725,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049e</t>
+          <t>6a4af7f3ae633549bd0f04a6</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -34722,12 +34738,12 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F645" t="inlineStr"/>
@@ -34757,7 +34773,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049f</t>
+          <t>6a4af7f3ae633549bd0f04a4</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -34770,12 +34786,12 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F646" t="inlineStr"/>
@@ -34805,7 +34821,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a7</t>
+          <t>6a4af7f3ae633549bd0f049f</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -34818,12 +34834,12 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -34853,7 +34869,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a6</t>
+          <t>6a4af7f3ae633549bd0f04a0</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -34866,12 +34882,12 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -34901,7 +34917,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a4</t>
+          <t>6a4af7f3ae633549bd0f04a2</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -34914,12 +34930,12 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -34949,7 +34965,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a0</t>
+          <t>6a4af7f3ae633549bd0f04a3</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -34962,12 +34978,12 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F650" t="inlineStr"/>
@@ -34997,7 +35013,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a2</t>
+          <t>6a4af7f3ae633549bd0f04a7</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -35010,12 +35026,12 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F651" t="inlineStr"/>
@@ -35045,7 +35061,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b0</t>
+          <t>6a4af7f3ae633549bd0f04af</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -35058,12 +35074,12 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -35429,7 +35445,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04af</t>
+          <t>6a4af7f3ae633549bd0f04b0</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -35442,12 +35458,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F660" t="inlineStr"/>
@@ -35525,7 +35541,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b7</t>
+          <t>6a4af7f3ae633549bd0f04ba</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -35538,12 +35554,12 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F662" t="inlineStr"/>
@@ -35573,7 +35589,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b8</t>
+          <t>6a4af7f3ae633549bd0f04bd</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -35586,12 +35602,12 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F663" t="inlineStr"/>
@@ -35621,7 +35637,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bb</t>
+          <t>6a4af7f3ae633549bd0f04b9</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -35634,12 +35650,12 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F664" t="inlineStr"/>
@@ -35669,7 +35685,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b9</t>
+          <t>6a4af7f3ae633549bd0f04bb</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -35682,12 +35698,12 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F665" t="inlineStr"/>
@@ -35717,7 +35733,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ba</t>
+          <t>6a4af7f3ae633549bd0f04b7</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -35730,12 +35746,12 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F666" t="inlineStr"/>
@@ -35765,7 +35781,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bd</t>
+          <t>6a4af7f3ae633549bd0f04b8</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -35778,12 +35794,12 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F667" t="inlineStr"/>
@@ -35813,7 +35829,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b5</t>
+          <t>6a4af7f3ae633549bd0f04b6</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -35826,12 +35842,12 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F668" t="inlineStr"/>
@@ -35861,7 +35877,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bc</t>
+          <t>6a4af7f3ae633549bd0f04b4</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -35874,12 +35890,12 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
@@ -35909,7 +35925,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b6</t>
+          <t>6a4af7f3ae633549bd0f04bc</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -35922,12 +35938,12 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F670" t="inlineStr"/>
@@ -35957,7 +35973,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b4</t>
+          <t>6a4af7f3ae633549bd0f04b5</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -35970,12 +35986,12 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F671" t="inlineStr"/>
@@ -36005,7 +36021,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bf</t>
+          <t>6a4af7f3ae633549bd0f04c1</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -36018,12 +36034,12 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F672" t="inlineStr"/>
@@ -36053,7 +36069,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c2</t>
+          <t>6a4af7f3ae633549bd0f04c4</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -36066,12 +36082,12 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
@@ -36101,7 +36117,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c0</t>
+          <t>6a4af7f3ae633549bd0f04c6</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -36114,12 +36130,12 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F674" t="inlineStr"/>
@@ -36149,7 +36165,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c1</t>
+          <t>6a4af7f3ae633549bd0f04c7</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -36162,12 +36178,12 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F675" t="inlineStr"/>
@@ -36197,7 +36213,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c3</t>
+          <t>6a4af7f3ae633549bd0f04bf</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -36210,12 +36226,12 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -36245,7 +36261,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c5</t>
+          <t>6a4af7f3ae633549bd0f04c0</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -36258,12 +36274,12 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
@@ -36293,7 +36309,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c6</t>
+          <t>6a4af7f3ae633549bd0f04c2</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -36306,12 +36322,12 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F678" t="inlineStr"/>
@@ -36341,7 +36357,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c8</t>
+          <t>6a4af7f3ae633549bd0f04c5</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -36354,12 +36370,12 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F679" t="inlineStr"/>
@@ -36389,7 +36405,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c7</t>
+          <t>6a4af7f3ae633549bd0f04c8</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -36402,12 +36418,12 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F680" t="inlineStr"/>
@@ -36437,7 +36453,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c4</t>
+          <t>6a4af7f3ae633549bd0f04c3</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -36450,12 +36466,12 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
@@ -36485,7 +36501,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d1</t>
+          <t>6a4af7f4ae633549bd0f04cd</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -36498,12 +36514,12 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F682" t="inlineStr"/>
@@ -36533,7 +36549,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d2</t>
+          <t>6a4af7f4ae633549bd0f04cf</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -36546,12 +36562,12 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F683" t="inlineStr"/>
@@ -36581,7 +36597,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ca</t>
+          <t>6a4af7f4ae633549bd0f04d0</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -36594,12 +36610,12 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F684" t="inlineStr"/>
@@ -36629,7 +36645,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cb</t>
+          <t>6a4af7f4ae633549bd0f04d3</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -36642,12 +36658,12 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F685" t="inlineStr"/>
@@ -36725,7 +36741,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d3</t>
+          <t>6a4af7f4ae633549bd0f04cb</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -36738,12 +36754,12 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F687" t="inlineStr"/>
@@ -36773,7 +36789,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ce</t>
+          <t>6a4af7f4ae633549bd0f04ca</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -36786,12 +36802,12 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F688" t="inlineStr"/>
@@ -36821,7 +36837,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d0</t>
+          <t>6a4af7f4ae633549bd0f04ce</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -36834,12 +36850,12 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F689" t="inlineStr"/>
@@ -36869,7 +36885,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cd</t>
+          <t>6a4af7f4ae633549bd0f04d2</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -36882,12 +36898,12 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F690" t="inlineStr"/>
@@ -36917,7 +36933,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cf</t>
+          <t>6a4af7f4ae633549bd0f04d1</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -36930,12 +36946,12 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F691" t="inlineStr"/>
@@ -37109,7 +37125,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dd</t>
+          <t>6a4af7f4ae633549bd0f04d8</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -37122,12 +37138,12 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F695" t="inlineStr"/>
@@ -37157,7 +37173,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d8</t>
+          <t>6a4af7f4ae633549bd0f04d9</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -37170,12 +37186,12 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F696" t="inlineStr"/>
@@ -37205,7 +37221,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d9</t>
+          <t>6a4af7f4ae633549bd0f04db</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -37218,12 +37234,12 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F697" t="inlineStr"/>
@@ -37301,7 +37317,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04db</t>
+          <t>6a4af7f4ae633549bd0f04dd</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -37314,12 +37330,12 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F699" t="inlineStr"/>
@@ -37445,7 +37461,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e2</t>
+          <t>6a4af7f4ae633549bd0f04e1</t>
         </is>
       </c>
       <c r="B702" t="n">
@@ -37458,12 +37474,12 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F702" t="inlineStr"/>
@@ -37493,7 +37509,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e3</t>
+          <t>6a4af7f4ae633549bd0f04e6</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -37506,12 +37522,12 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F703" t="inlineStr"/>
@@ -37541,7 +37557,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e5</t>
+          <t>6a4af7f4ae633549bd0f04e7</t>
         </is>
       </c>
       <c r="B704" t="n">
@@ -37554,12 +37570,12 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F704" t="inlineStr"/>
@@ -37589,7 +37605,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e1</t>
+          <t>6a4af7f4ae633549bd0f04e5</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -37602,12 +37618,12 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
@@ -37637,7 +37653,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e6</t>
+          <t>6a4af7f4ae633549bd0f04e9</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -37650,12 +37666,12 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F706" t="inlineStr"/>
@@ -37685,7 +37701,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e7</t>
+          <t>6a4af7f4ae633549bd0f04e0</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -37698,12 +37714,12 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F707" t="inlineStr"/>
@@ -37733,7 +37749,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e8</t>
+          <t>6a4af7f4ae633549bd0f04e4</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -37746,12 +37762,12 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F708" t="inlineStr"/>
@@ -37781,7 +37797,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e9</t>
+          <t>6a4af7f4ae633549bd0f04e2</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -37794,12 +37810,12 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F709" t="inlineStr"/>
@@ -37829,7 +37845,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e0</t>
+          <t>6a4af7f4ae633549bd0f04e3</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -37842,12 +37858,12 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F710" t="inlineStr"/>
@@ -37877,7 +37893,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e4</t>
+          <t>6a4af7f4ae633549bd0f04e8</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -37890,12 +37906,12 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F711" t="inlineStr"/>
@@ -37925,7 +37941,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ec</t>
+          <t>6a4af7f4ae633549bd0f04f2</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -37938,12 +37954,12 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F712" t="inlineStr"/>
@@ -37973,7 +37989,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f0</t>
+          <t>6a4af7f4ae633549bd0f04f3</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -37986,12 +38002,12 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F713" t="inlineStr"/>
@@ -38021,7 +38037,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f4</t>
+          <t>6a4af7f4ae633549bd0f04f1</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -38034,12 +38050,12 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -38069,7 +38085,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ee</t>
+          <t>6a4af7f4ae633549bd0f04ef</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -38082,12 +38098,12 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F715" t="inlineStr"/>
@@ -38117,7 +38133,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04eb</t>
+          <t>6a4af7f4ae633549bd0f04ed</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -38130,12 +38146,12 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F716" t="inlineStr"/>
@@ -38165,7 +38181,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f2</t>
+          <t>6a4af7f4ae633549bd0f04ec</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -38178,12 +38194,12 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F717" t="inlineStr"/>
@@ -38213,7 +38229,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f3</t>
+          <t>6a4af7f4ae633549bd0f04ee</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -38226,12 +38242,12 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F718" t="inlineStr"/>
@@ -38261,7 +38277,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f1</t>
+          <t>6a4af7f4ae633549bd0f04f0</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -38274,12 +38290,12 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F719" t="inlineStr"/>
@@ -38309,7 +38325,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ef</t>
+          <t>6a4af7f4ae633549bd0f04f4</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -38322,12 +38338,12 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F720" t="inlineStr"/>
@@ -38357,7 +38373,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ed</t>
+          <t>6a4af7f4ae633549bd0f04eb</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -38370,12 +38386,12 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F721" t="inlineStr"/>
@@ -38405,7 +38421,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f7</t>
+          <t>6a4af7f4ae633549bd0f04f9</t>
         </is>
       </c>
       <c r="B722" t="n">
@@ -38418,12 +38434,12 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F722" t="inlineStr"/>
@@ -38453,7 +38469,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fa</t>
+          <t>6a4af7f4ae633549bd0f04fc</t>
         </is>
       </c>
       <c r="B723" t="n">
@@ -38466,12 +38482,12 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F723" t="inlineStr"/>
@@ -38501,7 +38517,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f6</t>
+          <t>6a4af7f4ae633549bd0f04fd</t>
         </is>
       </c>
       <c r="B724" t="n">
@@ -38514,12 +38530,12 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F724" t="inlineStr"/>
@@ -38549,7 +38565,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f8</t>
+          <t>6a4af7f4ae633549bd0f04fe</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -38562,12 +38578,12 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
@@ -38597,7 +38613,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fb</t>
+          <t>6a4af7f4ae633549bd0f04f6</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -38610,12 +38626,12 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F726" t="inlineStr"/>
@@ -38645,7 +38661,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fd</t>
+          <t>6a4af7f4ae633549bd0f04f8</t>
         </is>
       </c>
       <c r="B727" t="n">
@@ -38658,12 +38674,12 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F727" t="inlineStr"/>
@@ -38693,7 +38709,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fe</t>
+          <t>6a4af7f4ae633549bd0f04ff</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -38706,12 +38722,12 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F728" t="inlineStr"/>
@@ -38741,7 +38757,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f9</t>
+          <t>6a4af7f4ae633549bd0f04fa</t>
         </is>
       </c>
       <c r="B729" t="n">
@@ -38754,12 +38770,12 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F729" t="inlineStr"/>
@@ -38789,7 +38805,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fc</t>
+          <t>6a4af7f4ae633549bd0f04f7</t>
         </is>
       </c>
       <c r="B730" t="n">
@@ -38802,12 +38818,12 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F730" t="inlineStr"/>
@@ -38837,7 +38853,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ff</t>
+          <t>6a4af7f4ae633549bd0f04fb</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -38850,12 +38866,12 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F731" t="inlineStr"/>
@@ -38885,7 +38901,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0502</t>
+          <t>6a4af7f4ae633549bd0f0505</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -38898,12 +38914,12 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F732" t="inlineStr"/>
@@ -38981,7 +38997,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0503</t>
+          <t>6a4af7f4ae633549bd0f0502</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -38994,12 +39010,12 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
@@ -39029,7 +39045,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0507</t>
+          <t>6a4af7f4ae633549bd0f0501</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -39042,12 +39058,12 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -39077,7 +39093,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0501</t>
+          <t>6a4af7f4ae633549bd0f0507</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -39090,12 +39106,12 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
@@ -39125,7 +39141,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0504</t>
+          <t>6a4af7f4ae633549bd0f0503</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -39138,12 +39154,12 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F737" t="inlineStr"/>
@@ -39221,7 +39237,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0505</t>
+          <t>6a4af7f4ae633549bd0f050a</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -39234,12 +39250,12 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F739" t="inlineStr"/>
@@ -39269,7 +39285,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050a</t>
+          <t>6a4af7f4ae633549bd0f0504</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -39282,12 +39298,12 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -39461,7 +39477,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0511</t>
+          <t>6a4af7f4ae633549bd0f050d</t>
         </is>
       </c>
       <c r="B744" t="n">
@@ -39474,12 +39490,12 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F744" t="inlineStr"/>
@@ -39509,7 +39525,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0515</t>
+          <t>6a4af7f5ae633549bd0f0511</t>
         </is>
       </c>
       <c r="B745" t="n">
@@ -39522,12 +39538,12 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F745" t="inlineStr"/>
@@ -39557,7 +39573,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050d</t>
+          <t>6a4af7f5ae633549bd0f0515</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -39570,12 +39586,12 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F746" t="inlineStr"/>
@@ -39605,7 +39621,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0510</t>
+          <t>6a4af7f5ae633549bd0f0513</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -39618,12 +39634,12 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F747" t="inlineStr"/>
@@ -39653,7 +39669,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0512</t>
+          <t>6a4af7f5ae633549bd0f0514</t>
         </is>
       </c>
       <c r="B748" t="n">
@@ -39666,12 +39682,12 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F748" t="inlineStr"/>
@@ -39701,7 +39717,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0514</t>
+          <t>6a4af7f5ae633549bd0f0512</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -39714,12 +39730,12 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
@@ -39749,7 +39765,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0513</t>
+          <t>6a4af7f5ae633549bd0f0510</t>
         </is>
       </c>
       <c r="B750" t="n">
@@ -39762,12 +39778,12 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F750" t="inlineStr"/>
@@ -39845,7 +39861,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0517</t>
+          <t>6a4af7f5ae633549bd0f0520</t>
         </is>
       </c>
       <c r="B752" t="n">
@@ -39858,12 +39874,12 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F752" t="inlineStr"/>
@@ -39893,7 +39909,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051b</t>
+          <t>6a4af7f5ae633549bd0f0519</t>
         </is>
       </c>
       <c r="B753" t="n">
@@ -39906,12 +39922,12 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F753" t="inlineStr"/>
@@ -39941,7 +39957,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051d</t>
+          <t>6a4af7f5ae633549bd0f0517</t>
         </is>
       </c>
       <c r="B754" t="n">
@@ -39954,12 +39970,12 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F754" t="inlineStr"/>
@@ -39989,7 +40005,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051c</t>
+          <t>6a4af7f5ae633549bd0f051e</t>
         </is>
       </c>
       <c r="B755" t="n">
@@ -40002,12 +40018,12 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F755" t="inlineStr"/>
@@ -40037,7 +40053,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051e</t>
+          <t>6a4af7f5ae633549bd0f0518</t>
         </is>
       </c>
       <c r="B756" t="n">
@@ -40050,12 +40066,12 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F756" t="inlineStr"/>
@@ -40085,7 +40101,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051f</t>
+          <t>6a4af7f5ae633549bd0f051a</t>
         </is>
       </c>
       <c r="B757" t="n">
@@ -40098,12 +40114,12 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F757" t="inlineStr"/>
@@ -40133,7 +40149,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0519</t>
+          <t>6a4af7f5ae633549bd0f051c</t>
         </is>
       </c>
       <c r="B758" t="n">
@@ -40146,12 +40162,12 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F758" t="inlineStr"/>
@@ -40181,7 +40197,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0520</t>
+          <t>6a4af7f5ae633549bd0f051b</t>
         </is>
       </c>
       <c r="B759" t="n">
@@ -40194,12 +40210,12 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F759" t="inlineStr"/>
@@ -40229,7 +40245,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0518</t>
+          <t>6a4af7f5ae633549bd0f051d</t>
         </is>
       </c>
       <c r="B760" t="n">
@@ -40242,12 +40258,12 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F760" t="inlineStr"/>
@@ -40277,7 +40293,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051a</t>
+          <t>6a4af7f5ae633549bd0f051f</t>
         </is>
       </c>
       <c r="B761" t="n">
@@ -40290,12 +40306,12 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>

--- a/datos/maestros/md_partidos.xlsx
+++ b/datos/maestros/md_partidos.xlsx
@@ -21773,7 +21773,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b8</t>
+          <t>6a4af7f0ae633549bd0f03b7</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -21786,29 +21786,29 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="inlineStr"/>
       <c r="H382" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
@@ -21821,7 +21821,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bf</t>
+          <t>6a4af7f0ae633549bd0f03ba</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -21834,19 +21834,19 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -21869,7 +21869,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b9</t>
+          <t>6a4af7f0ae633549bd0f03bb</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -21882,12 +21882,12 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
@@ -21899,12 +21899,12 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
@@ -21917,7 +21917,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b7</t>
+          <t>6a4af7f0ae633549bd0f03bd</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -21930,29 +21930,29 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
@@ -21965,7 +21965,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bd</t>
+          <t>6a4af7f0ae633549bd0f03bf</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -21978,29 +21978,29 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
       <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
@@ -22013,7 +22013,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ba</t>
+          <t>6a4af7f0ae633549bd0f03b9</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -22026,29 +22026,29 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F387" t="inlineStr"/>
       <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
@@ -22061,7 +22061,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03be</t>
+          <t>6a4af7f0ae633549bd0f03c0</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -22074,29 +22074,33 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
-        </is>
-      </c>
-      <c r="F388" t="inlineStr"/>
-      <c r="G388" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000d9</t>
+        </is>
+      </c>
+      <c r="F388" t="n">
+        <v>0</v>
+      </c>
+      <c r="G388" t="n">
+        <v>0</v>
+      </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
@@ -22104,12 +22108,16 @@
           <t>closed</t>
         </is>
       </c>
-      <c r="L388" t="inlineStr"/>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bb</t>
+          <t>6a4af7f0ae633549bd0f03b8</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -22122,12 +22130,12 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
@@ -22157,7 +22165,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bc</t>
+          <t>6a4af7f0ae633549bd0f03be</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -22170,19 +22178,19 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -22205,7 +22213,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c0</t>
+          <t>6a4af7f0ae633549bd0f03bc</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -22218,33 +22226,29 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
-        </is>
-      </c>
-      <c r="F391" t="n">
-        <v>0</v>
-      </c>
-      <c r="G391" t="n">
-        <v>0</v>
-      </c>
+          <t>504e581e4d8bec9a670000c6</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
@@ -22252,16 +22256,12 @@
           <t>closed</t>
         </is>
       </c>
-      <c r="L391" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="L391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0385</t>
+          <t>6a4af7efae633549bd0f0381</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -22274,33 +22274,33 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F392" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G392" t="n">
         <v>0</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
@@ -22317,7 +22317,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0386</t>
+          <t>6a4af7efae633549bd0f0387</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -22330,33 +22330,33 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F393" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G393" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
@@ -22373,7 +22373,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0381</t>
+          <t>6a4af7efae633549bd0f0385</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -22386,33 +22386,33 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G394" t="n">
         <v>0</v>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
           <t>19:00</t>
-        </is>
-      </c>
-      <c r="J394" t="inlineStr">
-        <is>
-          <t>21:00</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
@@ -22429,7 +22429,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0380</t>
+          <t>6a4af7efae633549bd0f0383</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -22442,33 +22442,33 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G395" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
@@ -22541,7 +22541,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0383</t>
+          <t>6a4af7efae633549bd0f0389</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -22554,33 +22554,33 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F397" t="n">
+        <v>0</v>
+      </c>
+      <c r="G397" t="n">
         <v>1</v>
       </c>
-      <c r="G397" t="n">
-        <v>2</v>
-      </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
@@ -22597,7 +22597,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0388</t>
+          <t>6a4af7efae633549bd0f0380</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -22610,19 +22610,19 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G398" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
@@ -22631,12 +22631,12 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
           <t>19:30</t>
-        </is>
-      </c>
-      <c r="J398" t="inlineStr">
-        <is>
-          <t>21:30</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
@@ -22653,7 +22653,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0387</t>
+          <t>6a4af7efae633549bd0f0388</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -22666,33 +22666,33 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F399" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G399" t="n">
         <v>1</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
@@ -22709,7 +22709,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0389</t>
+          <t>6a4af7efae633549bd0f0386</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -22722,33 +22722,33 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F400" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G400" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
@@ -22821,7 +22821,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0392</t>
+          <t>6a4af7efae633549bd0f038c</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -22834,33 +22834,33 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F402" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G402" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
@@ -22877,7 +22877,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038b</t>
+          <t>6a4af7efae633549bd0f038e</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -22890,33 +22890,33 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F403" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G403" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
@@ -22933,7 +22933,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038c</t>
+          <t>6a4af7efae633549bd0f038f</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -22946,33 +22946,33 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F404" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G404" t="n">
         <v>2</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
@@ -22989,7 +22989,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038d</t>
+          <t>6a4af7efae633549bd0f0392</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -23002,33 +23002,33 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F405" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G405" t="n">
         <v>0</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
@@ -23045,7 +23045,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038e</t>
+          <t>6a4af7efae633549bd0f0393</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -23058,33 +23058,33 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F406" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G406" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
@@ -23101,7 +23101,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0390</t>
+          <t>6a4af7efae633549bd0f0394</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -23114,23 +23114,23 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F407" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G407" t="n">
         <v>0</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -23157,7 +23157,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0391</t>
+          <t>6a4af7efae633549bd0f038d</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -23170,33 +23170,33 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F408" t="n">
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
@@ -23213,7 +23213,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0394</t>
+          <t>6a4af7efae633549bd0f0390</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -23226,23 +23226,23 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G409" t="n">
         <v>0</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -23269,7 +23269,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0393</t>
+          <t>6a4af7efae633549bd0f0391</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -23282,12 +23282,12 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -23298,17 +23298,17 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
@@ -23325,7 +23325,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038f</t>
+          <t>6a4af7efae633549bd0f038b</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -23338,19 +23338,19 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F411" t="n">
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
@@ -23359,12 +23359,12 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
@@ -23381,7 +23381,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039b</t>
+          <t>6a4af7efae633549bd0f0397</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -23394,19 +23394,19 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G412" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
@@ -23415,12 +23415,12 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
@@ -23437,7 +23437,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039f</t>
+          <t>6a4af7efae633549bd0f0398</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -23450,23 +23450,23 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G413" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -23493,7 +23493,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0399</t>
+          <t>6a4af7efae633549bd0f039a</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -23506,33 +23506,33 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G414" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
@@ -23549,7 +23549,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039a</t>
+          <t>6a4af7efae633549bd0f039b</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -23562,33 +23562,33 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G415" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
@@ -23605,7 +23605,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039d</t>
+          <t>6a4af7efae633549bd0f039c</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -23618,33 +23618,33 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G416" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
@@ -23661,7 +23661,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0398</t>
+          <t>6a4af7efae633549bd0f039d</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -23674,20 +23674,20 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F417" t="n">
+        <v>4</v>
+      </c>
+      <c r="G417" t="n">
         <v>0</v>
       </c>
-      <c r="G417" t="n">
-        <v>2</v>
-      </c>
       <c r="H417" t="inlineStr">
         <is>
           <t>2026-08-30</t>
@@ -23695,12 +23695,12 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
@@ -23717,7 +23717,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0397</t>
+          <t>6a4af7efae633549bd0f0396</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -23730,23 +23730,23 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F418" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G418" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -23773,7 +23773,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039c</t>
+          <t>6a4af7efae633549bd0f0399</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -23786,33 +23786,33 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F419" t="n">
         <v>3</v>
       </c>
       <c r="G419" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
@@ -23829,7 +23829,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0396</t>
+          <t>6a4af7efae633549bd0f039e</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -23842,33 +23842,33 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F420" t="n">
+        <v>2</v>
+      </c>
+      <c r="G420" t="n">
         <v>1</v>
       </c>
-      <c r="G420" t="n">
-        <v>0</v>
-      </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
@@ -23885,7 +23885,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039e</t>
+          <t>6a4af7efae633549bd0f039f</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -23898,19 +23898,19 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F421" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G421" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H421" t="inlineStr">
         <is>
@@ -23919,12 +23919,12 @@
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
@@ -23941,7 +23941,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a2</t>
+          <t>6a4af7efae633549bd0f03a4</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -23954,33 +23954,33 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F422" t="n">
+        <v>2</v>
+      </c>
+      <c r="G422" t="n">
         <v>3</v>
       </c>
-      <c r="G422" t="n">
-        <v>0</v>
-      </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
@@ -23997,7 +23997,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a1</t>
+          <t>6a4af7efae633549bd0f03a6</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -24010,33 +24010,33 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F423" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G423" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
@@ -24053,7 +24053,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a3</t>
+          <t>6a4af7efae633549bd0f03a5</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -24066,23 +24066,23 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F424" t="n">
         <v>1</v>
       </c>
       <c r="G424" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -24109,7 +24109,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a4</t>
+          <t>6a4af7efae633549bd0f03aa</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -24122,12 +24122,12 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -24138,17 +24138,17 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K425" t="inlineStr">
@@ -24165,7 +24165,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a6</t>
+          <t>6a4af7efae633549bd0f03a7</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -24178,33 +24178,33 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F426" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G426" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
@@ -24221,7 +24221,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a9</t>
+          <t>6a4af7efae633549bd0f03a8</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -24234,33 +24234,33 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G427" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
@@ -24277,7 +24277,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03aa</t>
+          <t>6a4af7efae633549bd0f03a9</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -24290,33 +24290,33 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G428" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
@@ -24333,7 +24333,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a5</t>
+          <t>6a4af7efae633549bd0f03a2</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -24346,33 +24346,33 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G429" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
@@ -24389,7 +24389,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a7</t>
+          <t>6a4af7efae633549bd0f03a1</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -24402,19 +24402,19 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G430" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H430" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a8</t>
+          <t>6a4af7efae633549bd0f03a3</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -24458,33 +24458,33 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G431" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
@@ -24549,7 +24549,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03af</t>
+          <t>6a4af7efae633549bd0f03b0</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -24562,19 +24562,19 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr"/>
       <c r="H433" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -24597,7 +24597,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b1</t>
+          <t>6a4af7efae633549bd0f03ad</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -24610,19 +24610,19 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr"/>
       <c r="H434" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -24645,7 +24645,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b4</t>
+          <t>6a4af7efae633549bd0f03b2</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -24658,19 +24658,19 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F435" t="inlineStr"/>
       <c r="G435" t="inlineStr"/>
       <c r="H435" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -24693,7 +24693,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b0</t>
+          <t>6a4af7efae633549bd0f03b4</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -24706,29 +24706,29 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
       <c r="G436" t="inlineStr"/>
       <c r="H436" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
@@ -24741,7 +24741,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ad</t>
+          <t>6a4af7efae633549bd0f03b1</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -24754,19 +24754,19 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr"/>
       <c r="H437" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -24789,7 +24789,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b2</t>
+          <t>6a4af7efae633549bd0f03af</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -24802,29 +24802,29 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr"/>
       <c r="H438" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K438" t="inlineStr">
@@ -24837,7 +24837,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b5</t>
+          <t>6a4af7efae633549bd0f03ac</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -24850,29 +24850,29 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr"/>
       <c r="H439" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
@@ -24885,7 +24885,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ae</t>
+          <t>6a4af7f0ae633549bd0f03b5</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -24898,29 +24898,29 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
       <c r="G440" t="inlineStr"/>
       <c r="H440" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
@@ -24933,7 +24933,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ac</t>
+          <t>6a4af7efae633549bd0f03ae</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -24946,19 +24946,19 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
       <c r="G441" t="inlineStr"/>
       <c r="H441" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -24981,7 +24981,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c3</t>
+          <t>6a4af7f0ae633549bd0f03cb</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -25011,12 +25011,12 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
@@ -25029,7 +25029,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c5</t>
+          <t>6a4af7f0ae633549bd0f03c8</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -25042,29 +25042,29 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
       <c r="G443" t="inlineStr"/>
       <c r="H443" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K443" t="inlineStr">
@@ -25077,7 +25077,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c9</t>
+          <t>6a4af7f0ae633549bd0f03c4</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -25090,12 +25090,12 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
@@ -25107,12 +25107,12 @@
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K444" t="inlineStr">
@@ -25125,7 +25125,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cb</t>
+          <t>6a4af7f0ae633549bd0f03c2</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -25138,29 +25138,29 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
       <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
@@ -25173,7 +25173,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c2</t>
+          <t>6a4af7f0ae633549bd0f03c3</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -25186,19 +25186,19 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
       <c r="G446" t="inlineStr"/>
       <c r="H446" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -25221,7 +25221,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c4</t>
+          <t>6a4af7f0ae633549bd0f03c5</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -25234,19 +25234,19 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
       <c r="G447" t="inlineStr"/>
       <c r="H447" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -25269,7 +25269,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c8</t>
+          <t>6a4af7f0ae633549bd0f03c9</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
@@ -25299,12 +25299,12 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K448" t="inlineStr">
@@ -25461,7 +25461,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cd</t>
+          <t>6a4af7f0ae633549bd0f03d1</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -25474,12 +25474,12 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
@@ -25509,7 +25509,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d0</t>
+          <t>6a4af7f0ae633549bd0f03d2</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -25522,12 +25522,12 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
@@ -25557,7 +25557,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d2</t>
+          <t>6a4af7f0ae633549bd0f03d3</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -25570,12 +25570,12 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F454" t="inlineStr"/>
@@ -25605,7 +25605,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d1</t>
+          <t>6a4af7f0ae633549bd0f03cd</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -25618,12 +25618,12 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -25653,7 +25653,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d3</t>
+          <t>6a4af7f0ae633549bd0f03cf</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -25666,12 +25666,12 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
@@ -25701,7 +25701,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ce</t>
+          <t>6a4af7f0ae633549bd0f03d0</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -25714,12 +25714,12 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -25749,7 +25749,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d5</t>
+          <t>6a4af7f0ae633549bd0f03d4</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -25762,12 +25762,12 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -25797,7 +25797,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d6</t>
+          <t>6a4af7f0ae633549bd0f03d5</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -25810,12 +25810,12 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -25845,7 +25845,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cf</t>
+          <t>6a4af7f0ae633549bd0f03d6</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -25858,12 +25858,12 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
@@ -25893,7 +25893,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d4</t>
+          <t>6a4af7f0ae633549bd0f03ce</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -25906,12 +25906,12 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -25941,7 +25941,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d8</t>
+          <t>6a4af7f0ae633549bd0f03d9</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -25954,12 +25954,12 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
@@ -25989,7 +25989,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dc</t>
+          <t>6a4af7f0ae633549bd0f03dd</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -26002,12 +26002,12 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -26037,7 +26037,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e1</t>
+          <t>6a4af7f0ae633549bd0f03da</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -26050,12 +26050,12 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -26085,7 +26085,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03db</t>
+          <t>6a4af7f0ae633549bd0f03de</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -26098,12 +26098,12 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
@@ -26133,7 +26133,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dd</t>
+          <t>6a4af7f0ae633549bd0f03e0</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -26146,12 +26146,12 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F466" t="inlineStr"/>
@@ -26181,7 +26181,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03de</t>
+          <t>6a4af7f0ae633549bd0f03dc</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -26229,7 +26229,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d9</t>
+          <t>6a4af7f0ae633549bd0f03e1</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -26242,12 +26242,12 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F468" t="inlineStr"/>
@@ -26277,7 +26277,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03da</t>
+          <t>6a4af7f0ae633549bd0f03d8</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -26290,12 +26290,12 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F469" t="inlineStr"/>
@@ -26325,7 +26325,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e0</t>
+          <t>6a4af7f0ae633549bd0f03df</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -26338,12 +26338,12 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
@@ -26373,7 +26373,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03df</t>
+          <t>6a4af7f0ae633549bd0f03db</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -26386,12 +26386,12 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -26421,7 +26421,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e7</t>
+          <t>6a4af7f0ae633549bd0f03e3</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -26434,12 +26434,12 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -26469,7 +26469,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e8</t>
+          <t>6a4af7f0ae633549bd0f03e4</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -26482,12 +26482,12 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -26517,7 +26517,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03eb</t>
+          <t>6a4af7f0ae633549bd0f03e6</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -26530,12 +26530,12 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -26547,12 +26547,12 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K474" t="inlineStr">
@@ -26565,7 +26565,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e4</t>
+          <t>6a4af7f0ae633549bd0f03e8</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -26578,12 +26578,12 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -26613,7 +26613,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e6</t>
+          <t>6a4af7f0ae633549bd0f03e7</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -26626,12 +26626,12 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
@@ -26643,12 +26643,12 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K476" t="inlineStr">
@@ -26661,7 +26661,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e9</t>
+          <t>6a4af7f0ae633549bd0f03eb</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -26674,12 +26674,12 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
@@ -26709,7 +26709,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e3</t>
+          <t>6a4af7f0ae633549bd0f03e5</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -26722,12 +26722,12 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -26757,7 +26757,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ec</t>
+          <t>6a4af7f0ae633549bd0f03ea</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -26770,12 +26770,12 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
@@ -26805,7 +26805,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e5</t>
+          <t>6a4af7f0ae633549bd0f03e9</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -26818,12 +26818,12 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -26853,7 +26853,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ea</t>
+          <t>6a4af7f0ae633549bd0f03ec</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -26866,12 +26866,12 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
@@ -26901,7 +26901,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f5</t>
+          <t>6a4af7f0ae633549bd0f03f7</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -26914,12 +26914,12 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -26949,7 +26949,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f0</t>
+          <t>6a4af7f0ae633549bd0f03f6</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -26962,12 +26962,12 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -27045,7 +27045,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f7</t>
+          <t>6a4af7f0ae633549bd0f03f0</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -27058,12 +27058,12 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -27093,7 +27093,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f6</t>
+          <t>6a4af7f0ae633549bd0f03f2</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -27106,12 +27106,12 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
@@ -27141,7 +27141,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ee</t>
+          <t>6a4af7f0ae633549bd0f03f5</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -27154,12 +27154,12 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F487" t="inlineStr"/>
@@ -27189,7 +27189,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f3</t>
+          <t>6a4af7f0ae633549bd0f03ef</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -27202,12 +27202,12 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -27237,7 +27237,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f4</t>
+          <t>6a4af7f0ae633549bd0f03ee</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -27250,12 +27250,12 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -27285,7 +27285,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f2</t>
+          <t>6a4af7f0ae633549bd0f03f3</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -27298,12 +27298,12 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -27333,7 +27333,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ef</t>
+          <t>6a4af7f0ae633549bd0f03f4</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -27861,7 +27861,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040c</t>
+          <t>6a4af7f1ae633549bd0f0409</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -27874,12 +27874,12 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -27909,7 +27909,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0407</t>
+          <t>6a4af7f1ae633549bd0f0404</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -27922,12 +27922,12 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -27957,7 +27957,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040d</t>
+          <t>6a4af7f1ae633549bd0f040b</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -27970,12 +27970,12 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -28005,7 +28005,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0404</t>
+          <t>6a4af7f1ae633549bd0f0407</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -28018,12 +28018,12 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -28101,7 +28101,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0408</t>
+          <t>6a4af7f1ae633549bd0f0406</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -28114,12 +28114,12 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F507" t="inlineStr"/>
@@ -28149,7 +28149,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0409</t>
+          <t>6a4af7f1ae633549bd0f040a</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -28162,12 +28162,12 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -28197,7 +28197,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040b</t>
+          <t>6a4af7f1ae633549bd0f040c</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -28210,12 +28210,12 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
@@ -28245,7 +28245,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0406</t>
+          <t>6a4af7f1ae633549bd0f040d</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -28258,12 +28258,12 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
@@ -28293,7 +28293,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040a</t>
+          <t>6a4af7f1ae633549bd0f0408</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -28306,12 +28306,12 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -28341,7 +28341,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0412</t>
+          <t>6a4af7f1ae633549bd0f0410</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -28354,12 +28354,12 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F512" t="inlineStr"/>
@@ -28389,7 +28389,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0411</t>
+          <t>6a4af7f1ae633549bd0f0415</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -28402,12 +28402,12 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F513" t="inlineStr"/>
@@ -28437,7 +28437,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0414</t>
+          <t>6a4af7f1ae633549bd0f0413</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -28450,12 +28450,12 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -28485,7 +28485,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040f</t>
+          <t>6a4af7f1ae633549bd0f0414</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -28498,12 +28498,12 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F515" t="inlineStr"/>
@@ -28533,7 +28533,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0410</t>
+          <t>6a4af7f1ae633549bd0f0411</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -28546,12 +28546,12 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F516" t="inlineStr"/>
@@ -28581,7 +28581,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0413</t>
+          <t>6a4af7f1ae633549bd0f0417</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -28594,12 +28594,12 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F517" t="inlineStr"/>
@@ -28629,7 +28629,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0415</t>
+          <t>6a4af7f1ae633549bd0f0418</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -28642,12 +28642,12 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
@@ -28677,7 +28677,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0417</t>
+          <t>6a4af7f1ae633549bd0f0412</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -28690,12 +28690,12 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -28725,7 +28725,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0418</t>
+          <t>6a4af7f1ae633549bd0f0416</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -28738,12 +28738,12 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F520" t="inlineStr"/>
@@ -28773,7 +28773,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0416</t>
+          <t>6a4af7f1ae633549bd0f040f</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -28786,12 +28786,12 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F521" t="inlineStr"/>
@@ -28917,7 +28917,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041f</t>
+          <t>6a4af7f1ae633549bd0f0423</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -28930,12 +28930,12 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F524" t="inlineStr"/>
@@ -28965,7 +28965,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041a</t>
+          <t>6a4af7f1ae633549bd0f041f</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -28978,12 +28978,12 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F525" t="inlineStr"/>
@@ -29013,7 +29013,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0422</t>
+          <t>6a4af7f1ae633549bd0f041a</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -29026,12 +29026,12 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F526" t="inlineStr"/>
@@ -29061,7 +29061,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0423</t>
+          <t>6a4af7f1ae633549bd0f041c</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F527" t="inlineStr"/>
@@ -29109,7 +29109,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041c</t>
+          <t>6a4af7f1ae633549bd0f0420</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -29122,12 +29122,12 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F528" t="inlineStr"/>
@@ -29157,7 +29157,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0420</t>
+          <t>6a4af7f1ae633549bd0f041d</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -29170,12 +29170,12 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -29205,7 +29205,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041d</t>
+          <t>6a4af7f1ae633549bd0f041b</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -29218,12 +29218,12 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -29253,7 +29253,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041b</t>
+          <t>6a4af7f1ae633549bd0f0422</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -29266,12 +29266,12 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -29637,7 +29637,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0425</t>
+          <t>6a4af7f1ae633549bd0f0429</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -29650,12 +29650,12 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F539" t="inlineStr"/>
@@ -29685,7 +29685,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0429</t>
+          <t>6a4af7f1ae633549bd0f0425</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -29698,12 +29698,12 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -29781,7 +29781,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0430</t>
+          <t>6a4af7f1ae633549bd0f0437</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -29794,12 +29794,12 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F542" t="inlineStr"/>
@@ -29829,7 +29829,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0432</t>
+          <t>6a4af7f1ae633549bd0f0439</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -29842,12 +29842,12 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F543" t="inlineStr"/>
@@ -29877,7 +29877,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0434</t>
+          <t>6a4af7f1ae633549bd0f0432</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -29890,12 +29890,12 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
@@ -29925,7 +29925,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0433</t>
+          <t>6a4af7f1ae633549bd0f0435</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -29938,12 +29938,12 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -29973,7 +29973,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0431</t>
+          <t>6a4af7f1ae633549bd0f0438</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -29986,12 +29986,12 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -30021,7 +30021,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0436</t>
+          <t>6a4af7f1ae633549bd0f0431</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -30034,12 +30034,12 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
@@ -30069,7 +30069,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0438</t>
+          <t>6a4af7f1ae633549bd0f0433</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -30082,12 +30082,12 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -30117,7 +30117,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0437</t>
+          <t>6a4af7f1ae633549bd0f0436</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -30130,12 +30130,12 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -30165,7 +30165,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0439</t>
+          <t>6a4af7f1ae633549bd0f0430</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -30178,12 +30178,12 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
@@ -30213,7 +30213,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0435</t>
+          <t>6a4af7f1ae633549bd0f0434</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -30226,12 +30226,12 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F551" t="inlineStr"/>
@@ -30261,7 +30261,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043b</t>
+          <t>6a4af7f2ae633549bd0f0444</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -30274,12 +30274,12 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -30309,7 +30309,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0444</t>
+          <t>6a4af7f2ae633549bd0f043f</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -30322,12 +30322,12 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -30357,7 +30357,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f043f</t>
+          <t>6a4af7f2ae633549bd0f0442</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -30370,12 +30370,12 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -30405,7 +30405,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0442</t>
+          <t>6a4af7f1ae633549bd0f043b</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -30418,12 +30418,12 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F555" t="inlineStr"/>
@@ -30453,7 +30453,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0443</t>
+          <t>6a4af7f1ae633549bd0f043c</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -30466,12 +30466,12 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -30501,7 +30501,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043c</t>
+          <t>6a4af7f2ae633549bd0f0440</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -30514,12 +30514,12 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -30549,7 +30549,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0440</t>
+          <t>6a4af7f1ae633549bd0f043e</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -30562,12 +30562,12 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
@@ -30597,7 +30597,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043e</t>
+          <t>6a4af7f2ae633549bd0f0443</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -30610,12 +30610,12 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F559" t="inlineStr"/>
@@ -30645,7 +30645,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0441</t>
+          <t>6a4af7f1ae633549bd0f043d</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -30658,12 +30658,12 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -30693,7 +30693,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043d</t>
+          <t>6a4af7f2ae633549bd0f0441</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -30706,12 +30706,12 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -30741,7 +30741,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044f</t>
+          <t>6a4af7f2ae633549bd0f0447</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -30754,12 +30754,12 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -30789,7 +30789,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0449</t>
+          <t>6a4af7f2ae633549bd0f0446</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -30802,12 +30802,12 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F563" t="inlineStr"/>
@@ -30837,7 +30837,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044c</t>
+          <t>6a4af7f2ae633549bd0f0448</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -30850,12 +30850,12 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F564" t="inlineStr"/>
@@ -30885,7 +30885,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044d</t>
+          <t>6a4af7f2ae633549bd0f044b</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -30898,12 +30898,12 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F565" t="inlineStr"/>
@@ -30933,7 +30933,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0447</t>
+          <t>6a4af7f2ae633549bd0f044a</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -30946,12 +30946,12 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
@@ -30981,7 +30981,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0448</t>
+          <t>6a4af7f2ae633549bd0f044e</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -30994,12 +30994,12 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F567" t="inlineStr"/>
@@ -31029,7 +31029,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0446</t>
+          <t>6a4af7f2ae633549bd0f044f</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -31042,12 +31042,12 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F568" t="inlineStr"/>
@@ -31077,7 +31077,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044b</t>
+          <t>6a4af7f2ae633549bd0f0449</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -31090,12 +31090,12 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F569" t="inlineStr"/>
@@ -31125,7 +31125,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044a</t>
+          <t>6a4af7f2ae633549bd0f044c</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -31138,12 +31138,12 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F570" t="inlineStr"/>
@@ -31173,7 +31173,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044e</t>
+          <t>6a4af7f2ae633549bd0f044d</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -31186,12 +31186,12 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -31221,7 +31221,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0459</t>
+          <t>6a4af7f2ae633549bd0f0454</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -31234,12 +31234,12 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F572" t="inlineStr"/>
@@ -31269,7 +31269,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0453</t>
+          <t>6a4af7f2ae633549bd0f0456</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -31282,12 +31282,12 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F573" t="inlineStr"/>
@@ -31317,7 +31317,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045a</t>
+          <t>6a4af7f2ae633549bd0f0457</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -31330,12 +31330,12 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F574" t="inlineStr"/>
@@ -31365,7 +31365,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0456</t>
+          <t>6a4af7f2ae633549bd0f0455</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -31378,12 +31378,12 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -31413,7 +31413,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0455</t>
+          <t>6a4af7f2ae633549bd0f0453</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -31426,12 +31426,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F576" t="inlineStr"/>
@@ -31461,7 +31461,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0457</t>
+          <t>6a4af7f2ae633549bd0f0458</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -31509,7 +31509,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0452</t>
+          <t>6a4af7f2ae633549bd0f045a</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -31522,12 +31522,12 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -31557,7 +31557,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0458</t>
+          <t>6a4af7f2ae633549bd0f0451</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -31570,12 +31570,12 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F579" t="inlineStr"/>
@@ -31605,7 +31605,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0454</t>
+          <t>6a4af7f2ae633549bd0f0459</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -31618,12 +31618,12 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F580" t="inlineStr"/>
@@ -31653,7 +31653,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0451</t>
+          <t>6a4af7f2ae633549bd0f0452</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -31666,12 +31666,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -31701,7 +31701,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0465</t>
+          <t>6a4af7f2ae633549bd0f045c</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -31714,12 +31714,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F582" t="inlineStr"/>
@@ -31749,7 +31749,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045e</t>
+          <t>6a4af7f2ae633549bd0f0461</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -31762,12 +31762,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -31797,7 +31797,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0464</t>
+          <t>6a4af7f2ae633549bd0f0462</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -31810,12 +31810,12 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F584" t="inlineStr"/>
@@ -31845,7 +31845,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045f</t>
+          <t>6a4af7f2ae633549bd0f0463</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -31858,12 +31858,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -31893,7 +31893,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045c</t>
+          <t>6a4af7f2ae633549bd0f045d</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -31906,12 +31906,12 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F586" t="inlineStr"/>
@@ -31941,7 +31941,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0463</t>
+          <t>6a4af7f2ae633549bd0f0460</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -31954,12 +31954,12 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -31989,7 +31989,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0461</t>
+          <t>6a4af7f2ae633549bd0f0465</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -32002,12 +32002,12 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -32037,7 +32037,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0462</t>
+          <t>6a4af7f2ae633549bd0f045e</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -32050,12 +32050,12 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -32085,7 +32085,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0460</t>
+          <t>6a4af7f2ae633549bd0f045f</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -32098,12 +32098,12 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -32133,7 +32133,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045d</t>
+          <t>6a4af7f2ae633549bd0f0464</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -32146,12 +32146,12 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -32325,7 +32325,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046b</t>
+          <t>6a4af7f2ae633549bd0f0467</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -32338,12 +32338,12 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F595" t="inlineStr"/>
@@ -32373,7 +32373,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046f</t>
+          <t>6a4af7f2ae633549bd0f046b</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -32386,12 +32386,12 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F596" t="inlineStr"/>
@@ -32421,7 +32421,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0468</t>
+          <t>6a4af7f2ae633549bd0f046f</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -32434,12 +32434,12 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F597" t="inlineStr"/>
@@ -32469,7 +32469,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0470</t>
+          <t>6a4af7f2ae633549bd0f0468</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -32482,12 +32482,12 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F598" t="inlineStr"/>
@@ -32517,7 +32517,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046e</t>
+          <t>6a4af7f2ae633549bd0f0470</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -32530,12 +32530,12 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -32565,7 +32565,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0467</t>
+          <t>6a4af7f2ae633549bd0f046e</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -32578,12 +32578,12 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F600" t="inlineStr"/>
@@ -32661,7 +32661,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0473</t>
+          <t>6a4af7f2ae633549bd0f0477</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -32674,12 +32674,12 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F602" t="inlineStr"/>
@@ -32709,7 +32709,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0476</t>
+          <t>6a4af7f2ae633549bd0f0478</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -32722,12 +32722,12 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
@@ -32757,7 +32757,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0477</t>
+          <t>6a4af7f2ae633549bd0f047a</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -32770,12 +32770,12 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -32805,7 +32805,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047a</t>
+          <t>6a4af7f2ae633549bd0f0479</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -32818,12 +32818,12 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F605" t="inlineStr"/>
@@ -32853,7 +32853,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0479</t>
+          <t>6a4af7f2ae633549bd0f0475</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -32866,12 +32866,12 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
@@ -32901,7 +32901,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0475</t>
+          <t>6a4af7f2ae633549bd0f0474</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -32914,12 +32914,12 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -32949,7 +32949,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0474</t>
+          <t>6a4af7f2ae633549bd0f047b</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -32962,12 +32962,12 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
@@ -32997,7 +32997,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047b</t>
+          <t>6a4af7f2ae633549bd0f0472</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -33010,12 +33010,12 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F609" t="inlineStr"/>
@@ -33045,7 +33045,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0478</t>
+          <t>6a4af7f2ae633549bd0f0473</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -33058,12 +33058,12 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F610" t="inlineStr"/>
@@ -33093,7 +33093,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0472</t>
+          <t>6a4af7f2ae633549bd0f0476</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -33106,12 +33106,12 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -33141,7 +33141,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0482</t>
+          <t>6a4af7f2ae633549bd0f047d</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -33154,12 +33154,12 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F612" t="inlineStr"/>
@@ -33189,7 +33189,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0484</t>
+          <t>6a4af7f2ae633549bd0f047f</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -33202,12 +33202,12 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F613" t="inlineStr"/>
@@ -33237,7 +33237,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0486</t>
+          <t>6a4af7f2ae633549bd0f0483</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -33250,12 +33250,12 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F614" t="inlineStr"/>
@@ -33285,7 +33285,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0485</t>
+          <t>6a4af7f2ae633549bd0f0482</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -33298,12 +33298,12 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -33381,7 +33381,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047e</t>
+          <t>6a4af7f3ae633549bd0f0486</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -33394,12 +33394,12 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F617" t="inlineStr"/>
@@ -33429,7 +33429,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047f</t>
+          <t>6a4af7f3ae633549bd0f0485</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -33442,12 +33442,12 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -33477,7 +33477,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047d</t>
+          <t>6a4af7f2ae633549bd0f047e</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -33490,12 +33490,12 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -33573,7 +33573,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0483</t>
+          <t>6a4af7f3ae633549bd0f0484</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -33586,12 +33586,12 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F621" t="inlineStr"/>
@@ -33621,7 +33621,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048c</t>
+          <t>6a4af7f3ae633549bd0f0491</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -33634,12 +33634,12 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F622" t="inlineStr"/>
@@ -33669,7 +33669,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048a</t>
+          <t>6a4af7f3ae633549bd0f0490</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -33682,12 +33682,12 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F623" t="inlineStr"/>
@@ -33717,7 +33717,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048e</t>
+          <t>6a4af7f3ae633549bd0f048a</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -33730,12 +33730,12 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
@@ -33765,7 +33765,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0490</t>
+          <t>6a4af7f3ae633549bd0f048c</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -33778,12 +33778,12 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F625" t="inlineStr"/>
@@ -33861,7 +33861,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048f</t>
+          <t>6a4af7f3ae633549bd0f048e</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -33874,12 +33874,12 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F627" t="inlineStr"/>
@@ -33909,7 +33909,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048d</t>
+          <t>6a4af7f3ae633549bd0f048f</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -33922,12 +33922,12 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F628" t="inlineStr"/>
@@ -33957,7 +33957,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0491</t>
+          <t>6a4af7f3ae633549bd0f0489</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -33970,12 +33970,12 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F629" t="inlineStr"/>
@@ -34005,7 +34005,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0489</t>
+          <t>6a4af7f3ae633549bd0f048d</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F630" t="inlineStr"/>
@@ -34101,7 +34101,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0498</t>
+          <t>6a4af7f3ae633549bd0f0494</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -34114,12 +34114,12 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F632" t="inlineStr"/>
@@ -34149,7 +34149,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049c</t>
+          <t>6a4af7f3ae633549bd0f0497</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -34162,12 +34162,12 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F633" t="inlineStr"/>
@@ -34197,7 +34197,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0495</t>
+          <t>6a4af7f3ae633549bd0f0499</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -34210,12 +34210,12 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F634" t="inlineStr"/>
@@ -34245,7 +34245,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0494</t>
+          <t>6a4af7f3ae633549bd0f0493</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -34258,12 +34258,12 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F635" t="inlineStr"/>
@@ -34293,7 +34293,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0497</t>
+          <t>6a4af7f3ae633549bd0f0496</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -34306,12 +34306,12 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F636" t="inlineStr"/>
@@ -34341,7 +34341,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0493</t>
+          <t>6a4af7f3ae633549bd0f049b</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -34354,12 +34354,12 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F637" t="inlineStr"/>
@@ -34389,7 +34389,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0496</t>
+          <t>6a4af7f3ae633549bd0f049a</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -34402,12 +34402,12 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F638" t="inlineStr"/>
@@ -34437,7 +34437,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0499</t>
+          <t>6a4af7f3ae633549bd0f0495</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
@@ -34485,7 +34485,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049b</t>
+          <t>6a4af7f3ae633549bd0f0498</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -34498,12 +34498,12 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F640" t="inlineStr"/>
@@ -34533,7 +34533,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049a</t>
+          <t>6a4af7f3ae633549bd0f049c</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -34546,12 +34546,12 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F641" t="inlineStr"/>
@@ -34629,7 +34629,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a1</t>
+          <t>6a4af7f3ae633549bd0f049f</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -34642,12 +34642,12 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
@@ -34677,7 +34677,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a5</t>
+          <t>6a4af7f3ae633549bd0f04a1</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -34690,12 +34690,12 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -34725,7 +34725,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a6</t>
+          <t>6a4af7f3ae633549bd0f04a5</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -34738,12 +34738,12 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F645" t="inlineStr"/>
@@ -34773,7 +34773,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a4</t>
+          <t>6a4af7f3ae633549bd0f04a6</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F646" t="inlineStr"/>
@@ -34821,7 +34821,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049f</t>
+          <t>6a4af7f3ae633549bd0f04a4</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -34834,12 +34834,12 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -35061,7 +35061,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04af</t>
+          <t>6a4af7f3ae633549bd0f04ab</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -35074,12 +35074,12 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -35109,7 +35109,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a9</t>
+          <t>6a4af7f3ae633549bd0f04ad</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -35122,12 +35122,12 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F653" t="inlineStr"/>
@@ -35157,7 +35157,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04aa</t>
+          <t>6a4af7f3ae633549bd0f04af</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -35170,12 +35170,12 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F654" t="inlineStr"/>
@@ -35205,7 +35205,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b2</t>
+          <t>6a4af7f3ae633549bd0f04b0</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -35218,12 +35218,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F655" t="inlineStr"/>
@@ -35253,7 +35253,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ac</t>
+          <t>6a4af7f3ae633549bd0f04b1</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -35266,12 +35266,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F656" t="inlineStr"/>
@@ -35301,7 +35301,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ae</t>
+          <t>6a4af7f3ae633549bd0f04ac</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -35314,12 +35314,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F657" t="inlineStr"/>
@@ -35349,7 +35349,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b1</t>
+          <t>6a4af7f3ae633549bd0f04ae</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -35362,12 +35362,12 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F658" t="inlineStr"/>
@@ -35397,7 +35397,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ad</t>
+          <t>6a4af7f3ae633549bd0f04b2</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -35410,12 +35410,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -35445,7 +35445,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b0</t>
+          <t>6a4af7f3ae633549bd0f04aa</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -35458,12 +35458,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F660" t="inlineStr"/>
@@ -35493,7 +35493,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ab</t>
+          <t>6a4af7f3ae633549bd0f04a9</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -35506,12 +35506,12 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F661" t="inlineStr"/>
@@ -35541,7 +35541,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ba</t>
+          <t>6a4af7f3ae633549bd0f04b4</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -35554,12 +35554,12 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F662" t="inlineStr"/>
@@ -35589,7 +35589,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bd</t>
+          <t>6a4af7f3ae633549bd0f04b7</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -35602,12 +35602,12 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F663" t="inlineStr"/>
@@ -35637,7 +35637,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b9</t>
+          <t>6a4af7f3ae633549bd0f04bb</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -35650,12 +35650,12 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F664" t="inlineStr"/>
@@ -35685,7 +35685,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bb</t>
+          <t>6a4af7f3ae633549bd0f04ba</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -35698,12 +35698,12 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F665" t="inlineStr"/>
@@ -35733,7 +35733,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b7</t>
+          <t>6a4af7f3ae633549bd0f04b9</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -35746,12 +35746,12 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F666" t="inlineStr"/>
@@ -35781,7 +35781,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b8</t>
+          <t>6a4af7f3ae633549bd0f04bd</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -35794,12 +35794,12 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F667" t="inlineStr"/>
@@ -35829,7 +35829,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b6</t>
+          <t>6a4af7f3ae633549bd0f04b5</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -35842,12 +35842,12 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F668" t="inlineStr"/>
@@ -35877,7 +35877,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b4</t>
+          <t>6a4af7f3ae633549bd0f04bc</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -35890,12 +35890,12 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
@@ -35925,7 +35925,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bc</t>
+          <t>6a4af7f3ae633549bd0f04b6</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -35938,12 +35938,12 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F670" t="inlineStr"/>
@@ -35973,7 +35973,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b5</t>
+          <t>6a4af7f3ae633549bd0f04b8</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -35986,12 +35986,12 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F671" t="inlineStr"/>
@@ -36021,7 +36021,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c1</t>
+          <t>6a4af7f3ae633549bd0f04c3</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -36034,12 +36034,12 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F672" t="inlineStr"/>
@@ -36069,7 +36069,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c4</t>
+          <t>6a4af7f3ae633549bd0f04c1</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -36082,12 +36082,12 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
@@ -36213,7 +36213,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bf</t>
+          <t>6a4af7f3ae633549bd0f04c8</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -36226,12 +36226,12 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -36405,7 +36405,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c8</t>
+          <t>6a4af7f3ae633549bd0f04bf</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -36418,12 +36418,12 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F680" t="inlineStr"/>
@@ -36453,7 +36453,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c3</t>
+          <t>6a4af7f3ae633549bd0f04c4</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -36466,12 +36466,12 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
@@ -36501,7 +36501,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cd</t>
+          <t>6a4af7f4ae633549bd0f04cf</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -36514,12 +36514,12 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F682" t="inlineStr"/>
@@ -36549,7 +36549,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cf</t>
+          <t>6a4af7f4ae633549bd0f04cd</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -36562,12 +36562,12 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F683" t="inlineStr"/>
@@ -36597,7 +36597,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d0</t>
+          <t>6a4af7f4ae633549bd0f04ce</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -36610,12 +36610,12 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F684" t="inlineStr"/>
@@ -36645,7 +36645,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d3</t>
+          <t>6a4af7f4ae633549bd0f04d0</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -36658,12 +36658,12 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F685" t="inlineStr"/>
@@ -36693,7 +36693,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cc</t>
+          <t>6a4af7f4ae633549bd0f04d3</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -36706,12 +36706,12 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F686" t="inlineStr"/>
@@ -36789,7 +36789,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ca</t>
+          <t>6a4af7f4ae633549bd0f04cc</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -36802,12 +36802,12 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F688" t="inlineStr"/>
@@ -36837,7 +36837,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ce</t>
+          <t>6a4af7f4ae633549bd0f04ca</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -36850,12 +36850,12 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F689" t="inlineStr"/>
@@ -36981,7 +36981,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d5</t>
+          <t>6a4af7f4ae633549bd0f04d9</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -36994,12 +36994,12 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F692" t="inlineStr"/>
@@ -37029,7 +37029,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d6</t>
+          <t>6a4af7f4ae633549bd0f04dc</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -37042,12 +37042,12 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F693" t="inlineStr"/>
@@ -37077,7 +37077,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04da</t>
+          <t>6a4af7f4ae633549bd0f04de</t>
         </is>
       </c>
       <c r="B694" t="n">
@@ -37090,12 +37090,12 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F694" t="inlineStr"/>
@@ -37125,7 +37125,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d8</t>
+          <t>6a4af7f4ae633549bd0f04d7</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -37138,12 +37138,12 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F695" t="inlineStr"/>
@@ -37173,7 +37173,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d9</t>
+          <t>6a4af7f4ae633549bd0f04d6</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -37186,12 +37186,12 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F696" t="inlineStr"/>
@@ -37221,7 +37221,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04db</t>
+          <t>6a4af7f4ae633549bd0f04d5</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -37234,12 +37234,12 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F697" t="inlineStr"/>
@@ -37269,7 +37269,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dc</t>
+          <t>6a4af7f4ae633549bd0f04da</t>
         </is>
       </c>
       <c r="B698" t="n">
@@ -37282,12 +37282,12 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F698" t="inlineStr"/>
@@ -37365,7 +37365,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04de</t>
+          <t>6a4af7f4ae633549bd0f04db</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -37378,12 +37378,12 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F700" t="inlineStr"/>
@@ -37413,7 +37413,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d7</t>
+          <t>6a4af7f4ae633549bd0f04d8</t>
         </is>
       </c>
       <c r="B701" t="n">
@@ -37426,12 +37426,12 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F701" t="inlineStr"/>
@@ -37461,7 +37461,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e1</t>
+          <t>6a4af7f4ae633549bd0f04e2</t>
         </is>
       </c>
       <c r="B702" t="n">
@@ -37474,12 +37474,12 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F702" t="inlineStr"/>
@@ -37509,7 +37509,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e6</t>
+          <t>6a4af7f4ae633549bd0f04e5</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -37522,12 +37522,12 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F703" t="inlineStr"/>
@@ -37605,7 +37605,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e5</t>
+          <t>6a4af7f4ae633549bd0f04e8</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -37618,12 +37618,12 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
@@ -37653,7 +37653,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e9</t>
+          <t>6a4af7f4ae633549bd0f04e4</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -37666,12 +37666,12 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F706" t="inlineStr"/>
@@ -37749,7 +37749,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e4</t>
+          <t>6a4af7f4ae633549bd0f04e9</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -37762,12 +37762,12 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F708" t="inlineStr"/>
@@ -37797,7 +37797,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e2</t>
+          <t>6a4af7f4ae633549bd0f04e1</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -37810,12 +37810,12 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F709" t="inlineStr"/>
@@ -37845,7 +37845,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e3</t>
+          <t>6a4af7f4ae633549bd0f04e6</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -37858,12 +37858,12 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F710" t="inlineStr"/>
@@ -37893,7 +37893,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e8</t>
+          <t>6a4af7f4ae633549bd0f04e3</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -37906,12 +37906,12 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F711" t="inlineStr"/>
@@ -37989,7 +37989,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f3</t>
+          <t>6a4af7f4ae633549bd0f04eb</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -38002,12 +38002,12 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F713" t="inlineStr"/>
@@ -38037,7 +38037,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f1</t>
+          <t>6a4af7f4ae633549bd0f04f3</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -38050,12 +38050,12 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -38085,7 +38085,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ef</t>
+          <t>6a4af7f4ae633549bd0f04ee</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -38098,12 +38098,12 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F715" t="inlineStr"/>
@@ -38133,7 +38133,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ed</t>
+          <t>6a4af7f4ae633549bd0f04f0</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -38146,12 +38146,12 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F716" t="inlineStr"/>
@@ -38181,7 +38181,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ec</t>
+          <t>6a4af7f4ae633549bd0f04f4</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -38194,12 +38194,12 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F717" t="inlineStr"/>
@@ -38229,7 +38229,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ee</t>
+          <t>6a4af7f4ae633549bd0f04ec</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -38242,12 +38242,12 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F718" t="inlineStr"/>
@@ -38277,7 +38277,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f0</t>
+          <t>6a4af7f4ae633549bd0f04ed</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -38290,12 +38290,12 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F719" t="inlineStr"/>
@@ -38325,7 +38325,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f4</t>
+          <t>6a4af7f4ae633549bd0f04ef</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -38338,12 +38338,12 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F720" t="inlineStr"/>
@@ -38373,7 +38373,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04eb</t>
+          <t>6a4af7f4ae633549bd0f04f1</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -38386,12 +38386,12 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F721" t="inlineStr"/>
@@ -38421,7 +38421,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f9</t>
+          <t>6a4af7f4ae633549bd0f04f8</t>
         </is>
       </c>
       <c r="B722" t="n">
@@ -38434,12 +38434,12 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F722" t="inlineStr"/>
@@ -38469,7 +38469,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fc</t>
+          <t>6a4af7f4ae633549bd0f04ff</t>
         </is>
       </c>
       <c r="B723" t="n">
@@ -38482,12 +38482,12 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F723" t="inlineStr"/>
@@ -38517,7 +38517,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fd</t>
+          <t>6a4af7f4ae633549bd0f04f9</t>
         </is>
       </c>
       <c r="B724" t="n">
@@ -38530,12 +38530,12 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F724" t="inlineStr"/>
@@ -38565,7 +38565,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fe</t>
+          <t>6a4af7f4ae633549bd0f04fc</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -38578,12 +38578,12 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
@@ -38613,7 +38613,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f6</t>
+          <t>6a4af7f4ae633549bd0f04fd</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -38626,12 +38626,12 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F726" t="inlineStr"/>
@@ -38661,7 +38661,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f8</t>
+          <t>6a4af7f4ae633549bd0f04fb</t>
         </is>
       </c>
       <c r="B727" t="n">
@@ -38674,12 +38674,12 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F727" t="inlineStr"/>
@@ -38709,7 +38709,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ff</t>
+          <t>6a4af7f4ae633549bd0f04fe</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -38722,12 +38722,12 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F728" t="inlineStr"/>
@@ -38853,7 +38853,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fb</t>
+          <t>6a4af7f4ae633549bd0f04f6</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -38866,12 +38866,12 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F731" t="inlineStr"/>
@@ -38901,7 +38901,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0505</t>
+          <t>6a4af7f4ae633549bd0f0508</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -38914,12 +38914,12 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F732" t="inlineStr"/>
@@ -38949,7 +38949,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0508</t>
+          <t>6a4af7f4ae633549bd0f0502</t>
         </is>
       </c>
       <c r="B733" t="n">
@@ -38962,12 +38962,12 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F733" t="inlineStr"/>
@@ -38997,7 +38997,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0502</t>
+          <t>6a4af7f4ae633549bd0f0501</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -39010,12 +39010,12 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
@@ -39045,7 +39045,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0501</t>
+          <t>6a4af7f4ae633549bd0f0503</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -39058,12 +39058,12 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -39141,7 +39141,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0503</t>
+          <t>6a4af7f4ae633549bd0f0506</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -39154,12 +39154,12 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F737" t="inlineStr"/>
@@ -39189,7 +39189,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0506</t>
+          <t>6a4af7f4ae633549bd0f050a</t>
         </is>
       </c>
       <c r="B738" t="n">
@@ -39202,12 +39202,12 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F738" t="inlineStr"/>
@@ -39237,7 +39237,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050a</t>
+          <t>6a4af7f4ae633549bd0f0504</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -39250,12 +39250,12 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F739" t="inlineStr"/>
@@ -39285,7 +39285,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0504</t>
+          <t>6a4af7f4ae633549bd0f0509</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -39298,12 +39298,12 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -39333,7 +39333,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0509</t>
+          <t>6a4af7f4ae633549bd0f0505</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -39346,12 +39346,12 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F741" t="inlineStr"/>
@@ -39381,7 +39381,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050c</t>
+          <t>6a4af7f5ae633549bd0f0514</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -39394,12 +39394,12 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F742" t="inlineStr"/>
@@ -39429,7 +39429,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050f</t>
+          <t>6a4af7f5ae633549bd0f0511</t>
         </is>
       </c>
       <c r="B743" t="n">
@@ -39442,12 +39442,12 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F743" t="inlineStr"/>
@@ -39477,7 +39477,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050d</t>
+          <t>6a4af7f5ae633549bd0f0515</t>
         </is>
       </c>
       <c r="B744" t="n">
@@ -39490,12 +39490,12 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F744" t="inlineStr"/>
@@ -39525,7 +39525,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0511</t>
+          <t>6a4af7f4ae633549bd0f050d</t>
         </is>
       </c>
       <c r="B745" t="n">
@@ -39538,12 +39538,12 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F745" t="inlineStr"/>
@@ -39573,7 +39573,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0515</t>
+          <t>6a4af7f5ae633549bd0f050f</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -39586,12 +39586,12 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F746" t="inlineStr"/>
@@ -39621,7 +39621,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0513</t>
+          <t>6a4af7f4ae633549bd0f050c</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -39634,12 +39634,12 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F747" t="inlineStr"/>
@@ -39669,7 +39669,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0514</t>
+          <t>6a4af7f5ae633549bd0f050e</t>
         </is>
       </c>
       <c r="B748" t="n">
@@ -39682,12 +39682,12 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F748" t="inlineStr"/>
@@ -39813,7 +39813,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050e</t>
+          <t>6a4af7f5ae633549bd0f0513</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -39826,12 +39826,12 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F751" t="inlineStr"/>
@@ -39861,7 +39861,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0520</t>
+          <t>6a4af7f5ae633549bd0f051f</t>
         </is>
       </c>
       <c r="B752" t="n">
@@ -39874,12 +39874,12 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F752" t="inlineStr"/>
@@ -39909,7 +39909,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0519</t>
+          <t>6a4af7f5ae633549bd0f051c</t>
         </is>
       </c>
       <c r="B753" t="n">
@@ -39922,12 +39922,12 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F753" t="inlineStr"/>
@@ -39957,7 +39957,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0517</t>
+          <t>6a4af7f5ae633549bd0f051d</t>
         </is>
       </c>
       <c r="B754" t="n">
@@ -39970,12 +39970,12 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F754" t="inlineStr"/>
@@ -40005,7 +40005,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051e</t>
+          <t>6a4af7f5ae633549bd0f051b</t>
         </is>
       </c>
       <c r="B755" t="n">
@@ -40018,12 +40018,12 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F755" t="inlineStr"/>
@@ -40053,7 +40053,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0518</t>
+          <t>6a4af7f5ae633549bd0f0517</t>
         </is>
       </c>
       <c r="B756" t="n">
@@ -40066,12 +40066,12 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F756" t="inlineStr"/>
@@ -40101,7 +40101,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051a</t>
+          <t>6a4af7f5ae633549bd0f0518</t>
         </is>
       </c>
       <c r="B757" t="n">
@@ -40114,12 +40114,12 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F757" t="inlineStr"/>
@@ -40149,7 +40149,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051c</t>
+          <t>6a4af7f5ae633549bd0f051a</t>
         </is>
       </c>
       <c r="B758" t="n">
@@ -40162,12 +40162,12 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F758" t="inlineStr"/>
@@ -40197,7 +40197,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051b</t>
+          <t>6a4af7f5ae633549bd0f0519</t>
         </is>
       </c>
       <c r="B759" t="n">
@@ -40210,12 +40210,12 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F759" t="inlineStr"/>
@@ -40245,7 +40245,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051d</t>
+          <t>6a4af7f5ae633549bd0f051e</t>
         </is>
       </c>
       <c r="B760" t="n">
@@ -40258,12 +40258,12 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F760" t="inlineStr"/>
@@ -40293,7 +40293,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051f</t>
+          <t>6a4af7f5ae633549bd0f0520</t>
         </is>
       </c>
       <c r="B761" t="n">
@@ -40306,12 +40306,12 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>

--- a/datos/maestros/md_partidos.xlsx
+++ b/datos/maestros/md_partidos.xlsx
@@ -21773,7 +21773,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b7</t>
+          <t>6a4af7f0ae633549bd0f03bb</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -21786,29 +21786,29 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="inlineStr"/>
       <c r="H382" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
@@ -21821,7 +21821,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ba</t>
+          <t>6a4af7f0ae633549bd0f03bd</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -21834,29 +21834,29 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
@@ -21869,7 +21869,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bb</t>
+          <t>6a4af7f0ae633549bd0f03bc</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -21882,29 +21882,29 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="inlineStr"/>
       <c r="H384" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
@@ -21917,7 +21917,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bd</t>
+          <t>6a4af7f0ae633549bd0f03be</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -21930,19 +21930,19 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -21965,7 +21965,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bf</t>
+          <t>6a4af7f0ae633549bd0f03b9</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -21978,29 +21978,29 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
       <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
@@ -22013,7 +22013,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b9</t>
+          <t>6a4af7f0ae633549bd0f03c0</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -22026,29 +22026,33 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
-        </is>
-      </c>
-      <c r="F387" t="inlineStr"/>
-      <c r="G387" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000d9</t>
+        </is>
+      </c>
+      <c r="F387" t="n">
+        <v>0</v>
+      </c>
+      <c r="G387" t="n">
+        <v>0</v>
+      </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
@@ -22056,12 +22060,16 @@
           <t>closed</t>
         </is>
       </c>
-      <c r="L387" t="inlineStr"/>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c0</t>
+          <t>6a4af7f0ae633549bd0f03b8</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -22074,50 +22082,42 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
-        </is>
-      </c>
-      <c r="F388" t="n">
-        <v>0</v>
-      </c>
-      <c r="G388" t="n">
-        <v>0</v>
-      </c>
+          <t>504e581e4d8bec9a670000d1</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="J388" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
       <c r="K388" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="L388" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="L388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b8</t>
+          <t>6a4af7f0ae633549bd0f03bf</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -22130,19 +22130,19 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -22165,7 +22165,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03be</t>
+          <t>6a4af7f0ae633549bd0f03b7</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -22178,29 +22178,29 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
@@ -22213,7 +22213,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bc</t>
+          <t>6a4af7f0ae633549bd0f03ba</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -22226,29 +22226,29 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
@@ -22261,7 +22261,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0381</t>
+          <t>6a4af7efae633549bd0f0380</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -22274,33 +22274,33 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F392" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G392" t="n">
         <v>0</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
@@ -22317,7 +22317,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0387</t>
+          <t>6a4af7efae633549bd0f0383</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -22330,33 +22330,33 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F393" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
@@ -22373,7 +22373,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0385</t>
+          <t>6a4af7efae633549bd0f0384</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -22386,33 +22386,33 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G394" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
@@ -22429,7 +22429,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0383</t>
+          <t>6a4af7efae633549bd0f0388</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -22442,33 +22442,33 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F395" t="n">
+        <v>2</v>
+      </c>
+      <c r="G395" t="n">
         <v>1</v>
       </c>
-      <c r="G395" t="n">
-        <v>2</v>
-      </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
@@ -22485,7 +22485,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0384</t>
+          <t>6a4af7efae633549bd0f0382</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -22498,23 +22498,23 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -22541,7 +22541,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0389</t>
+          <t>6a4af7efae633549bd0f0381</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -22554,23 +22554,23 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F397" t="n">
+        <v>2</v>
+      </c>
+      <c r="G397" t="n">
         <v>0</v>
       </c>
-      <c r="G397" t="n">
-        <v>1</v>
-      </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -22597,7 +22597,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0380</t>
+          <t>6a4af7efae633549bd0f0386</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -22610,33 +22610,33 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G398" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
@@ -22653,7 +22653,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0388</t>
+          <t>6a4af7efae633549bd0f0385</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -22666,33 +22666,33 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F399" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G399" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
@@ -22709,7 +22709,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0386</t>
+          <t>6a4af7efae633549bd0f0387</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -22722,33 +22722,33 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F400" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G400" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
@@ -22765,7 +22765,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0382</t>
+          <t>6a4af7efae633549bd0f0389</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -22778,23 +22778,23 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F401" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -22821,7 +22821,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038c</t>
+          <t>6a4af7efae633549bd0f038d</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -22834,33 +22834,33 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F402" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G402" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
@@ -22877,7 +22877,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038e</t>
+          <t>6a4af7efae633549bd0f0391</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -22890,23 +22890,23 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F403" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G403" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -22933,7 +22933,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038f</t>
+          <t>6a4af7efae633549bd0f0390</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -22946,33 +22946,33 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F404" t="n">
         <v>1</v>
       </c>
       <c r="G404" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
           <t>19:30</t>
-        </is>
-      </c>
-      <c r="J404" t="inlineStr">
-        <is>
-          <t>21:30</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
@@ -22989,7 +22989,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0392</t>
+          <t>6a4af7efae633549bd0f038c</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -23002,33 +23002,33 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F405" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G405" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
@@ -23045,7 +23045,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0393</t>
+          <t>6a4af7efae633549bd0f038b</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -23058,33 +23058,33 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F406" t="n">
         <v>1</v>
       </c>
       <c r="G406" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
@@ -23101,7 +23101,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0394</t>
+          <t>6a4af7efae633549bd0f038e</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -23114,33 +23114,33 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F407" t="n">
         <v>0</v>
       </c>
       <c r="G407" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
@@ -23157,7 +23157,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038d</t>
+          <t>6a4af7efae633549bd0f038f</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -23170,33 +23170,33 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F408" t="n">
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
@@ -23213,7 +23213,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0390</t>
+          <t>6a4af7efae633549bd0f0392</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -23226,23 +23226,23 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G409" t="n">
         <v>0</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -23269,7 +23269,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0391</t>
+          <t>6a4af7efae633549bd0f0393</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -23282,12 +23282,12 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -23298,17 +23298,17 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
@@ -23325,7 +23325,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038b</t>
+          <t>6a4af7efae633549bd0f0394</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -23338,19 +23338,19 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G411" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
@@ -23359,12 +23359,12 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
@@ -23941,7 +23941,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a4</t>
+          <t>6a4af7efae633549bd0f03a6</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -23954,19 +23954,19 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G422" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H422" t="inlineStr">
         <is>
@@ -23975,12 +23975,12 @@
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
@@ -23997,7 +23997,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a6</t>
+          <t>6a4af7efae633549bd0f03a7</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -24010,33 +24010,33 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F423" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G423" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
@@ -24053,7 +24053,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a5</t>
+          <t>6a4af7efae633549bd0f03a8</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -24066,33 +24066,33 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F424" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G424" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
@@ -24109,7 +24109,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03aa</t>
+          <t>6a4af7efae633549bd0f03a4</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -24122,12 +24122,12 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F425" t="n">
@@ -24138,17 +24138,17 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K425" t="inlineStr">
@@ -24165,7 +24165,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a7</t>
+          <t>6a4af7efae633549bd0f03aa</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -24178,33 +24178,33 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F426" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G426" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
@@ -24221,7 +24221,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a8</t>
+          <t>6a4af7efae633549bd0f03a1</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -24234,23 +24234,23 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G427" t="n">
         <v>2</v>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -24389,7 +24389,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a1</t>
+          <t>6a4af7efae633549bd0f03a3</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -24402,33 +24402,33 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G430" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
@@ -24445,7 +24445,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a3</t>
+          <t>6a4af7efae633549bd0f03a5</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -24458,23 +24458,23 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F431" t="n">
         <v>1</v>
       </c>
       <c r="G431" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -24501,7 +24501,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b3</t>
+          <t>6a4af7efae633549bd0f03ad</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -24514,12 +24514,12 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -24531,12 +24531,12 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
@@ -24597,7 +24597,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ad</t>
+          <t>6a4af7efae633549bd0f03b2</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -24610,29 +24610,29 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr"/>
       <c r="H434" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
@@ -24645,7 +24645,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b2</t>
+          <t>6a4af7efae633549bd0f03af</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -24658,29 +24658,29 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F435" t="inlineStr"/>
       <c r="G435" t="inlineStr"/>
       <c r="H435" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
@@ -24693,7 +24693,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b4</t>
+          <t>6a4af7efae633549bd0f03b1</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -24706,29 +24706,29 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
       <c r="G436" t="inlineStr"/>
       <c r="H436" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
@@ -24741,7 +24741,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b1</t>
+          <t>6a4af7efae633549bd0f03b4</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -24754,29 +24754,29 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr"/>
       <c r="H437" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
@@ -24789,7 +24789,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03af</t>
+          <t>6a4af7efae633549bd0f03ac</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -24802,29 +24802,29 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr"/>
       <c r="H438" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K438" t="inlineStr">
@@ -24837,7 +24837,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ac</t>
+          <t>6a4af7f0ae633549bd0f03b5</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -24850,29 +24850,29 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr"/>
       <c r="H439" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
@@ -24885,7 +24885,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b5</t>
+          <t>6a4af7efae633549bd0f03b3</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -24898,19 +24898,19 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
       <c r="G440" t="inlineStr"/>
       <c r="H440" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -24981,7 +24981,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cb</t>
+          <t>6a4af7f0ae633549bd0f03c4</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -24994,19 +24994,19 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
       <c r="G442" t="inlineStr"/>
       <c r="H442" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -25029,7 +25029,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c8</t>
+          <t>6a4af7f0ae633549bd0f03c7</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -25042,19 +25042,19 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
       <c r="G443" t="inlineStr"/>
       <c r="H443" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -25077,7 +25077,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c4</t>
+          <t>6a4af7f0ae633549bd0f03ca</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -25090,29 +25090,29 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
       <c r="G444" t="inlineStr"/>
       <c r="H444" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K444" t="inlineStr">
@@ -25125,7 +25125,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c2</t>
+          <t>6a4af7f0ae633549bd0f03c6</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -25138,29 +25138,29 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
       <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
@@ -25173,7 +25173,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c3</t>
+          <t>6a4af7f0ae633549bd0f03c2</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -25186,19 +25186,19 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
       <c r="G446" t="inlineStr"/>
       <c r="H446" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -25221,7 +25221,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c5</t>
+          <t>6a4af7f0ae633549bd0f03c3</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -25234,12 +25234,12 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -25251,12 +25251,12 @@
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K447" t="inlineStr">
@@ -25269,7 +25269,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c9</t>
+          <t>6a4af7f0ae633549bd0f03c5</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -25282,29 +25282,29 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
       <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K448" t="inlineStr">
@@ -25317,7 +25317,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c6</t>
+          <t>6a4af7f0ae633549bd0f03c9</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -25330,19 +25330,19 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
       <c r="G449" t="inlineStr"/>
       <c r="H449" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -25365,7 +25365,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c7</t>
+          <t>6a4af7f0ae633549bd0f03cb</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -25378,12 +25378,12 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
@@ -25395,12 +25395,12 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K450" t="inlineStr">
@@ -25413,7 +25413,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ca</t>
+          <t>6a4af7f0ae633549bd0f03c8</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -25426,29 +25426,29 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr"/>
       <c r="H451" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K451" t="inlineStr">
@@ -25461,7 +25461,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d1</t>
+          <t>6a4af7f0ae633549bd0f03d0</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -25474,12 +25474,12 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
@@ -25509,7 +25509,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d2</t>
+          <t>6a4af7f0ae633549bd0f03d1</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -25522,12 +25522,12 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
@@ -25557,7 +25557,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d3</t>
+          <t>6a4af7f0ae633549bd0f03d2</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -25570,12 +25570,12 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F454" t="inlineStr"/>
@@ -25605,7 +25605,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cd</t>
+          <t>6a4af7f0ae633549bd0f03d3</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -25618,12 +25618,12 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -25653,7 +25653,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cf</t>
+          <t>6a4af7f0ae633549bd0f03ce</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -25666,12 +25666,12 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
@@ -25701,7 +25701,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d0</t>
+          <t>6a4af7f0ae633549bd0f03d4</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -25714,12 +25714,12 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -25749,7 +25749,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d4</t>
+          <t>6a4af7f0ae633549bd0f03d6</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -25762,12 +25762,12 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -25845,7 +25845,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d6</t>
+          <t>6a4af7f0ae633549bd0f03cd</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -25858,12 +25858,12 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
@@ -25893,7 +25893,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ce</t>
+          <t>6a4af7f0ae633549bd0f03cf</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -25906,12 +25906,12 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -25941,7 +25941,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d9</t>
+          <t>6a4af7f0ae633549bd0f03dc</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -25954,12 +25954,12 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
@@ -25989,7 +25989,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dd</t>
+          <t>6a4af7f0ae633549bd0f03d9</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -26002,12 +26002,12 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -26037,7 +26037,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03da</t>
+          <t>6a4af7f0ae633549bd0f03de</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -26050,12 +26050,12 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -26085,7 +26085,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03de</t>
+          <t>6a4af7f0ae633549bd0f03da</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -26098,12 +26098,12 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
@@ -26181,7 +26181,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dc</t>
+          <t>6a4af7f0ae633549bd0f03df</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -26229,7 +26229,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e1</t>
+          <t>6a4af7f0ae633549bd0f03db</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -26242,12 +26242,12 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F468" t="inlineStr"/>
@@ -26277,7 +26277,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d8</t>
+          <t>6a4af7f0ae633549bd0f03dd</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -26290,12 +26290,12 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F469" t="inlineStr"/>
@@ -26325,7 +26325,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03df</t>
+          <t>6a4af7f0ae633549bd0f03e1</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -26338,12 +26338,12 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
@@ -26373,7 +26373,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03db</t>
+          <t>6a4af7f0ae633549bd0f03d8</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -26386,12 +26386,12 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -26421,7 +26421,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e3</t>
+          <t>6a4af7f0ae633549bd0f03e4</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -26434,12 +26434,12 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -26469,7 +26469,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e4</t>
+          <t>6a4af7f0ae633549bd0f03e6</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -26482,12 +26482,12 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -26499,12 +26499,12 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
@@ -26517,7 +26517,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e6</t>
+          <t>6a4af7f0ae633549bd0f03eb</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -26530,12 +26530,12 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -26547,12 +26547,12 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K474" t="inlineStr">
@@ -26661,7 +26661,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03eb</t>
+          <t>6a4af7f0ae633549bd0f03e5</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -26674,12 +26674,12 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
@@ -26709,7 +26709,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e5</t>
+          <t>6a4af7f0ae633549bd0f03ea</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -26722,12 +26722,12 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -26757,7 +26757,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ea</t>
+          <t>6a4af7f0ae633549bd0f03ec</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -26770,12 +26770,12 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
@@ -26805,7 +26805,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e9</t>
+          <t>6a4af7f0ae633549bd0f03e3</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -26818,12 +26818,12 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -26853,7 +26853,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ec</t>
+          <t>6a4af7f0ae633549bd0f03e9</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -26866,12 +26866,12 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
@@ -26901,7 +26901,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f7</t>
+          <t>6a4af7f0ae633549bd0f03f4</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -26914,12 +26914,12 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -26949,7 +26949,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f6</t>
+          <t>6a4af7f0ae633549bd0f03ee</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -26962,12 +26962,12 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -26997,7 +26997,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f1</t>
+          <t>6a4af7f0ae633549bd0f03f3</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -27010,12 +27010,12 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F484" t="inlineStr"/>
@@ -27045,7 +27045,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f0</t>
+          <t>6a4af7f0ae633549bd0f03f2</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -27058,12 +27058,12 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -27093,7 +27093,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f2</t>
+          <t>6a4af7f0ae633549bd0f03ef</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -27106,12 +27106,12 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
@@ -27189,7 +27189,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ef</t>
+          <t>6a4af7f0ae633549bd0f03f0</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -27202,12 +27202,12 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -27237,7 +27237,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ee</t>
+          <t>6a4af7f0ae633549bd0f03f1</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -27250,12 +27250,12 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -27285,7 +27285,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f3</t>
+          <t>6a4af7f0ae633549bd0f03f7</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -27298,12 +27298,12 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -27333,7 +27333,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f4</t>
+          <t>6a4af7f0ae633549bd0f03f6</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -27381,7 +27381,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0402</t>
+          <t>6a4af7f1ae633549bd0f0401</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -27394,12 +27394,12 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
@@ -27429,7 +27429,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fb</t>
+          <t>6a4af7f0ae633549bd0f03fa</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -27442,12 +27442,12 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
@@ -27477,7 +27477,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03ff</t>
+          <t>6a4af7f1ae633549bd0f03fd</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -27490,12 +27490,12 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F494" t="inlineStr"/>
@@ -27525,7 +27525,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0400</t>
+          <t>6a4af7f0ae633549bd0f03f9</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -27538,12 +27538,12 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -27573,7 +27573,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fe</t>
+          <t>6a4af7f1ae633549bd0f03fc</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -27586,12 +27586,12 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -27621,7 +27621,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fd</t>
+          <t>6a4af7f1ae633549bd0f03ff</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -27634,12 +27634,12 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F497" t="inlineStr"/>
@@ -27669,7 +27669,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f9</t>
+          <t>6a4af7f1ae633549bd0f0400</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -27682,12 +27682,12 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
@@ -27717,7 +27717,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fc</t>
+          <t>6a4af7f1ae633549bd0f03fe</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -27730,12 +27730,12 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -27765,7 +27765,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0401</t>
+          <t>6a4af7f1ae633549bd0f0402</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -27778,12 +27778,12 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -27813,7 +27813,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fa</t>
+          <t>6a4af7f0ae633549bd0f03fb</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -27826,12 +27826,12 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -27861,7 +27861,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0409</t>
+          <t>6a4af7f1ae633549bd0f0406</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -27874,12 +27874,12 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -27909,7 +27909,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0404</t>
+          <t>6a4af7f1ae633549bd0f040a</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -27922,12 +27922,12 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -27957,7 +27957,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040b</t>
+          <t>6a4af7f1ae633549bd0f040c</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -27970,12 +27970,12 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -28005,7 +28005,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0407</t>
+          <t>6a4af7f1ae633549bd0f040d</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -28018,12 +28018,12 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -28053,7 +28053,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0405</t>
+          <t>6a4af7f1ae633549bd0f0408</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -28066,12 +28066,12 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F506" t="inlineStr"/>
@@ -28101,7 +28101,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0406</t>
+          <t>6a4af7f1ae633549bd0f040b</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -28114,12 +28114,12 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F507" t="inlineStr"/>
@@ -28149,7 +28149,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040a</t>
+          <t>6a4af7f1ae633549bd0f0409</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -28162,12 +28162,12 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -28197,7 +28197,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040c</t>
+          <t>6a4af7f1ae633549bd0f0404</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -28210,12 +28210,12 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
@@ -28245,7 +28245,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040d</t>
+          <t>6a4af7f1ae633549bd0f0407</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -28258,12 +28258,12 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
@@ -28293,7 +28293,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0408</t>
+          <t>6a4af7f1ae633549bd0f0405</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -28306,12 +28306,12 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -28341,7 +28341,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0410</t>
+          <t>6a4af7f1ae633549bd0f0418</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -28354,12 +28354,12 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F512" t="inlineStr"/>
@@ -28389,7 +28389,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0415</t>
+          <t>6a4af7f1ae633549bd0f040f</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -28402,12 +28402,12 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F513" t="inlineStr"/>
@@ -28437,7 +28437,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0413</t>
+          <t>6a4af7f1ae633549bd0f0412</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -28450,12 +28450,12 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -28485,7 +28485,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0414</t>
+          <t>6a4af7f1ae633549bd0f0416</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -28498,12 +28498,12 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F515" t="inlineStr"/>
@@ -28581,7 +28581,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0417</t>
+          <t>6a4af7f1ae633549bd0f0414</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -28594,12 +28594,12 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F517" t="inlineStr"/>
@@ -28629,7 +28629,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0418</t>
+          <t>6a4af7f1ae633549bd0f0417</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -28642,12 +28642,12 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
@@ -28677,7 +28677,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0412</t>
+          <t>6a4af7f1ae633549bd0f0415</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -28690,12 +28690,12 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -28725,7 +28725,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0416</t>
+          <t>6a4af7f1ae633549bd0f0410</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -28738,12 +28738,12 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F520" t="inlineStr"/>
@@ -28773,7 +28773,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040f</t>
+          <t>6a4af7f1ae633549bd0f0413</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -28786,12 +28786,12 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F521" t="inlineStr"/>
@@ -29301,7 +29301,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042a</t>
+          <t>6a4af7f1ae633549bd0f0428</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -29314,12 +29314,12 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -29349,7 +29349,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042e</t>
+          <t>6a4af7f1ae633549bd0f042d</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -29362,12 +29362,12 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
@@ -29397,7 +29397,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042c</t>
+          <t>6a4af7f1ae633549bd0f042b</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
@@ -29445,7 +29445,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042b</t>
+          <t>6a4af7f1ae633549bd0f042c</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -29458,12 +29458,12 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -29493,7 +29493,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0428</t>
+          <t>6a4af7f1ae633549bd0f042a</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -29506,12 +29506,12 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -29541,7 +29541,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0426</t>
+          <t>6a4af7f1ae633549bd0f0427</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -29554,12 +29554,12 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -29589,7 +29589,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042d</t>
+          <t>6a4af7f1ae633549bd0f042e</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -29602,12 +29602,12 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -29637,7 +29637,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0429</t>
+          <t>6a4af7f1ae633549bd0f0425</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -29650,12 +29650,12 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F539" t="inlineStr"/>
@@ -29685,7 +29685,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0425</t>
+          <t>6a4af7f1ae633549bd0f0429</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -29698,12 +29698,12 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -29733,7 +29733,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0427</t>
+          <t>6a4af7f1ae633549bd0f0426</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -29746,12 +29746,12 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F541" t="inlineStr"/>
@@ -29781,7 +29781,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0437</t>
+          <t>6a4af7f1ae633549bd0f0438</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -29794,12 +29794,12 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F542" t="inlineStr"/>
@@ -29829,7 +29829,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0439</t>
+          <t>6a4af7f1ae633549bd0f0432</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -29842,12 +29842,12 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F543" t="inlineStr"/>
@@ -29877,7 +29877,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0432</t>
+          <t>6a4af7f1ae633549bd0f0435</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -29890,12 +29890,12 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
@@ -29925,7 +29925,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0435</t>
+          <t>6a4af7f1ae633549bd0f0437</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -29938,12 +29938,12 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -29973,7 +29973,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0438</t>
+          <t>6a4af7f1ae633549bd0f0434</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -29986,12 +29986,12 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -30021,7 +30021,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0431</t>
+          <t>6a4af7f1ae633549bd0f0439</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -30034,12 +30034,12 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
@@ -30069,7 +30069,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0433</t>
+          <t>6a4af7f1ae633549bd0f0430</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -30082,12 +30082,12 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -30117,7 +30117,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0436</t>
+          <t>6a4af7f1ae633549bd0f0431</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -30130,12 +30130,12 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -30165,7 +30165,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0430</t>
+          <t>6a4af7f1ae633549bd0f0433</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -30178,12 +30178,12 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
@@ -30213,7 +30213,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0434</t>
+          <t>6a4af7f1ae633549bd0f0436</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -30226,12 +30226,12 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F551" t="inlineStr"/>
@@ -30261,7 +30261,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0444</t>
+          <t>6a4af7f1ae633549bd0f043e</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -30274,12 +30274,12 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -30357,7 +30357,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0442</t>
+          <t>6a4af7f1ae633549bd0f043b</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -30370,12 +30370,12 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -30405,7 +30405,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043b</t>
+          <t>6a4af7f2ae633549bd0f0442</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -30418,12 +30418,12 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F555" t="inlineStr"/>
@@ -30453,7 +30453,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043c</t>
+          <t>6a4af7f2ae633549bd0f0443</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -30466,12 +30466,12 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -30501,7 +30501,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0440</t>
+          <t>6a4af7f2ae633549bd0f0444</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -30514,12 +30514,12 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -30549,7 +30549,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043e</t>
+          <t>6a4af7f2ae633549bd0f0441</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -30562,12 +30562,12 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
@@ -30597,7 +30597,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0443</t>
+          <t>6a4af7f1ae633549bd0f043d</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -30610,12 +30610,12 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F559" t="inlineStr"/>
@@ -30645,7 +30645,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043d</t>
+          <t>6a4af7f1ae633549bd0f043c</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -30658,12 +30658,12 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -30693,7 +30693,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0441</t>
+          <t>6a4af7f2ae633549bd0f0440</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -30706,12 +30706,12 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -30741,7 +30741,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0447</t>
+          <t>6a4af7f2ae633549bd0f044b</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -30754,12 +30754,12 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -30789,7 +30789,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0446</t>
+          <t>6a4af7f2ae633549bd0f044e</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -30802,12 +30802,12 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F563" t="inlineStr"/>
@@ -30837,7 +30837,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0448</t>
+          <t>6a4af7f2ae633549bd0f0446</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -30850,12 +30850,12 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F564" t="inlineStr"/>
@@ -30885,7 +30885,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044b</t>
+          <t>6a4af7f2ae633549bd0f044a</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -30898,12 +30898,12 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F565" t="inlineStr"/>
@@ -30933,7 +30933,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044a</t>
+          <t>6a4af7f2ae633549bd0f044f</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -30946,12 +30946,12 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
@@ -30981,7 +30981,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044e</t>
+          <t>6a4af7f2ae633549bd0f044d</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -30994,12 +30994,12 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F567" t="inlineStr"/>
@@ -31029,7 +31029,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044f</t>
+          <t>6a4af7f2ae633549bd0f0449</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -31042,12 +31042,12 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F568" t="inlineStr"/>
@@ -31077,7 +31077,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0449</t>
+          <t>6a4af7f2ae633549bd0f044c</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -31090,12 +31090,12 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F569" t="inlineStr"/>
@@ -31125,7 +31125,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044c</t>
+          <t>6a4af7f2ae633549bd0f0447</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -31138,12 +31138,12 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F570" t="inlineStr"/>
@@ -31173,7 +31173,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044d</t>
+          <t>6a4af7f2ae633549bd0f0448</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -31186,12 +31186,12 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -31221,7 +31221,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0454</t>
+          <t>6a4af7f2ae633549bd0f0453</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -31234,12 +31234,12 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F572" t="inlineStr"/>
@@ -31269,7 +31269,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0456</t>
+          <t>6a4af7f2ae633549bd0f0459</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -31282,12 +31282,12 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F573" t="inlineStr"/>
@@ -31317,7 +31317,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0457</t>
+          <t>6a4af7f2ae633549bd0f045a</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -31330,12 +31330,12 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F574" t="inlineStr"/>
@@ -31365,7 +31365,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0455</t>
+          <t>6a4af7f2ae633549bd0f0456</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -31378,12 +31378,12 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -31413,7 +31413,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0453</t>
+          <t>6a4af7f2ae633549bd0f0457</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -31426,12 +31426,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F576" t="inlineStr"/>
@@ -31461,7 +31461,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0458</t>
+          <t>6a4af7f2ae633549bd0f0455</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -31509,7 +31509,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045a</t>
+          <t>6a4af7f2ae633549bd0f0458</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -31522,12 +31522,12 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -31557,7 +31557,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0451</t>
+          <t>6a4af7f2ae633549bd0f0452</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -31570,12 +31570,12 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F579" t="inlineStr"/>
@@ -31605,7 +31605,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0459</t>
+          <t>6a4af7f2ae633549bd0f0454</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -31618,12 +31618,12 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F580" t="inlineStr"/>
@@ -31653,7 +31653,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0452</t>
+          <t>6a4af7f2ae633549bd0f0451</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -31666,12 +31666,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -31701,7 +31701,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045c</t>
+          <t>6a4af7f2ae633549bd0f045d</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -31714,12 +31714,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F582" t="inlineStr"/>
@@ -31749,7 +31749,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0461</t>
+          <t>6a4af7f2ae633549bd0f045f</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -31762,12 +31762,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -31797,7 +31797,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0462</t>
+          <t>6a4af7f2ae633549bd0f0460</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -31810,12 +31810,12 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F584" t="inlineStr"/>
@@ -31845,7 +31845,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0463</t>
+          <t>6a4af7f2ae633549bd0f0464</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -31858,12 +31858,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -31893,7 +31893,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045d</t>
+          <t>6a4af7f2ae633549bd0f0465</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -31906,12 +31906,12 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F586" t="inlineStr"/>
@@ -31941,7 +31941,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0460</t>
+          <t>6a4af7f2ae633549bd0f0463</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -31954,12 +31954,12 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -31989,7 +31989,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0465</t>
+          <t>6a4af7f2ae633549bd0f0462</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -32002,12 +32002,12 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -32037,7 +32037,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045e</t>
+          <t>6a4af7f2ae633549bd0f045c</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -32050,12 +32050,12 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -32085,7 +32085,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045f</t>
+          <t>6a4af7f2ae633549bd0f045e</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -32098,12 +32098,12 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -32133,7 +32133,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0464</t>
+          <t>6a4af7f2ae633549bd0f0461</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -32146,12 +32146,12 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -32181,7 +32181,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0469</t>
+          <t>6a4af7f2ae633549bd0f046f</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -32194,12 +32194,12 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F592" t="inlineStr"/>
@@ -32229,7 +32229,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046a</t>
+          <t>6a4af7f2ae633549bd0f0468</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -32242,12 +32242,12 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F593" t="inlineStr"/>
@@ -32277,7 +32277,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046c</t>
+          <t>6a4af7f2ae633549bd0f0470</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -32290,12 +32290,12 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F594" t="inlineStr"/>
@@ -32325,7 +32325,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0467</t>
+          <t>6a4af7f2ae633549bd0f046e</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -32338,12 +32338,12 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F595" t="inlineStr"/>
@@ -32373,7 +32373,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046b</t>
+          <t>6a4af7f2ae633549bd0f046d</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -32386,12 +32386,12 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F596" t="inlineStr"/>
@@ -32421,7 +32421,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046f</t>
+          <t>6a4af7f2ae633549bd0f0469</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -32434,12 +32434,12 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F597" t="inlineStr"/>
@@ -32469,7 +32469,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0468</t>
+          <t>6a4af7f2ae633549bd0f046c</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -32482,12 +32482,12 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F598" t="inlineStr"/>
@@ -32517,7 +32517,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0470</t>
+          <t>6a4af7f2ae633549bd0f046a</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -32530,12 +32530,12 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -32565,7 +32565,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046e</t>
+          <t>6a4af7f2ae633549bd0f0467</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -32578,12 +32578,12 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F600" t="inlineStr"/>
@@ -32613,7 +32613,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046d</t>
+          <t>6a4af7f2ae633549bd0f046b</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -32626,12 +32626,12 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F601" t="inlineStr"/>
@@ -32661,7 +32661,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0477</t>
+          <t>6a4af7f2ae633549bd0f0478</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -32674,12 +32674,12 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F602" t="inlineStr"/>
@@ -32709,7 +32709,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0478</t>
+          <t>6a4af7f2ae633549bd0f0472</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -32722,12 +32722,12 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
@@ -32757,7 +32757,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047a</t>
+          <t>6a4af7f2ae633549bd0f0473</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -32770,12 +32770,12 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -32805,7 +32805,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0479</t>
+          <t>6a4af7f2ae633549bd0f0476</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -32818,12 +32818,12 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F605" t="inlineStr"/>
@@ -32853,7 +32853,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0475</t>
+          <t>6a4af7f2ae633549bd0f0477</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -32866,12 +32866,12 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
@@ -32901,7 +32901,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0474</t>
+          <t>6a4af7f2ae633549bd0f0475</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -32914,12 +32914,12 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -32949,7 +32949,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047b</t>
+          <t>6a4af7f2ae633549bd0f0474</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -32962,12 +32962,12 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
@@ -32997,7 +32997,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0472</t>
+          <t>6a4af7f2ae633549bd0f047b</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -33010,12 +33010,12 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F609" t="inlineStr"/>
@@ -33045,7 +33045,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0473</t>
+          <t>6a4af7f2ae633549bd0f0479</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -33058,12 +33058,12 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F610" t="inlineStr"/>
@@ -33093,7 +33093,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0476</t>
+          <t>6a4af7f2ae633549bd0f047a</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -33106,12 +33106,12 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -33141,7 +33141,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047d</t>
+          <t>6a4af7f2ae633549bd0f0481</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -33154,12 +33154,12 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F612" t="inlineStr"/>
@@ -33189,7 +33189,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047f</t>
+          <t>6a4af7f3ae633549bd0f0484</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -33202,12 +33202,12 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F613" t="inlineStr"/>
@@ -33237,7 +33237,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0483</t>
+          <t>6a4af7f3ae633549bd0f0486</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -33250,12 +33250,12 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F614" t="inlineStr"/>
@@ -33285,7 +33285,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0482</t>
+          <t>6a4af7f2ae633549bd0f0480</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -33298,12 +33298,12 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -33333,7 +33333,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0481</t>
+          <t>6a4af7f3ae633549bd0f0485</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -33346,12 +33346,12 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F616" t="inlineStr"/>
@@ -33381,7 +33381,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0486</t>
+          <t>6a4af7f2ae633549bd0f0483</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -33394,12 +33394,12 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F617" t="inlineStr"/>
@@ -33429,7 +33429,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0485</t>
+          <t>6a4af7f2ae633549bd0f047d</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -33442,12 +33442,12 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -33525,7 +33525,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0480</t>
+          <t>6a4af7f2ae633549bd0f047f</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -33573,7 +33573,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0484</t>
+          <t>6a4af7f2ae633549bd0f0482</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -33586,12 +33586,12 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F621" t="inlineStr"/>
@@ -33621,7 +33621,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0491</t>
+          <t>6a4af7f3ae633549bd0f048a</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -33634,12 +33634,12 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F622" t="inlineStr"/>
@@ -33669,7 +33669,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0490</t>
+          <t>6a4af7f3ae633549bd0f048b</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -33682,12 +33682,12 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F623" t="inlineStr"/>
@@ -33717,7 +33717,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048a</t>
+          <t>6a4af7f3ae633549bd0f048c</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -33730,12 +33730,12 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
@@ -33765,7 +33765,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048c</t>
+          <t>6a4af7f3ae633549bd0f0491</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -33778,12 +33778,12 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F625" t="inlineStr"/>
@@ -33813,7 +33813,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0488</t>
+          <t>6a4af7f3ae633549bd0f0489</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -33826,12 +33826,12 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F626" t="inlineStr"/>
@@ -33861,7 +33861,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048e</t>
+          <t>6a4af7f3ae633549bd0f048d</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -33874,12 +33874,12 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F627" t="inlineStr"/>
@@ -33909,7 +33909,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048f</t>
+          <t>6a4af7f3ae633549bd0f0488</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -33922,12 +33922,12 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F628" t="inlineStr"/>
@@ -33957,7 +33957,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0489</t>
+          <t>6a4af7f3ae633549bd0f048e</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -33970,12 +33970,12 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F629" t="inlineStr"/>
@@ -34005,7 +34005,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048d</t>
+          <t>6a4af7f3ae633549bd0f048f</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F630" t="inlineStr"/>
@@ -34053,7 +34053,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048b</t>
+          <t>6a4af7f3ae633549bd0f0490</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -34066,12 +34066,12 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F631" t="inlineStr"/>
@@ -34197,7 +34197,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0499</t>
+          <t>6a4af7f3ae633549bd0f049c</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -34210,12 +34210,12 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F634" t="inlineStr"/>
@@ -34245,7 +34245,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0493</t>
+          <t>6a4af7f3ae633549bd0f0498</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -34258,12 +34258,12 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F635" t="inlineStr"/>
@@ -34293,7 +34293,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0496</t>
+          <t>6a4af7f3ae633549bd0f0495</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -34306,12 +34306,12 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F636" t="inlineStr"/>
@@ -34341,7 +34341,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049b</t>
+          <t>6a4af7f3ae633549bd0f049a</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -34354,12 +34354,12 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F637" t="inlineStr"/>
@@ -34389,7 +34389,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049a</t>
+          <t>6a4af7f3ae633549bd0f049b</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -34402,12 +34402,12 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F638" t="inlineStr"/>
@@ -34437,7 +34437,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0495</t>
+          <t>6a4af7f3ae633549bd0f0493</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
@@ -34485,7 +34485,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0498</t>
+          <t>6a4af7f3ae633549bd0f0496</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -34498,12 +34498,12 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F640" t="inlineStr"/>
@@ -34533,7 +34533,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049c</t>
+          <t>6a4af7f3ae633549bd0f0499</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -34546,12 +34546,12 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F641" t="inlineStr"/>
@@ -34581,7 +34581,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049e</t>
+          <t>6a4af7f3ae633549bd0f04a0</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -34594,12 +34594,12 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F642" t="inlineStr"/>
@@ -34629,7 +34629,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049f</t>
+          <t>6a4af7f3ae633549bd0f04a2</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -34642,12 +34642,12 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
@@ -34677,7 +34677,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a1</t>
+          <t>6a4af7f3ae633549bd0f04a3</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -34690,12 +34690,12 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -34725,7 +34725,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a5</t>
+          <t>6a4af7f3ae633549bd0f04a4</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -34738,12 +34738,12 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F645" t="inlineStr"/>
@@ -34773,7 +34773,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a6</t>
+          <t>6a4af7f3ae633549bd0f04a5</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F646" t="inlineStr"/>
@@ -34821,7 +34821,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a4</t>
+          <t>6a4af7f3ae633549bd0f04a1</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -34834,12 +34834,12 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -34869,7 +34869,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a0</t>
+          <t>6a4af7f3ae633549bd0f049e</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -34882,12 +34882,12 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -34917,7 +34917,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a2</t>
+          <t>6a4af7f3ae633549bd0f049f</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -34930,12 +34930,12 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -34965,7 +34965,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a3</t>
+          <t>6a4af7f3ae633549bd0f04a7</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -34978,12 +34978,12 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F650" t="inlineStr"/>
@@ -35013,7 +35013,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a7</t>
+          <t>6a4af7f3ae633549bd0f04a6</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -35026,12 +35026,12 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F651" t="inlineStr"/>
@@ -35061,7 +35061,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ab</t>
+          <t>6a4af7f3ae633549bd0f04ac</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -35074,12 +35074,12 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -35109,7 +35109,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ad</t>
+          <t>6a4af7f3ae633549bd0f04ae</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -35122,12 +35122,12 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F653" t="inlineStr"/>
@@ -35157,7 +35157,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04af</t>
+          <t>6a4af7f3ae633549bd0f04b2</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -35170,12 +35170,12 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F654" t="inlineStr"/>
@@ -35205,7 +35205,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b0</t>
+          <t>6a4af7f3ae633549bd0f04aa</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -35218,12 +35218,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F655" t="inlineStr"/>
@@ -35253,7 +35253,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b1</t>
+          <t>6a4af7f3ae633549bd0f04a9</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -35266,12 +35266,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F656" t="inlineStr"/>
@@ -35301,7 +35301,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ac</t>
+          <t>6a4af7f3ae633549bd0f04ab</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -35314,12 +35314,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F657" t="inlineStr"/>
@@ -35349,7 +35349,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ae</t>
+          <t>6a4af7f3ae633549bd0f04ad</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -35362,12 +35362,12 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F658" t="inlineStr"/>
@@ -35397,7 +35397,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b2</t>
+          <t>6a4af7f3ae633549bd0f04af</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -35410,12 +35410,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -35445,7 +35445,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04aa</t>
+          <t>6a4af7f3ae633549bd0f04b0</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -35458,12 +35458,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F660" t="inlineStr"/>
@@ -35493,7 +35493,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a9</t>
+          <t>6a4af7f3ae633549bd0f04b1</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -35506,12 +35506,12 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F661" t="inlineStr"/>
@@ -36021,7 +36021,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c3</t>
+          <t>6a4af7f3ae633549bd0f04c1</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -36034,12 +36034,12 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F672" t="inlineStr"/>
@@ -36069,7 +36069,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c1</t>
+          <t>6a4af7f3ae633549bd0f04c4</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -36082,12 +36082,12 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
@@ -36213,7 +36213,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c8</t>
+          <t>6a4af7f3ae633549bd0f04bf</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -36226,12 +36226,12 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -36405,7 +36405,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bf</t>
+          <t>6a4af7f3ae633549bd0f04c8</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -36418,12 +36418,12 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F680" t="inlineStr"/>
@@ -36453,7 +36453,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c4</t>
+          <t>6a4af7f3ae633549bd0f04c3</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -36466,12 +36466,12 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
@@ -36501,7 +36501,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cf</t>
+          <t>6a4af7f4ae633549bd0f04d1</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -36514,12 +36514,12 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F682" t="inlineStr"/>
@@ -36597,7 +36597,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ce</t>
+          <t>6a4af7f4ae633549bd0f04cf</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -36610,12 +36610,12 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F684" t="inlineStr"/>
@@ -36645,7 +36645,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d0</t>
+          <t>6a4af7f4ae633549bd0f04d3</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -36658,12 +36658,12 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F685" t="inlineStr"/>
@@ -36693,7 +36693,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d3</t>
+          <t>6a4af7f4ae633549bd0f04ce</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -36706,12 +36706,12 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F686" t="inlineStr"/>
@@ -36741,7 +36741,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cb</t>
+          <t>6a4af7f4ae633549bd0f04d0</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -36754,12 +36754,12 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F687" t="inlineStr"/>
@@ -36789,7 +36789,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cc</t>
+          <t>6a4af7f4ae633549bd0f04d2</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -36802,12 +36802,12 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F688" t="inlineStr"/>
@@ -36885,7 +36885,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d2</t>
+          <t>6a4af7f4ae633549bd0f04cb</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -36898,12 +36898,12 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F690" t="inlineStr"/>
@@ -36933,7 +36933,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d1</t>
+          <t>6a4af7f4ae633549bd0f04cc</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -36946,12 +36946,12 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F691" t="inlineStr"/>
@@ -36981,7 +36981,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d9</t>
+          <t>6a4af7f4ae633549bd0f04db</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -36994,12 +36994,12 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F692" t="inlineStr"/>
@@ -37029,7 +37029,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dc</t>
+          <t>6a4af7f4ae633549bd0f04d8</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -37042,12 +37042,12 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F693" t="inlineStr"/>
@@ -37077,7 +37077,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04de</t>
+          <t>6a4af7f4ae633549bd0f04d9</t>
         </is>
       </c>
       <c r="B694" t="n">
@@ -37090,12 +37090,12 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F694" t="inlineStr"/>
@@ -37125,7 +37125,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d7</t>
+          <t>6a4af7f4ae633549bd0f04dc</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -37138,12 +37138,12 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F695" t="inlineStr"/>
@@ -37365,7 +37365,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04db</t>
+          <t>6a4af7f4ae633549bd0f04de</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -37378,12 +37378,12 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F700" t="inlineStr"/>
@@ -37413,7 +37413,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d8</t>
+          <t>6a4af7f4ae633549bd0f04d7</t>
         </is>
       </c>
       <c r="B701" t="n">
@@ -37426,12 +37426,12 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F701" t="inlineStr"/>
@@ -37461,7 +37461,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e2</t>
+          <t>6a4af7f4ae633549bd0f04e1</t>
         </is>
       </c>
       <c r="B702" t="n">
@@ -37474,12 +37474,12 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F702" t="inlineStr"/>
@@ -37509,7 +37509,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e5</t>
+          <t>6a4af7f4ae633549bd0f04e6</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -37522,12 +37522,12 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F703" t="inlineStr"/>
@@ -37557,7 +37557,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e7</t>
+          <t>6a4af7f4ae633549bd0f04e3</t>
         </is>
       </c>
       <c r="B704" t="n">
@@ -37570,12 +37570,12 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F704" t="inlineStr"/>
@@ -37605,7 +37605,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e8</t>
+          <t>6a4af7f4ae633549bd0f04e2</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -37618,12 +37618,12 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
@@ -37653,7 +37653,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e4</t>
+          <t>6a4af7f4ae633549bd0f04e5</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -37666,12 +37666,12 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F706" t="inlineStr"/>
@@ -37701,7 +37701,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e0</t>
+          <t>6a4af7f4ae633549bd0f04e7</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -37714,12 +37714,12 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F707" t="inlineStr"/>
@@ -37749,7 +37749,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e9</t>
+          <t>6a4af7f4ae633549bd0f04e8</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -37762,12 +37762,12 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F708" t="inlineStr"/>
@@ -37797,7 +37797,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e1</t>
+          <t>6a4af7f4ae633549bd0f04e9</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -37810,12 +37810,12 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F709" t="inlineStr"/>
@@ -37845,7 +37845,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e6</t>
+          <t>6a4af7f4ae633549bd0f04e4</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -37858,12 +37858,12 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F710" t="inlineStr"/>
@@ -37893,7 +37893,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e3</t>
+          <t>6a4af7f4ae633549bd0f04e0</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -37906,12 +37906,12 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F711" t="inlineStr"/>
@@ -37941,7 +37941,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f2</t>
+          <t>6a4af7f4ae633549bd0f04f1</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -37954,12 +37954,12 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F712" t="inlineStr"/>
@@ -37989,7 +37989,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04eb</t>
+          <t>6a4af7f4ae633549bd0f04f2</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -38002,12 +38002,12 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F713" t="inlineStr"/>
@@ -38085,7 +38085,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ee</t>
+          <t>6a4af7f4ae633549bd0f04ed</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -38098,12 +38098,12 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F715" t="inlineStr"/>
@@ -38133,7 +38133,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f0</t>
+          <t>6a4af7f4ae633549bd0f04ec</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -38146,12 +38146,12 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F716" t="inlineStr"/>
@@ -38181,7 +38181,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f4</t>
+          <t>6a4af7f4ae633549bd0f04ef</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -38194,12 +38194,12 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F717" t="inlineStr"/>
@@ -38229,7 +38229,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ec</t>
+          <t>6a4af7f4ae633549bd0f04ee</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -38242,12 +38242,12 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F718" t="inlineStr"/>
@@ -38277,7 +38277,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ed</t>
+          <t>6a4af7f4ae633549bd0f04f0</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -38290,12 +38290,12 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F719" t="inlineStr"/>
@@ -38325,7 +38325,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ef</t>
+          <t>6a4af7f4ae633549bd0f04eb</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -38338,12 +38338,12 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F720" t="inlineStr"/>
@@ -38373,7 +38373,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f1</t>
+          <t>6a4af7f4ae633549bd0f04f4</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -38386,12 +38386,12 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F721" t="inlineStr"/>
@@ -38421,7 +38421,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f8</t>
+          <t>6a4af7f4ae633549bd0f04fd</t>
         </is>
       </c>
       <c r="B722" t="n">
@@ -38434,12 +38434,12 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F722" t="inlineStr"/>
@@ -38469,7 +38469,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ff</t>
+          <t>6a4af7f4ae633549bd0f04f9</t>
         </is>
       </c>
       <c r="B723" t="n">
@@ -38482,12 +38482,12 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F723" t="inlineStr"/>
@@ -38517,7 +38517,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f9</t>
+          <t>6a4af7f4ae633549bd0f04fc</t>
         </is>
       </c>
       <c r="B724" t="n">
@@ -38530,12 +38530,12 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F724" t="inlineStr"/>
@@ -38565,7 +38565,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fc</t>
+          <t>6a4af7f4ae633549bd0f04fe</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -38578,12 +38578,12 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
@@ -38613,7 +38613,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fd</t>
+          <t>6a4af7f4ae633549bd0f04ff</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -38626,12 +38626,12 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F726" t="inlineStr"/>
@@ -38661,7 +38661,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fb</t>
+          <t>6a4af7f4ae633549bd0f04f6</t>
         </is>
       </c>
       <c r="B727" t="n">
@@ -38674,12 +38674,12 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F727" t="inlineStr"/>
@@ -38709,7 +38709,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fe</t>
+          <t>6a4af7f4ae633549bd0f04f7</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -38722,12 +38722,12 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F728" t="inlineStr"/>
@@ -38757,7 +38757,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fa</t>
+          <t>6a4af7f4ae633549bd0f04f8</t>
         </is>
       </c>
       <c r="B729" t="n">
@@ -38770,12 +38770,12 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F729" t="inlineStr"/>
@@ -38805,7 +38805,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f7</t>
+          <t>6a4af7f4ae633549bd0f04fa</t>
         </is>
       </c>
       <c r="B730" t="n">
@@ -38818,12 +38818,12 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F730" t="inlineStr"/>
@@ -38853,7 +38853,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f6</t>
+          <t>6a4af7f4ae633549bd0f04fb</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -38866,12 +38866,12 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F731" t="inlineStr"/>
@@ -38901,7 +38901,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0508</t>
+          <t>6a4af7f4ae633549bd0f0501</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -38914,12 +38914,12 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F732" t="inlineStr"/>
@@ -38949,7 +38949,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0502</t>
+          <t>6a4af7f4ae633549bd0f0503</t>
         </is>
       </c>
       <c r="B733" t="n">
@@ -38962,12 +38962,12 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F733" t="inlineStr"/>
@@ -38997,7 +38997,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0501</t>
+          <t>6a4af7f4ae633549bd0f0508</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -39010,12 +39010,12 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
@@ -39045,7 +39045,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0503</t>
+          <t>6a4af7f4ae633549bd0f0507</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -39058,12 +39058,12 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -39093,7 +39093,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0507</t>
+          <t>6a4af7f4ae633549bd0f0502</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -39106,12 +39106,12 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
@@ -39141,7 +39141,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0506</t>
+          <t>6a4af7f4ae633549bd0f0509</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -39154,12 +39154,12 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F737" t="inlineStr"/>
@@ -39189,7 +39189,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050a</t>
+          <t>6a4af7f4ae633549bd0f0505</t>
         </is>
       </c>
       <c r="B738" t="n">
@@ -39202,12 +39202,12 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F738" t="inlineStr"/>
@@ -39237,7 +39237,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0504</t>
+          <t>6a4af7f4ae633549bd0f0506</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -39250,12 +39250,12 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F739" t="inlineStr"/>
@@ -39285,7 +39285,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0509</t>
+          <t>6a4af7f4ae633549bd0f050a</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -39298,12 +39298,12 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -39333,7 +39333,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0505</t>
+          <t>6a4af7f4ae633549bd0f0504</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -39346,12 +39346,12 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F741" t="inlineStr"/>
@@ -39381,7 +39381,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0514</t>
+          <t>6a4af7f5ae633549bd0f050e</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -39394,12 +39394,12 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F742" t="inlineStr"/>
@@ -39429,7 +39429,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0511</t>
+          <t>6a4af7f5ae633549bd0f0514</t>
         </is>
       </c>
       <c r="B743" t="n">
@@ -39442,12 +39442,12 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F743" t="inlineStr"/>
@@ -39477,7 +39477,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0515</t>
+          <t>6a4af7f5ae633549bd0f0513</t>
         </is>
       </c>
       <c r="B744" t="n">
@@ -39490,12 +39490,12 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F744" t="inlineStr"/>
@@ -39525,7 +39525,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050d</t>
+          <t>6a4af7f5ae633549bd0f0510</t>
         </is>
       </c>
       <c r="B745" t="n">
@@ -39538,12 +39538,12 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F745" t="inlineStr"/>
@@ -39573,7 +39573,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050f</t>
+          <t>6a4af7f5ae633549bd0f0512</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -39586,12 +39586,12 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F746" t="inlineStr"/>
@@ -39621,7 +39621,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050c</t>
+          <t>6a4af7f4ae633549bd0f050d</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -39634,12 +39634,12 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F747" t="inlineStr"/>
@@ -39669,7 +39669,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050e</t>
+          <t>6a4af7f5ae633549bd0f0511</t>
         </is>
       </c>
       <c r="B748" t="n">
@@ -39682,12 +39682,12 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F748" t="inlineStr"/>
@@ -39717,7 +39717,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0512</t>
+          <t>6a4af7f5ae633549bd0f0515</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -39730,12 +39730,12 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
@@ -39765,7 +39765,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0510</t>
+          <t>6a4af7f4ae633549bd0f050c</t>
         </is>
       </c>
       <c r="B750" t="n">
@@ -39778,12 +39778,12 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F750" t="inlineStr"/>
@@ -39813,7 +39813,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0513</t>
+          <t>6a4af7f5ae633549bd0f050f</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -39826,12 +39826,12 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F751" t="inlineStr"/>
@@ -39861,7 +39861,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051f</t>
+          <t>6a4af7f5ae633549bd0f0517</t>
         </is>
       </c>
       <c r="B752" t="n">
@@ -39874,12 +39874,12 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F752" t="inlineStr"/>
@@ -39909,7 +39909,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051c</t>
+          <t>6a4af7f5ae633549bd0f051b</t>
         </is>
       </c>
       <c r="B753" t="n">
@@ -39922,12 +39922,12 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F753" t="inlineStr"/>
@@ -40005,7 +40005,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051b</t>
+          <t>6a4af7f5ae633549bd0f051c</t>
         </is>
       </c>
       <c r="B755" t="n">
@@ -40018,12 +40018,12 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F755" t="inlineStr"/>
@@ -40053,7 +40053,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0517</t>
+          <t>6a4af7f5ae633549bd0f051e</t>
         </is>
       </c>
       <c r="B756" t="n">
@@ -40066,12 +40066,12 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F756" t="inlineStr"/>
@@ -40101,7 +40101,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0518</t>
+          <t>6a4af7f5ae633549bd0f051f</t>
         </is>
       </c>
       <c r="B757" t="n">
@@ -40114,12 +40114,12 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F757" t="inlineStr"/>
@@ -40149,7 +40149,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051a</t>
+          <t>6a4af7f5ae633549bd0f0519</t>
         </is>
       </c>
       <c r="B758" t="n">
@@ -40162,12 +40162,12 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F758" t="inlineStr"/>
@@ -40197,7 +40197,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0519</t>
+          <t>6a4af7f5ae633549bd0f0520</t>
         </is>
       </c>
       <c r="B759" t="n">
@@ -40210,12 +40210,12 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F759" t="inlineStr"/>
@@ -40245,7 +40245,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051e</t>
+          <t>6a4af7f5ae633549bd0f0518</t>
         </is>
       </c>
       <c r="B760" t="n">
@@ -40258,12 +40258,12 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F760" t="inlineStr"/>
@@ -40293,7 +40293,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0520</t>
+          <t>6a4af7f5ae633549bd0f051a</t>
         </is>
       </c>
       <c r="B761" t="n">
@@ -40306,12 +40306,12 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>

--- a/datos/maestros/md_partidos.xlsx
+++ b/datos/maestros/md_partidos.xlsx
@@ -21773,7 +21773,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bb</t>
+          <t>6a4af7f0ae633549bd0f03b7</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -21786,29 +21786,29 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="inlineStr"/>
       <c r="H382" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
@@ -21821,7 +21821,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bd</t>
+          <t>6a4af7f0ae633549bd0f03bb</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -21834,12 +21834,12 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
@@ -21851,12 +21851,12 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
@@ -21965,7 +21965,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b9</t>
+          <t>6a4af7f0ae633549bd0f03b8</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -21978,12 +21978,12 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
@@ -21995,12 +21995,12 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
@@ -22013,7 +22013,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c0</t>
+          <t>6a4af7f0ae633549bd0f03b9</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -22026,33 +22026,29 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
-        </is>
-      </c>
-      <c r="F387" t="n">
-        <v>0</v>
-      </c>
-      <c r="G387" t="n">
-        <v>0</v>
-      </c>
+          <t>520e4ee4a776cc826b00004b</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
@@ -22060,16 +22056,12 @@
           <t>closed</t>
         </is>
       </c>
-      <c r="L387" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="L387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b8</t>
+          <t>6a4af7f0ae633549bd0f03c0</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -22082,29 +22074,33 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
-        </is>
-      </c>
-      <c r="F388" t="inlineStr"/>
-      <c r="G388" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000d9</t>
+        </is>
+      </c>
+      <c r="F388" t="n">
+        <v>0</v>
+      </c>
+      <c r="G388" t="n">
+        <v>0</v>
+      </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
@@ -22112,7 +22108,11 @@
           <t>closed</t>
         </is>
       </c>
-      <c r="L388" t="inlineStr"/>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -22165,7 +22165,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b7</t>
+          <t>6a4af7f0ae633549bd0f03ba</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -22178,29 +22178,29 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
@@ -22213,7 +22213,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ba</t>
+          <t>6a4af7f0ae633549bd0f03bd</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -22226,29 +22226,29 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
@@ -22261,7 +22261,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0380</t>
+          <t>6a4af7efae633549bd0f0385</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -22274,12 +22274,12 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F392" t="n">
@@ -22290,17 +22290,17 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
@@ -22317,7 +22317,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0383</t>
+          <t>6a4af7efae633549bd0f0386</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -22330,33 +22330,33 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F393" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G393" t="n">
         <v>2</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
@@ -22373,7 +22373,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0384</t>
+          <t>6a4af7efae633549bd0f0382</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -22386,23 +22386,23 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G394" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -22429,7 +22429,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0388</t>
+          <t>6a4af7efae633549bd0f0381</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -22442,33 +22442,33 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F395" t="n">
         <v>2</v>
       </c>
       <c r="G395" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
@@ -22485,7 +22485,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0382</t>
+          <t>6a4af7efae633549bd0f0380</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -22498,33 +22498,33 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G396" t="n">
         <v>0</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
@@ -22541,7 +22541,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0381</t>
+          <t>6a4af7efae633549bd0f0388</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -22554,33 +22554,33 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F397" t="n">
         <v>2</v>
       </c>
       <c r="G397" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
@@ -22597,7 +22597,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0386</t>
+          <t>6a4af7efae633549bd0f0383</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -22610,33 +22610,33 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G398" t="n">
         <v>2</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
@@ -22653,7 +22653,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0385</t>
+          <t>6a4af7efae633549bd0f0384</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -22666,33 +22666,33 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F399" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G399" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
@@ -22709,7 +22709,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0387</t>
+          <t>6a4af7efae633549bd0f0389</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -22722,23 +22722,23 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F400" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G400" t="n">
         <v>1</v>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -22765,7 +22765,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0389</t>
+          <t>6a4af7efae633549bd0f0387</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -22778,23 +22778,23 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F401" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G401" t="n">
         <v>1</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -22877,7 +22877,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0391</t>
+          <t>6a4af7efae633549bd0f0390</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -22890,33 +22890,33 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F403" t="n">
         <v>1</v>
       </c>
       <c r="G403" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
           <t>19:30</t>
-        </is>
-      </c>
-      <c r="J403" t="inlineStr">
-        <is>
-          <t>21:30</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
@@ -22933,7 +22933,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0390</t>
+          <t>6a4af7efae633549bd0f0391</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -22946,33 +22946,33 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F404" t="n">
         <v>1</v>
       </c>
       <c r="G404" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
@@ -22989,7 +22989,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038c</t>
+          <t>6a4af7efae633549bd0f038b</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -23002,23 +23002,23 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F405" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G405" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -23045,7 +23045,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038b</t>
+          <t>6a4af7efae633549bd0f038c</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -23058,23 +23058,23 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F406" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G406" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -23381,7 +23381,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0397</t>
+          <t>6a4af7efae633549bd0f0398</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -23394,23 +23394,23 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G412" t="n">
         <v>2</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -23437,7 +23437,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0398</t>
+          <t>6a4af7efae633549bd0f039a</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -23450,33 +23450,33 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G413" t="n">
         <v>2</v>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
@@ -23493,7 +23493,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039a</t>
+          <t>6a4af7efae633549bd0f039c</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -23506,33 +23506,33 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G414" t="n">
         <v>2</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
@@ -23549,7 +23549,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039b</t>
+          <t>6a4af7efae633549bd0f0399</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -23562,23 +23562,23 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F415" t="n">
+        <v>3</v>
+      </c>
+      <c r="G415" t="n">
         <v>1</v>
       </c>
-      <c r="G415" t="n">
-        <v>0</v>
-      </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -23605,7 +23605,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039c</t>
+          <t>6a4af7efae633549bd0f0396</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -23618,19 +23618,19 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G416" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
@@ -23639,12 +23639,12 @@
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
@@ -23661,7 +23661,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039d</t>
+          <t>6a4af7efae633549bd0f039e</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -23674,33 +23674,33 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G417" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
@@ -23717,7 +23717,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0396</t>
+          <t>6a4af7efae633549bd0f039b</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -23730,12 +23730,12 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F418" t="n">
@@ -23746,17 +23746,17 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
           <t>19:30</t>
-        </is>
-      </c>
-      <c r="J418" t="inlineStr">
-        <is>
-          <t>21:30</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
@@ -23773,7 +23773,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0399</t>
+          <t>6a4af7efae633549bd0f039d</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -23786,19 +23786,19 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F419" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G419" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
@@ -23807,12 +23807,12 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
@@ -23829,7 +23829,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039e</t>
+          <t>6a4af7efae633549bd0f039f</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -23842,19 +23842,19 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F420" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G420" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
@@ -23863,12 +23863,12 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
@@ -23885,7 +23885,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039f</t>
+          <t>6a4af7efae633549bd0f0397</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -23898,23 +23898,23 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F421" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G421" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -23941,7 +23941,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a6</t>
+          <t>6a4af7efae633549bd0f03a7</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -23954,33 +23954,33 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G422" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
@@ -23997,7 +23997,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a7</t>
+          <t>6a4af7efae633549bd0f03aa</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -24010,33 +24010,33 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F423" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G423" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
@@ -24053,7 +24053,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a8</t>
+          <t>6a4af7efae633549bd0f03a2</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -24066,19 +24066,19 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F424" t="n">
         <v>3</v>
       </c>
       <c r="G424" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H424" t="inlineStr">
         <is>
@@ -24087,12 +24087,12 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
@@ -24109,7 +24109,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a4</t>
+          <t>6a4af7efae633549bd0f03a3</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -24122,33 +24122,33 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F425" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G425" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K425" t="inlineStr">
@@ -24165,7 +24165,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03aa</t>
+          <t>6a4af7efae633549bd0f03a5</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -24178,23 +24178,23 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F426" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G426" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -24221,7 +24221,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a1</t>
+          <t>6a4af7efae633549bd0f03a9</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -24234,20 +24234,20 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F427" t="n">
+        <v>0</v>
+      </c>
+      <c r="G427" t="n">
         <v>5</v>
       </c>
-      <c r="G427" t="n">
-        <v>2</v>
-      </c>
       <c r="H427" t="inlineStr">
         <is>
           <t>2026-09-06</t>
@@ -24255,12 +24255,12 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
@@ -24277,7 +24277,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a9</t>
+          <t>6a4af7efae633549bd0f03a1</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -24290,19 +24290,19 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G428" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
@@ -24311,12 +24311,12 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
@@ -24333,7 +24333,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a2</t>
+          <t>6a4af7efae633549bd0f03a8</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -24346,19 +24346,19 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F429" t="n">
         <v>3</v>
       </c>
       <c r="G429" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
@@ -24367,12 +24367,12 @@
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
@@ -24389,7 +24389,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a3</t>
+          <t>6a4af7efae633549bd0f03a4</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -24402,33 +24402,33 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G430" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
@@ -24445,7 +24445,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a5</t>
+          <t>6a4af7efae633549bd0f03a6</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -24458,12 +24458,12 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -24474,17 +24474,17 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
           <t>19:00</t>
-        </is>
-      </c>
-      <c r="J431" t="inlineStr">
-        <is>
-          <t>21:00</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
@@ -24501,7 +24501,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ad</t>
+          <t>6a4af7efae633549bd0f03ac</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -24514,29 +24514,29 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
       <c r="G432" t="inlineStr"/>
       <c r="H432" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
@@ -24549,7 +24549,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b0</t>
+          <t>6a4af7f0ae633549bd0f03b5</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -24562,29 +24562,29 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr"/>
       <c r="H433" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
@@ -24597,7 +24597,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b2</t>
+          <t>6a4af7efae633549bd0f03b3</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -24610,19 +24610,19 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr"/>
       <c r="H434" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -24645,7 +24645,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03af</t>
+          <t>6a4af7efae633549bd0f03ae</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -24658,12 +24658,12 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F435" t="inlineStr"/>
@@ -24675,12 +24675,12 @@
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
@@ -24693,7 +24693,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b1</t>
+          <t>6a4af7efae633549bd0f03b0</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -24706,12 +24706,12 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -24723,12 +24723,12 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
@@ -24741,7 +24741,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b4</t>
+          <t>6a4af7efae633549bd0f03ad</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -24754,29 +24754,29 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr"/>
       <c r="H437" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
@@ -24789,7 +24789,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ac</t>
+          <t>6a4af7efae633549bd0f03b2</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -24802,12 +24802,12 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
@@ -24819,12 +24819,12 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K438" t="inlineStr">
@@ -24837,7 +24837,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b5</t>
+          <t>6a4af7efae633549bd0f03b1</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -24850,29 +24850,29 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr"/>
       <c r="H439" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
@@ -24885,7 +24885,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b3</t>
+          <t>6a4af7efae633549bd0f03af</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -24898,12 +24898,12 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F440" t="inlineStr"/>
@@ -24915,12 +24915,12 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
@@ -24933,7 +24933,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ae</t>
+          <t>6a4af7efae633549bd0f03b4</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -24946,29 +24946,29 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
       <c r="G441" t="inlineStr"/>
       <c r="H441" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K441" t="inlineStr">
@@ -24981,7 +24981,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c4</t>
+          <t>6a4af7f0ae633549bd0f03cb</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -24994,19 +24994,19 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
       <c r="G442" t="inlineStr"/>
       <c r="H442" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -25029,7 +25029,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c7</t>
+          <t>6a4af7f0ae633549bd0f03c8</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -25042,19 +25042,19 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
       <c r="G443" t="inlineStr"/>
       <c r="H443" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -25077,7 +25077,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ca</t>
+          <t>6a4af7f0ae633549bd0f03c4</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -25090,29 +25090,29 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
       <c r="G444" t="inlineStr"/>
       <c r="H444" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K444" t="inlineStr">
@@ -25125,7 +25125,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c6</t>
+          <t>6a4af7f0ae633549bd0f03c2</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -25138,29 +25138,29 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
       <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
@@ -25173,7 +25173,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c2</t>
+          <t>6a4af7f0ae633549bd0f03c3</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -25186,19 +25186,19 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
       <c r="G446" t="inlineStr"/>
       <c r="H446" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -25221,7 +25221,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c3</t>
+          <t>6a4af7f0ae633549bd0f03c5</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -25234,12 +25234,12 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
@@ -25251,12 +25251,12 @@
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K447" t="inlineStr">
@@ -25269,7 +25269,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c5</t>
+          <t>6a4af7f0ae633549bd0f03c9</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -25282,29 +25282,29 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
       <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K448" t="inlineStr">
@@ -25317,7 +25317,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c9</t>
+          <t>6a4af7f0ae633549bd0f03c6</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -25330,19 +25330,19 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
       <c r="G449" t="inlineStr"/>
       <c r="H449" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -25365,7 +25365,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cb</t>
+          <t>6a4af7f0ae633549bd0f03c7</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -25378,12 +25378,12 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
@@ -25395,12 +25395,12 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K450" t="inlineStr">
@@ -25413,7 +25413,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c8</t>
+          <t>6a4af7f0ae633549bd0f03ca</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -25426,29 +25426,29 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr"/>
       <c r="H451" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K451" t="inlineStr">
@@ -25461,7 +25461,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d0</t>
+          <t>6a4af7f0ae633549bd0f03ce</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -25474,12 +25474,12 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
@@ -25653,7 +25653,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ce</t>
+          <t>6a4af7f0ae633549bd0f03d5</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -25666,12 +25666,12 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
@@ -25701,7 +25701,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d4</t>
+          <t>6a4af7f0ae633549bd0f03cd</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -25714,12 +25714,12 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -25749,7 +25749,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d6</t>
+          <t>6a4af7f0ae633549bd0f03cf</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -25762,12 +25762,12 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -25797,7 +25797,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d5</t>
+          <t>6a4af7f0ae633549bd0f03d0</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -25810,12 +25810,12 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -25845,7 +25845,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cd</t>
+          <t>6a4af7f0ae633549bd0f03d4</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -25858,12 +25858,12 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
@@ -25893,7 +25893,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cf</t>
+          <t>6a4af7f0ae633549bd0f03d6</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -25906,12 +25906,12 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -25941,7 +25941,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dc</t>
+          <t>6a4af7f0ae633549bd0f03e1</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -25954,12 +25954,12 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
@@ -25989,7 +25989,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d9</t>
+          <t>6a4af7f0ae633549bd0f03d8</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -26002,12 +26002,12 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -26037,7 +26037,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03de</t>
+          <t>6a4af7f0ae633549bd0f03db</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -26050,12 +26050,12 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -26085,7 +26085,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03da</t>
+          <t>6a4af7f0ae633549bd0f03dd</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -26098,12 +26098,12 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
@@ -26133,7 +26133,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e0</t>
+          <t>6a4af7f0ae633549bd0f03df</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -26146,12 +26146,12 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F466" t="inlineStr"/>
@@ -26181,7 +26181,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03df</t>
+          <t>6a4af7f0ae633549bd0f03da</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -26229,7 +26229,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03db</t>
+          <t>6a4af7f0ae633549bd0f03e0</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -26242,12 +26242,12 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F468" t="inlineStr"/>
@@ -26277,7 +26277,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dd</t>
+          <t>6a4af7f0ae633549bd0f03d9</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -26290,12 +26290,12 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F469" t="inlineStr"/>
@@ -26325,7 +26325,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e1</t>
+          <t>6a4af7f0ae633549bd0f03de</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -26338,12 +26338,12 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
@@ -26373,7 +26373,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d8</t>
+          <t>6a4af7f0ae633549bd0f03dc</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -26386,12 +26386,12 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -26421,7 +26421,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e4</t>
+          <t>6a4af7f0ae633549bd0f03ea</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -26434,12 +26434,12 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -26469,7 +26469,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e6</t>
+          <t>6a4af7f0ae633549bd0f03e5</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -26482,12 +26482,12 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -26499,12 +26499,12 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
@@ -26517,7 +26517,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03eb</t>
+          <t>6a4af7f0ae633549bd0f03e9</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -26530,12 +26530,12 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -26565,7 +26565,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e8</t>
+          <t>6a4af7f0ae633549bd0f03e3</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -26578,12 +26578,12 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -26613,7 +26613,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e7</t>
+          <t>6a4af7f0ae633549bd0f03ec</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -26626,12 +26626,12 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
@@ -26661,7 +26661,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e5</t>
+          <t>6a4af7f0ae633549bd0f03e4</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -26674,12 +26674,12 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
@@ -26709,7 +26709,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ea</t>
+          <t>6a4af7f0ae633549bd0f03e6</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -26722,12 +26722,12 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -26739,12 +26739,12 @@
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K478" t="inlineStr">
@@ -26757,7 +26757,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ec</t>
+          <t>6a4af7f0ae633549bd0f03e8</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -26770,12 +26770,12 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
@@ -26805,7 +26805,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e3</t>
+          <t>6a4af7f0ae633549bd0f03e7</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -26818,12 +26818,12 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -26853,7 +26853,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e9</t>
+          <t>6a4af7f0ae633549bd0f03eb</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -26866,12 +26866,12 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
@@ -26901,7 +26901,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f4</t>
+          <t>6a4af7f0ae633549bd0f03ef</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -26914,12 +26914,12 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -26949,7 +26949,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ee</t>
+          <t>6a4af7f0ae633549bd0f03f0</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -26962,12 +26962,12 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -26997,7 +26997,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f3</t>
+          <t>6a4af7f0ae633549bd0f03f1</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -27010,12 +27010,12 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F484" t="inlineStr"/>
@@ -27045,7 +27045,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f2</t>
+          <t>6a4af7f0ae633549bd0f03f7</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -27058,12 +27058,12 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -27093,7 +27093,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ef</t>
+          <t>6a4af7f0ae633549bd0f03f6</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -27106,12 +27106,12 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
@@ -27141,7 +27141,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f5</t>
+          <t>6a4af7f0ae633549bd0f03ee</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -27154,12 +27154,12 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F487" t="inlineStr"/>
@@ -27189,7 +27189,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f0</t>
+          <t>6a4af7f0ae633549bd0f03f3</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -27202,12 +27202,12 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -27237,7 +27237,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f1</t>
+          <t>6a4af7f0ae633549bd0f03f4</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -27250,12 +27250,12 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -27285,7 +27285,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f7</t>
+          <t>6a4af7f0ae633549bd0f03f2</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -27298,12 +27298,12 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -27333,7 +27333,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f6</t>
+          <t>6a4af7f0ae633549bd0f03f5</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -27381,7 +27381,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0401</t>
+          <t>6a4af7f0ae633549bd0f03f9</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -27394,12 +27394,12 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
@@ -27429,7 +27429,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fa</t>
+          <t>6a4af7f1ae633549bd0f03fc</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -27442,12 +27442,12 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
@@ -27477,7 +27477,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fd</t>
+          <t>6a4af7f1ae633549bd0f03ff</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -27490,12 +27490,12 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F494" t="inlineStr"/>
@@ -27525,7 +27525,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f9</t>
+          <t>6a4af7f1ae633549bd0f03fe</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -27538,12 +27538,12 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -27573,7 +27573,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fc</t>
+          <t>6a4af7f1ae633549bd0f0400</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -27586,12 +27586,12 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -27621,7 +27621,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03ff</t>
+          <t>6a4af7f0ae633549bd0f03fb</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -27634,12 +27634,12 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F497" t="inlineStr"/>
@@ -27669,7 +27669,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0400</t>
+          <t>6a4af7f1ae633549bd0f0402</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -27682,12 +27682,12 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
@@ -27717,7 +27717,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fe</t>
+          <t>6a4af7f1ae633549bd0f0401</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -27730,12 +27730,12 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -27765,7 +27765,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0402</t>
+          <t>6a4af7f0ae633549bd0f03fa</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -27778,12 +27778,12 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -27813,7 +27813,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fb</t>
+          <t>6a4af7f1ae633549bd0f03fd</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -27826,12 +27826,12 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -27861,7 +27861,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0406</t>
+          <t>6a4af7f1ae633549bd0f040a</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -27874,12 +27874,12 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -27909,7 +27909,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040a</t>
+          <t>6a4af7f1ae633549bd0f0406</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -27922,12 +27922,12 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -27957,7 +27957,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040c</t>
+          <t>6a4af7f1ae633549bd0f040d</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -27970,12 +27970,12 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -28005,7 +28005,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040d</t>
+          <t>6a4af7f1ae633549bd0f040c</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -28018,12 +28018,12 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -28149,7 +28149,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0409</t>
+          <t>6a4af7f1ae633549bd0f0404</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -28162,12 +28162,12 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -28197,7 +28197,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0404</t>
+          <t>6a4af7f1ae633549bd0f0409</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -28210,12 +28210,12 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
@@ -28245,7 +28245,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0407</t>
+          <t>6a4af7f1ae633549bd0f0405</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -28258,12 +28258,12 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
@@ -28293,7 +28293,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0405</t>
+          <t>6a4af7f1ae633549bd0f0407</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -28306,12 +28306,12 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -28341,7 +28341,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0418</t>
+          <t>6a4af7f1ae633549bd0f0410</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -28354,12 +28354,12 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F512" t="inlineStr"/>
@@ -28389,7 +28389,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040f</t>
+          <t>6a4af7f1ae633549bd0f0418</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -28402,12 +28402,12 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F513" t="inlineStr"/>
@@ -28437,7 +28437,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0412</t>
+          <t>6a4af7f1ae633549bd0f040f</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -28450,12 +28450,12 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -28533,7 +28533,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0411</t>
+          <t>6a4af7f1ae633549bd0f0412</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -28546,12 +28546,12 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F516" t="inlineStr"/>
@@ -28581,7 +28581,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0414</t>
+          <t>6a4af7f1ae633549bd0f0411</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -28594,12 +28594,12 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F517" t="inlineStr"/>
@@ -28629,7 +28629,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0417</t>
+          <t>6a4af7f1ae633549bd0f0414</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -28642,12 +28642,12 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
@@ -28677,7 +28677,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0415</t>
+          <t>6a4af7f1ae633549bd0f0413</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -28690,12 +28690,12 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -28725,7 +28725,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0410</t>
+          <t>6a4af7f1ae633549bd0f0417</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -28738,12 +28738,12 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F520" t="inlineStr"/>
@@ -28773,7 +28773,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0413</t>
+          <t>6a4af7f1ae633549bd0f0415</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -28786,12 +28786,12 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F521" t="inlineStr"/>
@@ -28821,7 +28821,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041e</t>
+          <t>6a4af7f1ae633549bd0f041f</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -28834,12 +28834,12 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F522" t="inlineStr"/>
@@ -28869,7 +28869,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0421</t>
+          <t>6a4af7f1ae633549bd0f041c</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -28882,12 +28882,12 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F523" t="inlineStr"/>
@@ -28917,7 +28917,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0423</t>
+          <t>6a4af7f1ae633549bd0f0420</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -28930,12 +28930,12 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F524" t="inlineStr"/>
@@ -28965,7 +28965,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041f</t>
+          <t>6a4af7f1ae633549bd0f0422</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -28978,12 +28978,12 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F525" t="inlineStr"/>
@@ -29013,7 +29013,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041a</t>
+          <t>6a4af7f1ae633549bd0f0423</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -29026,12 +29026,12 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F526" t="inlineStr"/>
@@ -29061,7 +29061,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041c</t>
+          <t>6a4af7f1ae633549bd0f041b</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F527" t="inlineStr"/>
@@ -29109,7 +29109,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0420</t>
+          <t>6a4af7f1ae633549bd0f041d</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -29122,12 +29122,12 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F528" t="inlineStr"/>
@@ -29157,7 +29157,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041d</t>
+          <t>6a4af7f1ae633549bd0f0421</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -29170,12 +29170,12 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -29205,7 +29205,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041b</t>
+          <t>6a4af7f1ae633549bd0f041e</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -29218,12 +29218,12 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -29253,7 +29253,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0422</t>
+          <t>6a4af7f1ae633549bd0f041a</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -29266,12 +29266,12 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -29301,7 +29301,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0428</t>
+          <t>6a4af7f1ae633549bd0f0427</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -29314,12 +29314,12 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -29349,7 +29349,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042d</t>
+          <t>6a4af7f1ae633549bd0f042e</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -29362,12 +29362,12 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
@@ -29493,7 +29493,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042a</t>
+          <t>6a4af7f1ae633549bd0f0428</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -29506,12 +29506,12 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -29541,7 +29541,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0427</t>
+          <t>6a4af7f1ae633549bd0f0426</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -29554,12 +29554,12 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -29589,7 +29589,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042e</t>
+          <t>6a4af7f1ae633549bd0f042d</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -29602,12 +29602,12 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -29637,7 +29637,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0425</t>
+          <t>6a4af7f1ae633549bd0f0429</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -29650,12 +29650,12 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F539" t="inlineStr"/>
@@ -29685,7 +29685,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0429</t>
+          <t>6a4af7f1ae633549bd0f0425</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -29698,12 +29698,12 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -29733,7 +29733,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0426</t>
+          <t>6a4af7f1ae633549bd0f042a</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -29746,12 +29746,12 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F541" t="inlineStr"/>
@@ -29781,7 +29781,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0438</t>
+          <t>6a4af7f1ae633549bd0f0439</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -29794,12 +29794,12 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F542" t="inlineStr"/>
@@ -29829,7 +29829,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0432</t>
+          <t>6a4af7f1ae633549bd0f0434</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -29842,12 +29842,12 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F543" t="inlineStr"/>
@@ -29877,7 +29877,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0435</t>
+          <t>6a4af7f1ae633549bd0f0430</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -29890,12 +29890,12 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
@@ -29925,7 +29925,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0437</t>
+          <t>6a4af7f1ae633549bd0f0433</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -29938,12 +29938,12 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -29973,7 +29973,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0434</t>
+          <t>6a4af7f1ae633549bd0f0431</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -29986,12 +29986,12 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -30021,7 +30021,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0439</t>
+          <t>6a4af7f1ae633549bd0f0436</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -30034,12 +30034,12 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
@@ -30069,7 +30069,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0430</t>
+          <t>6a4af7f1ae633549bd0f0438</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -30082,12 +30082,12 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -30117,7 +30117,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0431</t>
+          <t>6a4af7f1ae633549bd0f0432</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -30130,12 +30130,12 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -30165,7 +30165,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0433</t>
+          <t>6a4af7f1ae633549bd0f0435</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -30178,12 +30178,12 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
@@ -30213,7 +30213,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0436</t>
+          <t>6a4af7f1ae633549bd0f0437</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -30226,12 +30226,12 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F551" t="inlineStr"/>
@@ -30261,7 +30261,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043e</t>
+          <t>6a4af7f2ae633549bd0f0441</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -30274,12 +30274,12 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -30309,7 +30309,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f043f</t>
+          <t>6a4af7f1ae633549bd0f043d</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -30322,12 +30322,12 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -30357,7 +30357,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043b</t>
+          <t>6a4af7f2ae633549bd0f0444</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -30370,12 +30370,12 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -30405,7 +30405,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0442</t>
+          <t>6a4af7f1ae633549bd0f043c</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -30418,12 +30418,12 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F555" t="inlineStr"/>
@@ -30453,7 +30453,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0443</t>
+          <t>6a4af7f2ae633549bd0f0440</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -30466,12 +30466,12 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -30501,7 +30501,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0444</t>
+          <t>6a4af7f1ae633549bd0f043e</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -30514,12 +30514,12 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -30549,7 +30549,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0441</t>
+          <t>6a4af7f2ae633549bd0f043f</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -30562,12 +30562,12 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
@@ -30597,7 +30597,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043d</t>
+          <t>6a4af7f2ae633549bd0f0442</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -30610,12 +30610,12 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F559" t="inlineStr"/>
@@ -30645,7 +30645,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043c</t>
+          <t>6a4af7f1ae633549bd0f043b</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -30658,12 +30658,12 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -30693,7 +30693,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0440</t>
+          <t>6a4af7f2ae633549bd0f0443</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -30706,12 +30706,12 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -30789,7 +30789,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044e</t>
+          <t>6a4af7f2ae633549bd0f0447</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -30802,12 +30802,12 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F563" t="inlineStr"/>
@@ -30837,7 +30837,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0446</t>
+          <t>6a4af7f2ae633549bd0f0448</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -30850,12 +30850,12 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F564" t="inlineStr"/>
@@ -30885,7 +30885,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044a</t>
+          <t>6a4af7f2ae633549bd0f0449</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -30898,12 +30898,12 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F565" t="inlineStr"/>
@@ -30933,7 +30933,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044f</t>
+          <t>6a4af7f2ae633549bd0f044c</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -30946,12 +30946,12 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
@@ -31029,7 +31029,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0449</t>
+          <t>6a4af7f2ae633549bd0f044f</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -31042,12 +31042,12 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F568" t="inlineStr"/>
@@ -31077,7 +31077,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044c</t>
+          <t>6a4af7f2ae633549bd0f044e</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -31090,12 +31090,12 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F569" t="inlineStr"/>
@@ -31125,7 +31125,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0447</t>
+          <t>6a4af7f2ae633549bd0f0446</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -31138,12 +31138,12 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F570" t="inlineStr"/>
@@ -31173,7 +31173,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0448</t>
+          <t>6a4af7f2ae633549bd0f044a</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -31186,12 +31186,12 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -31317,7 +31317,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045a</t>
+          <t>6a4af7f2ae633549bd0f0451</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -31330,12 +31330,12 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F574" t="inlineStr"/>
@@ -31365,7 +31365,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0456</t>
+          <t>6a4af7f2ae633549bd0f0454</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -31378,12 +31378,12 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -31413,7 +31413,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0457</t>
+          <t>6a4af7f2ae633549bd0f0452</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -31426,12 +31426,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F576" t="inlineStr"/>
@@ -31557,7 +31557,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0452</t>
+          <t>6a4af7f2ae633549bd0f0456</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -31570,12 +31570,12 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F579" t="inlineStr"/>
@@ -31605,7 +31605,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0454</t>
+          <t>6a4af7f2ae633549bd0f0457</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -31618,12 +31618,12 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F580" t="inlineStr"/>
@@ -31653,7 +31653,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0451</t>
+          <t>6a4af7f2ae633549bd0f045a</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -31666,12 +31666,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -31701,7 +31701,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045d</t>
+          <t>6a4af7f2ae633549bd0f0460</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -31714,12 +31714,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F582" t="inlineStr"/>
@@ -31749,7 +31749,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045f</t>
+          <t>6a4af7f2ae633549bd0f0464</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -31762,12 +31762,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -31797,7 +31797,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0460</t>
+          <t>6a4af7f2ae633549bd0f045d</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -31810,12 +31810,12 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F584" t="inlineStr"/>
@@ -31845,7 +31845,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0464</t>
+          <t>6a4af7f2ae633549bd0f0465</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -31858,12 +31858,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -31893,7 +31893,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0465</t>
+          <t>6a4af7f2ae633549bd0f0462</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -31906,12 +31906,12 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F586" t="inlineStr"/>
@@ -31989,7 +31989,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0462</t>
+          <t>6a4af7f2ae633549bd0f045c</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -32002,12 +32002,12 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -32037,7 +32037,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045c</t>
+          <t>6a4af7f2ae633549bd0f0461</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -32050,12 +32050,12 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -32085,7 +32085,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045e</t>
+          <t>6a4af7f2ae633549bd0f045f</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -32098,12 +32098,12 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -32133,7 +32133,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0461</t>
+          <t>6a4af7f2ae633549bd0f045e</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -32146,12 +32146,12 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -32181,7 +32181,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046f</t>
+          <t>6a4af7f2ae633549bd0f0469</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -32194,12 +32194,12 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F592" t="inlineStr"/>
@@ -32229,7 +32229,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0468</t>
+          <t>6a4af7f2ae633549bd0f046a</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -32242,12 +32242,12 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F593" t="inlineStr"/>
@@ -32277,7 +32277,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0470</t>
+          <t>6a4af7f2ae633549bd0f046d</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -32290,12 +32290,12 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F594" t="inlineStr"/>
@@ -32373,7 +32373,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046d</t>
+          <t>6a4af7f2ae633549bd0f0470</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -32386,12 +32386,12 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F596" t="inlineStr"/>
@@ -32421,7 +32421,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0469</t>
+          <t>6a4af7f2ae633549bd0f0468</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -32434,12 +32434,12 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F597" t="inlineStr"/>
@@ -32469,7 +32469,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046c</t>
+          <t>6a4af7f2ae633549bd0f046f</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -32482,12 +32482,12 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F598" t="inlineStr"/>
@@ -32517,7 +32517,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046a</t>
+          <t>6a4af7f2ae633549bd0f046b</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -32530,12 +32530,12 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -32613,7 +32613,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046b</t>
+          <t>6a4af7f2ae633549bd0f046c</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -32626,12 +32626,12 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F601" t="inlineStr"/>
@@ -32661,7 +32661,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0478</t>
+          <t>6a4af7f2ae633549bd0f0474</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -32674,12 +32674,12 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F602" t="inlineStr"/>
@@ -32709,7 +32709,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0472</t>
+          <t>6a4af7f2ae633549bd0f0479</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -32722,12 +32722,12 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
@@ -32757,7 +32757,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0473</t>
+          <t>6a4af7f2ae633549bd0f047b</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -32770,12 +32770,12 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -32805,7 +32805,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0476</t>
+          <t>6a4af7f2ae633549bd0f047a</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -32818,12 +32818,12 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F605" t="inlineStr"/>
@@ -32853,7 +32853,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0477</t>
+          <t>6a4af7f2ae633549bd0f0478</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -32866,12 +32866,12 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
@@ -32901,7 +32901,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0475</t>
+          <t>6a4af7f2ae633549bd0f0472</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -32914,12 +32914,12 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -32949,7 +32949,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0474</t>
+          <t>6a4af7f2ae633549bd0f0473</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -32962,12 +32962,12 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
@@ -32997,7 +32997,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047b</t>
+          <t>6a4af7f2ae633549bd0f0476</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -33010,12 +33010,12 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F609" t="inlineStr"/>
@@ -33045,7 +33045,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0479</t>
+          <t>6a4af7f2ae633549bd0f0477</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -33058,12 +33058,12 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F610" t="inlineStr"/>
@@ -33093,7 +33093,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047a</t>
+          <t>6a4af7f2ae633549bd0f0475</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -33106,12 +33106,12 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -33189,7 +33189,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0484</t>
+          <t>6a4af7f2ae633549bd0f047e</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -33202,12 +33202,12 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F613" t="inlineStr"/>
@@ -33237,7 +33237,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0486</t>
+          <t>6a4af7f3ae633549bd0f0484</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -33250,12 +33250,12 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F614" t="inlineStr"/>
@@ -33285,7 +33285,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0480</t>
+          <t>6a4af7f2ae633549bd0f0483</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -33298,12 +33298,12 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -33333,7 +33333,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0485</t>
+          <t>6a4af7f2ae633549bd0f047d</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -33346,12 +33346,12 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F616" t="inlineStr"/>
@@ -33381,7 +33381,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0483</t>
+          <t>6a4af7f2ae633549bd0f047f</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -33394,12 +33394,12 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F617" t="inlineStr"/>
@@ -33429,7 +33429,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047d</t>
+          <t>6a4af7f2ae633549bd0f0482</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -33442,12 +33442,12 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -33477,7 +33477,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047e</t>
+          <t>6a4af7f3ae633549bd0f0486</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -33490,12 +33490,12 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -33525,7 +33525,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047f</t>
+          <t>6a4af7f3ae633549bd0f0485</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -33573,7 +33573,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0482</t>
+          <t>6a4af7f2ae633549bd0f0480</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -33586,12 +33586,12 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F621" t="inlineStr"/>
@@ -33669,7 +33669,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048b</t>
+          <t>6a4af7f3ae633549bd0f048c</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -33682,12 +33682,12 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F623" t="inlineStr"/>
@@ -33717,7 +33717,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048c</t>
+          <t>6a4af7f3ae633549bd0f0490</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -33730,12 +33730,12 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
@@ -33765,7 +33765,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0491</t>
+          <t>6a4af7f3ae633549bd0f048e</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -33778,12 +33778,12 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F625" t="inlineStr"/>
@@ -33813,7 +33813,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0489</t>
+          <t>6a4af7f3ae633549bd0f0488</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -33826,12 +33826,12 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F626" t="inlineStr"/>
@@ -33861,7 +33861,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048d</t>
+          <t>6a4af7f3ae633549bd0f0489</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -33874,12 +33874,12 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F627" t="inlineStr"/>
@@ -33909,7 +33909,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0488</t>
+          <t>6a4af7f3ae633549bd0f048f</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -33922,12 +33922,12 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F628" t="inlineStr"/>
@@ -33957,7 +33957,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048e</t>
+          <t>6a4af7f3ae633549bd0f048d</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -33970,12 +33970,12 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F629" t="inlineStr"/>
@@ -34005,7 +34005,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048f</t>
+          <t>6a4af7f3ae633549bd0f048b</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F630" t="inlineStr"/>
@@ -34053,7 +34053,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0490</t>
+          <t>6a4af7f3ae633549bd0f0491</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -34066,12 +34066,12 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F631" t="inlineStr"/>
@@ -34101,7 +34101,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0494</t>
+          <t>6a4af7f3ae633549bd0f0493</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -34114,12 +34114,12 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F632" t="inlineStr"/>
@@ -34149,7 +34149,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0497</t>
+          <t>6a4af7f3ae633549bd0f0494</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -34162,12 +34162,12 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F633" t="inlineStr"/>
@@ -34197,7 +34197,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049c</t>
+          <t>6a4af7f3ae633549bd0f0496</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -34210,12 +34210,12 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F634" t="inlineStr"/>
@@ -34245,7 +34245,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0498</t>
+          <t>6a4af7f3ae633549bd0f0497</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -34258,12 +34258,12 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F635" t="inlineStr"/>
@@ -34293,7 +34293,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0495</t>
+          <t>6a4af7f3ae633549bd0f0499</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -34306,12 +34306,12 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F636" t="inlineStr"/>
@@ -34437,7 +34437,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0493</t>
+          <t>6a4af7f3ae633549bd0f0498</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
@@ -34485,7 +34485,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0496</t>
+          <t>6a4af7f3ae633549bd0f049c</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -34498,12 +34498,12 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F640" t="inlineStr"/>
@@ -34533,7 +34533,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0499</t>
+          <t>6a4af7f3ae633549bd0f0495</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -34546,12 +34546,12 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F641" t="inlineStr"/>
@@ -34581,7 +34581,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a0</t>
+          <t>6a4af7f3ae633549bd0f049e</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -34594,12 +34594,12 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F642" t="inlineStr"/>
@@ -34629,7 +34629,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a2</t>
+          <t>6a4af7f3ae633549bd0f049f</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -34642,12 +34642,12 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
@@ -34677,7 +34677,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a3</t>
+          <t>6a4af7f3ae633549bd0f04a1</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -34690,12 +34690,12 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -34725,7 +34725,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a4</t>
+          <t>6a4af7f3ae633549bd0f04a5</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -34738,12 +34738,12 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F645" t="inlineStr"/>
@@ -34773,7 +34773,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a5</t>
+          <t>6a4af7f3ae633549bd0f04a6</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F646" t="inlineStr"/>
@@ -34821,7 +34821,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a1</t>
+          <t>6a4af7f3ae633549bd0f04a4</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -34834,12 +34834,12 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -34869,7 +34869,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049e</t>
+          <t>6a4af7f3ae633549bd0f04a0</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -34882,12 +34882,12 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -34917,7 +34917,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049f</t>
+          <t>6a4af7f3ae633549bd0f04a2</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -34930,12 +34930,12 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -34965,7 +34965,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a7</t>
+          <t>6a4af7f3ae633549bd0f04a3</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -34978,12 +34978,12 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F650" t="inlineStr"/>
@@ -35013,7 +35013,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a6</t>
+          <t>6a4af7f3ae633549bd0f04a7</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -35026,12 +35026,12 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F651" t="inlineStr"/>
@@ -35061,7 +35061,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ac</t>
+          <t>6a4af7f3ae633549bd0f04b2</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -35074,12 +35074,12 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -35109,7 +35109,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ae</t>
+          <t>6a4af7f3ae633549bd0f04a9</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -35122,12 +35122,12 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F653" t="inlineStr"/>
@@ -35157,7 +35157,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b2</t>
+          <t>6a4af7f3ae633549bd0f04aa</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -35170,12 +35170,12 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F654" t="inlineStr"/>
@@ -35205,7 +35205,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04aa</t>
+          <t>6a4af7f3ae633549bd0f04ad</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -35218,12 +35218,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F655" t="inlineStr"/>
@@ -35253,7 +35253,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a9</t>
+          <t>6a4af7f3ae633549bd0f04af</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -35266,12 +35266,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F656" t="inlineStr"/>
@@ -35349,7 +35349,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ad</t>
+          <t>6a4af7f3ae633549bd0f04b0</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -35362,12 +35362,12 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F658" t="inlineStr"/>
@@ -35397,7 +35397,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04af</t>
+          <t>6a4af7f3ae633549bd0f04ac</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -35410,12 +35410,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -35445,7 +35445,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b0</t>
+          <t>6a4af7f3ae633549bd0f04ae</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -35458,12 +35458,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F660" t="inlineStr"/>
@@ -35541,7 +35541,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b4</t>
+          <t>6a4af7f3ae633549bd0f04ba</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -35554,12 +35554,12 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F662" t="inlineStr"/>
@@ -35589,7 +35589,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b7</t>
+          <t>6a4af7f3ae633549bd0f04b9</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -35602,12 +35602,12 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F663" t="inlineStr"/>
@@ -35637,7 +35637,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bb</t>
+          <t>6a4af7f3ae633549bd0f04bd</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -35650,12 +35650,12 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F664" t="inlineStr"/>
@@ -35685,7 +35685,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ba</t>
+          <t>6a4af7f3ae633549bd0f04bb</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -35698,12 +35698,12 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F665" t="inlineStr"/>
@@ -35733,7 +35733,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b9</t>
+          <t>6a4af7f3ae633549bd0f04b6</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -35746,12 +35746,12 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F666" t="inlineStr"/>
@@ -35781,7 +35781,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bd</t>
+          <t>6a4af7f3ae633549bd0f04b8</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -35794,12 +35794,12 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F667" t="inlineStr"/>
@@ -35829,7 +35829,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b5</t>
+          <t>6a4af7f3ae633549bd0f04b4</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -35842,12 +35842,12 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F668" t="inlineStr"/>
@@ -35877,7 +35877,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bc</t>
+          <t>6a4af7f3ae633549bd0f04b7</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -35890,12 +35890,12 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
@@ -35925,7 +35925,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b6</t>
+          <t>6a4af7f3ae633549bd0f04b5</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -35938,12 +35938,12 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F670" t="inlineStr"/>
@@ -35973,7 +35973,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b8</t>
+          <t>6a4af7f3ae633549bd0f04bc</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -35986,12 +35986,12 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F671" t="inlineStr"/>
@@ -36021,7 +36021,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c1</t>
+          <t>6a4af7f3ae633549bd0f04c6</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -36034,12 +36034,12 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F672" t="inlineStr"/>
@@ -36069,7 +36069,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c4</t>
+          <t>6a4af7f3ae633549bd0f04bf</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -36082,12 +36082,12 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
@@ -36117,7 +36117,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c6</t>
+          <t>6a4af7f3ae633549bd0f04c7</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -36130,12 +36130,12 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F674" t="inlineStr"/>
@@ -36165,7 +36165,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c7</t>
+          <t>6a4af7f3ae633549bd0f04c4</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -36178,12 +36178,12 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F675" t="inlineStr"/>
@@ -36213,7 +36213,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bf</t>
+          <t>6a4af7f3ae633549bd0f04c8</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -36226,12 +36226,12 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -36261,7 +36261,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c0</t>
+          <t>6a4af7f3ae633549bd0f04c1</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -36274,12 +36274,12 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
@@ -36309,7 +36309,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c2</t>
+          <t>6a4af7f3ae633549bd0f04c3</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -36322,12 +36322,12 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F678" t="inlineStr"/>
@@ -36357,7 +36357,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c5</t>
+          <t>6a4af7f3ae633549bd0f04c2</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -36370,12 +36370,12 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F679" t="inlineStr"/>
@@ -36405,7 +36405,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c8</t>
+          <t>6a4af7f3ae633549bd0f04c0</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -36418,12 +36418,12 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F680" t="inlineStr"/>
@@ -36453,7 +36453,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c3</t>
+          <t>6a4af7f3ae633549bd0f04c5</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -36466,12 +36466,12 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
@@ -36501,7 +36501,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d1</t>
+          <t>6a4af7f4ae633549bd0f04ca</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -36514,12 +36514,12 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F682" t="inlineStr"/>
@@ -36549,7 +36549,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cd</t>
+          <t>6a4af7f4ae633549bd0f04ce</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -36562,12 +36562,12 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F683" t="inlineStr"/>
@@ -36597,7 +36597,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cf</t>
+          <t>6a4af7f4ae633549bd0f04cb</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -36610,12 +36610,12 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F684" t="inlineStr"/>
@@ -36645,7 +36645,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d3</t>
+          <t>6a4af7f4ae633549bd0f04cc</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -36658,12 +36658,12 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F685" t="inlineStr"/>
@@ -36693,7 +36693,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ce</t>
+          <t>6a4af7f4ae633549bd0f04d0</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -36706,12 +36706,12 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F686" t="inlineStr"/>
@@ -36741,7 +36741,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d0</t>
+          <t>6a4af7f4ae633549bd0f04d2</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -36754,12 +36754,12 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F687" t="inlineStr"/>
@@ -36789,7 +36789,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d2</t>
+          <t>6a4af7f4ae633549bd0f04d1</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -36802,12 +36802,12 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F688" t="inlineStr"/>
@@ -36837,7 +36837,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ca</t>
+          <t>6a4af7f4ae633549bd0f04cd</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -36850,12 +36850,12 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F689" t="inlineStr"/>
@@ -36885,7 +36885,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cb</t>
+          <t>6a4af7f4ae633549bd0f04cf</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -36898,12 +36898,12 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F690" t="inlineStr"/>
@@ -36933,7 +36933,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cc</t>
+          <t>6a4af7f4ae633549bd0f04d3</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -36946,12 +36946,12 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F691" t="inlineStr"/>
@@ -36981,7 +36981,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04db</t>
+          <t>6a4af7f4ae633549bd0f04da</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -36994,12 +36994,12 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F692" t="inlineStr"/>
@@ -37029,7 +37029,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d8</t>
+          <t>6a4af7f4ae633549bd0f04dd</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -37042,12 +37042,12 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F693" t="inlineStr"/>
@@ -37077,7 +37077,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d9</t>
+          <t>6a4af7f4ae633549bd0f04d7</t>
         </is>
       </c>
       <c r="B694" t="n">
@@ -37090,12 +37090,12 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F694" t="inlineStr"/>
@@ -37125,7 +37125,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dc</t>
+          <t>6a4af7f4ae633549bd0f04de</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -37138,12 +37138,12 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F695" t="inlineStr"/>
@@ -37173,7 +37173,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d6</t>
+          <t>6a4af7f4ae633549bd0f04db</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -37186,12 +37186,12 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F696" t="inlineStr"/>
@@ -37221,7 +37221,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d5</t>
+          <t>6a4af7f4ae633549bd0f04d8</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -37234,12 +37234,12 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F697" t="inlineStr"/>
@@ -37269,7 +37269,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04da</t>
+          <t>6a4af7f4ae633549bd0f04d9</t>
         </is>
       </c>
       <c r="B698" t="n">
@@ -37282,12 +37282,12 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F698" t="inlineStr"/>
@@ -37317,7 +37317,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dd</t>
+          <t>6a4af7f4ae633549bd0f04dc</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -37330,12 +37330,12 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F699" t="inlineStr"/>
@@ -37365,7 +37365,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04de</t>
+          <t>6a4af7f4ae633549bd0f04d6</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -37378,12 +37378,12 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F700" t="inlineStr"/>
@@ -37413,7 +37413,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d7</t>
+          <t>6a4af7f4ae633549bd0f04d5</t>
         </is>
       </c>
       <c r="B701" t="n">
@@ -37426,12 +37426,12 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F701" t="inlineStr"/>
@@ -37509,7 +37509,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e6</t>
+          <t>6a4af7f4ae633549bd0f04e2</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -37522,12 +37522,12 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F703" t="inlineStr"/>
@@ -37605,7 +37605,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e2</t>
+          <t>6a4af7f4ae633549bd0f04e6</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -37618,12 +37618,12 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
@@ -37653,7 +37653,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e5</t>
+          <t>6a4af7f4ae633549bd0f04e7</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -37666,12 +37666,12 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F706" t="inlineStr"/>
@@ -37701,7 +37701,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e7</t>
+          <t>6a4af7f4ae633549bd0f04e8</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -37714,12 +37714,12 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F707" t="inlineStr"/>
@@ -37749,7 +37749,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e8</t>
+          <t>6a4af7f4ae633549bd0f04e9</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -37762,12 +37762,12 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F708" t="inlineStr"/>
@@ -37797,7 +37797,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e9</t>
+          <t>6a4af7f4ae633549bd0f04e0</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -37810,12 +37810,12 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F709" t="inlineStr"/>
@@ -37893,7 +37893,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e0</t>
+          <t>6a4af7f4ae633549bd0f04e5</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -37906,12 +37906,12 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F711" t="inlineStr"/>
@@ -37941,7 +37941,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f1</t>
+          <t>6a4af7f4ae633549bd0f04f3</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -37954,12 +37954,12 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F712" t="inlineStr"/>
@@ -37989,7 +37989,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f2</t>
+          <t>6a4af7f4ae633549bd0f04eb</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -38002,12 +38002,12 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F713" t="inlineStr"/>
@@ -38037,7 +38037,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f3</t>
+          <t>6a4af7f4ae633549bd0f04f0</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -38050,12 +38050,12 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -38085,7 +38085,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ed</t>
+          <t>6a4af7f4ae633549bd0f04f4</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -38098,12 +38098,12 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F715" t="inlineStr"/>
@@ -38133,7 +38133,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ec</t>
+          <t>6a4af7f4ae633549bd0f04ee</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -38146,12 +38146,12 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F716" t="inlineStr"/>
@@ -38229,7 +38229,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ee</t>
+          <t>6a4af7f4ae633549bd0f04ec</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -38242,12 +38242,12 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F718" t="inlineStr"/>
@@ -38277,7 +38277,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f0</t>
+          <t>6a4af7f4ae633549bd0f04ed</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -38290,12 +38290,12 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F719" t="inlineStr"/>
@@ -38325,7 +38325,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04eb</t>
+          <t>6a4af7f4ae633549bd0f04f2</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -38338,12 +38338,12 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F720" t="inlineStr"/>
@@ -38373,7 +38373,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f4</t>
+          <t>6a4af7f4ae633549bd0f04f1</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -38386,12 +38386,12 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F721" t="inlineStr"/>
@@ -38421,7 +38421,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fd</t>
+          <t>6a4af7f4ae633549bd0f04fb</t>
         </is>
       </c>
       <c r="B722" t="n">
@@ -38434,12 +38434,12 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F722" t="inlineStr"/>
@@ -38469,7 +38469,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f9</t>
+          <t>6a4af7f4ae633549bd0f04fd</t>
         </is>
       </c>
       <c r="B723" t="n">
@@ -38482,12 +38482,12 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F723" t="inlineStr"/>
@@ -38517,7 +38517,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fc</t>
+          <t>6a4af7f4ae633549bd0f04f6</t>
         </is>
       </c>
       <c r="B724" t="n">
@@ -38530,12 +38530,12 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F724" t="inlineStr"/>
@@ -38565,7 +38565,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fe</t>
+          <t>6a4af7f4ae633549bd0f04f7</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -38578,12 +38578,12 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
@@ -38613,7 +38613,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ff</t>
+          <t>6a4af7f4ae633549bd0f04f8</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -38626,12 +38626,12 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F726" t="inlineStr"/>
@@ -38661,7 +38661,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f6</t>
+          <t>6a4af7f4ae633549bd0f04fa</t>
         </is>
       </c>
       <c r="B727" t="n">
@@ -38674,12 +38674,12 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F727" t="inlineStr"/>
@@ -38709,7 +38709,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f7</t>
+          <t>6a4af7f4ae633549bd0f04ff</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -38722,12 +38722,12 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F728" t="inlineStr"/>
@@ -38757,7 +38757,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f8</t>
+          <t>6a4af7f4ae633549bd0f04fe</t>
         </is>
       </c>
       <c r="B729" t="n">
@@ -38770,12 +38770,12 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F729" t="inlineStr"/>
@@ -38805,7 +38805,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fa</t>
+          <t>6a4af7f4ae633549bd0f04f9</t>
         </is>
       </c>
       <c r="B730" t="n">
@@ -38818,12 +38818,12 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F730" t="inlineStr"/>
@@ -38853,7 +38853,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fb</t>
+          <t>6a4af7f4ae633549bd0f04fc</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -38866,12 +38866,12 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F731" t="inlineStr"/>
@@ -38901,7 +38901,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0501</t>
+          <t>6a4af7f4ae633549bd0f0505</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -38914,12 +38914,12 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F732" t="inlineStr"/>
@@ -38949,7 +38949,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0503</t>
+          <t>6a4af7f4ae633549bd0f0508</t>
         </is>
       </c>
       <c r="B733" t="n">
@@ -38962,12 +38962,12 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F733" t="inlineStr"/>
@@ -38997,7 +38997,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0508</t>
+          <t>6a4af7f4ae633549bd0f0509</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -39010,12 +39010,12 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
@@ -39045,7 +39045,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0507</t>
+          <t>6a4af7f4ae633549bd0f0504</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -39058,12 +39058,12 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -39093,7 +39093,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0502</t>
+          <t>6a4af7f4ae633549bd0f0506</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -39106,12 +39106,12 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
@@ -39141,7 +39141,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0509</t>
+          <t>6a4af7f4ae633549bd0f0503</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -39154,12 +39154,12 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F737" t="inlineStr"/>
@@ -39189,7 +39189,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0505</t>
+          <t>6a4af7f4ae633549bd0f0507</t>
         </is>
       </c>
       <c r="B738" t="n">
@@ -39202,12 +39202,12 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F738" t="inlineStr"/>
@@ -39237,7 +39237,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0506</t>
+          <t>6a4af7f4ae633549bd0f0501</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -39250,12 +39250,12 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F739" t="inlineStr"/>
@@ -39333,7 +39333,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0504</t>
+          <t>6a4af7f4ae633549bd0f0502</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -39346,12 +39346,12 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F741" t="inlineStr"/>
@@ -39381,7 +39381,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050e</t>
+          <t>6a4af7f5ae633549bd0f0511</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -39394,12 +39394,12 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F742" t="inlineStr"/>
@@ -39429,7 +39429,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0514</t>
+          <t>6a4af7f5ae633549bd0f0513</t>
         </is>
       </c>
       <c r="B743" t="n">
@@ -39442,12 +39442,12 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F743" t="inlineStr"/>
@@ -39477,7 +39477,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0513</t>
+          <t>6a4af7f5ae633549bd0f0512</t>
         </is>
       </c>
       <c r="B744" t="n">
@@ -39490,12 +39490,12 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F744" t="inlineStr"/>
@@ -39573,7 +39573,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0512</t>
+          <t>6a4af7f5ae633549bd0f0514</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -39586,12 +39586,12 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F746" t="inlineStr"/>
@@ -39621,7 +39621,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050d</t>
+          <t>6a4af7f5ae633549bd0f050e</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -39634,12 +39634,12 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F747" t="inlineStr"/>
@@ -39669,7 +39669,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0511</t>
+          <t>6a4af7f5ae633549bd0f050f</t>
         </is>
       </c>
       <c r="B748" t="n">
@@ -39682,12 +39682,12 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F748" t="inlineStr"/>
@@ -39717,7 +39717,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0515</t>
+          <t>6a4af7f4ae633549bd0f050c</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -39730,12 +39730,12 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
@@ -39765,7 +39765,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050c</t>
+          <t>6a4af7f4ae633549bd0f050d</t>
         </is>
       </c>
       <c r="B750" t="n">
@@ -39778,12 +39778,12 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F750" t="inlineStr"/>
@@ -39813,7 +39813,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050f</t>
+          <t>6a4af7f5ae633549bd0f0515</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -39826,12 +39826,12 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F751" t="inlineStr"/>
@@ -39909,7 +39909,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051b</t>
+          <t>6a4af7f5ae633549bd0f051d</t>
         </is>
       </c>
       <c r="B753" t="n">
@@ -39922,12 +39922,12 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F753" t="inlineStr"/>
@@ -39957,7 +39957,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051d</t>
+          <t>6a4af7f5ae633549bd0f051e</t>
         </is>
       </c>
       <c r="B754" t="n">
@@ -39970,12 +39970,12 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F754" t="inlineStr"/>
@@ -40005,7 +40005,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051c</t>
+          <t>6a4af7f5ae633549bd0f0518</t>
         </is>
       </c>
       <c r="B755" t="n">
@@ -40018,12 +40018,12 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F755" t="inlineStr"/>
@@ -40053,7 +40053,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051e</t>
+          <t>6a4af7f5ae633549bd0f051a</t>
         </is>
       </c>
       <c r="B756" t="n">
@@ -40066,12 +40066,12 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F756" t="inlineStr"/>
@@ -40101,7 +40101,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051f</t>
+          <t>6a4af7f5ae633549bd0f0519</t>
         </is>
       </c>
       <c r="B757" t="n">
@@ -40114,12 +40114,12 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F757" t="inlineStr"/>
@@ -40149,7 +40149,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0519</t>
+          <t>6a4af7f5ae633549bd0f0520</t>
         </is>
       </c>
       <c r="B758" t="n">
@@ -40162,12 +40162,12 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F758" t="inlineStr"/>
@@ -40197,7 +40197,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0520</t>
+          <t>6a4af7f5ae633549bd0f051f</t>
         </is>
       </c>
       <c r="B759" t="n">
@@ -40210,12 +40210,12 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F759" t="inlineStr"/>
@@ -40245,7 +40245,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0518</t>
+          <t>6a4af7f5ae633549bd0f051c</t>
         </is>
       </c>
       <c r="B760" t="n">
@@ -40258,12 +40258,12 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F760" t="inlineStr"/>
@@ -40293,7 +40293,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051a</t>
+          <t>6a4af7f5ae633549bd0f051b</t>
         </is>
       </c>
       <c r="B761" t="n">
@@ -40306,12 +40306,12 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>

--- a/datos/maestros/md_partidos.xlsx
+++ b/datos/maestros/md_partidos.xlsx
@@ -21773,7 +21773,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b7</t>
+          <t>6a4af7f0ae633549bd0f03ba</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -21786,29 +21786,29 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="inlineStr"/>
       <c r="H382" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
@@ -21821,7 +21821,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bb</t>
+          <t>6a4af7f0ae633549bd0f03be</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -21834,29 +21834,29 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
@@ -21869,7 +21869,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bc</t>
+          <t>6a4af7f0ae633549bd0f03bb</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -21882,29 +21882,29 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="inlineStr"/>
       <c r="H384" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
@@ -21917,7 +21917,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03be</t>
+          <t>6a4af7f0ae633549bd0f03bc</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -21930,19 +21930,19 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -21965,7 +21965,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b8</t>
+          <t>6a4af7f0ae633549bd0f03c0</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -21978,29 +21978,33 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
-        </is>
-      </c>
-      <c r="F386" t="inlineStr"/>
-      <c r="G386" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000d9</t>
+        </is>
+      </c>
+      <c r="F386" t="n">
+        <v>0</v>
+      </c>
+      <c r="G386" t="n">
+        <v>0</v>
+      </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
@@ -22008,12 +22012,16 @@
           <t>closed</t>
         </is>
       </c>
-      <c r="L386" t="inlineStr"/>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b9</t>
+          <t>6a4af7f0ae633549bd0f03b8</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -22026,12 +22034,12 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F387" t="inlineStr"/>
@@ -22043,12 +22051,12 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
@@ -22061,7 +22069,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c0</t>
+          <t>6a4af7f0ae633549bd0f03bf</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -22074,50 +22082,42 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
-        </is>
-      </c>
-      <c r="F388" t="n">
-        <v>0</v>
-      </c>
-      <c r="G388" t="n">
-        <v>0</v>
-      </c>
+          <t>504e581e4d8bec9a670000d0</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="J388" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
       <c r="K388" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="L388" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="L388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bf</t>
+          <t>6a4af7f0ae633549bd0f03b9</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -22130,29 +22130,29 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
@@ -22165,7 +22165,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ba</t>
+          <t>6a4af7f0ae633549bd0f03b7</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -22178,29 +22178,29 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
@@ -22261,7 +22261,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0385</t>
+          <t>6a4af7efae633549bd0f0387</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -22274,33 +22274,33 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F392" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G392" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
@@ -22317,7 +22317,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0386</t>
+          <t>6a4af7efae633549bd0f0389</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -22330,33 +22330,33 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F393" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G393" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
@@ -22373,7 +22373,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0382</t>
+          <t>6a4af7efae633549bd0f0383</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -22386,20 +22386,20 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F394" t="n">
+        <v>1</v>
+      </c>
+      <c r="G394" t="n">
         <v>2</v>
       </c>
-      <c r="G394" t="n">
-        <v>0</v>
-      </c>
       <c r="H394" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -22407,12 +22407,12 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
@@ -22429,7 +22429,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0381</t>
+          <t>6a4af7efae633549bd0f0384</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -22442,23 +22442,23 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G395" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -22485,7 +22485,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0380</t>
+          <t>6a4af7efae633549bd0f0385</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -22498,12 +22498,12 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F396" t="n">
@@ -22514,17 +22514,17 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
@@ -22597,7 +22597,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0383</t>
+          <t>6a4af7efae633549bd0f0382</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -22610,19 +22610,19 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F398" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G398" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
@@ -22631,12 +22631,12 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
@@ -22653,7 +22653,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0384</t>
+          <t>6a4af7efae633549bd0f0381</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -22666,23 +22666,23 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F399" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G399" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -22709,7 +22709,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0389</t>
+          <t>6a4af7efae633549bd0f0386</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -22722,33 +22722,33 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F400" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G400" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
@@ -22765,7 +22765,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0387</t>
+          <t>6a4af7efae633549bd0f0380</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -22778,33 +22778,33 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F401" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
@@ -22877,7 +22877,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0390</t>
+          <t>6a4af7efae633549bd0f0391</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -22890,33 +22890,33 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F403" t="n">
         <v>1</v>
       </c>
       <c r="G403" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
@@ -22933,7 +22933,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0391</t>
+          <t>6a4af7efae633549bd0f0390</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -22946,33 +22946,33 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F404" t="n">
         <v>1</v>
       </c>
       <c r="G404" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
           <t>19:30</t>
-        </is>
-      </c>
-      <c r="J404" t="inlineStr">
-        <is>
-          <t>21:30</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
@@ -23269,7 +23269,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0393</t>
+          <t>6a4af7efae633549bd0f0394</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -23282,33 +23282,33 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G410" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
@@ -23325,7 +23325,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0394</t>
+          <t>6a4af7efae633549bd0f0393</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -23338,33 +23338,33 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
@@ -23381,7 +23381,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0398</t>
+          <t>6a4af7efae633549bd0f0396</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -23394,23 +23394,23 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F412" t="n">
+        <v>1</v>
+      </c>
+      <c r="G412" t="n">
         <v>0</v>
       </c>
-      <c r="G412" t="n">
-        <v>2</v>
-      </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -23437,7 +23437,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039a</t>
+          <t>6a4af7efae633549bd0f0399</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -23450,33 +23450,33 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G413" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
@@ -23493,7 +23493,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039c</t>
+          <t>6a4af7efae633549bd0f039e</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -23506,23 +23506,23 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G414" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -23549,7 +23549,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0399</t>
+          <t>6a4af7efae633549bd0f039a</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -23562,33 +23562,33 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G415" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
@@ -23605,7 +23605,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0396</t>
+          <t>6a4af7efae633549bd0f039c</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -23618,19 +23618,19 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G416" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
@@ -23639,12 +23639,12 @@
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
@@ -23661,7 +23661,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039e</t>
+          <t>6a4af7efae633549bd0f0397</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -23674,33 +23674,33 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F417" t="n">
+        <v>5</v>
+      </c>
+      <c r="G417" t="n">
         <v>2</v>
       </c>
-      <c r="G417" t="n">
-        <v>1</v>
-      </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
@@ -23717,7 +23717,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039b</t>
+          <t>6a4af7efae633549bd0f0398</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -23730,33 +23730,33 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F418" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G418" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
@@ -23829,7 +23829,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039f</t>
+          <t>6a4af7efae633549bd0f039b</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -23842,33 +23842,33 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F420" t="n">
         <v>1</v>
       </c>
       <c r="G420" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
           <t>19:30</t>
-        </is>
-      </c>
-      <c r="J420" t="inlineStr">
-        <is>
-          <t>21:30</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
@@ -23885,7 +23885,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0397</t>
+          <t>6a4af7efae633549bd0f039f</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -23898,23 +23898,23 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F421" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G421" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -23941,7 +23941,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a7</t>
+          <t>6a4af7efae633549bd0f03a3</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -23954,33 +23954,33 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G422" t="n">
         <v>0</v>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
@@ -23997,7 +23997,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03aa</t>
+          <t>6a4af7efae633549bd0f03a4</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -24010,12 +24010,12 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -24026,17 +24026,17 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
@@ -24053,7 +24053,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a2</t>
+          <t>6a4af7efae633549bd0f03a5</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -24066,33 +24066,33 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F424" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G424" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
@@ -24109,7 +24109,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a3</t>
+          <t>6a4af7efae633549bd0f03a6</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -24122,33 +24122,33 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F425" t="n">
         <v>1</v>
       </c>
       <c r="G425" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
           <t>19:00</t>
-        </is>
-      </c>
-      <c r="J425" t="inlineStr">
-        <is>
-          <t>21:00</t>
         </is>
       </c>
       <c r="K425" t="inlineStr">
@@ -24165,7 +24165,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a5</t>
+          <t>6a4af7efae633549bd0f03a8</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -24178,33 +24178,33 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F426" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G426" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
@@ -24221,7 +24221,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a9</t>
+          <t>6a4af7efae633549bd0f03aa</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -24234,33 +24234,33 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G427" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
@@ -24277,7 +24277,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a1</t>
+          <t>6a4af7efae633549bd0f03a9</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -24290,20 +24290,20 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F428" t="n">
+        <v>0</v>
+      </c>
+      <c r="G428" t="n">
         <v>5</v>
       </c>
-      <c r="G428" t="n">
-        <v>2</v>
-      </c>
       <c r="H428" t="inlineStr">
         <is>
           <t>2026-09-06</t>
@@ -24311,12 +24311,12 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
@@ -24333,7 +24333,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a8</t>
+          <t>6a4af7efae633549bd0f03a1</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -24346,23 +24346,23 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G429" t="n">
         <v>2</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -24389,7 +24389,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a4</t>
+          <t>6a4af7efae633549bd0f03a7</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -24402,33 +24402,33 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G430" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
@@ -24445,7 +24445,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a6</t>
+          <t>6a4af7efae633549bd0f03a2</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -24458,33 +24458,33 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G431" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
@@ -24501,7 +24501,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ac</t>
+          <t>6a4af7efae633549bd0f03b0</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -24514,12 +24514,12 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -24531,17 +24531,17 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>running</t>
         </is>
       </c>
       <c r="L432" t="inlineStr"/>
@@ -24549,7 +24549,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b5</t>
+          <t>6a4af7efae633549bd0f03ad</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -24562,34 +24562,34 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr"/>
       <c r="H433" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>running</t>
         </is>
       </c>
       <c r="L433" t="inlineStr"/>
@@ -24597,7 +24597,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b3</t>
+          <t>6a4af7efae633549bd0f03b2</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -24610,19 +24610,19 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr"/>
       <c r="H434" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -24637,7 +24637,7 @@
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>running</t>
         </is>
       </c>
       <c r="L434" t="inlineStr"/>
@@ -24645,7 +24645,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ae</t>
+          <t>6a4af7efae633549bd0f03af</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -24658,12 +24658,12 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F435" t="inlineStr"/>
@@ -24675,17 +24675,17 @@
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>running</t>
         </is>
       </c>
       <c r="L435" t="inlineStr"/>
@@ -24693,7 +24693,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b0</t>
+          <t>6a4af7efae633549bd0f03b1</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -24706,12 +24706,12 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
@@ -24723,17 +24723,17 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>running</t>
         </is>
       </c>
       <c r="L436" t="inlineStr"/>
@@ -24741,7 +24741,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ad</t>
+          <t>6a4af7efae633549bd0f03ac</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -24754,34 +24754,34 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr"/>
       <c r="H437" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>running</t>
         </is>
       </c>
       <c r="L437" t="inlineStr"/>
@@ -24789,7 +24789,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b2</t>
+          <t>6a4af7efae633549bd0f03b3</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -24802,19 +24802,19 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr"/>
       <c r="H438" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -24829,7 +24829,7 @@
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>running</t>
         </is>
       </c>
       <c r="L438" t="inlineStr"/>
@@ -24837,7 +24837,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b1</t>
+          <t>6a4af7f0ae633549bd0f03b5</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -24850,34 +24850,34 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr"/>
       <c r="H439" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>running</t>
         </is>
       </c>
       <c r="L439" t="inlineStr"/>
@@ -24885,7 +24885,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03af</t>
+          <t>6a4af7efae633549bd0f03b4</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -24898,42 +24898,50 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
-        </is>
-      </c>
-      <c r="F440" t="inlineStr"/>
-      <c r="G440" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000cb</t>
+        </is>
+      </c>
+      <c r="F440" t="n">
+        <v>1</v>
+      </c>
+      <c r="G440" t="n">
+        <v>0</v>
+      </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>next</t>
-        </is>
-      </c>
-      <c r="L440" t="inlineStr"/>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b4</t>
+          <t>6a4af7efae633549bd0f03ae</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -24946,34 +24954,34 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
       <c r="G441" t="inlineStr"/>
       <c r="H441" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>running</t>
         </is>
       </c>
       <c r="L441" t="inlineStr"/>
@@ -24981,7 +24989,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cb</t>
+          <t>6a4af7f0ae633549bd0f03c7</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -24994,12 +25002,12 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -25011,17 +25019,17 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L442" t="inlineStr"/>
@@ -25029,7 +25037,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c8</t>
+          <t>6a4af7f0ae633549bd0f03c2</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -25042,12 +25050,12 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
@@ -25059,17 +25067,17 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L443" t="inlineStr"/>
@@ -25117,7 +25125,7 @@
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L444" t="inlineStr"/>
@@ -25125,7 +25133,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c2</t>
+          <t>6a4af7f0ae633549bd0f03c8</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -25138,12 +25146,12 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
@@ -25155,17 +25163,17 @@
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L445" t="inlineStr"/>
@@ -25173,7 +25181,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c3</t>
+          <t>6a4af7f0ae633549bd0f03c9</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -25186,34 +25194,34 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
       <c r="G446" t="inlineStr"/>
       <c r="H446" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L446" t="inlineStr"/>
@@ -25261,7 +25269,7 @@
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L447" t="inlineStr"/>
@@ -25269,7 +25277,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c9</t>
+          <t>6a4af7f0ae633549bd0f03cb</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -25282,34 +25290,34 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
       <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L448" t="inlineStr"/>
@@ -25317,7 +25325,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c6</t>
+          <t>6a4af7f0ae633549bd0f03c3</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -25330,34 +25338,34 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
       <c r="G449" t="inlineStr"/>
       <c r="H449" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K449" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L449" t="inlineStr"/>
@@ -25365,7 +25373,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c7</t>
+          <t>6a4af7f0ae633549bd0f03ca</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -25378,12 +25386,12 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
@@ -25395,17 +25403,17 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K450" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L450" t="inlineStr"/>
@@ -25413,7 +25421,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ca</t>
+          <t>6a4af7f0ae633549bd0f03c6</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -25426,19 +25434,19 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr"/>
       <c r="H451" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -25453,7 +25461,7 @@
       </c>
       <c r="K451" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L451" t="inlineStr"/>
@@ -25509,7 +25517,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d1</t>
+          <t>6a4af7f0ae633549bd0f03d4</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -25522,12 +25530,12 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
@@ -25557,7 +25565,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d2</t>
+          <t>6a4af7f0ae633549bd0f03cd</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -25570,12 +25578,12 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F454" t="inlineStr"/>
@@ -25605,7 +25613,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d3</t>
+          <t>6a4af7f0ae633549bd0f03cf</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -25618,12 +25626,12 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -25653,7 +25661,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d5</t>
+          <t>6a4af7f0ae633549bd0f03d0</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -25666,12 +25674,12 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
@@ -25701,7 +25709,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cd</t>
+          <t>6a4af7f0ae633549bd0f03d5</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -25714,12 +25722,12 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -25749,7 +25757,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cf</t>
+          <t>6a4af7f0ae633549bd0f03d1</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -25762,12 +25770,12 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -25797,7 +25805,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d0</t>
+          <t>6a4af7f0ae633549bd0f03d2</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -25810,12 +25818,12 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -25845,7 +25853,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d4</t>
+          <t>6a4af7f0ae633549bd0f03d3</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -25858,12 +25866,12 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
@@ -25941,7 +25949,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e1</t>
+          <t>6a4af7f0ae633549bd0f03db</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -25954,12 +25962,12 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
@@ -25989,7 +25997,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d8</t>
+          <t>6a4af7f0ae633549bd0f03dd</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -26002,12 +26010,12 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -26037,7 +26045,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03db</t>
+          <t>6a4af7f0ae633549bd0f03d9</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -26050,12 +26058,12 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -26085,7 +26093,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dd</t>
+          <t>6a4af7f0ae633549bd0f03da</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -26098,12 +26106,12 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
@@ -26133,7 +26141,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03df</t>
+          <t>6a4af7f0ae633549bd0f03de</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -26146,12 +26154,12 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F466" t="inlineStr"/>
@@ -26181,7 +26189,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03da</t>
+          <t>6a4af7f0ae633549bd0f03e0</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -26194,12 +26202,12 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -26229,7 +26237,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e0</t>
+          <t>6a4af7f0ae633549bd0f03df</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -26242,12 +26250,12 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F468" t="inlineStr"/>
@@ -26277,7 +26285,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d9</t>
+          <t>6a4af7f0ae633549bd0f03dc</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -26290,12 +26298,12 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F469" t="inlineStr"/>
@@ -26325,7 +26333,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03de</t>
+          <t>6a4af7f0ae633549bd0f03d8</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -26338,12 +26346,12 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
@@ -26373,7 +26381,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dc</t>
+          <t>6a4af7f0ae633549bd0f03e1</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -26386,12 +26394,12 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -26421,7 +26429,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ea</t>
+          <t>6a4af7f0ae633549bd0f03e4</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -26434,12 +26442,12 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -26469,7 +26477,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e5</t>
+          <t>6a4af7f0ae633549bd0f03e6</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -26482,12 +26490,12 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -26499,12 +26507,12 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
@@ -26517,7 +26525,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e9</t>
+          <t>6a4af7f0ae633549bd0f03ec</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -26530,12 +26538,12 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -26565,7 +26573,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e3</t>
+          <t>6a4af7f0ae633549bd0f03e7</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -26578,12 +26586,12 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -26613,7 +26621,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ec</t>
+          <t>6a4af7f0ae633549bd0f03e8</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -26626,12 +26634,12 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
@@ -26661,7 +26669,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e4</t>
+          <t>6a4af7f0ae633549bd0f03eb</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -26674,12 +26682,12 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
@@ -26709,7 +26717,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e6</t>
+          <t>6a4af7f0ae633549bd0f03e5</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -26722,12 +26730,12 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -26739,12 +26747,12 @@
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K478" t="inlineStr">
@@ -26757,7 +26765,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e8</t>
+          <t>6a4af7f0ae633549bd0f03ea</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -26770,12 +26778,12 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
@@ -26805,7 +26813,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e7</t>
+          <t>6a4af7f0ae633549bd0f03e9</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -26818,12 +26826,12 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -26853,7 +26861,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03eb</t>
+          <t>6a4af7f0ae633549bd0f03e3</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -26866,12 +26874,12 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
@@ -26901,7 +26909,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ef</t>
+          <t>6a4af7f0ae633549bd0f03f3</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -26914,12 +26922,12 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -26949,7 +26957,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f0</t>
+          <t>6a4af7f0ae633549bd0f03ee</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -26962,12 +26970,12 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -26997,7 +27005,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f1</t>
+          <t>6a4af7f0ae633549bd0f03f4</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -27010,12 +27018,12 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F484" t="inlineStr"/>
@@ -27045,7 +27053,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f7</t>
+          <t>6a4af7f0ae633549bd0f03f6</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -27058,12 +27066,12 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -27093,7 +27101,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f6</t>
+          <t>6a4af7f0ae633549bd0f03f2</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -27106,12 +27114,12 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
@@ -27141,7 +27149,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ee</t>
+          <t>6a4af7f0ae633549bd0f03f5</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -27154,12 +27162,12 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F487" t="inlineStr"/>
@@ -27189,7 +27197,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f3</t>
+          <t>6a4af7f0ae633549bd0f03ef</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -27202,12 +27210,12 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -27237,7 +27245,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f4</t>
+          <t>6a4af7f0ae633549bd0f03f0</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -27250,12 +27258,12 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -27285,7 +27293,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f2</t>
+          <t>6a4af7f0ae633549bd0f03f1</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -27298,12 +27306,12 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -27333,7 +27341,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f5</t>
+          <t>6a4af7f0ae633549bd0f03f7</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -27346,12 +27354,12 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -27381,7 +27389,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f9</t>
+          <t>6a4af7f1ae633549bd0f0402</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -27394,12 +27402,12 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
@@ -27429,7 +27437,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fc</t>
+          <t>6a4af7f0ae633549bd0f03fa</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -27442,12 +27450,12 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
@@ -27477,7 +27485,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03ff</t>
+          <t>6a4af7f1ae633549bd0f03fc</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -27490,12 +27498,12 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F494" t="inlineStr"/>
@@ -27525,7 +27533,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fe</t>
+          <t>6a4af7f1ae633549bd0f0401</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -27538,12 +27546,12 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -27573,7 +27581,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0400</t>
+          <t>6a4af7f0ae633549bd0f03f9</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -27586,12 +27594,12 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -27621,7 +27629,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fb</t>
+          <t>6a4af7f1ae633549bd0f03fd</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -27634,12 +27642,12 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F497" t="inlineStr"/>
@@ -27669,7 +27677,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0402</t>
+          <t>6a4af7f1ae633549bd0f03fe</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -27682,12 +27690,12 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
@@ -27717,7 +27725,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0401</t>
+          <t>6a4af7f1ae633549bd0f0400</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -27730,12 +27738,12 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -27765,7 +27773,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fa</t>
+          <t>6a4af7f1ae633549bd0f03ff</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -27778,12 +27786,12 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -27813,7 +27821,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fd</t>
+          <t>6a4af7f0ae633549bd0f03fb</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -27826,12 +27834,12 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -27861,7 +27869,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040a</t>
+          <t>6a4af7f1ae633549bd0f040c</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -27874,12 +27882,12 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -27909,7 +27917,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0406</t>
+          <t>6a4af7f1ae633549bd0f0407</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -27922,12 +27930,12 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -28005,7 +28013,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040c</t>
+          <t>6a4af7f1ae633549bd0f0404</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -28018,12 +28026,12 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -28053,7 +28061,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0408</t>
+          <t>6a4af7f1ae633549bd0f0405</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -28066,12 +28074,12 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F506" t="inlineStr"/>
@@ -28101,7 +28109,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040b</t>
+          <t>6a4af7f1ae633549bd0f0408</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -28114,12 +28122,12 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F507" t="inlineStr"/>
@@ -28149,7 +28157,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0404</t>
+          <t>6a4af7f1ae633549bd0f0409</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -28162,12 +28170,12 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -28197,7 +28205,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0409</t>
+          <t>6a4af7f1ae633549bd0f040b</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -28210,12 +28218,12 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
@@ -28245,7 +28253,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0405</t>
+          <t>6a4af7f1ae633549bd0f0406</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -28258,12 +28266,12 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
@@ -28293,7 +28301,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0407</t>
+          <t>6a4af7f1ae633549bd0f040a</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -28306,12 +28314,12 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -28341,7 +28349,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0410</t>
+          <t>6a4af7f1ae633549bd0f040f</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -28354,12 +28362,12 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F512" t="inlineStr"/>
@@ -28389,7 +28397,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0418</t>
+          <t>6a4af7f1ae633549bd0f0410</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -28402,12 +28410,12 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F513" t="inlineStr"/>
@@ -28437,7 +28445,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040f</t>
+          <t>6a4af7f1ae633549bd0f0413</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -28450,12 +28458,12 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -28485,7 +28493,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0416</t>
+          <t>6a4af7f1ae633549bd0f0418</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -28498,12 +28506,12 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F515" t="inlineStr"/>
@@ -28581,7 +28589,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0411</t>
+          <t>6a4af7f1ae633549bd0f0416</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -28594,12 +28602,12 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F517" t="inlineStr"/>
@@ -28677,7 +28685,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0413</t>
+          <t>6a4af7f1ae633549bd0f0411</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -28690,12 +28698,12 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -28725,7 +28733,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0417</t>
+          <t>6a4af7f1ae633549bd0f0415</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -28738,12 +28746,12 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F520" t="inlineStr"/>
@@ -28773,7 +28781,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0415</t>
+          <t>6a4af7f1ae633549bd0f0417</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -28786,12 +28794,12 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F521" t="inlineStr"/>
@@ -28821,7 +28829,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041f</t>
+          <t>6a4af7f1ae633549bd0f041e</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -28834,12 +28842,12 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F522" t="inlineStr"/>
@@ -28869,7 +28877,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041c</t>
+          <t>6a4af7f1ae633549bd0f041b</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -28882,12 +28890,12 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F523" t="inlineStr"/>
@@ -28917,7 +28925,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0420</t>
+          <t>6a4af7f1ae633549bd0f041d</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -28930,12 +28938,12 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F524" t="inlineStr"/>
@@ -28965,7 +28973,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0422</t>
+          <t>6a4af7f1ae633549bd0f041c</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -28978,12 +28986,12 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F525" t="inlineStr"/>
@@ -29013,7 +29021,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0423</t>
+          <t>6a4af7f1ae633549bd0f0420</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -29026,12 +29034,12 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F526" t="inlineStr"/>
@@ -29061,7 +29069,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041b</t>
+          <t>6a4af7f1ae633549bd0f0422</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -29074,12 +29082,12 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F527" t="inlineStr"/>
@@ -29109,7 +29117,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041d</t>
+          <t>6a4af7f1ae633549bd0f041a</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -29122,12 +29130,12 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F528" t="inlineStr"/>
@@ -29157,7 +29165,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0421</t>
+          <t>6a4af7f1ae633549bd0f0423</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -29170,12 +29178,12 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -29205,7 +29213,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041e</t>
+          <t>6a4af7f1ae633549bd0f041f</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -29218,12 +29226,12 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -29253,7 +29261,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041a</t>
+          <t>6a4af7f1ae633549bd0f0421</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -29266,12 +29274,12 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -29301,7 +29309,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0427</t>
+          <t>6a4af7f1ae633549bd0f0428</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -29314,12 +29322,12 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -29349,7 +29357,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042e</t>
+          <t>6a4af7f1ae633549bd0f042b</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -29362,12 +29370,12 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
@@ -29397,7 +29405,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042b</t>
+          <t>6a4af7f1ae633549bd0f042d</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -29410,12 +29418,12 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
@@ -29493,7 +29501,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0428</t>
+          <t>6a4af7f1ae633549bd0f042a</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -29506,12 +29514,12 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -29541,7 +29549,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0426</t>
+          <t>6a4af7f1ae633549bd0f0427</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -29554,12 +29562,12 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -29589,7 +29597,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042d</t>
+          <t>6a4af7f1ae633549bd0f042e</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -29602,12 +29610,12 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -29637,7 +29645,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0429</t>
+          <t>6a4af7f1ae633549bd0f0425</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -29650,12 +29658,12 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F539" t="inlineStr"/>
@@ -29685,7 +29693,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0425</t>
+          <t>6a4af7f1ae633549bd0f0429</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -29698,12 +29706,12 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -29733,7 +29741,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042a</t>
+          <t>6a4af7f1ae633549bd0f0426</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -29746,12 +29754,12 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F541" t="inlineStr"/>
@@ -29781,7 +29789,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0439</t>
+          <t>6a4af7f1ae633549bd0f0437</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -29794,12 +29802,12 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F542" t="inlineStr"/>
@@ -29829,7 +29837,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0434</t>
+          <t>6a4af7f1ae633549bd0f0430</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -29842,12 +29850,12 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F543" t="inlineStr"/>
@@ -29877,7 +29885,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0430</t>
+          <t>6a4af7f1ae633549bd0f0432</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -29890,12 +29898,12 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
@@ -29925,7 +29933,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0433</t>
+          <t>6a4af7f1ae633549bd0f0435</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -29938,12 +29946,12 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -29973,7 +29981,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0431</t>
+          <t>6a4af7f1ae633549bd0f0439</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -29986,12 +29994,12 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -30021,7 +30029,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0436</t>
+          <t>6a4af7f1ae633549bd0f0438</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -30034,12 +30042,12 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
@@ -30069,7 +30077,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0438</t>
+          <t>6a4af7f1ae633549bd0f0431</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -30082,12 +30090,12 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -30117,7 +30125,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0432</t>
+          <t>6a4af7f1ae633549bd0f0433</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -30130,12 +30138,12 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -30165,7 +30173,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0435</t>
+          <t>6a4af7f1ae633549bd0f0436</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -30178,12 +30186,12 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
@@ -30213,7 +30221,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0437</t>
+          <t>6a4af7f1ae633549bd0f0434</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -30226,12 +30234,12 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F551" t="inlineStr"/>
@@ -30261,7 +30269,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0441</t>
+          <t>6a4af7f1ae633549bd0f043d</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -30274,12 +30282,12 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -30309,7 +30317,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043d</t>
+          <t>6a4af7f2ae633549bd0f0441</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -30322,12 +30330,12 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -30357,7 +30365,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0444</t>
+          <t>6a4af7f1ae633549bd0f043c</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -30370,12 +30378,12 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -30405,7 +30413,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043c</t>
+          <t>6a4af7f2ae633549bd0f0440</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -30418,12 +30426,12 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F555" t="inlineStr"/>
@@ -30453,7 +30461,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0440</t>
+          <t>6a4af7f1ae633549bd0f043e</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -30466,12 +30474,12 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -30501,7 +30509,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043e</t>
+          <t>6a4af7f2ae633549bd0f0442</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -30514,12 +30522,12 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -30597,7 +30605,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0442</t>
+          <t>6a4af7f2ae633549bd0f0443</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -30610,12 +30618,12 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F559" t="inlineStr"/>
@@ -30693,7 +30701,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0443</t>
+          <t>6a4af7f2ae633549bd0f0444</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -30706,12 +30714,12 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -30741,7 +30749,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044b</t>
+          <t>6a4af7f2ae633549bd0f044d</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -30754,12 +30762,12 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -30789,7 +30797,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0447</t>
+          <t>6a4af7f2ae633549bd0f044e</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -30802,12 +30810,12 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F563" t="inlineStr"/>
@@ -30837,7 +30845,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0448</t>
+          <t>6a4af7f2ae633549bd0f044f</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -30850,12 +30858,12 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F564" t="inlineStr"/>
@@ -30885,7 +30893,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0449</t>
+          <t>6a4af7f2ae633549bd0f0446</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -30898,12 +30906,12 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F565" t="inlineStr"/>
@@ -30933,7 +30941,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044c</t>
+          <t>6a4af7f2ae633549bd0f044b</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -30946,12 +30954,12 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
@@ -30981,7 +30989,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044d</t>
+          <t>6a4af7f2ae633549bd0f044a</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -30994,12 +31002,12 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F567" t="inlineStr"/>
@@ -31029,7 +31037,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044f</t>
+          <t>6a4af7f2ae633549bd0f0447</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -31042,12 +31050,12 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F568" t="inlineStr"/>
@@ -31077,7 +31085,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044e</t>
+          <t>6a4af7f2ae633549bd0f0448</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -31090,12 +31098,12 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F569" t="inlineStr"/>
@@ -31125,7 +31133,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0446</t>
+          <t>6a4af7f2ae633549bd0f0449</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -31138,12 +31146,12 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F570" t="inlineStr"/>
@@ -31173,7 +31181,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044a</t>
+          <t>6a4af7f2ae633549bd0f044c</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -31186,12 +31194,12 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -31221,7 +31229,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0453</t>
+          <t>6a4af7f2ae633549bd0f0452</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -31234,12 +31242,12 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F572" t="inlineStr"/>
@@ -31269,7 +31277,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0459</t>
+          <t>6a4af7f2ae633549bd0f0458</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -31282,12 +31290,12 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F573" t="inlineStr"/>
@@ -31317,7 +31325,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0451</t>
+          <t>6a4af7f2ae633549bd0f0455</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -31330,12 +31338,12 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F574" t="inlineStr"/>
@@ -31365,7 +31373,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0454</t>
+          <t>6a4af7f2ae633549bd0f0456</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -31378,12 +31386,12 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -31413,7 +31421,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0452</t>
+          <t>6a4af7f2ae633549bd0f0457</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -31426,12 +31434,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F576" t="inlineStr"/>
@@ -31461,7 +31469,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0455</t>
+          <t>6a4af7f2ae633549bd0f045a</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -31474,12 +31482,12 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -31509,7 +31517,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0458</t>
+          <t>6a4af7f2ae633549bd0f0453</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -31522,12 +31530,12 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -31557,7 +31565,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0456</t>
+          <t>6a4af7f2ae633549bd0f0451</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -31570,12 +31578,12 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F579" t="inlineStr"/>
@@ -31605,7 +31613,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0457</t>
+          <t>6a4af7f2ae633549bd0f0454</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -31618,12 +31626,12 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F580" t="inlineStr"/>
@@ -31653,7 +31661,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045a</t>
+          <t>6a4af7f2ae633549bd0f0459</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -31666,12 +31674,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -31701,7 +31709,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0460</t>
+          <t>6a4af7f2ae633549bd0f0462</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -31714,12 +31722,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F582" t="inlineStr"/>
@@ -31749,7 +31757,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0464</t>
+          <t>6a4af7f2ae633549bd0f0461</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -31762,12 +31770,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -31797,7 +31805,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045d</t>
+          <t>6a4af7f2ae633549bd0f0463</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -31810,12 +31818,12 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F584" t="inlineStr"/>
@@ -31845,7 +31853,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0465</t>
+          <t>6a4af7f2ae633549bd0f045d</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -31858,12 +31866,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -31893,7 +31901,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0462</t>
+          <t>6a4af7f2ae633549bd0f0465</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -31906,12 +31914,12 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F586" t="inlineStr"/>
@@ -31941,7 +31949,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0463</t>
+          <t>6a4af7f2ae633549bd0f0460</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -31954,12 +31962,12 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -31989,7 +31997,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045c</t>
+          <t>6a4af7f2ae633549bd0f045f</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -32002,12 +32010,12 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -32037,7 +32045,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0461</t>
+          <t>6a4af7f2ae633549bd0f0464</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -32050,12 +32058,12 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -32085,7 +32093,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045f</t>
+          <t>6a4af7f2ae633549bd0f045e</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -32098,12 +32106,12 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -32133,7 +32141,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045e</t>
+          <t>6a4af7f2ae633549bd0f045c</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -32146,12 +32154,12 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -32181,7 +32189,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0469</t>
+          <t>6a4af7f2ae633549bd0f0468</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -32194,12 +32202,12 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F592" t="inlineStr"/>
@@ -32229,7 +32237,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046a</t>
+          <t>6a4af7f2ae633549bd0f0470</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -32242,12 +32250,12 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F593" t="inlineStr"/>
@@ -32277,7 +32285,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046d</t>
+          <t>6a4af7f2ae633549bd0f046e</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -32290,12 +32298,12 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F594" t="inlineStr"/>
@@ -32325,7 +32333,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046e</t>
+          <t>6a4af7f2ae633549bd0f0467</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -32338,12 +32346,12 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F595" t="inlineStr"/>
@@ -32373,7 +32381,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0470</t>
+          <t>6a4af7f2ae633549bd0f046d</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -32386,12 +32394,12 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F596" t="inlineStr"/>
@@ -32421,7 +32429,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0468</t>
+          <t>6a4af7f2ae633549bd0f0469</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -32434,12 +32442,12 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F597" t="inlineStr"/>
@@ -32469,7 +32477,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046f</t>
+          <t>6a4af7f2ae633549bd0f046a</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -32482,12 +32490,12 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F598" t="inlineStr"/>
@@ -32517,7 +32525,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046b</t>
+          <t>6a4af7f2ae633549bd0f046c</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -32530,12 +32538,12 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -32565,7 +32573,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0467</t>
+          <t>6a4af7f2ae633549bd0f046b</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -32578,12 +32586,12 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F600" t="inlineStr"/>
@@ -32613,7 +32621,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046c</t>
+          <t>6a4af7f2ae633549bd0f046f</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -32626,12 +32634,12 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F601" t="inlineStr"/>
@@ -32709,7 +32717,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0479</t>
+          <t>6a4af7f2ae633549bd0f0475</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -32722,12 +32730,12 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
@@ -32805,7 +32813,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047a</t>
+          <t>6a4af7f2ae633549bd0f0477</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -32818,12 +32826,12 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F605" t="inlineStr"/>
@@ -32853,7 +32861,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0478</t>
+          <t>6a4af7f2ae633549bd0f0472</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -32866,12 +32874,12 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
@@ -32901,7 +32909,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0472</t>
+          <t>6a4af7f2ae633549bd0f0473</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -32914,12 +32922,12 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -32949,7 +32957,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0473</t>
+          <t>6a4af7f2ae633549bd0f0476</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -32962,12 +32970,12 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
@@ -32997,7 +33005,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0476</t>
+          <t>6a4af7f2ae633549bd0f0478</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -33010,12 +33018,12 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F609" t="inlineStr"/>
@@ -33045,7 +33053,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0477</t>
+          <t>6a4af7f2ae633549bd0f047a</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -33058,12 +33066,12 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F610" t="inlineStr"/>
@@ -33093,7 +33101,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0475</t>
+          <t>6a4af7f2ae633549bd0f0479</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -33106,12 +33114,12 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -33141,7 +33149,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0481</t>
+          <t>6a4af7f2ae633549bd0f0480</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -33154,12 +33162,12 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F612" t="inlineStr"/>
@@ -33189,7 +33197,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047e</t>
+          <t>6a4af7f2ae633549bd0f0481</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -33202,12 +33210,12 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F613" t="inlineStr"/>
@@ -33285,7 +33293,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0483</t>
+          <t>6a4af7f3ae633549bd0f0485</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -33298,12 +33306,12 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -33333,7 +33341,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047d</t>
+          <t>6a4af7f2ae633549bd0f0482</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -33346,12 +33354,12 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F616" t="inlineStr"/>
@@ -33381,7 +33389,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047f</t>
+          <t>6a4af7f3ae633549bd0f0486</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -33394,12 +33402,12 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F617" t="inlineStr"/>
@@ -33429,7 +33437,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0482</t>
+          <t>6a4af7f2ae633549bd0f047d</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -33442,12 +33450,12 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -33477,7 +33485,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0486</t>
+          <t>6a4af7f2ae633549bd0f0483</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -33490,12 +33498,12 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -33525,7 +33533,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0485</t>
+          <t>6a4af7f2ae633549bd0f047e</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -33538,12 +33546,12 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -33573,7 +33581,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0480</t>
+          <t>6a4af7f2ae633549bd0f047f</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -33586,12 +33594,12 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F621" t="inlineStr"/>
@@ -33621,7 +33629,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048a</t>
+          <t>6a4af7f3ae633549bd0f0490</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -33634,12 +33642,12 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F622" t="inlineStr"/>
@@ -33669,7 +33677,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048c</t>
+          <t>6a4af7f3ae633549bd0f048b</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -33682,12 +33690,12 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F623" t="inlineStr"/>
@@ -33717,7 +33725,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0490</t>
+          <t>6a4af7f3ae633549bd0f048c</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -33730,12 +33738,12 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
@@ -33765,7 +33773,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048e</t>
+          <t>6a4af7f3ae633549bd0f0489</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -33778,12 +33786,12 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F625" t="inlineStr"/>
@@ -33813,7 +33821,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0488</t>
+          <t>6a4af7f3ae633549bd0f0491</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -33826,12 +33834,12 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F626" t="inlineStr"/>
@@ -33861,7 +33869,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0489</t>
+          <t>6a4af7f3ae633549bd0f048d</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -33874,12 +33882,12 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F627" t="inlineStr"/>
@@ -33957,7 +33965,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048d</t>
+          <t>6a4af7f3ae633549bd0f0488</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -33970,12 +33978,12 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F629" t="inlineStr"/>
@@ -34005,7 +34013,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048b</t>
+          <t>6a4af7f3ae633549bd0f048e</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -34018,12 +34026,12 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F630" t="inlineStr"/>
@@ -34053,7 +34061,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0491</t>
+          <t>6a4af7f3ae633549bd0f048a</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -34066,12 +34074,12 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F631" t="inlineStr"/>
@@ -34101,7 +34109,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0493</t>
+          <t>6a4af7f3ae633549bd0f0496</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -34114,12 +34122,12 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F632" t="inlineStr"/>
@@ -34149,7 +34157,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0494</t>
+          <t>6a4af7f3ae633549bd0f0493</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -34162,12 +34170,12 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F633" t="inlineStr"/>
@@ -34197,7 +34205,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0496</t>
+          <t>6a4af7f3ae633549bd0f0499</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -34210,12 +34218,12 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F634" t="inlineStr"/>
@@ -34245,7 +34253,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0497</t>
+          <t>6a4af7f3ae633549bd0f0494</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -34258,12 +34266,12 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F635" t="inlineStr"/>
@@ -34293,7 +34301,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0499</t>
+          <t>6a4af7f3ae633549bd0f0497</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -34306,12 +34314,12 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F636" t="inlineStr"/>
@@ -34437,7 +34445,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0498</t>
+          <t>6a4af7f3ae633549bd0f049c</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -34450,12 +34458,12 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
@@ -34485,7 +34493,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049c</t>
+          <t>6a4af7f3ae633549bd0f0498</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -34498,12 +34506,12 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F640" t="inlineStr"/>
@@ -34581,7 +34589,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049e</t>
+          <t>6a4af7f3ae633549bd0f04a0</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -34594,12 +34602,12 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F642" t="inlineStr"/>
@@ -34677,7 +34685,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a1</t>
+          <t>6a4af7f3ae633549bd0f04a2</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -34690,12 +34698,12 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -34725,7 +34733,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a5</t>
+          <t>6a4af7f3ae633549bd0f04a3</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -34738,12 +34746,12 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F645" t="inlineStr"/>
@@ -34773,7 +34781,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a6</t>
+          <t>6a4af7f3ae633549bd0f04a4</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -34786,12 +34794,12 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F646" t="inlineStr"/>
@@ -34821,7 +34829,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a4</t>
+          <t>6a4af7f3ae633549bd0f04a7</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -34834,12 +34842,12 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -34869,7 +34877,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a0</t>
+          <t>6a4af7f3ae633549bd0f04a6</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -34882,12 +34890,12 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -34917,7 +34925,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a2</t>
+          <t>6a4af7f3ae633549bd0f04a5</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -34930,12 +34938,12 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -34965,7 +34973,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a3</t>
+          <t>6a4af7f3ae633549bd0f04a1</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -34978,12 +34986,12 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F650" t="inlineStr"/>
@@ -35013,7 +35021,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a7</t>
+          <t>6a4af7f3ae633549bd0f049e</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -35026,12 +35034,12 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F651" t="inlineStr"/>
@@ -35061,7 +35069,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b2</t>
+          <t>6a4af7f3ae633549bd0f04af</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -35074,12 +35082,12 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -35109,7 +35117,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a9</t>
+          <t>6a4af7f3ae633549bd0f04ab</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -35122,12 +35130,12 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F653" t="inlineStr"/>
@@ -35157,7 +35165,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04aa</t>
+          <t>6a4af7f3ae633549bd0f04b0</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -35170,12 +35178,12 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F654" t="inlineStr"/>
@@ -35253,7 +35261,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04af</t>
+          <t>6a4af7f3ae633549bd0f04b1</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -35266,12 +35274,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F656" t="inlineStr"/>
@@ -35301,7 +35309,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ab</t>
+          <t>6a4af7f3ae633549bd0f04ac</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -35314,12 +35322,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F657" t="inlineStr"/>
@@ -35349,7 +35357,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b0</t>
+          <t>6a4af7f3ae633549bd0f04ae</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -35362,12 +35370,12 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F658" t="inlineStr"/>
@@ -35397,7 +35405,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ac</t>
+          <t>6a4af7f3ae633549bd0f04b2</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -35410,12 +35418,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -35445,7 +35453,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ae</t>
+          <t>6a4af7f3ae633549bd0f04a9</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -35458,12 +35466,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F660" t="inlineStr"/>
@@ -35493,7 +35501,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b1</t>
+          <t>6a4af7f3ae633549bd0f04aa</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -35506,12 +35514,12 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F661" t="inlineStr"/>
@@ -35541,7 +35549,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ba</t>
+          <t>6a4af7f3ae633549bd0f04b9</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -35554,12 +35562,12 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F662" t="inlineStr"/>
@@ -35589,7 +35597,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b9</t>
+          <t>6a4af7f3ae633549bd0f04bc</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -35602,12 +35610,12 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F663" t="inlineStr"/>
@@ -35637,7 +35645,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bd</t>
+          <t>6a4af7f3ae633549bd0f04ba</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -35650,12 +35658,12 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F664" t="inlineStr"/>
@@ -35685,7 +35693,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bb</t>
+          <t>6a4af7f3ae633549bd0f04bd</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -35698,12 +35706,12 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F665" t="inlineStr"/>
@@ -35733,7 +35741,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b6</t>
+          <t>6a4af7f3ae633549bd0f04bb</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -35746,12 +35754,12 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F666" t="inlineStr"/>
@@ -35781,7 +35789,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b8</t>
+          <t>6a4af7f3ae633549bd0f04b6</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -35794,12 +35802,12 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F667" t="inlineStr"/>
@@ -35925,7 +35933,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b5</t>
+          <t>6a4af7f3ae633549bd0f04b8</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -35938,12 +35946,12 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F670" t="inlineStr"/>
@@ -35973,7 +35981,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bc</t>
+          <t>6a4af7f3ae633549bd0f04b5</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -35986,12 +35994,12 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F671" t="inlineStr"/>
@@ -36021,7 +36029,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c6</t>
+          <t>6a4af7f3ae633549bd0f04c3</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -36034,12 +36042,12 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F672" t="inlineStr"/>
@@ -36069,7 +36077,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bf</t>
+          <t>6a4af7f3ae633549bd0f04c1</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -36082,12 +36090,12 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
@@ -36117,7 +36125,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c7</t>
+          <t>6a4af7f3ae633549bd0f04c6</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -36130,12 +36138,12 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F674" t="inlineStr"/>
@@ -36165,7 +36173,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c4</t>
+          <t>6a4af7f3ae633549bd0f04c7</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -36178,12 +36186,12 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F675" t="inlineStr"/>
@@ -36213,7 +36221,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c8</t>
+          <t>6a4af7f3ae633549bd0f04c2</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -36226,12 +36234,12 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -36261,7 +36269,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c1</t>
+          <t>6a4af7f3ae633549bd0f04c8</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -36274,12 +36282,12 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
@@ -36309,7 +36317,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c3</t>
+          <t>6a4af7f3ae633549bd0f04c0</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -36322,12 +36330,12 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F678" t="inlineStr"/>
@@ -36357,7 +36365,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c2</t>
+          <t>6a4af7f3ae633549bd0f04c5</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -36370,12 +36378,12 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F679" t="inlineStr"/>
@@ -36405,7 +36413,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c0</t>
+          <t>6a4af7f3ae633549bd0f04bf</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -36418,12 +36426,12 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F680" t="inlineStr"/>
@@ -36453,7 +36461,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c5</t>
+          <t>6a4af7f3ae633549bd0f04c4</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -36466,12 +36474,12 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
@@ -36501,7 +36509,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ca</t>
+          <t>6a4af7f4ae633549bd0f04cf</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -36514,12 +36522,12 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F682" t="inlineStr"/>
@@ -36549,7 +36557,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ce</t>
+          <t>6a4af7f4ae633549bd0f04cd</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -36562,12 +36570,12 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F683" t="inlineStr"/>
@@ -36597,7 +36605,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cb</t>
+          <t>6a4af7f4ae633549bd0f04d3</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -36610,12 +36618,12 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F684" t="inlineStr"/>
@@ -36645,7 +36653,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cc</t>
+          <t>6a4af7f4ae633549bd0f04d0</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -36658,12 +36666,12 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F685" t="inlineStr"/>
@@ -36693,7 +36701,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d0</t>
+          <t>6a4af7f4ae633549bd0f04ce</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -36706,12 +36714,12 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F686" t="inlineStr"/>
@@ -36741,7 +36749,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d2</t>
+          <t>6a4af7f4ae633549bd0f04ca</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -36754,12 +36762,12 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F687" t="inlineStr"/>
@@ -36789,7 +36797,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d1</t>
+          <t>6a4af7f4ae633549bd0f04cb</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -36802,12 +36810,12 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F688" t="inlineStr"/>
@@ -36837,7 +36845,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cd</t>
+          <t>6a4af7f4ae633549bd0f04cc</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -36850,12 +36858,12 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F689" t="inlineStr"/>
@@ -36885,7 +36893,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cf</t>
+          <t>6a4af7f4ae633549bd0f04d2</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -36898,12 +36906,12 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F690" t="inlineStr"/>
@@ -36933,7 +36941,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d3</t>
+          <t>6a4af7f4ae633549bd0f04d1</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -36946,12 +36954,12 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F691" t="inlineStr"/>
@@ -36981,7 +36989,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04da</t>
+          <t>6a4af7f4ae633549bd0f04d8</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -36994,12 +37002,12 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F692" t="inlineStr"/>
@@ -37029,7 +37037,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dd</t>
+          <t>6a4af7f4ae633549bd0f04dc</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -37042,12 +37050,12 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F693" t="inlineStr"/>
@@ -37077,7 +37085,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d7</t>
+          <t>6a4af7f4ae633549bd0f04de</t>
         </is>
       </c>
       <c r="B694" t="n">
@@ -37090,12 +37098,12 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F694" t="inlineStr"/>
@@ -37125,7 +37133,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04de</t>
+          <t>6a4af7f4ae633549bd0f04d7</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -37138,12 +37146,12 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F695" t="inlineStr"/>
@@ -37173,7 +37181,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04db</t>
+          <t>6a4af7f4ae633549bd0f04da</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -37186,12 +37194,12 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F696" t="inlineStr"/>
@@ -37221,7 +37229,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d8</t>
+          <t>6a4af7f4ae633549bd0f04d6</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -37234,12 +37242,12 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F697" t="inlineStr"/>
@@ -37269,7 +37277,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d9</t>
+          <t>6a4af7f4ae633549bd0f04d5</t>
         </is>
       </c>
       <c r="B698" t="n">
@@ -37282,12 +37290,12 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F698" t="inlineStr"/>
@@ -37317,7 +37325,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dc</t>
+          <t>6a4af7f4ae633549bd0f04dd</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -37330,12 +37338,12 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F699" t="inlineStr"/>
@@ -37365,7 +37373,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d6</t>
+          <t>6a4af7f4ae633549bd0f04db</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -37378,12 +37386,12 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F700" t="inlineStr"/>
@@ -37413,7 +37421,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d5</t>
+          <t>6a4af7f4ae633549bd0f04d9</t>
         </is>
       </c>
       <c r="B701" t="n">
@@ -37426,12 +37434,12 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F701" t="inlineStr"/>
@@ -37509,7 +37517,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e2</t>
+          <t>6a4af7f4ae633549bd0f04e6</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -37522,12 +37530,12 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F703" t="inlineStr"/>
@@ -37605,7 +37613,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e6</t>
+          <t>6a4af7f4ae633549bd0f04e2</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -37618,12 +37626,12 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
@@ -37797,7 +37805,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e0</t>
+          <t>6a4af7f4ae633549bd0f04e4</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -37810,12 +37818,12 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F709" t="inlineStr"/>
@@ -37845,7 +37853,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e4</t>
+          <t>6a4af7f4ae633549bd0f04e0</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -37858,12 +37866,12 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F710" t="inlineStr"/>
@@ -37941,7 +37949,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f3</t>
+          <t>6a4af7f4ae633549bd0f04eb</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -37954,12 +37962,12 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F712" t="inlineStr"/>
@@ -37989,7 +37997,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04eb</t>
+          <t>6a4af7f4ae633549bd0f04f2</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -38002,12 +38010,12 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F713" t="inlineStr"/>
@@ -38037,7 +38045,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f0</t>
+          <t>6a4af7f4ae633549bd0f04f1</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -38050,12 +38058,12 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -38085,7 +38093,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f4</t>
+          <t>6a4af7f4ae633549bd0f04f3</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -38098,12 +38106,12 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F715" t="inlineStr"/>
@@ -38133,7 +38141,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ee</t>
+          <t>6a4af7f4ae633549bd0f04ef</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -38146,12 +38154,12 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F716" t="inlineStr"/>
@@ -38181,7 +38189,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ef</t>
+          <t>6a4af7f4ae633549bd0f04ec</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -38194,12 +38202,12 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F717" t="inlineStr"/>
@@ -38229,7 +38237,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ec</t>
+          <t>6a4af7f4ae633549bd0f04ed</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -38242,12 +38250,12 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F718" t="inlineStr"/>
@@ -38277,7 +38285,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ed</t>
+          <t>6a4af7f4ae633549bd0f04f0</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -38290,12 +38298,12 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F719" t="inlineStr"/>
@@ -38325,7 +38333,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f2</t>
+          <t>6a4af7f4ae633549bd0f04ee</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -38338,12 +38346,12 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F720" t="inlineStr"/>
@@ -38373,7 +38381,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f1</t>
+          <t>6a4af7f4ae633549bd0f04f4</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -38386,12 +38394,12 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F721" t="inlineStr"/>
@@ -38421,7 +38429,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fb</t>
+          <t>6a4af7f4ae633549bd0f04f6</t>
         </is>
       </c>
       <c r="B722" t="n">
@@ -38434,12 +38442,12 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F722" t="inlineStr"/>
@@ -38469,7 +38477,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fd</t>
+          <t>6a4af7f4ae633549bd0f04f8</t>
         </is>
       </c>
       <c r="B723" t="n">
@@ -38482,12 +38490,12 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F723" t="inlineStr"/>
@@ -38517,7 +38525,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f6</t>
+          <t>6a4af7f4ae633549bd0f04ff</t>
         </is>
       </c>
       <c r="B724" t="n">
@@ -38530,12 +38538,12 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F724" t="inlineStr"/>
@@ -38565,7 +38573,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f7</t>
+          <t>6a4af7f4ae633549bd0f04fe</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -38578,12 +38586,12 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
@@ -38613,7 +38621,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f8</t>
+          <t>6a4af7f4ae633549bd0f04f9</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -38626,12 +38634,12 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F726" t="inlineStr"/>
@@ -38661,7 +38669,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fa</t>
+          <t>6a4af7f4ae633549bd0f04fc</t>
         </is>
       </c>
       <c r="B727" t="n">
@@ -38674,12 +38682,12 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F727" t="inlineStr"/>
@@ -38709,7 +38717,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ff</t>
+          <t>6a4af7f4ae633549bd0f04fb</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -38722,12 +38730,12 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F728" t="inlineStr"/>
@@ -38757,7 +38765,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fe</t>
+          <t>6a4af7f4ae633549bd0f04fd</t>
         </is>
       </c>
       <c r="B729" t="n">
@@ -38770,12 +38778,12 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F729" t="inlineStr"/>
@@ -38805,7 +38813,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f9</t>
+          <t>6a4af7f4ae633549bd0f04f7</t>
         </is>
       </c>
       <c r="B730" t="n">
@@ -38818,12 +38826,12 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F730" t="inlineStr"/>
@@ -38853,7 +38861,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fc</t>
+          <t>6a4af7f4ae633549bd0f04fa</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -38866,12 +38874,12 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F731" t="inlineStr"/>
@@ -38997,7 +39005,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0509</t>
+          <t>6a4af7f4ae633549bd0f0502</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -39010,12 +39018,12 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
@@ -39045,7 +39053,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0504</t>
+          <t>6a4af7f4ae633549bd0f0501</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -39058,12 +39066,12 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -39093,7 +39101,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0506</t>
+          <t>6a4af7f4ae633549bd0f0507</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -39106,12 +39114,12 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
@@ -39189,7 +39197,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0507</t>
+          <t>6a4af7f4ae633549bd0f0506</t>
         </is>
       </c>
       <c r="B738" t="n">
@@ -39202,12 +39210,12 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F738" t="inlineStr"/>
@@ -39237,7 +39245,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0501</t>
+          <t>6a4af7f4ae633549bd0f050a</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -39250,12 +39258,12 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F739" t="inlineStr"/>
@@ -39285,7 +39293,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050a</t>
+          <t>6a4af7f4ae633549bd0f0504</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -39298,12 +39306,12 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -39333,7 +39341,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0502</t>
+          <t>6a4af7f4ae633549bd0f0509</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -39346,12 +39354,12 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F741" t="inlineStr"/>
@@ -39381,7 +39389,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0511</t>
+          <t>6a4af7f5ae633549bd0f0510</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -39394,12 +39402,12 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F742" t="inlineStr"/>
@@ -39429,7 +39437,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0513</t>
+          <t>6a4af7f4ae633549bd0f050d</t>
         </is>
       </c>
       <c r="B743" t="n">
@@ -39442,12 +39450,12 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F743" t="inlineStr"/>
@@ -39477,7 +39485,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0512</t>
+          <t>6a4af7f5ae633549bd0f0511</t>
         </is>
       </c>
       <c r="B744" t="n">
@@ -39490,12 +39498,12 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F744" t="inlineStr"/>
@@ -39525,7 +39533,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0510</t>
+          <t>6a4af7f5ae633549bd0f0515</t>
         </is>
       </c>
       <c r="B745" t="n">
@@ -39538,12 +39546,12 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F745" t="inlineStr"/>
@@ -39573,7 +39581,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0514</t>
+          <t>6a4af7f4ae633549bd0f050c</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -39586,12 +39594,12 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F746" t="inlineStr"/>
@@ -39621,7 +39629,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050e</t>
+          <t>6a4af7f5ae633549bd0f050f</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -39634,12 +39642,12 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F747" t="inlineStr"/>
@@ -39669,7 +39677,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050f</t>
+          <t>6a4af7f5ae633549bd0f050e</t>
         </is>
       </c>
       <c r="B748" t="n">
@@ -39682,12 +39690,12 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F748" t="inlineStr"/>
@@ -39717,7 +39725,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050c</t>
+          <t>6a4af7f5ae633549bd0f0513</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -39730,12 +39738,12 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
@@ -39765,7 +39773,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050d</t>
+          <t>6a4af7f5ae633549bd0f0514</t>
         </is>
       </c>
       <c r="B750" t="n">
@@ -39778,12 +39786,12 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F750" t="inlineStr"/>
@@ -39813,7 +39821,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0515</t>
+          <t>6a4af7f5ae633549bd0f0512</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -39826,12 +39834,12 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F751" t="inlineStr"/>
@@ -39861,7 +39869,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0517</t>
+          <t>6a4af7f5ae633549bd0f051c</t>
         </is>
       </c>
       <c r="B752" t="n">
@@ -39874,12 +39882,12 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F752" t="inlineStr"/>
@@ -39909,7 +39917,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051d</t>
+          <t>6a4af7f5ae633549bd0f0518</t>
         </is>
       </c>
       <c r="B753" t="n">
@@ -39922,12 +39930,12 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F753" t="inlineStr"/>
@@ -39957,7 +39965,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051e</t>
+          <t>6a4af7f5ae633549bd0f0517</t>
         </is>
       </c>
       <c r="B754" t="n">
@@ -39970,12 +39978,12 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F754" t="inlineStr"/>
@@ -40005,7 +40013,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0518</t>
+          <t>6a4af7f5ae633549bd0f051a</t>
         </is>
       </c>
       <c r="B755" t="n">
@@ -40018,12 +40026,12 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F755" t="inlineStr"/>
@@ -40053,7 +40061,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051a</t>
+          <t>6a4af7f5ae633549bd0f051e</t>
         </is>
       </c>
       <c r="B756" t="n">
@@ -40066,12 +40074,12 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F756" t="inlineStr"/>
@@ -40101,7 +40109,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0519</t>
+          <t>6a4af7f5ae633549bd0f0520</t>
         </is>
       </c>
       <c r="B757" t="n">
@@ -40114,12 +40122,12 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F757" t="inlineStr"/>
@@ -40149,7 +40157,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0520</t>
+          <t>6a4af7f5ae633549bd0f0519</t>
         </is>
       </c>
       <c r="B758" t="n">
@@ -40162,12 +40170,12 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F758" t="inlineStr"/>
@@ -40245,7 +40253,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051c</t>
+          <t>6a4af7f5ae633549bd0f051b</t>
         </is>
       </c>
       <c r="B760" t="n">
@@ -40258,12 +40266,12 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F760" t="inlineStr"/>
@@ -40293,7 +40301,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051b</t>
+          <t>6a4af7f5ae633549bd0f051d</t>
         </is>
       </c>
       <c r="B761" t="n">
@@ -40306,12 +40314,12 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>

--- a/datos/maestros/md_partidos.xlsx
+++ b/datos/maestros/md_partidos.xlsx
@@ -21773,7 +21773,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ba</t>
+          <t>6a4af7f0ae633549bd0f03c0</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -21786,29 +21786,33 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
-        </is>
-      </c>
-      <c r="F382" t="inlineStr"/>
-      <c r="G382" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000d9</t>
+        </is>
+      </c>
+      <c r="F382" t="n">
+        <v>0</v>
+      </c>
+      <c r="G382" t="n">
+        <v>0</v>
+      </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
@@ -21816,12 +21820,16 @@
           <t>closed</t>
         </is>
       </c>
-      <c r="L382" t="inlineStr"/>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03be</t>
+          <t>6a4af7f0ae633549bd0f03bf</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -21834,29 +21842,29 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
@@ -21869,7 +21877,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bb</t>
+          <t>6a4af7f0ae633549bd0f03ba</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -21882,19 +21890,19 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="inlineStr"/>
       <c r="H384" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -21917,7 +21925,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bc</t>
+          <t>6a4af7f0ae633549bd0f03bd</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -21930,19 +21938,19 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -21965,7 +21973,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c0</t>
+          <t>6a4af7f0ae633549bd0f03b7</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -21978,33 +21986,29 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
-        </is>
-      </c>
-      <c r="F386" t="n">
-        <v>0</v>
-      </c>
-      <c r="G386" t="n">
-        <v>0</v>
-      </c>
+          <t>504e581e4d8bec9a670000cb</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
@@ -22012,16 +22016,12 @@
           <t>closed</t>
         </is>
       </c>
-      <c r="L386" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="L386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b8</t>
+          <t>6a4af7f0ae633549bd0f03bb</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -22034,12 +22034,12 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F387" t="inlineStr"/>
@@ -22069,7 +22069,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bf</t>
+          <t>6a4af7f0ae633549bd0f03bc</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -22082,12 +22082,12 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F388" t="inlineStr"/>
@@ -22099,12 +22099,12 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
@@ -22117,7 +22117,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b9</t>
+          <t>6a4af7f0ae633549bd0f03be</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -22130,19 +22130,19 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -22165,7 +22165,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b7</t>
+          <t>6a4af7f0ae633549bd0f03b8</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -22178,29 +22178,29 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
@@ -22213,7 +22213,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bd</t>
+          <t>6a4af7f0ae633549bd0f03b9</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -22226,12 +22226,12 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
@@ -22261,7 +22261,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0387</t>
+          <t>6a4af7efae633549bd0f0380</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -22274,33 +22274,33 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F392" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G392" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
@@ -22317,7 +22317,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0389</t>
+          <t>6a4af7efae633549bd0f0383</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -22330,33 +22330,33 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F393" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
@@ -22373,7 +22373,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0383</t>
+          <t>6a4af7efae633549bd0f0384</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -22386,33 +22386,33 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F394" t="n">
         <v>1</v>
       </c>
       <c r="G394" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
@@ -22429,7 +22429,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0384</t>
+          <t>6a4af7efae633549bd0f0388</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -22442,33 +22442,33 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G395" t="n">
         <v>1</v>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
@@ -22485,7 +22485,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0385</t>
+          <t>6a4af7efae633549bd0f0382</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -22498,33 +22498,33 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G396" t="n">
         <v>0</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
@@ -22541,7 +22541,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0388</t>
+          <t>6a4af7efae633549bd0f0381</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -22554,33 +22554,33 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F397" t="n">
         <v>2</v>
       </c>
       <c r="G397" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
@@ -22597,7 +22597,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0382</t>
+          <t>6a4af7efae633549bd0f0386</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -22610,33 +22610,33 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F398" t="n">
         <v>2</v>
       </c>
       <c r="G398" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
@@ -22653,7 +22653,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0381</t>
+          <t>6a4af7efae633549bd0f0385</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -22666,33 +22666,33 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F399" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G399" t="n">
         <v>0</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
           <t>19:00</t>
-        </is>
-      </c>
-      <c r="J399" t="inlineStr">
-        <is>
-          <t>21:00</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
@@ -22709,7 +22709,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0386</t>
+          <t>6a4af7efae633549bd0f0387</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -22722,33 +22722,33 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F400" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G400" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
@@ -22765,7 +22765,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0380</t>
+          <t>6a4af7efae633549bd0f0389</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -22778,33 +22778,33 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F401" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
@@ -22821,7 +22821,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038d</t>
+          <t>6a4af7efae633549bd0f0390</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -22834,12 +22834,12 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F402" t="n">
@@ -22850,17 +22850,17 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
@@ -22877,7 +22877,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0391</t>
+          <t>6a4af7efae633549bd0f0393</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -22890,12 +22890,12 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F403" t="n">
@@ -22906,17 +22906,17 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
@@ -22933,7 +22933,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0390</t>
+          <t>6a4af7efae633549bd0f0394</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -22946,23 +22946,23 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F404" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G404" t="n">
         <v>0</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -22989,7 +22989,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038b</t>
+          <t>6a4af7efae633549bd0f038f</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -23002,19 +23002,19 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F405" t="n">
         <v>1</v>
       </c>
       <c r="G405" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
@@ -23023,12 +23023,12 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
@@ -23045,7 +23045,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038c</t>
+          <t>6a4af7efae633549bd0f0392</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -23058,33 +23058,33 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F406" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G406" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
@@ -23101,7 +23101,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038e</t>
+          <t>6a4af7efae633549bd0f038c</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -23114,19 +23114,19 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F407" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G407" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
@@ -23135,12 +23135,12 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
@@ -23157,7 +23157,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038f</t>
+          <t>6a4af7efae633549bd0f038b</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -23170,19 +23170,19 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F408" t="n">
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
@@ -23191,12 +23191,12 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
@@ -23213,7 +23213,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0392</t>
+          <t>6a4af7efae633549bd0f038d</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -23226,33 +23226,33 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G409" t="n">
         <v>0</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
@@ -23269,7 +23269,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0394</t>
+          <t>6a4af7efae633549bd0f038e</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -23282,33 +23282,33 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F410" t="n">
         <v>0</v>
       </c>
       <c r="G410" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
@@ -23325,7 +23325,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0393</t>
+          <t>6a4af7efae633549bd0f0391</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -23338,12 +23338,12 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -23354,17 +23354,17 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
@@ -23381,7 +23381,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0396</t>
+          <t>6a4af7efae633549bd0f039e</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -23394,33 +23394,33 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F412" t="n">
+        <v>2</v>
+      </c>
+      <c r="G412" t="n">
         <v>1</v>
       </c>
-      <c r="G412" t="n">
-        <v>0</v>
-      </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
@@ -23493,7 +23493,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039e</t>
+          <t>6a4af7efae633549bd0f039f</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -23506,19 +23506,19 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
@@ -23527,12 +23527,12 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
@@ -23549,7 +23549,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039a</t>
+          <t>6a4af7efae633549bd0f0397</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -23562,12 +23562,12 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F415" t="n">
@@ -23578,17 +23578,17 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
@@ -23605,7 +23605,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039c</t>
+          <t>6a4af7efae633549bd0f0398</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -23618,33 +23618,33 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G416" t="n">
         <v>2</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
@@ -23661,7 +23661,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0397</t>
+          <t>6a4af7efae633549bd0f039a</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -23674,12 +23674,12 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F417" t="n">
@@ -23690,17 +23690,17 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
@@ -23717,7 +23717,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0398</t>
+          <t>6a4af7efae633549bd0f039c</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -23730,33 +23730,33 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F418" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G418" t="n">
         <v>2</v>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
@@ -23885,7 +23885,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039f</t>
+          <t>6a4af7efae633549bd0f0396</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -23898,23 +23898,23 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F421" t="n">
         <v>1</v>
       </c>
       <c r="G421" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -23941,7 +23941,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a3</t>
+          <t>6a4af7efae633549bd0f03a1</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -23954,33 +23954,33 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G422" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
@@ -23997,7 +23997,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a4</t>
+          <t>6a4af7efae633549bd0f03a9</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -24010,33 +24010,33 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F423" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G423" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
@@ -24053,7 +24053,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a5</t>
+          <t>6a4af7efae633549bd0f03a6</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -24066,12 +24066,12 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F424" t="n">
@@ -24082,17 +24082,17 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
           <t>19:00</t>
-        </is>
-      </c>
-      <c r="J424" t="inlineStr">
-        <is>
-          <t>21:00</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
@@ -24109,7 +24109,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a6</t>
+          <t>6a4af7efae633549bd0f03a4</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -24122,19 +24122,19 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F425" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G425" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H425" t="inlineStr">
         <is>
@@ -24143,12 +24143,12 @@
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K425" t="inlineStr">
@@ -24165,7 +24165,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a8</t>
+          <t>6a4af7efae633549bd0f03a7</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -24178,23 +24178,23 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F426" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G426" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -24221,7 +24221,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03aa</t>
+          <t>6a4af7efae633549bd0f03a5</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -24234,23 +24234,23 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G427" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -24277,7 +24277,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a9</t>
+          <t>6a4af7efae633549bd0f03a2</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -24290,23 +24290,23 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F428" t="n">
+        <v>3</v>
+      </c>
+      <c r="G428" t="n">
         <v>0</v>
       </c>
-      <c r="G428" t="n">
-        <v>5</v>
-      </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -24333,7 +24333,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a1</t>
+          <t>6a4af7efae633549bd0f03a3</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -24346,33 +24346,33 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G429" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
@@ -24389,7 +24389,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a7</t>
+          <t>6a4af7efae633549bd0f03a8</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -24402,23 +24402,23 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G430" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -24445,7 +24445,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a2</t>
+          <t>6a4af7efae633549bd0f03aa</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -24458,20 +24458,20 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F431" t="n">
+        <v>2</v>
+      </c>
+      <c r="G431" t="n">
         <v>3</v>
       </c>
-      <c r="G431" t="n">
-        <v>0</v>
-      </c>
       <c r="H431" t="inlineStr">
         <is>
           <t>2026-09-05</t>
@@ -24479,12 +24479,12 @@
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
@@ -24501,7 +24501,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b0</t>
+          <t>6a4af7efae633549bd0f03b1</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -24514,16 +24514,20 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
-        </is>
-      </c>
-      <c r="F432" t="inlineStr"/>
-      <c r="G432" t="inlineStr"/>
+          <t>52038563b8d07d930b00008a</t>
+        </is>
+      </c>
+      <c r="F432" t="n">
+        <v>2</v>
+      </c>
+      <c r="G432" t="n">
+        <v>1</v>
+      </c>
       <c r="H432" t="inlineStr">
         <is>
           <t>2026-09-12</t>
@@ -24531,12 +24535,12 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
@@ -24544,12 +24548,16 @@
           <t>running</t>
         </is>
       </c>
-      <c r="L432" t="inlineStr"/>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ad</t>
+          <t>6a4af7efae633549bd0f03ac</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -24562,29 +24570,33 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
-        </is>
-      </c>
-      <c r="F433" t="inlineStr"/>
-      <c r="G433" t="inlineStr"/>
+          <t>51b889b1e401a15f2c0000f0</t>
+        </is>
+      </c>
+      <c r="F433" t="n">
+        <v>1</v>
+      </c>
+      <c r="G433" t="n">
+        <v>1</v>
+      </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
@@ -24592,12 +24604,16 @@
           <t>running</t>
         </is>
       </c>
-      <c r="L433" t="inlineStr"/>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b2</t>
+          <t>6a4af7efae633549bd0f03ae</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -24610,29 +24626,29 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr"/>
       <c r="H434" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
@@ -24645,7 +24661,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03af</t>
+          <t>6a4af7efae633549bd0f03b2</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -24658,29 +24674,33 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
-        </is>
-      </c>
-      <c r="F435" t="inlineStr"/>
-      <c r="G435" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000ca</t>
+        </is>
+      </c>
+      <c r="F435" t="n">
+        <v>4</v>
+      </c>
+      <c r="G435" t="n">
+        <v>1</v>
+      </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
@@ -24688,12 +24708,16 @@
           <t>running</t>
         </is>
       </c>
-      <c r="L435" t="inlineStr"/>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b1</t>
+          <t>6a4af7efae633549bd0f03b3</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -24706,29 +24730,29 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F436" t="inlineStr"/>
       <c r="G436" t="inlineStr"/>
       <c r="H436" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
@@ -24741,7 +24765,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ac</t>
+          <t>6a4af7efae633549bd0f03b4</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -24754,29 +24778,33 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
-        </is>
-      </c>
-      <c r="F437" t="inlineStr"/>
-      <c r="G437" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000cb</t>
+        </is>
+      </c>
+      <c r="F437" t="n">
+        <v>1</v>
+      </c>
+      <c r="G437" t="n">
+        <v>0</v>
+      </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
@@ -24784,12 +24812,16 @@
           <t>running</t>
         </is>
       </c>
-      <c r="L437" t="inlineStr"/>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b3</t>
+          <t>6a4af7efae633549bd0f03b0</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -24802,29 +24834,33 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
-        </is>
-      </c>
-      <c r="F438" t="inlineStr"/>
-      <c r="G438" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000d0</t>
+        </is>
+      </c>
+      <c r="F438" t="n">
+        <v>0</v>
+      </c>
+      <c r="G438" t="n">
+        <v>2</v>
+      </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K438" t="inlineStr">
@@ -24832,7 +24868,11 @@
           <t>running</t>
         </is>
       </c>
-      <c r="L438" t="inlineStr"/>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -24885,7 +24925,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b4</t>
+          <t>6a4af7efae633549bd0f03af</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -24898,33 +24938,29 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
-        </is>
-      </c>
-      <c r="F440" t="n">
-        <v>1</v>
-      </c>
-      <c r="G440" t="n">
-        <v>0</v>
-      </c>
+          <t>504e581e4d8bec9a670000c7</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr"/>
       <c r="H440" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
@@ -24932,16 +24968,12 @@
           <t>running</t>
         </is>
       </c>
-      <c r="L440" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="L440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ae</t>
+          <t>6a4af7efae633549bd0f03ad</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -24954,12 +24986,12 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -24971,12 +25003,12 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K441" t="inlineStr">
@@ -24989,7 +25021,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c7</t>
+          <t>6a4af7f0ae633549bd0f03ca</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -25002,12 +25034,12 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -25019,12 +25051,12 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
@@ -25037,7 +25069,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c2</t>
+          <t>6a4af7f0ae633549bd0f03cb</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -25050,29 +25082,29 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
       <c r="G443" t="inlineStr"/>
       <c r="H443" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K443" t="inlineStr">
@@ -25181,7 +25213,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c9</t>
+          <t>6a4af7f0ae633549bd0f03c3</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -25194,29 +25226,29 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
       <c r="G446" t="inlineStr"/>
       <c r="H446" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K446" t="inlineStr">
@@ -25229,7 +25261,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c5</t>
+          <t>6a4af7f0ae633549bd0f03c2</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -25242,29 +25274,29 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
       <c r="G447" t="inlineStr"/>
       <c r="H447" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K447" t="inlineStr">
@@ -25277,7 +25309,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cb</t>
+          <t>6a4af7f0ae633549bd0f03c5</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -25290,12 +25322,12 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
@@ -25325,7 +25357,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c3</t>
+          <t>6a4af7f0ae633549bd0f03c9</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -25338,29 +25370,29 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
       <c r="G449" t="inlineStr"/>
       <c r="H449" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K449" t="inlineStr">
@@ -25373,7 +25405,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ca</t>
+          <t>6a4af7f0ae633549bd0f03c6</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -25386,19 +25418,19 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
       <c r="G450" t="inlineStr"/>
       <c r="H450" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -25421,7 +25453,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c6</t>
+          <t>6a4af7f0ae633549bd0f03c7</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -25434,29 +25466,29 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr"/>
       <c r="H451" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K451" t="inlineStr">
@@ -25469,7 +25501,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ce</t>
+          <t>6a4af7f0ae633549bd0f03d1</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -25482,12 +25514,12 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
@@ -25517,7 +25549,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d4</t>
+          <t>6a4af7f0ae633549bd0f03d2</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -25530,12 +25562,12 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
@@ -25565,7 +25597,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cd</t>
+          <t>6a4af7f0ae633549bd0f03d3</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -25578,12 +25610,12 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F454" t="inlineStr"/>
@@ -25613,7 +25645,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cf</t>
+          <t>6a4af7f0ae633549bd0f03d4</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -25626,12 +25658,12 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -25661,7 +25693,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d0</t>
+          <t>6a4af7f0ae633549bd0f03d5</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -25674,12 +25706,12 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
@@ -25709,7 +25741,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d5</t>
+          <t>6a4af7f0ae633549bd0f03ce</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -25722,12 +25754,12 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -25757,7 +25789,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d1</t>
+          <t>6a4af7f0ae633549bd0f03d6</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -25770,12 +25802,12 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -25805,7 +25837,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d2</t>
+          <t>6a4af7f0ae633549bd0f03cd</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -25818,12 +25850,12 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -25853,7 +25885,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d3</t>
+          <t>6a4af7f0ae633549bd0f03cf</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -25866,12 +25898,12 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
@@ -25901,7 +25933,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d6</t>
+          <t>6a4af7f0ae633549bd0f03d0</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -25914,12 +25946,12 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -25949,7 +25981,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03db</t>
+          <t>6a4af7f0ae633549bd0f03e1</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -25962,12 +25994,12 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
@@ -25997,7 +26029,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dd</t>
+          <t>6a4af7f0ae633549bd0f03d8</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -26010,12 +26042,12 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -26045,7 +26077,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d9</t>
+          <t>6a4af7f0ae633549bd0f03db</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -26058,12 +26090,12 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -26093,7 +26125,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03da</t>
+          <t>6a4af7f0ae633549bd0f03dd</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -26106,12 +26138,12 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
@@ -26141,7 +26173,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03de</t>
+          <t>6a4af7f0ae633549bd0f03df</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -26154,12 +26186,12 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F466" t="inlineStr"/>
@@ -26189,7 +26221,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e0</t>
+          <t>6a4af7f0ae633549bd0f03da</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -26202,12 +26234,12 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -26237,7 +26269,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03df</t>
+          <t>6a4af7f0ae633549bd0f03e0</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -26250,12 +26282,12 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F468" t="inlineStr"/>
@@ -26285,7 +26317,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dc</t>
+          <t>6a4af7f0ae633549bd0f03d9</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -26298,12 +26330,12 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F469" t="inlineStr"/>
@@ -26333,7 +26365,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d8</t>
+          <t>6a4af7f0ae633549bd0f03de</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -26346,12 +26378,12 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
@@ -26381,7 +26413,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e1</t>
+          <t>6a4af7f0ae633549bd0f03dc</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -26394,12 +26426,12 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -26429,7 +26461,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e4</t>
+          <t>6a4af7f0ae633549bd0f03e8</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -26442,12 +26474,12 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -26477,7 +26509,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e6</t>
+          <t>6a4af7f0ae633549bd0f03e7</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -26490,12 +26522,12 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -26507,12 +26539,12 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
@@ -26525,7 +26557,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ec</t>
+          <t>6a4af7f0ae633549bd0f03e5</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -26538,12 +26570,12 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -26573,7 +26605,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e7</t>
+          <t>6a4af7f0ae633549bd0f03ea</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -26586,12 +26618,12 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -26621,7 +26653,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e8</t>
+          <t>6a4af7f0ae633549bd0f03ec</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -26634,12 +26666,12 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
@@ -26669,7 +26701,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03eb</t>
+          <t>6a4af7f0ae633549bd0f03e3</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -26682,12 +26714,12 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
@@ -26717,7 +26749,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e5</t>
+          <t>6a4af7f0ae633549bd0f03e9</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -26730,12 +26762,12 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -26765,7 +26797,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ea</t>
+          <t>6a4af7f0ae633549bd0f03e4</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -26778,12 +26810,12 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
@@ -26813,7 +26845,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e9</t>
+          <t>6a4af7f0ae633549bd0f03e6</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -26826,12 +26858,12 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -26843,12 +26875,12 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K480" t="inlineStr">
@@ -26861,7 +26893,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e3</t>
+          <t>6a4af7f0ae633549bd0f03eb</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -26874,12 +26906,12 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
@@ -26909,7 +26941,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f3</t>
+          <t>6a4af7f0ae633549bd0f03f2</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -26922,12 +26954,12 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -26957,7 +26989,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ee</t>
+          <t>6a4af7f0ae633549bd0f03f7</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -26970,12 +27002,12 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -27005,7 +27037,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f4</t>
+          <t>6a4af7f0ae633549bd0f03f1</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -27018,12 +27050,12 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F484" t="inlineStr"/>
@@ -27053,7 +27085,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f6</t>
+          <t>6a4af7f0ae633549bd0f03f0</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -27066,12 +27098,12 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -27101,7 +27133,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f2</t>
+          <t>6a4af7f0ae633549bd0f03f6</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -27114,12 +27146,12 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
@@ -27149,7 +27181,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f5</t>
+          <t>6a4af7f0ae633549bd0f03ee</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -27162,12 +27194,12 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F487" t="inlineStr"/>
@@ -27197,7 +27229,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ef</t>
+          <t>6a4af7f0ae633549bd0f03f3</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -27210,12 +27242,12 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -27245,7 +27277,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f0</t>
+          <t>6a4af7f0ae633549bd0f03f4</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -27258,12 +27290,12 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -27293,7 +27325,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f1</t>
+          <t>6a4af7f0ae633549bd0f03ef</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -27306,12 +27338,12 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -27341,7 +27373,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f7</t>
+          <t>6a4af7f0ae633549bd0f03f5</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -27354,12 +27386,12 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -27389,7 +27421,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0402</t>
+          <t>6a4af7f0ae633549bd0f03fa</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -27402,12 +27434,12 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
@@ -27437,7 +27469,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fa</t>
+          <t>6a4af7f0ae633549bd0f03fb</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -27450,12 +27482,12 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
@@ -27485,7 +27517,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fc</t>
+          <t>6a4af7f1ae633549bd0f0401</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -27498,12 +27530,12 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F494" t="inlineStr"/>
@@ -27533,7 +27565,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0401</t>
+          <t>6a4af7f0ae633549bd0f03f9</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -27546,12 +27578,12 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -27581,7 +27613,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f9</t>
+          <t>6a4af7f1ae633549bd0f03fc</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -27594,12 +27626,12 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -27725,7 +27757,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0400</t>
+          <t>6a4af7f1ae633549bd0f03ff</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -27738,12 +27770,12 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -27773,7 +27805,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03ff</t>
+          <t>6a4af7f1ae633549bd0f0400</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -27786,12 +27818,12 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -27821,7 +27853,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fb</t>
+          <t>6a4af7f1ae633549bd0f0402</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -27834,12 +27866,12 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -27869,7 +27901,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040c</t>
+          <t>6a4af7f1ae633549bd0f0407</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -27882,12 +27914,12 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -27917,7 +27949,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0407</t>
+          <t>6a4af7f1ae633549bd0f0405</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -27930,12 +27962,12 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -28013,7 +28045,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0404</t>
+          <t>6a4af7f1ae633549bd0f0409</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -28026,12 +28058,12 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -28061,7 +28093,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0405</t>
+          <t>6a4af7f1ae633549bd0f0404</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -28074,12 +28106,12 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F506" t="inlineStr"/>
@@ -28157,7 +28189,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0409</t>
+          <t>6a4af7f1ae633549bd0f040b</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -28170,12 +28202,12 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -28205,7 +28237,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040b</t>
+          <t>6a4af7f1ae633549bd0f0406</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -28218,12 +28250,12 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
@@ -28253,7 +28285,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0406</t>
+          <t>6a4af7f1ae633549bd0f040a</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -28266,12 +28298,12 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
@@ -28301,7 +28333,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040a</t>
+          <t>6a4af7f1ae633549bd0f040c</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -28314,12 +28346,12 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -28349,7 +28381,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040f</t>
+          <t>6a4af7f1ae633549bd0f0412</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -28362,12 +28394,12 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F512" t="inlineStr"/>
@@ -28397,7 +28429,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0410</t>
+          <t>6a4af7f1ae633549bd0f0416</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -28410,12 +28442,12 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F513" t="inlineStr"/>
@@ -28445,7 +28477,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0413</t>
+          <t>6a4af7f1ae633549bd0f040f</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -28458,12 +28490,12 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -28493,7 +28525,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0418</t>
+          <t>6a4af7f1ae633549bd0f0415</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -28506,12 +28538,12 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F515" t="inlineStr"/>
@@ -28541,7 +28573,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0412</t>
+          <t>6a4af7f1ae633549bd0f0410</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -28554,12 +28586,12 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F516" t="inlineStr"/>
@@ -28589,7 +28621,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0416</t>
+          <t>6a4af7f1ae633549bd0f0413</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -28602,12 +28634,12 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F517" t="inlineStr"/>
@@ -28637,7 +28669,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0414</t>
+          <t>6a4af7f1ae633549bd0f0418</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -28650,12 +28682,12 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
@@ -28733,7 +28765,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0415</t>
+          <t>6a4af7f1ae633549bd0f0414</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -28746,12 +28778,12 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F520" t="inlineStr"/>
@@ -28829,7 +28861,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041e</t>
+          <t>6a4af7f1ae633549bd0f041d</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -28842,12 +28874,12 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F522" t="inlineStr"/>
@@ -28925,7 +28957,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041d</t>
+          <t>6a4af7f1ae633549bd0f041c</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -28938,12 +28970,12 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F524" t="inlineStr"/>
@@ -28973,7 +29005,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041c</t>
+          <t>6a4af7f1ae633549bd0f0420</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -28986,12 +29018,12 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F525" t="inlineStr"/>
@@ -29021,7 +29053,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0420</t>
+          <t>6a4af7f1ae633549bd0f041f</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -29034,12 +29066,12 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F526" t="inlineStr"/>
@@ -29117,7 +29149,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041a</t>
+          <t>6a4af7f1ae633549bd0f0423</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -29130,12 +29162,12 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F528" t="inlineStr"/>
@@ -29165,7 +29197,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0423</t>
+          <t>6a4af7f1ae633549bd0f041a</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -29178,12 +29210,12 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -29213,7 +29245,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041f</t>
+          <t>6a4af7f1ae633549bd0f041e</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -29226,12 +29258,12 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -29357,7 +29389,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042b</t>
+          <t>6a4af7f1ae633549bd0f042d</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -29370,12 +29402,12 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
@@ -29405,7 +29437,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042d</t>
+          <t>6a4af7f1ae633549bd0f042b</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -29418,12 +29450,12 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
@@ -29789,7 +29821,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0437</t>
+          <t>6a4af7f1ae633549bd0f0433</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -29802,12 +29834,12 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F542" t="inlineStr"/>
@@ -29837,7 +29869,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0430</t>
+          <t>6a4af7f1ae633549bd0f0431</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -29850,12 +29882,12 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F543" t="inlineStr"/>
@@ -29885,7 +29917,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0432</t>
+          <t>6a4af7f1ae633549bd0f0430</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -29898,12 +29930,12 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
@@ -29933,7 +29965,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0435</t>
+          <t>6a4af7f1ae633549bd0f0436</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -29946,12 +29978,12 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -29981,7 +30013,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0439</t>
+          <t>6a4af7f1ae633549bd0f0434</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -29994,12 +30026,12 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -30029,7 +30061,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0438</t>
+          <t>6a4af7f1ae633549bd0f0437</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -30042,12 +30074,12 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
@@ -30077,7 +30109,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0431</t>
+          <t>6a4af7f1ae633549bd0f0439</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -30090,12 +30122,12 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -30125,7 +30157,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0433</t>
+          <t>6a4af7f1ae633549bd0f0432</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -30138,12 +30170,12 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -30173,7 +30205,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0436</t>
+          <t>6a4af7f1ae633549bd0f0435</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -30186,12 +30218,12 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
@@ -30221,7 +30253,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0434</t>
+          <t>6a4af7f1ae633549bd0f0438</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -30234,12 +30266,12 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F551" t="inlineStr"/>
@@ -30269,7 +30301,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043d</t>
+          <t>6a4af7f1ae633549bd0f043e</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -30282,12 +30314,12 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -30317,7 +30349,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0441</t>
+          <t>6a4af7f2ae633549bd0f043f</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -30330,12 +30362,12 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -30461,7 +30493,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043e</t>
+          <t>6a4af7f2ae633549bd0f0442</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -30474,12 +30506,12 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -30509,7 +30541,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0442</t>
+          <t>6a4af7f1ae633549bd0f043d</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -30522,12 +30554,12 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -30557,7 +30589,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f043f</t>
+          <t>6a4af7f2ae633549bd0f0441</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -30570,12 +30602,12 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
@@ -30605,7 +30637,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0443</t>
+          <t>6a4af7f2ae633549bd0f0444</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -30618,12 +30650,12 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F559" t="inlineStr"/>
@@ -30653,7 +30685,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043b</t>
+          <t>6a4af7f2ae633549bd0f0443</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -30666,12 +30698,12 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -30701,7 +30733,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0444</t>
+          <t>6a4af7f1ae633549bd0f043b</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -30714,12 +30746,12 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -30749,7 +30781,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044d</t>
+          <t>6a4af7f2ae633549bd0f0447</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -30762,12 +30794,12 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -30797,7 +30829,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044e</t>
+          <t>6a4af7f2ae633549bd0f0448</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -30810,12 +30842,12 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F563" t="inlineStr"/>
@@ -30845,7 +30877,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044f</t>
+          <t>6a4af7f2ae633549bd0f044a</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -30858,12 +30890,12 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F564" t="inlineStr"/>
@@ -30893,7 +30925,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0446</t>
+          <t>6a4af7f2ae633549bd0f044e</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -30906,12 +30938,12 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F565" t="inlineStr"/>
@@ -30941,7 +30973,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044b</t>
+          <t>6a4af7f2ae633549bd0f044d</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -30954,12 +30986,12 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
@@ -30989,7 +31021,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044a</t>
+          <t>6a4af7f2ae633549bd0f044c</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -31002,12 +31034,12 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F567" t="inlineStr"/>
@@ -31037,7 +31069,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0447</t>
+          <t>6a4af7f2ae633549bd0f0449</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -31050,12 +31082,12 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F568" t="inlineStr"/>
@@ -31085,7 +31117,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0448</t>
+          <t>6a4af7f2ae633549bd0f044f</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -31098,12 +31130,12 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F569" t="inlineStr"/>
@@ -31133,7 +31165,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0449</t>
+          <t>6a4af7f2ae633549bd0f044b</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -31146,12 +31178,12 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F570" t="inlineStr"/>
@@ -31181,7 +31213,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044c</t>
+          <t>6a4af7f2ae633549bd0f0446</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -31194,12 +31226,12 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -31229,7 +31261,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0452</t>
+          <t>6a4af7f2ae633549bd0f0455</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -31242,12 +31274,12 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F572" t="inlineStr"/>
@@ -31325,7 +31357,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0455</t>
+          <t>6a4af7f2ae633549bd0f0456</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -31338,12 +31370,12 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F574" t="inlineStr"/>
@@ -31373,7 +31405,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0456</t>
+          <t>6a4af7f2ae633549bd0f0457</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -31386,12 +31418,12 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -31421,7 +31453,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0457</t>
+          <t>6a4af7f2ae633549bd0f045a</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -31434,12 +31466,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F576" t="inlineStr"/>
@@ -31469,7 +31501,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045a</t>
+          <t>6a4af7f2ae633549bd0f0453</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -31482,12 +31514,12 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -31517,7 +31549,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0453</t>
+          <t>6a4af7f2ae633549bd0f0459</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -31530,12 +31562,12 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -31661,7 +31693,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0459</t>
+          <t>6a4af7f2ae633549bd0f0452</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -31674,12 +31706,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -31709,7 +31741,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0462</t>
+          <t>6a4af7f2ae633549bd0f0460</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -31722,12 +31754,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F582" t="inlineStr"/>
@@ -31757,7 +31789,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0461</t>
+          <t>6a4af7f2ae633549bd0f045e</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -31770,12 +31802,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -31805,7 +31837,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0463</t>
+          <t>6a4af7f2ae633549bd0f045f</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -31818,12 +31850,12 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F584" t="inlineStr"/>
@@ -31853,7 +31885,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045d</t>
+          <t>6a4af7f2ae633549bd0f0464</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -31866,12 +31898,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -31901,7 +31933,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0465</t>
+          <t>6a4af7f2ae633549bd0f045c</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -31914,12 +31946,12 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F586" t="inlineStr"/>
@@ -31949,7 +31981,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0460</t>
+          <t>6a4af7f2ae633549bd0f0461</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -31962,12 +31994,12 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -31997,7 +32029,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045f</t>
+          <t>6a4af7f2ae633549bd0f0463</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -32010,12 +32042,12 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -32045,7 +32077,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0464</t>
+          <t>6a4af7f2ae633549bd0f0462</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -32058,12 +32090,12 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -32093,7 +32125,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045e</t>
+          <t>6a4af7f2ae633549bd0f045d</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -32106,12 +32138,12 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -32141,7 +32173,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045c</t>
+          <t>6a4af7f2ae633549bd0f0465</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -32154,12 +32186,12 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -32189,7 +32221,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0468</t>
+          <t>6a4af7f2ae633549bd0f0467</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -32202,12 +32234,12 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F592" t="inlineStr"/>
@@ -32237,7 +32269,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0470</t>
+          <t>6a4af7f2ae633549bd0f046a</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -32250,12 +32282,12 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F593" t="inlineStr"/>
@@ -32285,7 +32317,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046e</t>
+          <t>6a4af7f2ae633549bd0f046c</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -32298,12 +32330,12 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F594" t="inlineStr"/>
@@ -32333,7 +32365,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0467</t>
+          <t>6a4af7f2ae633549bd0f046f</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -32346,12 +32378,12 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F595" t="inlineStr"/>
@@ -32381,7 +32413,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046d</t>
+          <t>6a4af7f2ae633549bd0f046b</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -32394,12 +32426,12 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F596" t="inlineStr"/>
@@ -32429,7 +32461,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0469</t>
+          <t>6a4af7f2ae633549bd0f046e</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -32442,12 +32474,12 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F597" t="inlineStr"/>
@@ -32477,7 +32509,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046a</t>
+          <t>6a4af7f2ae633549bd0f0468</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -32490,12 +32522,12 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F598" t="inlineStr"/>
@@ -32525,7 +32557,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046c</t>
+          <t>6a4af7f2ae633549bd0f0470</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -32538,12 +32570,12 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -32573,7 +32605,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046b</t>
+          <t>6a4af7f2ae633549bd0f0469</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -32586,12 +32618,12 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F600" t="inlineStr"/>
@@ -32621,7 +32653,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046f</t>
+          <t>6a4af7f2ae633549bd0f046d</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -32634,12 +32666,12 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F601" t="inlineStr"/>
@@ -32669,7 +32701,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0474</t>
+          <t>6a4af7f2ae633549bd0f0475</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -32682,12 +32714,12 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F602" t="inlineStr"/>
@@ -32717,7 +32749,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0475</t>
+          <t>6a4af7f2ae633549bd0f0479</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -32730,12 +32762,12 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
@@ -32813,7 +32845,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0477</t>
+          <t>6a4af7f2ae633549bd0f047a</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -32826,12 +32858,12 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F605" t="inlineStr"/>
@@ -32861,7 +32893,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0472</t>
+          <t>6a4af7f2ae633549bd0f0478</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -32874,12 +32906,12 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
@@ -32909,7 +32941,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0473</t>
+          <t>6a4af7f2ae633549bd0f0477</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -32922,12 +32954,12 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -32957,7 +32989,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0476</t>
+          <t>6a4af7f2ae633549bd0f0472</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -32970,12 +33002,12 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
@@ -33005,7 +33037,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0478</t>
+          <t>6a4af7f2ae633549bd0f0473</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -33018,12 +33050,12 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F609" t="inlineStr"/>
@@ -33053,7 +33085,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047a</t>
+          <t>6a4af7f2ae633549bd0f0476</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -33066,12 +33098,12 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F610" t="inlineStr"/>
@@ -33101,7 +33133,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0479</t>
+          <t>6a4af7f2ae633549bd0f0474</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -33114,12 +33146,12 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -33149,7 +33181,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0480</t>
+          <t>6a4af7f2ae633549bd0f047e</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -33162,12 +33194,12 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F612" t="inlineStr"/>
@@ -33341,7 +33373,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0482</t>
+          <t>6a4af7f2ae633549bd0f047d</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -33354,12 +33386,12 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F616" t="inlineStr"/>
@@ -33389,7 +33421,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0486</t>
+          <t>6a4af7f2ae633549bd0f047f</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -33402,12 +33434,12 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F617" t="inlineStr"/>
@@ -33437,7 +33469,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047d</t>
+          <t>6a4af7f2ae633549bd0f0483</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -33450,12 +33482,12 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -33485,7 +33517,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0483</t>
+          <t>6a4af7f2ae633549bd0f0482</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -33498,12 +33530,12 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -33533,7 +33565,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047e</t>
+          <t>6a4af7f3ae633549bd0f0486</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -33546,12 +33578,12 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -33581,7 +33613,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047f</t>
+          <t>6a4af7f2ae633549bd0f0480</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -33594,12 +33626,12 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F621" t="inlineStr"/>
@@ -33629,7 +33661,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0490</t>
+          <t>6a4af7f3ae633549bd0f0488</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -33642,12 +33674,12 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F622" t="inlineStr"/>
@@ -33677,7 +33709,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048b</t>
+          <t>6a4af7f3ae633549bd0f0489</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -33690,12 +33722,12 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F623" t="inlineStr"/>
@@ -33725,7 +33757,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048c</t>
+          <t>6a4af7f3ae633549bd0f048d</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -33738,12 +33770,12 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
@@ -33773,7 +33805,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0489</t>
+          <t>6a4af7f3ae633549bd0f048f</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -33786,12 +33818,12 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F625" t="inlineStr"/>
@@ -33821,7 +33853,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0491</t>
+          <t>6a4af7f3ae633549bd0f048b</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -33834,12 +33866,12 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F626" t="inlineStr"/>
@@ -33869,7 +33901,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048d</t>
+          <t>6a4af7f3ae633549bd0f0491</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -33882,12 +33914,12 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F627" t="inlineStr"/>
@@ -33917,7 +33949,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048f</t>
+          <t>6a4af7f3ae633549bd0f048a</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -33930,12 +33962,12 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F628" t="inlineStr"/>
@@ -33965,7 +33997,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0488</t>
+          <t>6a4af7f3ae633549bd0f048c</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -33978,12 +34010,12 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F629" t="inlineStr"/>
@@ -34013,7 +34045,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048e</t>
+          <t>6a4af7f3ae633549bd0f0490</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -34026,12 +34058,12 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F630" t="inlineStr"/>
@@ -34061,7 +34093,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048a</t>
+          <t>6a4af7f3ae633549bd0f048e</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -34074,12 +34106,12 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F631" t="inlineStr"/>
@@ -34109,7 +34141,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0496</t>
+          <t>6a4af7f3ae633549bd0f049b</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -34122,12 +34154,12 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F632" t="inlineStr"/>
@@ -34157,7 +34189,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0493</t>
+          <t>6a4af7f3ae633549bd0f049c</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -34170,12 +34202,12 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F633" t="inlineStr"/>
@@ -34205,7 +34237,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0499</t>
+          <t>6a4af7f3ae633549bd0f049a</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -34218,12 +34250,12 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F634" t="inlineStr"/>
@@ -34349,7 +34381,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049a</t>
+          <t>6a4af7f3ae633549bd0f0499</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -34362,12 +34394,12 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F637" t="inlineStr"/>
@@ -34397,7 +34429,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049b</t>
+          <t>6a4af7f3ae633549bd0f0493</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -34410,12 +34442,12 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F638" t="inlineStr"/>
@@ -34445,7 +34477,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049c</t>
+          <t>6a4af7f3ae633549bd0f0496</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -34458,12 +34490,12 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
@@ -34493,7 +34525,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0498</t>
+          <t>6a4af7f3ae633549bd0f0495</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -34506,12 +34538,12 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F640" t="inlineStr"/>
@@ -34541,7 +34573,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0495</t>
+          <t>6a4af7f3ae633549bd0f0498</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -34554,12 +34586,12 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F641" t="inlineStr"/>
@@ -34589,7 +34621,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a0</t>
+          <t>6a4af7f3ae633549bd0f049e</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -34602,12 +34634,12 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F642" t="inlineStr"/>
@@ -34685,7 +34717,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a2</t>
+          <t>6a4af7f3ae633549bd0f04a1</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -34698,12 +34730,12 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -34733,7 +34765,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a3</t>
+          <t>6a4af7f3ae633549bd0f04a5</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -34746,12 +34778,12 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F645" t="inlineStr"/>
@@ -34781,7 +34813,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a4</t>
+          <t>6a4af7f3ae633549bd0f04a6</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -34794,12 +34826,12 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F646" t="inlineStr"/>
@@ -34829,7 +34861,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a7</t>
+          <t>6a4af7f3ae633549bd0f04a4</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -34842,12 +34874,12 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -34877,7 +34909,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a6</t>
+          <t>6a4af7f3ae633549bd0f04a0</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -34890,12 +34922,12 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -34925,7 +34957,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a5</t>
+          <t>6a4af7f3ae633549bd0f04a2</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -34938,12 +34970,12 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -34973,7 +35005,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a1</t>
+          <t>6a4af7f3ae633549bd0f04a3</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -34986,12 +35018,12 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F650" t="inlineStr"/>
@@ -35021,7 +35053,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049e</t>
+          <t>6a4af7f3ae633549bd0f04a7</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -35034,12 +35066,12 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F651" t="inlineStr"/>
@@ -35069,7 +35101,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04af</t>
+          <t>6a4af7f3ae633549bd0f04b1</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -35082,12 +35114,12 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -35117,7 +35149,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ab</t>
+          <t>6a4af7f3ae633549bd0f04ac</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -35130,12 +35162,12 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F653" t="inlineStr"/>
@@ -35165,7 +35197,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b0</t>
+          <t>6a4af7f3ae633549bd0f04ae</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -35178,12 +35210,12 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F654" t="inlineStr"/>
@@ -35213,7 +35245,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ad</t>
+          <t>6a4af7f3ae633549bd0f04ab</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -35226,12 +35258,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F655" t="inlineStr"/>
@@ -35261,7 +35293,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b1</t>
+          <t>6a4af7f3ae633549bd0f04ad</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -35274,12 +35306,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F656" t="inlineStr"/>
@@ -35309,7 +35341,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ac</t>
+          <t>6a4af7f3ae633549bd0f04af</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -35322,12 +35354,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F657" t="inlineStr"/>
@@ -35357,7 +35389,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ae</t>
+          <t>6a4af7f3ae633549bd0f04a9</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -35370,12 +35402,12 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F658" t="inlineStr"/>
@@ -35405,7 +35437,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b2</t>
+          <t>6a4af7f3ae633549bd0f04aa</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -35418,12 +35450,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -35453,7 +35485,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a9</t>
+          <t>6a4af7f3ae633549bd0f04b0</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -35466,12 +35498,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F660" t="inlineStr"/>
@@ -35501,7 +35533,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04aa</t>
+          <t>6a4af7f3ae633549bd0f04b2</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -35514,12 +35546,12 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F661" t="inlineStr"/>
@@ -35549,7 +35581,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b9</t>
+          <t>6a4af7f3ae633549bd0f04b8</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -35562,12 +35594,12 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F662" t="inlineStr"/>
@@ -35597,7 +35629,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bc</t>
+          <t>6a4af7f3ae633549bd0f04bb</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -35610,12 +35642,12 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F663" t="inlineStr"/>
@@ -35645,7 +35677,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ba</t>
+          <t>6a4af7f3ae633549bd0f04b9</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -35658,12 +35690,12 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F664" t="inlineStr"/>
@@ -35693,7 +35725,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bd</t>
+          <t>6a4af7f3ae633549bd0f04ba</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -35706,12 +35738,12 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F665" t="inlineStr"/>
@@ -35741,7 +35773,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bb</t>
+          <t>6a4af7f3ae633549bd0f04bd</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -35754,12 +35786,12 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F666" t="inlineStr"/>
@@ -35789,7 +35821,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b6</t>
+          <t>6a4af7f3ae633549bd0f04b5</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -35802,12 +35834,12 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F667" t="inlineStr"/>
@@ -35837,7 +35869,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b4</t>
+          <t>6a4af7f3ae633549bd0f04bc</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -35850,12 +35882,12 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F668" t="inlineStr"/>
@@ -35885,7 +35917,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b7</t>
+          <t>6a4af7f3ae633549bd0f04b4</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -35898,12 +35930,12 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
@@ -35933,7 +35965,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b8</t>
+          <t>6a4af7f3ae633549bd0f04b7</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -35946,12 +35978,12 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F670" t="inlineStr"/>
@@ -35981,7 +36013,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b5</t>
+          <t>6a4af7f3ae633549bd0f04b6</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -35994,12 +36026,12 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F671" t="inlineStr"/>
@@ -36029,7 +36061,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c3</t>
+          <t>6a4af7f3ae633549bd0f04c0</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -36042,12 +36074,12 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F672" t="inlineStr"/>
@@ -36077,7 +36109,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c1</t>
+          <t>6a4af7f3ae633549bd0f04c5</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -36090,12 +36122,12 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
@@ -36125,7 +36157,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c6</t>
+          <t>6a4af7f3ae633549bd0f04bf</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -36138,12 +36170,12 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F674" t="inlineStr"/>
@@ -36221,7 +36253,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c2</t>
+          <t>6a4af7f3ae633549bd0f04c4</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -36234,12 +36266,12 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -36269,7 +36301,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c8</t>
+          <t>6a4af7f3ae633549bd0f04c1</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -36282,12 +36314,12 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
@@ -36317,7 +36349,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c0</t>
+          <t>6a4af7f3ae633549bd0f04c3</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -36330,12 +36362,12 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F678" t="inlineStr"/>
@@ -36365,7 +36397,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c5</t>
+          <t>6a4af7f3ae633549bd0f04c6</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -36378,12 +36410,12 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F679" t="inlineStr"/>
@@ -36413,7 +36445,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bf</t>
+          <t>6a4af7f3ae633549bd0f04c8</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -36426,12 +36458,12 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F680" t="inlineStr"/>
@@ -36461,7 +36493,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c4</t>
+          <t>6a4af7f3ae633549bd0f04c2</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -36474,12 +36506,12 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
@@ -36509,7 +36541,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cf</t>
+          <t>6a4af7f4ae633549bd0f04cc</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -36522,12 +36554,12 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F682" t="inlineStr"/>
@@ -36557,7 +36589,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cd</t>
+          <t>6a4af7f4ae633549bd0f04d3</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -36570,12 +36602,12 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F683" t="inlineStr"/>
@@ -36605,7 +36637,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d3</t>
+          <t>6a4af7f4ae633549bd0f04ce</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -36618,12 +36650,12 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F684" t="inlineStr"/>
@@ -36653,7 +36685,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d0</t>
+          <t>6a4af7f4ae633549bd0f04cd</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -36666,12 +36698,12 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F685" t="inlineStr"/>
@@ -36701,7 +36733,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ce</t>
+          <t>6a4af7f4ae633549bd0f04d0</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -36714,12 +36746,12 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F686" t="inlineStr"/>
@@ -36749,7 +36781,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ca</t>
+          <t>6a4af7f4ae633549bd0f04cf</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -36762,12 +36794,12 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F687" t="inlineStr"/>
@@ -36797,7 +36829,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cb</t>
+          <t>6a4af7f4ae633549bd0f04d1</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -36810,12 +36842,12 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F688" t="inlineStr"/>
@@ -36845,7 +36877,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cc</t>
+          <t>6a4af7f4ae633549bd0f04ca</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -36858,12 +36890,12 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F689" t="inlineStr"/>
@@ -36941,7 +36973,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d1</t>
+          <t>6a4af7f4ae633549bd0f04cb</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -36954,12 +36986,12 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F691" t="inlineStr"/>
@@ -36989,7 +37021,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d8</t>
+          <t>6a4af7f4ae633549bd0f04de</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -37002,12 +37034,12 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F692" t="inlineStr"/>
@@ -37037,7 +37069,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dc</t>
+          <t>6a4af7f4ae633549bd0f04d8</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -37050,12 +37082,12 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F693" t="inlineStr"/>
@@ -37085,7 +37117,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04de</t>
+          <t>6a4af7f4ae633549bd0f04d9</t>
         </is>
       </c>
       <c r="B694" t="n">
@@ -37098,12 +37130,12 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F694" t="inlineStr"/>
@@ -37133,7 +37165,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d7</t>
+          <t>6a4af7f4ae633549bd0f04dc</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -37146,12 +37178,12 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F695" t="inlineStr"/>
@@ -37181,7 +37213,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04da</t>
+          <t>6a4af7f4ae633549bd0f04db</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -37194,12 +37226,12 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F696" t="inlineStr"/>
@@ -37229,7 +37261,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d6</t>
+          <t>6a4af7f4ae633549bd0f04d5</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -37242,12 +37274,12 @@
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F697" t="inlineStr"/>
@@ -37277,7 +37309,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d5</t>
+          <t>6a4af7f4ae633549bd0f04d6</t>
         </is>
       </c>
       <c r="B698" t="n">
@@ -37290,12 +37322,12 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F698" t="inlineStr"/>
@@ -37325,7 +37357,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dd</t>
+          <t>6a4af7f4ae633549bd0f04da</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -37338,12 +37370,12 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F699" t="inlineStr"/>
@@ -37373,7 +37405,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04db</t>
+          <t>6a4af7f4ae633549bd0f04dd</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -37386,12 +37418,12 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F700" t="inlineStr"/>
@@ -37421,7 +37453,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d9</t>
+          <t>6a4af7f4ae633549bd0f04d7</t>
         </is>
       </c>
       <c r="B701" t="n">
@@ -37434,12 +37466,12 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F701" t="inlineStr"/>
@@ -37517,7 +37549,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e6</t>
+          <t>6a4af7f4ae633549bd0f04e2</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -37530,12 +37562,12 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F703" t="inlineStr"/>
@@ -37613,7 +37645,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e2</t>
+          <t>6a4af7f4ae633549bd0f04e6</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -37626,12 +37658,12 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
@@ -37805,7 +37837,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e4</t>
+          <t>6a4af7f4ae633549bd0f04e0</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -37818,12 +37850,12 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F709" t="inlineStr"/>
@@ -37853,7 +37885,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e0</t>
+          <t>6a4af7f4ae633549bd0f04e4</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -37866,12 +37898,12 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F710" t="inlineStr"/>
@@ -37949,7 +37981,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04eb</t>
+          <t>6a4af7f4ae633549bd0f04ed</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -37962,12 +37994,12 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F712" t="inlineStr"/>
@@ -37997,7 +38029,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f2</t>
+          <t>6a4af7f4ae633549bd0f04ec</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -38010,12 +38042,12 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F713" t="inlineStr"/>
@@ -38045,7 +38077,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f1</t>
+          <t>6a4af7f4ae633549bd0f04ef</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -38058,12 +38090,12 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -38093,7 +38125,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f3</t>
+          <t>6a4af7f4ae633549bd0f04f0</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -38106,12 +38138,12 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F715" t="inlineStr"/>
@@ -38141,7 +38173,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ef</t>
+          <t>6a4af7f4ae633549bd0f04f4</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -38154,12 +38186,12 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F716" t="inlineStr"/>
@@ -38189,7 +38221,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ec</t>
+          <t>6a4af7f4ae633549bd0f04f1</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -38202,12 +38234,12 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F717" t="inlineStr"/>
@@ -38237,7 +38269,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ed</t>
+          <t>6a4af7f4ae633549bd0f04f2</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -38250,12 +38282,12 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F718" t="inlineStr"/>
@@ -38285,7 +38317,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f0</t>
+          <t>6a4af7f4ae633549bd0f04f3</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -38298,12 +38330,12 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F719" t="inlineStr"/>
@@ -38333,7 +38365,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ee</t>
+          <t>6a4af7f4ae633549bd0f04eb</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -38346,12 +38378,12 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F720" t="inlineStr"/>
@@ -38381,7 +38413,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f4</t>
+          <t>6a4af7f4ae633549bd0f04ee</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -38394,12 +38426,12 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F721" t="inlineStr"/>
@@ -38669,7 +38701,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fc</t>
+          <t>6a4af7f4ae633549bd0f04fb</t>
         </is>
       </c>
       <c r="B727" t="n">
@@ -38682,12 +38714,12 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F727" t="inlineStr"/>
@@ -38717,7 +38749,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fb</t>
+          <t>6a4af7f4ae633549bd0f04fd</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -38730,12 +38762,12 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F728" t="inlineStr"/>
@@ -38765,7 +38797,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fd</t>
+          <t>6a4af7f4ae633549bd0f04fc</t>
         </is>
       </c>
       <c r="B729" t="n">
@@ -38778,12 +38810,12 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F729" t="inlineStr"/>
@@ -38909,7 +38941,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0505</t>
+          <t>6a4af7f4ae633549bd0f0501</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -38922,12 +38954,12 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F732" t="inlineStr"/>
@@ -38957,7 +38989,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0508</t>
+          <t>6a4af7f4ae633549bd0f0504</t>
         </is>
       </c>
       <c r="B733" t="n">
@@ -38970,12 +39002,12 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F733" t="inlineStr"/>
@@ -39005,7 +39037,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0502</t>
+          <t>6a4af7f4ae633549bd0f0503</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -39018,12 +39050,12 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
@@ -39053,7 +39085,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0501</t>
+          <t>6a4af7f4ae633549bd0f0507</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -39066,12 +39098,12 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -39101,7 +39133,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0507</t>
+          <t>6a4af7f4ae633549bd0f0508</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -39114,12 +39146,12 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
@@ -39149,7 +39181,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0503</t>
+          <t>6a4af7f4ae633549bd0f0502</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -39162,12 +39194,12 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F737" t="inlineStr"/>
@@ -39197,7 +39229,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0506</t>
+          <t>6a4af7f4ae633549bd0f0509</t>
         </is>
       </c>
       <c r="B738" t="n">
@@ -39210,12 +39242,12 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F738" t="inlineStr"/>
@@ -39245,7 +39277,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050a</t>
+          <t>6a4af7f4ae633549bd0f0505</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -39258,12 +39290,12 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F739" t="inlineStr"/>
@@ -39293,7 +39325,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0504</t>
+          <t>6a4af7f4ae633549bd0f0506</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -39306,12 +39338,12 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -39341,7 +39373,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0509</t>
+          <t>6a4af7f4ae633549bd0f050a</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -39354,12 +39386,12 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F741" t="inlineStr"/>
@@ -39389,7 +39421,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0510</t>
+          <t>6a4af7f5ae633549bd0f050e</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -39402,12 +39434,12 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F742" t="inlineStr"/>
@@ -39437,7 +39469,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050d</t>
+          <t>6a4af7f5ae633549bd0f050f</t>
         </is>
       </c>
       <c r="B743" t="n">
@@ -39450,12 +39482,12 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F743" t="inlineStr"/>
@@ -39485,7 +39517,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0511</t>
+          <t>6a4af7f4ae633549bd0f050c</t>
         </is>
       </c>
       <c r="B744" t="n">
@@ -39498,12 +39530,12 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F744" t="inlineStr"/>
@@ -39581,7 +39613,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050c</t>
+          <t>6a4af7f5ae633549bd0f0511</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -39594,12 +39626,12 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F746" t="inlineStr"/>
@@ -39629,7 +39661,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050f</t>
+          <t>6a4af7f4ae633549bd0f050d</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -39642,12 +39674,12 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F747" t="inlineStr"/>
@@ -39677,7 +39709,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050e</t>
+          <t>6a4af7f5ae633549bd0f0512</t>
         </is>
       </c>
       <c r="B748" t="n">
@@ -39690,12 +39722,12 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F748" t="inlineStr"/>
@@ -39725,7 +39757,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0513</t>
+          <t>6a4af7f5ae633549bd0f0510</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -39738,12 +39770,12 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
@@ -39773,7 +39805,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0514</t>
+          <t>6a4af7f5ae633549bd0f0513</t>
         </is>
       </c>
       <c r="B750" t="n">
@@ -39786,12 +39818,12 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F750" t="inlineStr"/>
@@ -39821,7 +39853,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0512</t>
+          <t>6a4af7f5ae633549bd0f0514</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -39834,12 +39866,12 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F751" t="inlineStr"/>
@@ -39869,7 +39901,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051c</t>
+          <t>6a4af7f5ae633549bd0f0518</t>
         </is>
       </c>
       <c r="B752" t="n">
@@ -39882,12 +39914,12 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F752" t="inlineStr"/>
@@ -39917,7 +39949,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0518</t>
+          <t>6a4af7f5ae633549bd0f051a</t>
         </is>
       </c>
       <c r="B753" t="n">
@@ -39930,12 +39962,12 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F753" t="inlineStr"/>
@@ -39965,7 +39997,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0517</t>
+          <t>6a4af7f5ae633549bd0f051b</t>
         </is>
       </c>
       <c r="B754" t="n">
@@ -39978,12 +40010,12 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F754" t="inlineStr"/>
@@ -40013,7 +40045,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051a</t>
+          <t>6a4af7f5ae633549bd0f051c</t>
         </is>
       </c>
       <c r="B755" t="n">
@@ -40026,12 +40058,12 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F755" t="inlineStr"/>
@@ -40061,7 +40093,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051e</t>
+          <t>6a4af7f5ae633549bd0f051d</t>
         </is>
       </c>
       <c r="B756" t="n">
@@ -40074,12 +40106,12 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F756" t="inlineStr"/>
@@ -40109,7 +40141,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0520</t>
+          <t>6a4af7f5ae633549bd0f051f</t>
         </is>
       </c>
       <c r="B757" t="n">
@@ -40122,12 +40154,12 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F757" t="inlineStr"/>
@@ -40157,7 +40189,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0519</t>
+          <t>6a4af7f5ae633549bd0f0520</t>
         </is>
       </c>
       <c r="B758" t="n">
@@ -40170,12 +40202,12 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F758" t="inlineStr"/>
@@ -40205,7 +40237,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051f</t>
+          <t>6a4af7f5ae633549bd0f0519</t>
         </is>
       </c>
       <c r="B759" t="n">
@@ -40218,12 +40250,12 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F759" t="inlineStr"/>
@@ -40253,7 +40285,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051b</t>
+          <t>6a4af7f5ae633549bd0f0517</t>
         </is>
       </c>
       <c r="B760" t="n">
@@ -40266,12 +40298,12 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F760" t="inlineStr"/>
@@ -40301,7 +40333,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f051d</t>
+          <t>6a4af7f5ae633549bd0f051e</t>
         </is>
       </c>
       <c r="B761" t="n">
@@ -40314,12 +40346,12 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>

--- a/datos/maestros/md_partidos.xlsx
+++ b/datos/maestros/md_partidos.xlsx
@@ -21773,7 +21773,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c0</t>
+          <t>6a4af7f0ae633549bd0f03b7</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -21786,33 +21786,29 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
-        </is>
-      </c>
-      <c r="F382" t="n">
-        <v>0</v>
-      </c>
-      <c r="G382" t="n">
-        <v>0</v>
-      </c>
+          <t>504e581e4d8bec9a670000cb</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="inlineStr"/>
       <c r="H382" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
@@ -21820,16 +21816,12 @@
           <t>closed</t>
         </is>
       </c>
-      <c r="L382" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="L382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bf</t>
+          <t>6a4af7f0ae633549bd0f03ba</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -21842,19 +21834,19 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -21877,7 +21869,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ba</t>
+          <t>6a4af7f0ae633549bd0f03bb</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -21890,19 +21882,19 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="inlineStr"/>
       <c r="H384" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -21973,7 +21965,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b7</t>
+          <t>6a4af7f0ae633549bd0f03bf</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -21986,12 +21978,12 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
@@ -22003,12 +21995,12 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
@@ -22021,7 +22013,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bb</t>
+          <t>6a4af7f0ae633549bd0f03b9</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -22034,12 +22026,12 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F387" t="inlineStr"/>
@@ -22051,12 +22043,12 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
@@ -22069,7 +22061,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bc</t>
+          <t>6a4af7f0ae633549bd0f03c0</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -22082,29 +22074,33 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
-        </is>
-      </c>
-      <c r="F388" t="inlineStr"/>
-      <c r="G388" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000d9</t>
+        </is>
+      </c>
+      <c r="F388" t="n">
+        <v>0</v>
+      </c>
+      <c r="G388" t="n">
+        <v>0</v>
+      </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
@@ -22112,12 +22108,16 @@
           <t>closed</t>
         </is>
       </c>
-      <c r="L388" t="inlineStr"/>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03be</t>
+          <t>6a4af7f0ae633549bd0f03b8</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -22130,29 +22130,29 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
@@ -22165,7 +22165,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b8</t>
+          <t>6a4af7f0ae633549bd0f03be</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -22178,29 +22178,29 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
@@ -22213,7 +22213,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b9</t>
+          <t>6a4af7f0ae633549bd0f03bc</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -22226,19 +22226,19 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -22261,7 +22261,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0380</t>
+          <t>6a4af7efae633549bd0f0385</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -22274,12 +22274,12 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F392" t="n">
@@ -22290,17 +22290,17 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
@@ -22317,7 +22317,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0383</t>
+          <t>6a4af7efae633549bd0f0387</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -22330,33 +22330,33 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F393" t="n">
+        <v>4</v>
+      </c>
+      <c r="G393" t="n">
         <v>1</v>
       </c>
-      <c r="G393" t="n">
-        <v>2</v>
-      </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
@@ -22373,7 +22373,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0384</t>
+          <t>6a4af7efae633549bd0f0389</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -22386,23 +22386,23 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G394" t="n">
         <v>1</v>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -22429,7 +22429,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0388</t>
+          <t>6a4af7efae633549bd0f0383</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -22442,33 +22442,33 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F395" t="n">
+        <v>1</v>
+      </c>
+      <c r="G395" t="n">
         <v>2</v>
       </c>
-      <c r="G395" t="n">
-        <v>1</v>
-      </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
@@ -22485,7 +22485,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0382</t>
+          <t>6a4af7efae633549bd0f0380</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -22498,33 +22498,33 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G396" t="n">
         <v>0</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
@@ -22541,7 +22541,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0381</t>
+          <t>6a4af7efae633549bd0f0384</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -22554,23 +22554,23 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -22597,7 +22597,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0386</t>
+          <t>6a4af7efae633549bd0f0388</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -22610,33 +22610,33 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F398" t="n">
         <v>2</v>
       </c>
       <c r="G398" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
@@ -22653,7 +22653,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0385</t>
+          <t>6a4af7efae633549bd0f0382</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -22666,33 +22666,33 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F399" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G399" t="n">
         <v>0</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
@@ -22709,7 +22709,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0387</t>
+          <t>6a4af7efae633549bd0f0381</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -22722,23 +22722,23 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F400" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G400" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -22765,7 +22765,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0389</t>
+          <t>6a4af7efae633549bd0f0386</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -22778,33 +22778,33 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F401" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G401" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
@@ -22821,7 +22821,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0390</t>
+          <t>6a4af7efae633549bd0f0391</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -22834,33 +22834,33 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F402" t="n">
         <v>1</v>
       </c>
       <c r="G402" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
@@ -23101,7 +23101,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038c</t>
+          <t>6a4af7efae633549bd0f038b</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -23114,23 +23114,23 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F407" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -23157,7 +23157,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038b</t>
+          <t>6a4af7efae633549bd0f038c</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -23170,23 +23170,23 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G408" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -23213,7 +23213,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038d</t>
+          <t>6a4af7efae633549bd0f038e</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -23226,33 +23226,33 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G409" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
@@ -23269,7 +23269,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038e</t>
+          <t>6a4af7efae633549bd0f038d</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -23282,33 +23282,33 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F410" t="n">
+        <v>1</v>
+      </c>
+      <c r="G410" t="n">
         <v>0</v>
       </c>
-      <c r="G410" t="n">
-        <v>5</v>
-      </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
@@ -23325,7 +23325,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0391</t>
+          <t>6a4af7efae633549bd0f0390</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -23338,33 +23338,33 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F411" t="n">
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
           <t>19:30</t>
-        </is>
-      </c>
-      <c r="J411" t="inlineStr">
-        <is>
-          <t>21:30</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
@@ -23381,7 +23381,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039e</t>
+          <t>6a4af7efae633549bd0f039d</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -23394,33 +23394,33 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G412" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
           <t>17:00</t>
-        </is>
-      </c>
-      <c r="J412" t="inlineStr">
-        <is>
-          <t>19:00</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
@@ -23437,7 +23437,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0399</t>
+          <t>6a4af7efae633549bd0f0397</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -23450,33 +23450,33 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
@@ -23493,7 +23493,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039f</t>
+          <t>6a4af7efae633549bd0f0398</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -23506,23 +23506,23 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F414" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G414" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -23549,7 +23549,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0397</t>
+          <t>6a4af7efae633549bd0f0396</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -23562,23 +23562,23 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G415" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -23605,7 +23605,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0398</t>
+          <t>6a4af7efae633549bd0f039a</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -23618,33 +23618,33 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G416" t="n">
         <v>2</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
@@ -23661,7 +23661,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039a</t>
+          <t>6a4af7efae633549bd0f039c</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -23674,33 +23674,33 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G417" t="n">
         <v>2</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
@@ -23717,7 +23717,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039c</t>
+          <t>6a4af7efae633549bd0f039b</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -23730,33 +23730,33 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F418" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G418" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
@@ -23773,7 +23773,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039d</t>
+          <t>6a4af7efae633549bd0f039e</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -23786,33 +23786,33 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F419" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G419" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
@@ -23829,7 +23829,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039b</t>
+          <t>6a4af7efae633549bd0f039f</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -23842,33 +23842,33 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F420" t="n">
         <v>1</v>
       </c>
       <c r="G420" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
@@ -23885,7 +23885,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0396</t>
+          <t>6a4af7efae633549bd0f0399</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -23898,33 +23898,33 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F421" t="n">
+        <v>3</v>
+      </c>
+      <c r="G421" t="n">
         <v>1</v>
       </c>
-      <c r="G421" t="n">
-        <v>0</v>
-      </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
           <t>19:30</t>
-        </is>
-      </c>
-      <c r="J421" t="inlineStr">
-        <is>
-          <t>21:30</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
@@ -24501,7 +24501,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b1</t>
+          <t>6a4af7efae633549bd0f03b0</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -24514,20 +24514,20 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F432" t="n">
+        <v>0</v>
+      </c>
+      <c r="G432" t="n">
         <v>2</v>
       </c>
-      <c r="G432" t="n">
-        <v>1</v>
-      </c>
       <c r="H432" t="inlineStr">
         <is>
           <t>2026-09-12</t>
@@ -24535,12 +24535,12 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
@@ -24557,7 +24557,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ac</t>
+          <t>6a4af7f0ae633549bd0f03b5</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -24570,33 +24570,29 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
-        </is>
-      </c>
-      <c r="F433" t="n">
-        <v>1</v>
-      </c>
-      <c r="G433" t="n">
-        <v>1</v>
-      </c>
+          <t>504e581e4d8bec9a670000cc</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="inlineStr"/>
       <c r="H433" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
@@ -24604,16 +24600,12 @@
           <t>running</t>
         </is>
       </c>
-      <c r="L433" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="L433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ae</t>
+          <t>6a4af7efae633549bd0f03b1</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -24626,29 +24618,33 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
-        </is>
-      </c>
-      <c r="F434" t="inlineStr"/>
-      <c r="G434" t="inlineStr"/>
+          <t>52038563b8d07d930b00008a</t>
+        </is>
+      </c>
+      <c r="F434" t="n">
+        <v>2</v>
+      </c>
+      <c r="G434" t="n">
+        <v>1</v>
+      </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
@@ -24656,12 +24652,16 @@
           <t>running</t>
         </is>
       </c>
-      <c r="L434" t="inlineStr"/>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b2</t>
+          <t>6a4af7efae633549bd0f03b4</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -24674,23 +24674,23 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G435" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -24717,7 +24717,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b3</t>
+          <t>6a4af7efae633549bd0f03ac</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -24730,29 +24730,33 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
-        </is>
-      </c>
-      <c r="F436" t="inlineStr"/>
-      <c r="G436" t="inlineStr"/>
+          <t>51b889b1e401a15f2c0000f0</t>
+        </is>
+      </c>
+      <c r="F436" t="n">
+        <v>1</v>
+      </c>
+      <c r="G436" t="n">
+        <v>1</v>
+      </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
@@ -24760,12 +24764,16 @@
           <t>running</t>
         </is>
       </c>
-      <c r="L436" t="inlineStr"/>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b4</t>
+          <t>6a4af7efae633549bd0f03ae</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -24778,33 +24786,33 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F437" t="n">
         <v>1</v>
       </c>
       <c r="G437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
@@ -24821,7 +24829,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b0</t>
+          <t>6a4af7efae633549bd0f03b2</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -24834,19 +24842,19 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F438" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G438" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H438" t="inlineStr">
         <is>
@@ -24855,12 +24863,12 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K438" t="inlineStr">
@@ -24877,7 +24885,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b5</t>
+          <t>6a4af7efae633549bd0f03af</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -24890,29 +24898,33 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
-        </is>
-      </c>
-      <c r="F439" t="inlineStr"/>
-      <c r="G439" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000c7</t>
+        </is>
+      </c>
+      <c r="F439" t="n">
+        <v>2</v>
+      </c>
+      <c r="G439" t="n">
+        <v>4</v>
+      </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
@@ -24920,12 +24932,16 @@
           <t>running</t>
         </is>
       </c>
-      <c r="L439" t="inlineStr"/>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03af</t>
+          <t>6a4af7efae633549bd0f03b3</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -24938,16 +24954,20 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
-        </is>
-      </c>
-      <c r="F440" t="inlineStr"/>
-      <c r="G440" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000c8</t>
+        </is>
+      </c>
+      <c r="F440" t="n">
+        <v>0</v>
+      </c>
+      <c r="G440" t="n">
+        <v>3</v>
+      </c>
       <c r="H440" t="inlineStr">
         <is>
           <t>2026-09-13</t>
@@ -24955,12 +24975,12 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
@@ -24968,7 +24988,11 @@
           <t>running</t>
         </is>
       </c>
-      <c r="L440" t="inlineStr"/>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -24994,8 +25018,12 @@
           <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
-      <c r="F441" t="inlineStr"/>
-      <c r="G441" t="inlineStr"/>
+      <c r="F441" t="n">
+        <v>1</v>
+      </c>
+      <c r="G441" t="n">
+        <v>1</v>
+      </c>
       <c r="H441" t="inlineStr">
         <is>
           <t>2026-09-13</t>
@@ -25016,12 +25044,16 @@
           <t>running</t>
         </is>
       </c>
-      <c r="L441" t="inlineStr"/>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ca</t>
+          <t>6a4af7f0ae633549bd0f03c5</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -25034,12 +25066,12 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -25051,12 +25083,12 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
@@ -25069,7 +25101,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cb</t>
+          <t>6a4af7f0ae633549bd0f03c9</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -25082,29 +25114,29 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F443" t="inlineStr"/>
       <c r="G443" t="inlineStr"/>
       <c r="H443" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K443" t="inlineStr">
@@ -25117,7 +25149,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c4</t>
+          <t>6a4af7f0ae633549bd0f03c6</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -25130,29 +25162,29 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
       <c r="G444" t="inlineStr"/>
       <c r="H444" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K444" t="inlineStr">
@@ -25165,7 +25197,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c8</t>
+          <t>6a4af7f0ae633549bd0f03c7</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -25178,19 +25210,19 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
       <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -25213,7 +25245,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c3</t>
+          <t>6a4af7f0ae633549bd0f03ca</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -25226,12 +25258,12 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -25243,12 +25275,12 @@
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K446" t="inlineStr">
@@ -25261,7 +25293,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c2</t>
+          <t>6a4af7f0ae633549bd0f03cb</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -25274,29 +25306,29 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F447" t="inlineStr"/>
       <c r="G447" t="inlineStr"/>
       <c r="H447" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K447" t="inlineStr">
@@ -25309,7 +25341,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c5</t>
+          <t>6a4af7f0ae633549bd0f03c4</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -25322,19 +25354,19 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F448" t="inlineStr"/>
       <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -25357,7 +25389,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c9</t>
+          <t>6a4af7f0ae633549bd0f03c8</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -25370,12 +25402,12 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
@@ -25387,12 +25419,12 @@
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K449" t="inlineStr">
@@ -25405,7 +25437,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c6</t>
+          <t>6a4af7f0ae633549bd0f03c3</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -25418,29 +25450,29 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
       <c r="G450" t="inlineStr"/>
       <c r="H450" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K450" t="inlineStr">
@@ -25453,7 +25485,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c7</t>
+          <t>6a4af7f0ae633549bd0f03c2</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -25466,29 +25498,29 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr"/>
       <c r="H451" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K451" t="inlineStr">
@@ -25501,7 +25533,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d1</t>
+          <t>6a4af7f0ae633549bd0f03ce</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -25514,12 +25546,12 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
@@ -25549,7 +25581,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d2</t>
+          <t>6a4af7f0ae633549bd0f03cd</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -25562,12 +25594,12 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
@@ -25597,7 +25629,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d3</t>
+          <t>6a4af7f0ae633549bd0f03cf</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -25610,12 +25642,12 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F454" t="inlineStr"/>
@@ -25645,7 +25677,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d4</t>
+          <t>6a4af7f0ae633549bd0f03d0</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -25658,12 +25690,12 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F455" t="inlineStr"/>
@@ -25693,7 +25725,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d5</t>
+          <t>6a4af7f0ae633549bd0f03d4</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -25706,12 +25738,12 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F456" t="inlineStr"/>
@@ -25741,7 +25773,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ce</t>
+          <t>6a4af7f0ae633549bd0f03d1</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -25754,12 +25786,12 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -25789,7 +25821,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d6</t>
+          <t>6a4af7f0ae633549bd0f03d2</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -25802,12 +25834,12 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -25837,7 +25869,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cd</t>
+          <t>6a4af7f0ae633549bd0f03d3</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -25850,12 +25882,12 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -25885,7 +25917,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cf</t>
+          <t>6a4af7f0ae633549bd0f03d5</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -25898,12 +25930,12 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
@@ -25933,7 +25965,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d0</t>
+          <t>6a4af7f0ae633549bd0f03d6</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -25946,12 +25978,12 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -25981,7 +26013,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e1</t>
+          <t>6a4af7f0ae633549bd0f03da</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -25994,12 +26026,12 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
@@ -26029,7 +26061,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d8</t>
+          <t>6a4af7f0ae633549bd0f03df</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -26042,12 +26074,12 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F463" t="inlineStr"/>
@@ -26077,7 +26109,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03db</t>
+          <t>6a4af7f0ae633549bd0f03d9</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -26090,12 +26122,12 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F464" t="inlineStr"/>
@@ -26125,7 +26157,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dd</t>
+          <t>6a4af7f0ae633549bd0f03de</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -26138,12 +26170,12 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F465" t="inlineStr"/>
@@ -26173,7 +26205,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03df</t>
+          <t>6a4af7f0ae633549bd0f03e0</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -26186,12 +26218,12 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F466" t="inlineStr"/>
@@ -26221,7 +26253,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03da</t>
+          <t>6a4af7f0ae633549bd0f03dc</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -26234,12 +26266,12 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -26269,7 +26301,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e0</t>
+          <t>6a4af7f0ae633549bd0f03e1</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -26282,12 +26314,12 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F468" t="inlineStr"/>
@@ -26317,7 +26349,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d9</t>
+          <t>6a4af7f0ae633549bd0f03d8</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -26330,12 +26362,12 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F469" t="inlineStr"/>
@@ -26365,7 +26397,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03de</t>
+          <t>6a4af7f0ae633549bd0f03db</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -26378,12 +26410,12 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
@@ -26413,7 +26445,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dc</t>
+          <t>6a4af7f0ae633549bd0f03dd</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -26426,12 +26458,12 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -26461,7 +26493,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e8</t>
+          <t>6a4af7f0ae633549bd0f03e5</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -26474,12 +26506,12 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -26509,7 +26541,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e7</t>
+          <t>6a4af7f0ae633549bd0f03eb</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -26522,12 +26554,12 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -26557,7 +26589,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e5</t>
+          <t>6a4af7f0ae633549bd0f03e8</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -26570,12 +26602,12 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -26605,7 +26637,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ea</t>
+          <t>6a4af7f0ae633549bd0f03e7</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -26618,12 +26650,12 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -26653,7 +26685,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ec</t>
+          <t>6a4af7f0ae633549bd0f03e4</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -26666,12 +26698,12 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
@@ -26749,7 +26781,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e9</t>
+          <t>6a4af7f0ae633549bd0f03e6</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -26762,12 +26794,12 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -26779,12 +26811,12 @@
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K478" t="inlineStr">
@@ -26797,7 +26829,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e4</t>
+          <t>6a4af7f0ae633549bd0f03ec</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -26810,12 +26842,12 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
@@ -26845,7 +26877,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e6</t>
+          <t>6a4af7f0ae633549bd0f03e9</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -26858,12 +26890,12 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -26875,12 +26907,12 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K480" t="inlineStr">
@@ -26893,7 +26925,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03eb</t>
+          <t>6a4af7f0ae633549bd0f03ea</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -26906,12 +26938,12 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
@@ -26941,7 +26973,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f2</t>
+          <t>6a4af7f0ae633549bd0f03f3</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -26954,12 +26986,12 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -26989,7 +27021,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f7</t>
+          <t>6a4af7f0ae633549bd0f03f4</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -27002,12 +27034,12 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -27037,7 +27069,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f1</t>
+          <t>6a4af7f0ae633549bd0f03f6</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -27050,12 +27082,12 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F484" t="inlineStr"/>
@@ -27085,7 +27117,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f0</t>
+          <t>6a4af7f0ae633549bd0f03f1</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -27098,12 +27130,12 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -27133,7 +27165,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f6</t>
+          <t>6a4af7f0ae633549bd0f03f0</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -27146,12 +27178,12 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
@@ -27181,7 +27213,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ee</t>
+          <t>6a4af7f0ae633549bd0f03f5</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -27194,12 +27226,12 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F487" t="inlineStr"/>
@@ -27229,7 +27261,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f3</t>
+          <t>6a4af7f0ae633549bd0f03ef</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -27242,12 +27274,12 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -27277,7 +27309,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f4</t>
+          <t>6a4af7f0ae633549bd0f03f7</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -27290,12 +27322,12 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -27325,7 +27357,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ef</t>
+          <t>6a4af7f0ae633549bd0f03f2</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -27338,12 +27370,12 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -27373,7 +27405,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f5</t>
+          <t>6a4af7f0ae633549bd0f03ee</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -27386,12 +27418,12 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -27421,7 +27453,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fa</t>
+          <t>6a4af7f1ae633549bd0f0402</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -27434,12 +27466,12 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
@@ -27517,7 +27549,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0401</t>
+          <t>6a4af7f1ae633549bd0f03ff</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -27530,12 +27562,12 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F494" t="inlineStr"/>
@@ -27565,7 +27597,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f9</t>
+          <t>6a4af7f1ae633549bd0f0400</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -27578,12 +27610,12 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -27613,7 +27645,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fc</t>
+          <t>6a4af7f1ae633549bd0f03fe</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -27626,12 +27658,12 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -27709,7 +27741,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fe</t>
+          <t>6a4af7f0ae633549bd0f03f9</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -27722,12 +27754,12 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
@@ -27757,7 +27789,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03ff</t>
+          <t>6a4af7f1ae633549bd0f03fc</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -27770,12 +27802,12 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -27805,7 +27837,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0400</t>
+          <t>6a4af7f1ae633549bd0f0401</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -27818,12 +27850,12 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -27853,7 +27885,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0402</t>
+          <t>6a4af7f0ae633549bd0f03fa</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -27866,12 +27898,12 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -27901,7 +27933,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0407</t>
+          <t>6a4af7f1ae633549bd0f0404</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -27914,12 +27946,12 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -27949,7 +27981,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0405</t>
+          <t>6a4af7f1ae633549bd0f0409</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -27962,12 +27994,12 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -27997,7 +28029,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040d</t>
+          <t>6a4af7f1ae633549bd0f0405</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -28010,12 +28042,12 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -28045,7 +28077,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0409</t>
+          <t>6a4af7f1ae633549bd0f0407</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -28058,12 +28090,12 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -28093,7 +28125,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0404</t>
+          <t>6a4af7f1ae633549bd0f040c</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -28106,12 +28138,12 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F506" t="inlineStr"/>
@@ -28141,7 +28173,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0408</t>
+          <t>6a4af7f1ae633549bd0f040a</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -28154,12 +28186,12 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F507" t="inlineStr"/>
@@ -28189,7 +28221,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040b</t>
+          <t>6a4af7f1ae633549bd0f0406</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -28202,12 +28234,12 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -28237,7 +28269,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0406</t>
+          <t>6a4af7f1ae633549bd0f040b</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -28250,12 +28282,12 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
@@ -28285,7 +28317,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040a</t>
+          <t>6a4af7f1ae633549bd0f040d</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -28298,12 +28330,12 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
@@ -28333,7 +28365,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040c</t>
+          <t>6a4af7f1ae633549bd0f0408</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -28346,12 +28378,12 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -28381,7 +28413,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0412</t>
+          <t>6a4af7f1ae633549bd0f0413</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -28394,12 +28426,12 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F512" t="inlineStr"/>
@@ -28429,7 +28461,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0416</t>
+          <t>6a4af7f1ae633549bd0f0410</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -28442,12 +28474,12 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F513" t="inlineStr"/>
@@ -28477,7 +28509,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040f</t>
+          <t>6a4af7f1ae633549bd0f0415</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -28490,12 +28522,12 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -28525,7 +28557,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0415</t>
+          <t>6a4af7f1ae633549bd0f0418</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -28538,12 +28570,12 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F515" t="inlineStr"/>
@@ -28573,7 +28605,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0410</t>
+          <t>6a4af7f1ae633549bd0f0414</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -28586,12 +28618,12 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F516" t="inlineStr"/>
@@ -28621,7 +28653,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0413</t>
+          <t>6a4af7f1ae633549bd0f0411</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -28634,12 +28666,12 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F517" t="inlineStr"/>
@@ -28669,7 +28701,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0418</t>
+          <t>6a4af7f1ae633549bd0f0416</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -28682,12 +28714,12 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
@@ -28717,7 +28749,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0411</t>
+          <t>6a4af7f1ae633549bd0f0417</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -28730,12 +28762,12 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -28765,7 +28797,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0414</t>
+          <t>6a4af7f1ae633549bd0f0412</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -28778,12 +28810,12 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F520" t="inlineStr"/>
@@ -28813,7 +28845,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0417</t>
+          <t>6a4af7f1ae633549bd0f040f</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -28826,12 +28858,12 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F521" t="inlineStr"/>
@@ -28861,7 +28893,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041d</t>
+          <t>6a4af7f1ae633549bd0f041a</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -28874,12 +28906,12 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F522" t="inlineStr"/>
@@ -28909,7 +28941,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041b</t>
+          <t>6a4af7f1ae633549bd0f0423</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -28922,12 +28954,12 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F523" t="inlineStr"/>
@@ -28957,7 +28989,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041c</t>
+          <t>6a4af7f1ae633549bd0f041f</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -28970,12 +29002,12 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F524" t="inlineStr"/>
@@ -29005,7 +29037,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0420</t>
+          <t>6a4af7f1ae633549bd0f0421</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -29018,12 +29050,12 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F525" t="inlineStr"/>
@@ -29053,7 +29085,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041f</t>
+          <t>6a4af7f1ae633549bd0f041e</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -29066,12 +29098,12 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F526" t="inlineStr"/>
@@ -29101,7 +29133,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0422</t>
+          <t>6a4af7f1ae633549bd0f041b</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -29114,12 +29146,12 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F527" t="inlineStr"/>
@@ -29149,7 +29181,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0423</t>
+          <t>6a4af7f1ae633549bd0f041d</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -29162,12 +29194,12 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F528" t="inlineStr"/>
@@ -29197,7 +29229,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041a</t>
+          <t>6a4af7f1ae633549bd0f0422</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -29210,12 +29242,12 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -29245,7 +29277,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041e</t>
+          <t>6a4af7f1ae633549bd0f041c</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -29258,12 +29290,12 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -29293,7 +29325,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0421</t>
+          <t>6a4af7f1ae633549bd0f0420</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -29306,12 +29338,12 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -29821,7 +29853,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0433</t>
+          <t>6a4af7f1ae633549bd0f0438</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -29834,12 +29866,12 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F542" t="inlineStr"/>
@@ -29869,7 +29901,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0431</t>
+          <t>6a4af7f1ae633549bd0f0432</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -29882,12 +29914,12 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F543" t="inlineStr"/>
@@ -29917,7 +29949,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0430</t>
+          <t>6a4af7f1ae633549bd0f0435</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -29930,12 +29962,12 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
@@ -29965,7 +29997,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0436</t>
+          <t>6a4af7f1ae633549bd0f0437</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -29978,12 +30010,12 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -30061,7 +30093,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0437</t>
+          <t>6a4af7f1ae633549bd0f0439</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -30074,12 +30106,12 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
@@ -30109,7 +30141,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0439</t>
+          <t>6a4af7f1ae633549bd0f0430</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -30122,12 +30154,12 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -30157,7 +30189,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0432</t>
+          <t>6a4af7f1ae633549bd0f0431</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -30170,12 +30202,12 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -30205,7 +30237,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0435</t>
+          <t>6a4af7f1ae633549bd0f0433</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -30218,12 +30250,12 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
@@ -30253,7 +30285,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0438</t>
+          <t>6a4af7f1ae633549bd0f0436</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -30266,12 +30298,12 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F551" t="inlineStr"/>
@@ -30301,7 +30333,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043e</t>
+          <t>6a4af7f1ae633549bd0f043b</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -30314,12 +30346,12 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -30349,7 +30381,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f043f</t>
+          <t>6a4af7f1ae633549bd0f043c</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -30362,12 +30394,12 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -30397,7 +30429,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043c</t>
+          <t>6a4af7f2ae633549bd0f043f</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -30410,12 +30442,12 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -30541,7 +30573,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043d</t>
+          <t>6a4af7f2ae633549bd0f0443</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -30554,12 +30586,12 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -30589,7 +30621,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0441</t>
+          <t>6a4af7f2ae633549bd0f0444</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -30602,12 +30634,12 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
@@ -30637,7 +30669,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0444</t>
+          <t>6a4af7f2ae633549bd0f0441</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -30650,12 +30682,12 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F559" t="inlineStr"/>
@@ -30685,7 +30717,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0443</t>
+          <t>6a4af7f1ae633549bd0f043d</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -30698,12 +30730,12 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -30733,7 +30765,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043b</t>
+          <t>6a4af7f1ae633549bd0f043e</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -30746,12 +30778,12 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -30781,7 +30813,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0447</t>
+          <t>6a4af7f2ae633549bd0f044b</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -30794,12 +30826,12 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -30829,7 +30861,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0448</t>
+          <t>6a4af7f2ae633549bd0f0446</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -30842,12 +30874,12 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F563" t="inlineStr"/>
@@ -30973,7 +31005,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044d</t>
+          <t>6a4af7f2ae633549bd0f044f</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -30986,12 +31018,12 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
@@ -31021,7 +31053,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044c</t>
+          <t>6a4af7f2ae633549bd0f044d</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -31034,12 +31066,12 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F567" t="inlineStr"/>
@@ -31069,7 +31101,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0449</t>
+          <t>6a4af7f2ae633549bd0f044c</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -31082,12 +31114,12 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F568" t="inlineStr"/>
@@ -31117,7 +31149,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044f</t>
+          <t>6a4af7f2ae633549bd0f0449</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -31130,12 +31162,12 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F569" t="inlineStr"/>
@@ -31165,7 +31197,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044b</t>
+          <t>6a4af7f2ae633549bd0f0447</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -31178,12 +31210,12 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F570" t="inlineStr"/>
@@ -31213,7 +31245,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0446</t>
+          <t>6a4af7f2ae633549bd0f0448</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -31226,12 +31258,12 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -31261,7 +31293,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0455</t>
+          <t>6a4af7f2ae633549bd0f0451</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -31274,12 +31306,12 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F572" t="inlineStr"/>
@@ -31309,7 +31341,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0458</t>
+          <t>6a4af7f2ae633549bd0f0459</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -31322,12 +31354,12 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F573" t="inlineStr"/>
@@ -31357,7 +31389,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0456</t>
+          <t>6a4af7f2ae633549bd0f0452</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -31370,12 +31402,12 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F574" t="inlineStr"/>
@@ -31405,7 +31437,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0457</t>
+          <t>6a4af7f2ae633549bd0f0454</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -31418,12 +31450,12 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -31453,7 +31485,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045a</t>
+          <t>6a4af7f2ae633549bd0f0456</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -31466,12 +31498,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F576" t="inlineStr"/>
@@ -31501,7 +31533,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0453</t>
+          <t>6a4af7f2ae633549bd0f0457</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -31514,12 +31546,12 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -31549,7 +31581,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0459</t>
+          <t>6a4af7f2ae633549bd0f0455</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -31562,12 +31594,12 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -31597,7 +31629,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0451</t>
+          <t>6a4af7f2ae633549bd0f0453</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -31610,12 +31642,12 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F579" t="inlineStr"/>
@@ -31645,7 +31677,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0454</t>
+          <t>6a4af7f2ae633549bd0f0458</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -31658,12 +31690,12 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F580" t="inlineStr"/>
@@ -31693,7 +31725,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0452</t>
+          <t>6a4af7f2ae633549bd0f045a</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -31706,12 +31738,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -31741,7 +31773,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0460</t>
+          <t>6a4af7f2ae633549bd0f045d</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -31754,12 +31786,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F582" t="inlineStr"/>
@@ -31789,7 +31821,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045e</t>
+          <t>6a4af7f2ae633549bd0f045f</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -31802,12 +31834,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -31837,7 +31869,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045f</t>
+          <t>6a4af7f2ae633549bd0f0464</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -31850,12 +31882,12 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F584" t="inlineStr"/>
@@ -31885,7 +31917,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0464</t>
+          <t>6a4af7f2ae633549bd0f045e</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -31898,12 +31930,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -32029,7 +32061,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0463</t>
+          <t>6a4af7f2ae633549bd0f0462</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -32042,12 +32074,12 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -32077,7 +32109,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0462</t>
+          <t>6a4af7f2ae633549bd0f0463</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -32090,12 +32122,12 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -32125,7 +32157,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045d</t>
+          <t>6a4af7f2ae633549bd0f0465</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -32138,12 +32170,12 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -32173,7 +32205,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0465</t>
+          <t>6a4af7f2ae633549bd0f0460</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -32186,12 +32218,12 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -32269,7 +32301,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046a</t>
+          <t>6a4af7f2ae633549bd0f046d</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -32282,12 +32314,12 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F593" t="inlineStr"/>
@@ -32317,7 +32349,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046c</t>
+          <t>6a4af7f2ae633549bd0f0469</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -32330,12 +32362,12 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F594" t="inlineStr"/>
@@ -32365,7 +32397,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046f</t>
+          <t>6a4af7f2ae633549bd0f0468</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -32378,12 +32410,12 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F595" t="inlineStr"/>
@@ -32413,7 +32445,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046b</t>
+          <t>6a4af7f2ae633549bd0f0470</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -32426,12 +32458,12 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F596" t="inlineStr"/>
@@ -32509,7 +32541,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0468</t>
+          <t>6a4af7f2ae633549bd0f046b</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -32522,12 +32554,12 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F598" t="inlineStr"/>
@@ -32557,7 +32589,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0470</t>
+          <t>6a4af7f2ae633549bd0f046f</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -32570,12 +32602,12 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F599" t="inlineStr"/>
@@ -32605,7 +32637,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0469</t>
+          <t>6a4af7f2ae633549bd0f046a</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -32618,12 +32650,12 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F600" t="inlineStr"/>
@@ -32653,7 +32685,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046d</t>
+          <t>6a4af7f2ae633549bd0f046c</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -32666,12 +32698,12 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F601" t="inlineStr"/>
@@ -32701,7 +32733,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0475</t>
+          <t>6a4af7f2ae633549bd0f0472</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -32714,12 +32746,12 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F602" t="inlineStr"/>
@@ -32749,7 +32781,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0479</t>
+          <t>6a4af7f2ae633549bd0f0473</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -32762,12 +32794,12 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
@@ -32797,7 +32829,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047b</t>
+          <t>6a4af7f2ae633549bd0f0476</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -32810,12 +32842,12 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -32893,7 +32925,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0478</t>
+          <t>6a4af7f2ae633549bd0f0479</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -32906,12 +32938,12 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
@@ -32941,7 +32973,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0477</t>
+          <t>6a4af7f2ae633549bd0f047b</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -32954,12 +32986,12 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -32989,7 +33021,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0472</t>
+          <t>6a4af7f2ae633549bd0f0474</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -33002,12 +33034,12 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F608" t="inlineStr"/>
@@ -33037,7 +33069,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0473</t>
+          <t>6a4af7f2ae633549bd0f0475</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -33050,12 +33082,12 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F609" t="inlineStr"/>
@@ -33085,7 +33117,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0476</t>
+          <t>6a4af7f2ae633549bd0f0478</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -33098,12 +33130,12 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F610" t="inlineStr"/>
@@ -33133,7 +33165,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0474</t>
+          <t>6a4af7f2ae633549bd0f0477</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -33146,12 +33178,12 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F611" t="inlineStr"/>
@@ -33181,7 +33213,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047e</t>
+          <t>6a4af7f2ae633549bd0f047d</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -33194,12 +33226,12 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F612" t="inlineStr"/>
@@ -33229,7 +33261,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0481</t>
+          <t>6a4af7f2ae633549bd0f047f</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -33242,12 +33274,12 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F613" t="inlineStr"/>
@@ -33277,7 +33309,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0484</t>
+          <t>6a4af7f2ae633549bd0f0482</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -33290,12 +33322,12 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F614" t="inlineStr"/>
@@ -33325,7 +33357,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0485</t>
+          <t>6a4af7f3ae633549bd0f0486</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -33338,12 +33370,12 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -33373,7 +33405,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047d</t>
+          <t>6a4af7f2ae633549bd0f0480</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -33386,12 +33418,12 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F616" t="inlineStr"/>
@@ -33421,7 +33453,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f047f</t>
+          <t>6a4af7f2ae633549bd0f047e</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -33434,12 +33466,12 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F617" t="inlineStr"/>
@@ -33469,7 +33501,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0483</t>
+          <t>6a4af7f3ae633549bd0f0484</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -33482,12 +33514,12 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -33517,7 +33549,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0482</t>
+          <t>6a4af7f2ae633549bd0f0481</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -33530,12 +33562,12 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -33565,7 +33597,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0486</t>
+          <t>6a4af7f3ae633549bd0f0485</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -33578,12 +33610,12 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -33613,7 +33645,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0480</t>
+          <t>6a4af7f2ae633549bd0f0483</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -33626,12 +33658,12 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F621" t="inlineStr"/>
@@ -33661,7 +33693,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0488</t>
+          <t>6a4af7f3ae633549bd0f048b</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -33674,12 +33706,12 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F622" t="inlineStr"/>
@@ -33709,7 +33741,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0489</t>
+          <t>6a4af7f3ae633549bd0f048a</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -33722,12 +33754,12 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F623" t="inlineStr"/>
@@ -33757,7 +33789,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048d</t>
+          <t>6a4af7f3ae633549bd0f048c</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -33770,12 +33802,12 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
@@ -33805,7 +33837,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048f</t>
+          <t>6a4af7f3ae633549bd0f0490</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -33818,12 +33850,12 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F625" t="inlineStr"/>
@@ -33853,7 +33885,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048b</t>
+          <t>6a4af7f3ae633549bd0f0488</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -33866,12 +33898,12 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F626" t="inlineStr"/>
@@ -33901,7 +33933,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0491</t>
+          <t>6a4af7f3ae633549bd0f048e</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -33914,12 +33946,12 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F627" t="inlineStr"/>
@@ -33949,7 +33981,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048a</t>
+          <t>6a4af7f3ae633549bd0f048f</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -33962,12 +33994,12 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F628" t="inlineStr"/>
@@ -33997,7 +34029,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048c</t>
+          <t>6a4af7f3ae633549bd0f048d</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -34010,12 +34042,12 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F629" t="inlineStr"/>
@@ -34045,7 +34077,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0490</t>
+          <t>6a4af7f3ae633549bd0f0489</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -34058,12 +34090,12 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F630" t="inlineStr"/>
@@ -34093,7 +34125,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f048e</t>
+          <t>6a4af7f3ae633549bd0f0491</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -34106,12 +34138,12 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F631" t="inlineStr"/>
@@ -34141,7 +34173,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049b</t>
+          <t>6a4af7f3ae633549bd0f049a</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -34154,12 +34186,12 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F632" t="inlineStr"/>
@@ -34189,7 +34221,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049c</t>
+          <t>6a4af7f3ae633549bd0f049b</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -34202,12 +34234,12 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F633" t="inlineStr"/>
@@ -34237,7 +34269,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049a</t>
+          <t>6a4af7f3ae633549bd0f0493</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -34250,12 +34282,12 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F634" t="inlineStr"/>
@@ -34285,7 +34317,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0494</t>
+          <t>6a4af7f3ae633549bd0f0496</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -34298,12 +34330,12 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F635" t="inlineStr"/>
@@ -34333,7 +34365,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0497</t>
+          <t>6a4af7f3ae633549bd0f0499</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -34346,12 +34378,12 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F636" t="inlineStr"/>
@@ -34381,7 +34413,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0499</t>
+          <t>6a4af7f3ae633549bd0f0494</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -34394,12 +34426,12 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F637" t="inlineStr"/>
@@ -34429,7 +34461,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0493</t>
+          <t>6a4af7f3ae633549bd0f0497</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -34442,12 +34474,12 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F638" t="inlineStr"/>
@@ -34477,7 +34509,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0496</t>
+          <t>6a4af7f3ae633549bd0f049c</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -34490,12 +34522,12 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F639" t="inlineStr"/>
@@ -34525,7 +34557,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0495</t>
+          <t>6a4af7f3ae633549bd0f0498</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -34538,12 +34570,12 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F640" t="inlineStr"/>
@@ -34573,7 +34605,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f0498</t>
+          <t>6a4af7f3ae633549bd0f0495</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -34586,12 +34618,12 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F641" t="inlineStr"/>
@@ -34621,7 +34653,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049e</t>
+          <t>6a4af7f3ae633549bd0f04a4</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -34634,12 +34666,12 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F642" t="inlineStr"/>
@@ -34669,7 +34701,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f049f</t>
+          <t>6a4af7f3ae633549bd0f04a1</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -34682,12 +34714,12 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
@@ -34717,7 +34749,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a1</t>
+          <t>6a4af7f3ae633549bd0f049e</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -34730,12 +34762,12 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -34765,7 +34797,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a5</t>
+          <t>6a4af7f3ae633549bd0f049f</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -34778,12 +34810,12 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F645" t="inlineStr"/>
@@ -34813,7 +34845,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a6</t>
+          <t>6a4af7f3ae633549bd0f04a5</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -34826,12 +34858,12 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F646" t="inlineStr"/>
@@ -34861,7 +34893,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a4</t>
+          <t>6a4af7f3ae633549bd0f04a7</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -34874,12 +34906,12 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -34909,7 +34941,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a0</t>
+          <t>6a4af7f3ae633549bd0f04a6</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -34922,12 +34954,12 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -34957,7 +34989,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a2</t>
+          <t>6a4af7f3ae633549bd0f04a0</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -34970,12 +35002,12 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -35005,7 +35037,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a3</t>
+          <t>6a4af7f3ae633549bd0f04a2</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -35018,12 +35050,12 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F650" t="inlineStr"/>
@@ -35053,7 +35085,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a7</t>
+          <t>6a4af7f3ae633549bd0f04a3</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -35066,12 +35098,12 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F651" t="inlineStr"/>
@@ -35101,7 +35133,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b1</t>
+          <t>6a4af7f3ae633549bd0f04b2</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -35114,12 +35146,12 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -35149,7 +35181,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ac</t>
+          <t>6a4af7f3ae633549bd0f04a9</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -35162,12 +35194,12 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F653" t="inlineStr"/>
@@ -35197,7 +35229,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ae</t>
+          <t>6a4af7f3ae633549bd0f04aa</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -35210,12 +35242,12 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F654" t="inlineStr"/>
@@ -35245,7 +35277,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ab</t>
+          <t>6a4af7f3ae633549bd0f04ad</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -35258,12 +35290,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F655" t="inlineStr"/>
@@ -35293,7 +35325,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04ad</t>
+          <t>6a4af7f3ae633549bd0f04af</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -35306,12 +35338,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F656" t="inlineStr"/>
@@ -35341,7 +35373,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04af</t>
+          <t>6a4af7f3ae633549bd0f04ab</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -35354,12 +35386,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F657" t="inlineStr"/>
@@ -35389,7 +35421,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04a9</t>
+          <t>6a4af7f3ae633549bd0f04b0</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -35402,12 +35434,12 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F658" t="inlineStr"/>
@@ -35437,7 +35469,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04aa</t>
+          <t>6a4af7f3ae633549bd0f04ac</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -35450,12 +35482,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F659" t="inlineStr"/>
@@ -35485,7 +35517,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b0</t>
+          <t>6a4af7f3ae633549bd0f04ae</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -35498,12 +35530,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F660" t="inlineStr"/>
@@ -35533,7 +35565,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b2</t>
+          <t>6a4af7f3ae633549bd0f04b1</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -35546,12 +35578,12 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F661" t="inlineStr"/>
@@ -35581,7 +35613,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b8</t>
+          <t>6a4af7f3ae633549bd0f04b6</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -35594,12 +35626,12 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F662" t="inlineStr"/>
@@ -35677,7 +35709,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b9</t>
+          <t>6a4af7f3ae633549bd0f04bc</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -35690,12 +35722,12 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F664" t="inlineStr"/>
@@ -35773,7 +35805,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bd</t>
+          <t>6a4af7f3ae633549bd0f04b9</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -35786,12 +35818,12 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F666" t="inlineStr"/>
@@ -35821,7 +35853,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b5</t>
+          <t>6a4af7f3ae633549bd0f04bd</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -35834,12 +35866,12 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F667" t="inlineStr"/>
@@ -35869,7 +35901,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bc</t>
+          <t>6a4af7f3ae633549bd0f04b5</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -35882,12 +35914,12 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F668" t="inlineStr"/>
@@ -35917,7 +35949,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b4</t>
+          <t>6a4af7f3ae633549bd0f04b8</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -35930,12 +35962,12 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
@@ -35965,7 +35997,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b7</t>
+          <t>6a4af7f3ae633549bd0f04b4</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -35978,12 +36010,12 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F670" t="inlineStr"/>
@@ -36013,7 +36045,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04b6</t>
+          <t>6a4af7f3ae633549bd0f04b7</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -36026,12 +36058,12 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F671" t="inlineStr"/>
@@ -36061,7 +36093,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c0</t>
+          <t>6a4af7f3ae633549bd0f04c6</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -36074,12 +36106,12 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F672" t="inlineStr"/>
@@ -36109,7 +36141,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c5</t>
+          <t>6a4af7f3ae633549bd0f04bf</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -36122,12 +36154,12 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
@@ -36157,7 +36189,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04bf</t>
+          <t>6a4af7f3ae633549bd0f04c7</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -36170,12 +36202,12 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F674" t="inlineStr"/>
@@ -36205,7 +36237,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c7</t>
+          <t>6a4af7f3ae633549bd0f04c4</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -36218,12 +36250,12 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F675" t="inlineStr"/>
@@ -36253,7 +36285,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c4</t>
+          <t>6a4af7f3ae633549bd0f04c8</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -36266,12 +36298,12 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -36397,7 +36429,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c6</t>
+          <t>6a4af7f3ae633549bd0f04c2</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -36410,12 +36442,12 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F679" t="inlineStr"/>
@@ -36445,7 +36477,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c8</t>
+          <t>6a4af7f3ae633549bd0f04c0</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -36458,12 +36490,12 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F680" t="inlineStr"/>
@@ -36493,7 +36525,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>6a4af7f3ae633549bd0f04c2</t>
+          <t>6a4af7f3ae633549bd0f04c5</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -36506,12 +36538,12 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
@@ -36541,7 +36573,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cc</t>
+          <t>6a4af7f4ae633549bd0f04cd</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -36554,12 +36586,12 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F682" t="inlineStr"/>
@@ -36589,7 +36621,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d3</t>
+          <t>6a4af7f4ae633549bd0f04d1</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -36602,12 +36634,12 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F683" t="inlineStr"/>
@@ -36637,7 +36669,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ce</t>
+          <t>6a4af7f4ae633549bd0f04cb</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -36650,12 +36682,12 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F684" t="inlineStr"/>
@@ -36685,7 +36717,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cd</t>
+          <t>6a4af7f4ae633549bd0f04cc</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -36698,12 +36730,12 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F685" t="inlineStr"/>
@@ -36733,7 +36765,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d0</t>
+          <t>6a4af7f4ae633549bd0f04ca</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -36746,12 +36778,12 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F686" t="inlineStr"/>
@@ -36781,7 +36813,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cf</t>
+          <t>6a4af7f4ae633549bd0f04ce</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -36794,12 +36826,12 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F687" t="inlineStr"/>
@@ -36829,7 +36861,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d1</t>
+          <t>6a4af7f4ae633549bd0f04d0</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -36842,12 +36874,12 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F688" t="inlineStr"/>
@@ -36877,7 +36909,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ca</t>
+          <t>6a4af7f4ae633549bd0f04d2</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -36890,12 +36922,12 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F689" t="inlineStr"/>
@@ -36925,7 +36957,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d2</t>
+          <t>6a4af7f4ae633549bd0f04d3</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -36938,12 +36970,12 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F690" t="inlineStr"/>
@@ -36973,7 +37005,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04cb</t>
+          <t>6a4af7f4ae633549bd0f04cf</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -36986,12 +37018,12 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F691" t="inlineStr"/>
@@ -37021,7 +37053,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04de</t>
+          <t>6a4af7f4ae633549bd0f04d9</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -37034,12 +37066,12 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F692" t="inlineStr"/>
@@ -37069,7 +37101,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d8</t>
+          <t>6a4af7f4ae633549bd0f04dc</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -37082,12 +37114,12 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F693" t="inlineStr"/>
@@ -37117,7 +37149,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d9</t>
+          <t>6a4af7f4ae633549bd0f04de</t>
         </is>
       </c>
       <c r="B694" t="n">
@@ -37130,12 +37162,12 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F694" t="inlineStr"/>
@@ -37165,7 +37197,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dc</t>
+          <t>6a4af7f4ae633549bd0f04d7</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -37178,12 +37210,12 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F695" t="inlineStr"/>
@@ -37213,7 +37245,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04db</t>
+          <t>6a4af7f4ae633549bd0f04d6</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -37226,12 +37258,12 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F696" t="inlineStr"/>
@@ -37309,7 +37341,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d6</t>
+          <t>6a4af7f4ae633549bd0f04da</t>
         </is>
       </c>
       <c r="B698" t="n">
@@ -37322,12 +37354,12 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F698" t="inlineStr"/>
@@ -37357,7 +37389,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04da</t>
+          <t>6a4af7f4ae633549bd0f04dd</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -37370,12 +37402,12 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F699" t="inlineStr"/>
@@ -37405,7 +37437,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04dd</t>
+          <t>6a4af7f4ae633549bd0f04db</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -37418,12 +37450,12 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F700" t="inlineStr"/>
@@ -37453,7 +37485,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04d7</t>
+          <t>6a4af7f4ae633549bd0f04d8</t>
         </is>
       </c>
       <c r="B701" t="n">
@@ -37466,12 +37498,12 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F701" t="inlineStr"/>
@@ -37501,7 +37533,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e1</t>
+          <t>6a4af7f4ae633549bd0f04e0</t>
         </is>
       </c>
       <c r="B702" t="n">
@@ -37514,12 +37546,12 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F702" t="inlineStr"/>
@@ -37549,7 +37581,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e2</t>
+          <t>6a4af7f4ae633549bd0f04e4</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -37562,12 +37594,12 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F703" t="inlineStr"/>
@@ -37597,7 +37629,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e3</t>
+          <t>6a4af7f4ae633549bd0f04e5</t>
         </is>
       </c>
       <c r="B704" t="n">
@@ -37610,12 +37642,12 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F704" t="inlineStr"/>
@@ -37645,7 +37677,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e6</t>
+          <t>6a4af7f4ae633549bd0f04e2</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -37658,12 +37690,12 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
@@ -37693,7 +37725,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e7</t>
+          <t>6a4af7f4ae633549bd0f04e3</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -37706,12 +37738,12 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F706" t="inlineStr"/>
@@ -37789,7 +37821,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e9</t>
+          <t>6a4af7f4ae633549bd0f04e1</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -37802,12 +37834,12 @@
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F708" t="inlineStr"/>
@@ -37837,7 +37869,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e0</t>
+          <t>6a4af7f4ae633549bd0f04e6</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -37850,12 +37882,12 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F709" t="inlineStr"/>
@@ -37885,7 +37917,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e4</t>
+          <t>6a4af7f4ae633549bd0f04e7</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -37898,12 +37930,12 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F710" t="inlineStr"/>
@@ -37933,7 +37965,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04e5</t>
+          <t>6a4af7f4ae633549bd0f04e9</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -37946,12 +37978,12 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F711" t="inlineStr"/>
@@ -37981,7 +38013,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ed</t>
+          <t>6a4af7f4ae633549bd0f04ec</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -37994,12 +38026,12 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F712" t="inlineStr"/>
@@ -38029,7 +38061,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ec</t>
+          <t>6a4af7f4ae633549bd0f04f0</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -38042,12 +38074,12 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F713" t="inlineStr"/>
@@ -38077,7 +38109,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ef</t>
+          <t>6a4af7f4ae633549bd0f04f4</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -38090,12 +38122,12 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F714" t="inlineStr"/>
@@ -38125,7 +38157,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f0</t>
+          <t>6a4af7f4ae633549bd0f04ee</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -38138,12 +38170,12 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F715" t="inlineStr"/>
@@ -38173,7 +38205,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f4</t>
+          <t>6a4af7f4ae633549bd0f04eb</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -38186,12 +38218,12 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F716" t="inlineStr"/>
@@ -38221,7 +38253,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f1</t>
+          <t>6a4af7f4ae633549bd0f04f2</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -38234,12 +38266,12 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F717" t="inlineStr"/>
@@ -38269,7 +38301,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f2</t>
+          <t>6a4af7f4ae633549bd0f04f3</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -38282,12 +38314,12 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F718" t="inlineStr"/>
@@ -38317,7 +38349,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f3</t>
+          <t>6a4af7f4ae633549bd0f04f1</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -38330,12 +38362,12 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F719" t="inlineStr"/>
@@ -38365,7 +38397,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04eb</t>
+          <t>6a4af7f4ae633549bd0f04ef</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -38378,12 +38410,12 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F720" t="inlineStr"/>
@@ -38413,7 +38445,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ee</t>
+          <t>6a4af7f4ae633549bd0f04ed</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -38426,12 +38458,12 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F721" t="inlineStr"/>
@@ -38461,7 +38493,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f6</t>
+          <t>6a4af7f4ae633549bd0f04f7</t>
         </is>
       </c>
       <c r="B722" t="n">
@@ -38474,12 +38506,12 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F722" t="inlineStr"/>
@@ -38509,7 +38541,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f8</t>
+          <t>6a4af7f4ae633549bd0f04ff</t>
         </is>
       </c>
       <c r="B723" t="n">
@@ -38522,12 +38554,12 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F723" t="inlineStr"/>
@@ -38557,7 +38589,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04ff</t>
+          <t>6a4af7f4ae633549bd0f04f9</t>
         </is>
       </c>
       <c r="B724" t="n">
@@ -38570,12 +38602,12 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F724" t="inlineStr"/>
@@ -38605,7 +38637,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fe</t>
+          <t>6a4af7f4ae633549bd0f04fc</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -38618,12 +38650,12 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F725" t="inlineStr"/>
@@ -38653,7 +38685,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f9</t>
+          <t>6a4af7f4ae633549bd0f04fe</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -38666,12 +38698,12 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F726" t="inlineStr"/>
@@ -38701,7 +38733,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fb</t>
+          <t>6a4af7f4ae633549bd0f04fd</t>
         </is>
       </c>
       <c r="B727" t="n">
@@ -38714,12 +38746,12 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F727" t="inlineStr"/>
@@ -38749,7 +38781,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fd</t>
+          <t>6a4af7f4ae633549bd0f04fb</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -38762,12 +38794,12 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F728" t="inlineStr"/>
@@ -38797,7 +38829,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04fc</t>
+          <t>6a4af7f4ae633549bd0f04f6</t>
         </is>
       </c>
       <c r="B729" t="n">
@@ -38810,12 +38842,12 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F729" t="inlineStr"/>
@@ -38845,7 +38877,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f04f7</t>
+          <t>6a4af7f4ae633549bd0f04f8</t>
         </is>
       </c>
       <c r="B730" t="n">
@@ -38858,12 +38890,12 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F730" t="inlineStr"/>
@@ -38941,7 +38973,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0501</t>
+          <t>6a4af7f4ae633549bd0f0505</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -38954,12 +38986,12 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F732" t="inlineStr"/>
@@ -38989,7 +39021,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0504</t>
+          <t>6a4af7f4ae633549bd0f0508</t>
         </is>
       </c>
       <c r="B733" t="n">
@@ -39002,12 +39034,12 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F733" t="inlineStr"/>
@@ -39037,7 +39069,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0503</t>
+          <t>6a4af7f4ae633549bd0f0502</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -39050,12 +39082,12 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
@@ -39085,7 +39117,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0507</t>
+          <t>6a4af7f4ae633549bd0f0501</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -39098,12 +39130,12 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -39133,7 +39165,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0508</t>
+          <t>6a4af7f4ae633549bd0f0503</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -39146,12 +39178,12 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
@@ -39181,7 +39213,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0502</t>
+          <t>6a4af7f4ae633549bd0f0506</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -39194,12 +39226,12 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F737" t="inlineStr"/>
@@ -39229,7 +39261,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0509</t>
+          <t>6a4af7f4ae633549bd0f0507</t>
         </is>
       </c>
       <c r="B738" t="n">
@@ -39242,12 +39274,12 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F738" t="inlineStr"/>
@@ -39277,7 +39309,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0505</t>
+          <t>6a4af7f4ae633549bd0f0504</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -39290,12 +39322,12 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F739" t="inlineStr"/>
@@ -39325,7 +39357,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f0506</t>
+          <t>6a4af7f4ae633549bd0f050a</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -39338,12 +39370,12 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -39373,7 +39405,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050a</t>
+          <t>6a4af7f4ae633549bd0f0509</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -39386,12 +39418,12 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F741" t="inlineStr"/>
@@ -39421,7 +39453,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f050e</t>
+          <t>6a4af7f4ae633549bd0f050c</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -39434,12 +39466,12 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F742" t="inlineStr"/>
@@ -39517,7 +39549,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050c</t>
+          <t>6a4af7f5ae633549bd0f0511</t>
         </is>
       </c>
       <c r="B744" t="n">
@@ -39530,12 +39562,12 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F744" t="inlineStr"/>
@@ -39613,7 +39645,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0511</t>
+          <t>6a4af7f4ae633549bd0f050d</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -39626,12 +39658,12 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F746" t="inlineStr"/>
@@ -39661,7 +39693,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>6a4af7f4ae633549bd0f050d</t>
+          <t>6a4af7f5ae633549bd0f0510</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -39674,12 +39706,12 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F747" t="inlineStr"/>
@@ -39757,7 +39789,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0510</t>
+          <t>6a4af7f5ae633549bd0f0514</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -39770,12 +39802,12 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
@@ -39853,7 +39885,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>6a4af7f5ae633549bd0f0514</t>
+          <t>6a4af7f5ae633549bd0f050e</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -39866,12 +39898,12 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F751" t="inlineStr"/>

--- a/datos/maestros/md_partidos.xlsx
+++ b/datos/maestros/md_partidos.xlsx
@@ -21773,7 +21773,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0380</t>
+          <t>6a4af7efae633549bd0f0382</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -21786,33 +21786,33 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G382" t="n">
         <v>0</v>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
@@ -21829,7 +21829,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0383</t>
+          <t>6a4af7efae633549bd0f0381</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -21842,33 +21842,33 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F383" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G383" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
@@ -21885,7 +21885,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0384</t>
+          <t>6a4af7efae633549bd0f0386</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -21898,33 +21898,33 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F384" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G384" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
@@ -21941,7 +21941,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0388</t>
+          <t>6a4af7efae633549bd0f0380</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -21954,19 +21954,19 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F385" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G385" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H385" t="inlineStr">
         <is>
@@ -21975,12 +21975,12 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
           <t>19:30</t>
-        </is>
-      </c>
-      <c r="J385" t="inlineStr">
-        <is>
-          <t>21:30</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
@@ -21997,7 +21997,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0389</t>
+          <t>6a4af7efae633549bd0f0388</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -22010,33 +22010,33 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F386" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G386" t="n">
         <v>1</v>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
@@ -22053,7 +22053,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0387</t>
+          <t>6a4af7efae633549bd0f0389</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -22066,23 +22066,23 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F387" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G387" t="n">
         <v>1</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -22109,7 +22109,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0385</t>
+          <t>6a4af7efae633549bd0f0383</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -22122,33 +22122,33 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F388" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G388" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
@@ -22165,7 +22165,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0386</t>
+          <t>6a4af7efae633549bd0f0384</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -22178,33 +22178,33 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F389" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G389" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
@@ -22221,7 +22221,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0381</t>
+          <t>6a4af7efae633549bd0f0385</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -22234,33 +22234,33 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F390" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G390" t="n">
         <v>0</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
           <t>19:00</t>
-        </is>
-      </c>
-      <c r="J390" t="inlineStr">
-        <is>
-          <t>21:00</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
@@ -22277,7 +22277,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0382</t>
+          <t>6a4af7efae633549bd0f0387</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -22290,23 +22290,23 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F391" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G391" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -22445,7 +22445,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0393</t>
+          <t>6a4af7efae633549bd0f038b</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -22458,33 +22458,33 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F394" t="n">
         <v>1</v>
       </c>
       <c r="G394" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
@@ -22501,7 +22501,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0394</t>
+          <t>6a4af7efae633549bd0f038c</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -22514,33 +22514,33 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G395" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
@@ -22557,7 +22557,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0390</t>
+          <t>6a4af7efae633549bd0f038e</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -22570,19 +22570,19 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G396" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
@@ -22591,12 +22591,12 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
@@ -22669,7 +22669,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0391</t>
+          <t>6a4af7efae633549bd0f0390</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -22682,33 +22682,33 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F398" t="n">
         <v>1</v>
       </c>
       <c r="G398" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
           <t>19:30</t>
-        </is>
-      </c>
-      <c r="J398" t="inlineStr">
-        <is>
-          <t>21:30</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
@@ -22725,7 +22725,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038c</t>
+          <t>6a4af7efae633549bd0f0391</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -22738,33 +22738,33 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F399" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G399" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
@@ -22781,7 +22781,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038b</t>
+          <t>6a4af7efae633549bd0f0394</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -22794,19 +22794,19 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F400" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H400" t="inlineStr">
         <is>
@@ -22815,12 +22815,12 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
@@ -22837,7 +22837,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f038e</t>
+          <t>6a4af7efae633549bd0f0393</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -22850,33 +22850,33 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F401" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G401" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
@@ -22893,7 +22893,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0396</t>
+          <t>6a4af7efae633549bd0f039a</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -22906,33 +22906,33 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F402" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G402" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
@@ -22949,7 +22949,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0399</t>
+          <t>6a4af7efae633549bd0f039c</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -22962,33 +22962,33 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F403" t="n">
         <v>3</v>
       </c>
       <c r="G403" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
@@ -23005,7 +23005,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039e</t>
+          <t>6a4af7efae633549bd0f039d</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -23018,33 +23018,33 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F404" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G404" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
           <t>17:00</t>
-        </is>
-      </c>
-      <c r="J404" t="inlineStr">
-        <is>
-          <t>19:00</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
@@ -23061,7 +23061,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039f</t>
+          <t>6a4af7efae633549bd0f0399</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -23074,33 +23074,33 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F405" t="n">
+        <v>3</v>
+      </c>
+      <c r="G405" t="n">
         <v>1</v>
       </c>
-      <c r="G405" t="n">
-        <v>3</v>
-      </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
           <t>19:30</t>
-        </is>
-      </c>
-      <c r="J405" t="inlineStr">
-        <is>
-          <t>21:30</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
@@ -23117,7 +23117,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0397</t>
+          <t>6a4af7efae633549bd0f039b</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -23130,19 +23130,19 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F406" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G406" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
@@ -23151,12 +23151,12 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
           <t>19:30</t>
-        </is>
-      </c>
-      <c r="J406" t="inlineStr">
-        <is>
-          <t>21:30</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
@@ -23173,7 +23173,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f0398</t>
+          <t>6a4af7efae633549bd0f039f</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -23186,23 +23186,23 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -23229,7 +23229,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039a</t>
+          <t>6a4af7efae633549bd0f0396</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -23242,33 +23242,33 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
@@ -23285,7 +23285,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039b</t>
+          <t>6a4af7efae633549bd0f039e</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -23298,33 +23298,33 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F409" t="n">
+        <v>2</v>
+      </c>
+      <c r="G409" t="n">
         <v>1</v>
       </c>
-      <c r="G409" t="n">
-        <v>0</v>
-      </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
@@ -23341,7 +23341,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039c</t>
+          <t>6a4af7efae633549bd0f0397</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -23354,33 +23354,33 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G410" t="n">
         <v>2</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
@@ -23397,7 +23397,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f039d</t>
+          <t>6a4af7efae633549bd0f0398</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -23410,19 +23410,19 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F411" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G411" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
@@ -23431,12 +23431,12 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
@@ -23453,7 +23453,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a1</t>
+          <t>6a4af7efae633549bd0f03a3</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -23466,33 +23466,33 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
@@ -23509,7 +23509,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a9</t>
+          <t>6a4af7efae633549bd0f03a4</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -23522,33 +23522,33 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G413" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
@@ -23565,7 +23565,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a6</t>
+          <t>6a4af7efae633549bd0f03a5</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -23578,12 +23578,12 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F414" t="n">
@@ -23594,17 +23594,17 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
@@ -23621,7 +23621,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a7</t>
+          <t>6a4af7efae633549bd0f03a6</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -23634,33 +23634,33 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F415" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G415" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
@@ -23677,7 +23677,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a8</t>
+          <t>6a4af7efae633549bd0f03a7</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -23690,23 +23690,23 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F416" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G416" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -23733,7 +23733,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a4</t>
+          <t>6a4af7efae633549bd0f03a8</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -23746,33 +23746,33 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F417" t="n">
+        <v>3</v>
+      </c>
+      <c r="G417" t="n">
         <v>2</v>
       </c>
-      <c r="G417" t="n">
-        <v>3</v>
-      </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
@@ -23789,7 +23789,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a2</t>
+          <t>6a4af7efae633549bd0f03a9</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -23802,23 +23802,23 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F418" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G418" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -23845,7 +23845,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a3</t>
+          <t>6a4af7efae633549bd0f03a1</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -23858,33 +23858,33 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F419" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G419" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
@@ -23901,7 +23901,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03a5</t>
+          <t>6a4af7efae633549bd0f03aa</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -23914,23 +23914,23 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F420" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G420" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -23957,7 +23957,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03aa</t>
+          <t>6a4af7efae633549bd0f03a2</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -23970,19 +23970,19 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F421" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G421" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H421" t="inlineStr">
         <is>
@@ -23991,12 +23991,12 @@
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
@@ -24013,7 +24013,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b2</t>
+          <t>6a4af7efae633549bd0f03af</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -24026,33 +24026,33 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F422" t="n">
+        <v>2</v>
+      </c>
+      <c r="G422" t="n">
         <v>4</v>
       </c>
-      <c r="G422" t="n">
-        <v>1</v>
-      </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
@@ -24125,7 +24125,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b1</t>
+          <t>6a4af7efae633549bd0f03b4</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -24138,33 +24138,33 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F424" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G424" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
@@ -24181,7 +24181,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03b4</t>
+          <t>6a4af7efae633549bd0f03b1</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -24194,33 +24194,33 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F425" t="n">
+        <v>2</v>
+      </c>
+      <c r="G425" t="n">
         <v>1</v>
       </c>
-      <c r="G425" t="n">
-        <v>0</v>
-      </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K425" t="inlineStr">
@@ -24293,7 +24293,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03af</t>
+          <t>6a4af7efae633549bd0f03ac</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -24306,33 +24306,33 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F427" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G427" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
@@ -24349,7 +24349,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ad</t>
+          <t>6a4af7efae633549bd0f03ae</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -24362,12 +24362,12 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -24383,12 +24383,12 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
@@ -24405,7 +24405,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ac</t>
+          <t>6a4af7efae633549bd0f03b2</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -24418,16 +24418,16 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G429" t="n">
         <v>1</v>
@@ -24439,12 +24439,12 @@
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
@@ -24461,7 +24461,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>6a4af7efae633549bd0f03ae</t>
+          <t>6a4af7efae633549bd0f03ad</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -24474,12 +24474,12 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F430" t="n">
@@ -24495,12 +24495,12 @@
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
@@ -24573,7 +24573,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bf</t>
+          <t>6a4af7f0ae633549bd0f03c0</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -24586,42 +24586,50 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
-        </is>
-      </c>
-      <c r="F432" t="inlineStr"/>
-      <c r="G432" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000d9</t>
+        </is>
+      </c>
+      <c r="F432" t="n">
+        <v>0</v>
+      </c>
+      <c r="G432" t="n">
+        <v>0</v>
+      </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>next</t>
-        </is>
-      </c>
-      <c r="L432" t="inlineStr"/>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b7</t>
+          <t>6a4af7f0ae633549bd0f03b9</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -24634,34 +24642,34 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr"/>
       <c r="H433" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>running</t>
         </is>
       </c>
       <c r="L433" t="inlineStr"/>
@@ -24669,7 +24677,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ba</t>
+          <t>6a4af7f0ae633549bd0f03b8</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -24682,19 +24690,19 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr"/>
       <c r="H434" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -24709,7 +24717,7 @@
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>running</t>
         </is>
       </c>
       <c r="L434" t="inlineStr"/>
@@ -24717,7 +24725,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bb</t>
+          <t>6a4af7f0ae633549bd0f03be</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -24730,34 +24738,34 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F435" t="inlineStr"/>
       <c r="G435" t="inlineStr"/>
       <c r="H435" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>running</t>
         </is>
       </c>
       <c r="L435" t="inlineStr"/>
@@ -24765,7 +24773,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03bd</t>
+          <t>6a4af7f0ae633549bd0f03b7</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -24778,42 +24786,50 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
-        </is>
-      </c>
-      <c r="F436" t="inlineStr"/>
-      <c r="G436" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000cb</t>
+        </is>
+      </c>
+      <c r="F436" t="n">
+        <v>0</v>
+      </c>
+      <c r="G436" t="n">
+        <v>1</v>
+      </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>next</t>
-        </is>
-      </c>
-      <c r="L436" t="inlineStr"/>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03be</t>
+          <t>6a4af7f0ae633549bd0f03bb</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -24826,34 +24842,34 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr"/>
       <c r="H437" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>running</t>
         </is>
       </c>
       <c r="L437" t="inlineStr"/>
@@ -24882,8 +24898,12 @@
           <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
-      <c r="F438" t="inlineStr"/>
-      <c r="G438" t="inlineStr"/>
+      <c r="F438" t="n">
+        <v>2</v>
+      </c>
+      <c r="G438" t="n">
+        <v>3</v>
+      </c>
       <c r="H438" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -24901,15 +24921,19 @@
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>next</t>
-        </is>
-      </c>
-      <c r="L438" t="inlineStr"/>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b9</t>
+          <t>6a4af7f0ae633549bd0f03ba</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -24922,34 +24946,34 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr"/>
       <c r="H439" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>running</t>
         </is>
       </c>
       <c r="L439" t="inlineStr"/>
@@ -24957,7 +24981,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03c0</t>
+          <t>6a4af7f0ae633549bd0f03bd</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -24970,50 +24994,42 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
-        </is>
-      </c>
-      <c r="F440" t="n">
-        <v>0</v>
-      </c>
-      <c r="G440" t="n">
-        <v>0</v>
-      </c>
+          <t>504e581e4d8bec9a670000c9</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr"/>
       <c r="H440" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>next</t>
-        </is>
-      </c>
-      <c r="L440" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03b8</t>
+          <t>6a4af7f0ae633549bd0f03bf</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -25026,19 +25042,23 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
-        </is>
-      </c>
-      <c r="F441" t="inlineStr"/>
-      <c r="G441" t="inlineStr"/>
+          <t>504e581e4d8bec9a670000d0</t>
+        </is>
+      </c>
+      <c r="F441" t="n">
+        <v>2</v>
+      </c>
+      <c r="G441" t="n">
+        <v>1</v>
+      </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -25053,10 +25073,14 @@
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>next</t>
-        </is>
-      </c>
-      <c r="L441" t="inlineStr"/>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -25101,7 +25125,7 @@
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L442" t="inlineStr"/>
@@ -25149,7 +25173,7 @@
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L443" t="inlineStr"/>
@@ -25197,7 +25221,7 @@
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L444" t="inlineStr"/>
@@ -25245,7 +25269,7 @@
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L445" t="inlineStr"/>
@@ -25293,7 +25317,7 @@
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L446" t="inlineStr"/>
@@ -25341,7 +25365,7 @@
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L447" t="inlineStr"/>
@@ -25389,7 +25413,7 @@
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L448" t="inlineStr"/>
@@ -25437,7 +25461,7 @@
       </c>
       <c r="K449" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L449" t="inlineStr"/>
@@ -25485,7 +25509,7 @@
       </c>
       <c r="K450" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L450" t="inlineStr"/>
@@ -25533,7 +25557,7 @@
       </c>
       <c r="K451" t="inlineStr">
         <is>
-          <t>future</t>
+          <t>next</t>
         </is>
       </c>
       <c r="L451" t="inlineStr"/>
@@ -25541,7 +25565,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d6</t>
+          <t>6a4af7f0ae633549bd0f03cf</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -25554,12 +25578,12 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F452" t="inlineStr"/>
@@ -25589,7 +25613,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ce</t>
+          <t>6a4af7f0ae633549bd0f03d0</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -25602,12 +25626,12 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F453" t="inlineStr"/>
@@ -25781,7 +25805,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cd</t>
+          <t>6a4af7f0ae633549bd0f03d4</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -25794,12 +25818,12 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F457" t="inlineStr"/>
@@ -25829,7 +25853,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03cf</t>
+          <t>6a4af7f0ae633549bd0f03d5</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -25842,12 +25866,12 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -25877,7 +25901,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d0</t>
+          <t>6a4af7f0ae633549bd0f03ce</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -25890,12 +25914,12 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -25925,7 +25949,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d4</t>
+          <t>6a4af7f0ae633549bd0f03d6</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -25938,12 +25962,12 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F460" t="inlineStr"/>
@@ -25973,7 +25997,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d5</t>
+          <t>6a4af7f0ae633549bd0f03cd</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -25986,12 +26010,12 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -26213,7 +26237,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03df</t>
+          <t>6a4af7f0ae633549bd0f03e0</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -26226,12 +26250,12 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F466" t="inlineStr"/>
@@ -26261,7 +26285,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e0</t>
+          <t>6a4af7f0ae633549bd0f03df</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -26274,12 +26298,12 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F467" t="inlineStr"/>
@@ -26357,7 +26381,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03d8</t>
+          <t>6a4af7f0ae633549bd0f03dd</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -26370,12 +26394,12 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F469" t="inlineStr"/>
@@ -26405,7 +26429,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03dd</t>
+          <t>6a4af7f0ae633549bd0f03e1</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -26418,12 +26442,12 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
@@ -26453,7 +26477,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e1</t>
+          <t>6a4af7f0ae633549bd0f03d8</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -26466,12 +26490,12 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -26501,7 +26525,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e5</t>
+          <t>6a4af7f0ae633549bd0f03e4</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -26514,12 +26538,12 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F472" t="inlineStr"/>
@@ -26549,7 +26573,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03eb</t>
+          <t>6a4af7f0ae633549bd0f03e6</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -26562,12 +26586,12 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -26579,12 +26603,12 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
@@ -26597,7 +26621,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e8</t>
+          <t>6a4af7f0ae633549bd0f03eb</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -26610,12 +26634,12 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -26645,7 +26669,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e7</t>
+          <t>6a4af7f0ae633549bd0f03e8</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -26658,12 +26682,12 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -26693,7 +26717,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e4</t>
+          <t>6a4af7f0ae633549bd0f03e7</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -26706,12 +26730,12 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
@@ -26741,7 +26765,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e3</t>
+          <t>6a4af7f0ae633549bd0f03e5</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -26754,12 +26778,12 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
@@ -26789,7 +26813,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e6</t>
+          <t>6a4af7f0ae633549bd0f03ea</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -26802,12 +26826,12 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -26819,12 +26843,12 @@
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K478" t="inlineStr">
@@ -26885,7 +26909,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03e9</t>
+          <t>6a4af7f0ae633549bd0f03e3</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -26898,12 +26922,12 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
@@ -26933,7 +26957,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ea</t>
+          <t>6a4af7f0ae633549bd0f03e9</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -26946,12 +26970,12 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
@@ -26981,7 +27005,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f3</t>
+          <t>6a4af7f0ae633549bd0f03f2</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -26994,12 +27018,12 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F482" t="inlineStr"/>
@@ -27029,7 +27053,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f4</t>
+          <t>6a4af7f0ae633549bd0f03f5</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -27042,12 +27066,12 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
@@ -27077,7 +27101,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f6</t>
+          <t>6a4af7f0ae633549bd0f03ef</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -27090,12 +27114,12 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F484" t="inlineStr"/>
@@ -27125,7 +27149,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f1</t>
+          <t>6a4af7f0ae633549bd0f03ee</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -27138,12 +27162,12 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F485" t="inlineStr"/>
@@ -27173,7 +27197,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f0</t>
+          <t>6a4af7f0ae633549bd0f03f3</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -27186,12 +27210,12 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
@@ -27221,7 +27245,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f5</t>
+          <t>6a4af7f0ae633549bd0f03f4</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -27234,12 +27258,12 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F487" t="inlineStr"/>
@@ -27269,7 +27293,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ef</t>
+          <t>6a4af7f0ae633549bd0f03f7</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -27282,12 +27306,12 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -27317,7 +27341,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f7</t>
+          <t>6a4af7f0ae633549bd0f03f6</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -27330,12 +27354,12 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
@@ -27365,7 +27389,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f2</t>
+          <t>6a4af7f0ae633549bd0f03f1</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -27378,12 +27402,12 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -27413,7 +27437,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03ee</t>
+          <t>6a4af7f0ae633549bd0f03f0</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -27426,12 +27450,12 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -27461,7 +27485,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03f9</t>
+          <t>6a4af7f1ae633549bd0f03fd</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -27474,12 +27498,12 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F492" t="inlineStr"/>
@@ -27509,7 +27533,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fc</t>
+          <t>6a4af7f1ae633549bd0f03fe</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -27522,12 +27546,12 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
@@ -27605,7 +27629,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fe</t>
+          <t>6a4af7f1ae633549bd0f0400</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -27618,12 +27642,12 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
@@ -27653,7 +27677,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0400</t>
+          <t>6a4af7f1ae633549bd0f0402</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -27666,12 +27690,12 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F496" t="inlineStr"/>
@@ -27749,7 +27773,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0402</t>
+          <t>6a4af7f0ae633549bd0f03fa</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -27762,12 +27786,12 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
@@ -27845,7 +27869,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>6a4af7f0ae633549bd0f03fa</t>
+          <t>6a4af7f0ae633549bd0f03f9</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -27858,12 +27882,12 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -27893,7 +27917,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f03fd</t>
+          <t>6a4af7f1ae633549bd0f03fc</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -27906,12 +27930,12 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F501" t="inlineStr"/>
@@ -27941,7 +27965,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0405</t>
+          <t>6a4af7f1ae633549bd0f0409</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -27954,12 +27978,12 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -27989,7 +28013,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0407</t>
+          <t>6a4af7f1ae633549bd0f040b</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -28002,12 +28026,12 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -28037,7 +28061,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040c</t>
+          <t>6a4af7f1ae633549bd0f0408</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -28050,12 +28074,12 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -28085,7 +28109,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0404</t>
+          <t>6a4af7f1ae633549bd0f040c</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -28098,12 +28122,12 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
@@ -28133,7 +28157,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0409</t>
+          <t>6a4af7f1ae633549bd0f040a</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -28146,12 +28170,12 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F506" t="inlineStr"/>
@@ -28181,7 +28205,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0408</t>
+          <t>6a4af7f1ae633549bd0f0406</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -28194,12 +28218,12 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F507" t="inlineStr"/>
@@ -28229,7 +28253,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040b</t>
+          <t>6a4af7f1ae633549bd0f040d</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -28242,12 +28266,12 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -28277,7 +28301,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040a</t>
+          <t>6a4af7f1ae633549bd0f0405</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -28290,12 +28314,12 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
@@ -28325,7 +28349,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0406</t>
+          <t>6a4af7f1ae633549bd0f0407</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -28338,12 +28362,12 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
@@ -28373,7 +28397,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040d</t>
+          <t>6a4af7f1ae633549bd0f0404</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -28386,12 +28410,12 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
@@ -28469,7 +28493,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0411</t>
+          <t>6a4af7f1ae633549bd0f0418</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -28482,12 +28506,12 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F513" t="inlineStr"/>
@@ -28517,7 +28541,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0414</t>
+          <t>6a4af7f1ae633549bd0f0416</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -28530,12 +28554,12 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
@@ -28565,7 +28589,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0413</t>
+          <t>6a4af7f1ae633549bd0f040f</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -28578,12 +28602,12 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F515" t="inlineStr"/>
@@ -28613,7 +28637,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0417</t>
+          <t>6a4af7f1ae633549bd0f0410</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -28626,12 +28650,12 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F516" t="inlineStr"/>
@@ -28709,7 +28733,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0410</t>
+          <t>6a4af7f1ae633549bd0f0413</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -28722,12 +28746,12 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
@@ -28757,7 +28781,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0418</t>
+          <t>6a4af7f1ae633549bd0f0414</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -28770,12 +28794,12 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -28805,7 +28829,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f040f</t>
+          <t>6a4af7f1ae633549bd0f0411</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -28818,12 +28842,12 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F520" t="inlineStr"/>
@@ -28853,7 +28877,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0416</t>
+          <t>6a4af7f1ae633549bd0f0417</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -28866,12 +28890,12 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F521" t="inlineStr"/>
@@ -28901,7 +28925,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041c</t>
+          <t>6a4af7f1ae633549bd0f041b</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -28914,12 +28938,12 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F522" t="inlineStr"/>
@@ -28949,7 +28973,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041f</t>
+          <t>6a4af7f1ae633549bd0f041d</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -28962,12 +28986,12 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F523" t="inlineStr"/>
@@ -28997,7 +29021,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041a</t>
+          <t>6a4af7f1ae633549bd0f0422</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -29010,12 +29034,12 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F524" t="inlineStr"/>
@@ -29045,7 +29069,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0420</t>
+          <t>6a4af7f1ae633549bd0f041c</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -29058,12 +29082,12 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F525" t="inlineStr"/>
@@ -29093,7 +29117,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0421</t>
+          <t>6a4af7f1ae633549bd0f0420</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -29106,12 +29130,12 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F526" t="inlineStr"/>
@@ -29141,7 +29165,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041e</t>
+          <t>6a4af7f1ae633549bd0f041f</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -29154,12 +29178,12 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F527" t="inlineStr"/>
@@ -29189,7 +29213,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0423</t>
+          <t>6a4af7f1ae633549bd0f041a</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -29202,12 +29226,12 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F528" t="inlineStr"/>
@@ -29237,7 +29261,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041b</t>
+          <t>6a4af7f1ae633549bd0f0423</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -29250,12 +29274,12 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -29285,7 +29309,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f041d</t>
+          <t>6a4af7f1ae633549bd0f0421</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -29298,12 +29322,12 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F530" t="inlineStr"/>
@@ -29333,7 +29357,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0422</t>
+          <t>6a4af7f1ae633549bd0f041e</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -29346,12 +29370,12 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -29381,7 +29405,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0428</t>
+          <t>6a4af7f1ae633549bd0f0429</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -29394,12 +29418,12 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -29429,7 +29453,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0426</t>
+          <t>6a4af7f1ae633549bd0f042c</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -29442,12 +29466,12 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
@@ -29477,7 +29501,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042d</t>
+          <t>6a4af7f1ae633549bd0f0426</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -29490,12 +29514,12 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F534" t="inlineStr"/>
@@ -29525,7 +29549,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0429</t>
+          <t>6a4af7f1ae633549bd0f042d</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -29538,12 +29562,12 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F535" t="inlineStr"/>
@@ -29573,7 +29597,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0425</t>
+          <t>6a4af7f1ae633549bd0f042a</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -29586,12 +29610,12 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -29669,7 +29693,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042a</t>
+          <t>6a4af7f1ae633549bd0f042e</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -29682,12 +29706,12 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F538" t="inlineStr"/>
@@ -29717,7 +29741,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042e</t>
+          <t>6a4af7f1ae633549bd0f0425</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -29730,12 +29754,12 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F539" t="inlineStr"/>
@@ -29765,7 +29789,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f042c</t>
+          <t>6a4af7f1ae633549bd0f0428</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -29778,12 +29802,12 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F540" t="inlineStr"/>
@@ -29861,7 +29885,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0439</t>
+          <t>6a4af7f1ae633549bd0f0430</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -29874,12 +29898,12 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F542" t="inlineStr"/>
@@ -29909,7 +29933,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0434</t>
+          <t>6a4af7f1ae633549bd0f0432</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -29922,12 +29946,12 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F543" t="inlineStr"/>
@@ -29957,7 +29981,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0430</t>
+          <t>6a4af7f1ae633549bd0f0435</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -29970,12 +29994,12 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F544" t="inlineStr"/>
@@ -30005,7 +30029,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0433</t>
+          <t>6a4af7f1ae633549bd0f0437</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -30018,12 +30042,12 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -30053,7 +30077,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0431</t>
+          <t>6a4af7f1ae633549bd0f0439</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -30066,12 +30090,12 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -30101,7 +30125,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0436</t>
+          <t>6a4af7f1ae633549bd0f0438</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -30114,12 +30138,12 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F547" t="inlineStr"/>
@@ -30149,7 +30173,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0438</t>
+          <t>6a4af7f1ae633549bd0f0431</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -30162,12 +30186,12 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -30197,7 +30221,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0432</t>
+          <t>6a4af7f1ae633549bd0f0433</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -30210,12 +30234,12 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -30245,7 +30269,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0435</t>
+          <t>6a4af7f1ae633549bd0f0436</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -30258,12 +30282,12 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F550" t="inlineStr"/>
@@ -30293,7 +30317,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f0437</t>
+          <t>6a4af7f1ae633549bd0f0434</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -30306,12 +30330,12 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F551" t="inlineStr"/>
@@ -30341,7 +30365,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0444</t>
+          <t>6a4af7f2ae633549bd0f043f</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -30354,12 +30378,12 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F552" t="inlineStr"/>
@@ -30389,7 +30413,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f043f</t>
+          <t>6a4af7f2ae633549bd0f0442</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -30402,12 +30426,12 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F553" t="inlineStr"/>
@@ -30437,7 +30461,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0442</t>
+          <t>6a4af7f1ae633549bd0f043b</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -30450,12 +30474,12 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F554" t="inlineStr"/>
@@ -30485,7 +30509,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043b</t>
+          <t>6a4af7f2ae633549bd0f0443</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -30498,12 +30522,12 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F555" t="inlineStr"/>
@@ -30533,7 +30557,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0443</t>
+          <t>6a4af7f2ae633549bd0f0444</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -30546,12 +30570,12 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F556" t="inlineStr"/>
@@ -30581,7 +30605,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043c</t>
+          <t>6a4af7f1ae633549bd0f043d</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -30594,12 +30618,12 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -30629,7 +30653,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0440</t>
+          <t>6a4af7f2ae633549bd0f0441</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -30642,12 +30666,12 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
@@ -30677,7 +30701,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043e</t>
+          <t>6a4af7f1ae633549bd0f043c</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -30690,12 +30714,12 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F559" t="inlineStr"/>
@@ -30725,7 +30749,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0441</t>
+          <t>6a4af7f2ae633549bd0f0440</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -30738,12 +30762,12 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -30773,7 +30797,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>6a4af7f1ae633549bd0f043d</t>
+          <t>6a4af7f1ae633549bd0f043e</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -30786,12 +30810,12 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -30821,7 +30845,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044e</t>
+          <t>6a4af7f2ae633549bd0f0449</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -30834,12 +30858,12 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -30869,7 +30893,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0447</t>
+          <t>6a4af7f2ae633549bd0f044f</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -30882,12 +30906,12 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F563" t="inlineStr"/>
@@ -30917,7 +30941,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0448</t>
+          <t>6a4af7f2ae633549bd0f044b</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -30930,12 +30954,12 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F564" t="inlineStr"/>
@@ -30965,7 +30989,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044c</t>
+          <t>6a4af7f2ae633549bd0f0446</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -30978,12 +31002,12 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F565" t="inlineStr"/>
@@ -31013,7 +31037,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0449</t>
+          <t>6a4af7f2ae633549bd0f044a</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -31026,12 +31050,12 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
@@ -31061,7 +31085,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044d</t>
+          <t>6a4af7f2ae633549bd0f0447</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -31074,12 +31098,12 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F567" t="inlineStr"/>
@@ -31109,7 +31133,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044f</t>
+          <t>6a4af7f2ae633549bd0f0448</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -31122,12 +31146,12 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="F568" t="inlineStr"/>
@@ -31157,7 +31181,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0446</t>
+          <t>6a4af7f2ae633549bd0f044e</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -31170,12 +31194,12 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F569" t="inlineStr"/>
@@ -31205,7 +31229,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044a</t>
+          <t>6a4af7f2ae633549bd0f044d</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -31218,12 +31242,12 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F570" t="inlineStr"/>
@@ -31253,7 +31277,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f044b</t>
+          <t>6a4af7f2ae633549bd0f044c</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -31266,12 +31290,12 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F571" t="inlineStr"/>
@@ -31301,7 +31325,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0455</t>
+          <t>6a4af7f2ae633549bd0f0451</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -31314,12 +31338,12 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="F572" t="inlineStr"/>
@@ -31349,7 +31373,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0458</t>
+          <t>6a4af7f2ae633549bd0f0459</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -31362,12 +31386,12 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F573" t="inlineStr"/>
@@ -31397,7 +31421,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0456</t>
+          <t>6a4af7f2ae633549bd0f0452</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -31410,12 +31434,12 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F574" t="inlineStr"/>
@@ -31445,7 +31469,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0457</t>
+          <t>6a4af7f2ae633549bd0f0454</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -31458,12 +31482,12 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -31493,7 +31517,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045a</t>
+          <t>6a4af7f2ae633549bd0f0456</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -31506,12 +31530,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="F576" t="inlineStr"/>
@@ -31541,7 +31565,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0453</t>
+          <t>6a4af7f2ae633549bd0f0457</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -31554,12 +31578,12 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -31589,7 +31613,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0459</t>
+          <t>6a4af7f2ae633549bd0f0455</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -31602,12 +31626,12 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -31637,7 +31661,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0451</t>
+          <t>6a4af7f2ae633549bd0f0453</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -31650,12 +31674,12 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="F579" t="inlineStr"/>
@@ -31685,7 +31709,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0454</t>
+          <t>6a4af7f2ae633549bd0f0458</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -31698,12 +31722,12 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F580" t="inlineStr"/>
@@ -31733,7 +31757,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0452</t>
+          <t>6a4af7f2ae633549bd0f045a</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -31746,12 +31770,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F581" t="inlineStr"/>
@@ -31781,7 +31805,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0464</t>
+          <t>6a4af7f2ae633549bd0f045c</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -31794,12 +31818,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d6</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="F582" t="inlineStr"/>
@@ -31829,7 +31853,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045d</t>
+          <t>6a4af7f2ae633549bd0f0461</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -31842,12 +31866,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="F583" t="inlineStr"/>
@@ -31877,7 +31901,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0465</t>
+          <t>6a4af7f2ae633549bd0f045f</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -31890,12 +31914,12 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="F584" t="inlineStr"/>
@@ -31925,7 +31949,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0460</t>
+          <t>6a4af7f2ae633549bd0f0464</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -31938,12 +31962,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="F585" t="inlineStr"/>
@@ -31973,7 +31997,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0463</t>
+          <t>6a4af7f2ae633549bd0f045e</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -31986,12 +32010,12 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="F586" t="inlineStr"/>
@@ -32021,7 +32045,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0462</t>
+          <t>6a4af7f2ae633549bd0f0465</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -32034,12 +32058,12 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>520e4ee4a776cc826b00004b</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -32069,7 +32093,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045c</t>
+          <t>6a4af7f2ae633549bd0f0460</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -32082,12 +32106,12 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="F588" t="inlineStr"/>
@@ -32117,7 +32141,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0461</t>
+          <t>6a4af7f2ae633549bd0f045d</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -32130,12 +32154,12 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -32165,7 +32189,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045e</t>
+          <t>6a4af7f2ae633549bd0f0462</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -32178,12 +32202,12 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -32213,7 +32237,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f045f</t>
+          <t>6a4af7f2ae633549bd0f0463</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -32226,12 +32250,12 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -32261,7 +32285,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f0469</t>
+          <t>6a4af7f2ae633549bd0f046c</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -32274,12 +32298,12 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="F592" t="inlineStr"/>
@@ -32309,7 +32333,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>6a4af7f2ae633549bd0f046a</t>
+          <t>6a4af7f2ae633549bd0f0469</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -32322,12 +32346,12 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="F